--- a/www/flightdata/xlsx/flights_metadata.xlsx
+++ b/www/flightdata/xlsx/flights_metadata.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1331" uniqueCount="876">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="887">
   <si>
     <t>flight</t>
   </si>
@@ -94,6 +94,9 @@
     <t>landing_location.altitude</t>
   </si>
   <si>
+    <t>EOSS-378</t>
+  </si>
+  <si>
     <t>EOSS-377</t>
   </si>
   <si>
@@ -355,6 +358,9 @@
     <t>EOSS-291</t>
   </si>
   <si>
+    <t>['KC0D-3', 'KC0D-12']</t>
+  </si>
+  <si>
     <t>['KC0D-2', 'AE0SS-1', 'AE0SS-2']</t>
   </si>
   <si>
@@ -490,6 +496,9 @@
     <t>['KC0D-15', 'AE0SS-12', 'AE0SS-13']</t>
   </si>
   <si>
+    <t>2025-06-14</t>
+  </si>
+  <si>
     <t>2025-05-10</t>
   </si>
   <si>
@@ -667,13 +676,16 @@
     <t>2019-07-13</t>
   </si>
   <si>
+    <t>2000gm</t>
+  </si>
+  <si>
     <t>3000gm</t>
   </si>
   <si>
     <t>1500gm</t>
   </si>
   <si>
-    <t>2000gm</t>
+    <t>1.25</t>
   </si>
   <si>
     <t>1.20</t>
@@ -682,9 +694,6 @@
     <t>1.30</t>
   </si>
   <si>
-    <t>1.25</t>
-  </si>
-  <si>
     <t>1.35</t>
   </si>
   <si>
@@ -706,6 +715,9 @@
     <t>1.17</t>
   </si>
   <si>
+    <t>167</t>
+  </si>
+  <si>
     <t>462</t>
   </si>
   <si>
@@ -934,6 +946,9 @@
     <t>322</t>
   </si>
   <si>
+    <t>[{'transition': 'high_to_low', 'altitude': 48702.0}]</t>
+  </si>
+  <si>
     <t>[{'transition': 'high_to_low', 'altitude': 54081.0}]</t>
   </si>
   <si>
@@ -1195,6 +1210,9 @@
     <t>[{'transition': 'high_to_low', 'altitude': 59923.0}]</t>
   </si>
   <si>
+    <t>2hrs 27mins 30secs</t>
+  </si>
+  <si>
     <t>1hrs 15mins 23secs</t>
   </si>
   <si>
@@ -1450,6 +1468,9 @@
     <t>2hrs 7mins 45secs</t>
   </si>
   <si>
+    <t>1.31</t>
+  </si>
+  <si>
     <t>15.13</t>
   </si>
   <si>
@@ -1696,6 +1717,9 @@
     <t>11.90</t>
   </si>
   <si>
+    <t>2.35</t>
+  </si>
+  <si>
     <t>3.34</t>
   </si>
   <si>
@@ -1888,12 +1912,12 @@
     <t>3.71</t>
   </si>
   <si>
+    <t>1.81</t>
+  </si>
+  <si>
     <t>1.70</t>
   </si>
   <si>
-    <t>1.81</t>
-  </si>
-  <si>
     <t>1.63</t>
   </si>
   <si>
@@ -1921,6 +1945,9 @@
     <t>1.48</t>
   </si>
   <si>
+    <t>5.46</t>
+  </si>
+  <si>
     <t>21.85</t>
   </si>
   <si>
@@ -2173,6 +2200,9 @@
     <t>4.41</t>
   </si>
   <si>
+    <t>9.87</t>
+  </si>
+  <si>
     <t>28.47</t>
   </si>
   <si>
@@ -2408,6 +2438,9 @@
   </si>
   <si>
     <t>23.38</t>
+  </si>
+  <si>
+    <t>7.93</t>
   </si>
   <si>
     <t>27.55</t>
@@ -2999,7 +3032,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z88"/>
+  <dimension ref="A1:Z89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:26">
@@ -3087,79 +3120,79 @@
         <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="H2">
-        <v>63097</v>
+        <v>89165</v>
       </c>
       <c r="I2">
-        <v>432</v>
+        <v>214</v>
       </c>
       <c r="J2" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="K2">
-        <v>4523</v>
+        <v>8850</v>
       </c>
       <c r="L2">
-        <v>15.88</v>
+        <v>19.08</v>
       </c>
       <c r="M2" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="N2" t="s">
-        <v>522</v>
+        <v>567</v>
       </c>
       <c r="O2" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="P2" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="Q2" t="s">
-        <v>527</v>
+        <v>727</v>
       </c>
       <c r="R2" t="s">
-        <v>719</v>
+        <v>728</v>
       </c>
       <c r="S2" t="s">
-        <v>798</v>
+        <v>808</v>
       </c>
       <c r="T2">
-        <v>39.2361666667</v>
+        <v>38.14616667</v>
       </c>
       <c r="U2">
-        <v>-103.6968333333</v>
+        <v>-97.77293333</v>
       </c>
       <c r="V2">
-        <v>5508</v>
+        <v>2927</v>
       </c>
       <c r="W2">
-        <v>39.0065</v>
+        <v>38.19725</v>
       </c>
       <c r="X2">
-        <v>-103.6801666667</v>
+        <v>-97.42755</v>
       </c>
       <c r="Y2">
-        <v>15.88</v>
+        <v>19.08</v>
       </c>
       <c r="Z2">
-        <v>5359</v>
+        <v>2948</v>
       </c>
     </row>
     <row r="3" spans="1:26">
@@ -3167,79 +3200,79 @@
         <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="G3" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="H3">
-        <v>93577</v>
+        <v>63097</v>
       </c>
       <c r="I3">
-        <v>455</v>
+        <v>432</v>
       </c>
       <c r="J3" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="K3">
-        <v>7660</v>
+        <v>4523</v>
       </c>
       <c r="L3">
-        <v>22.46</v>
+        <v>15.88</v>
       </c>
       <c r="M3" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="N3" t="s">
-        <v>560</v>
+        <v>529</v>
       </c>
       <c r="O3" t="s">
-        <v>624</v>
+        <v>633</v>
       </c>
       <c r="P3" t="s">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="Q3" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="R3" t="s">
-        <v>720</v>
+        <v>729</v>
       </c>
       <c r="S3" t="s">
-        <v>799</v>
+        <v>809</v>
       </c>
       <c r="T3">
-        <v>39.2365</v>
+        <v>39.2361666667</v>
       </c>
       <c r="U3">
-        <v>-103.6966666667</v>
+        <v>-103.6968333333</v>
       </c>
       <c r="V3">
-        <v>5773</v>
+        <v>5508</v>
       </c>
       <c r="W3">
-        <v>38.9131666667</v>
+        <v>39.0065</v>
       </c>
       <c r="X3">
-        <v>-103.65</v>
+        <v>-103.6801666667</v>
       </c>
       <c r="Y3">
-        <v>22.46</v>
+        <v>15.88</v>
       </c>
       <c r="Z3">
-        <v>5263</v>
+        <v>5359</v>
       </c>
     </row>
     <row r="4" spans="1:26">
@@ -3247,79 +3280,79 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E4" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F4" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="G4" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="H4">
-        <v>87039</v>
+        <v>93577</v>
       </c>
       <c r="I4">
-        <v>670</v>
+        <v>455</v>
       </c>
       <c r="J4" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="K4">
-        <v>7026</v>
+        <v>7660</v>
       </c>
       <c r="L4">
-        <v>24.29</v>
+        <v>22.46</v>
       </c>
       <c r="M4" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="N4" t="s">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="O4" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="P4" t="s">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="Q4" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="R4" t="s">
-        <v>721</v>
+        <v>730</v>
       </c>
       <c r="S4" t="s">
-        <v>800</v>
+        <v>810</v>
       </c>
       <c r="T4">
-        <v>39.2366666667</v>
+        <v>39.2365</v>
       </c>
       <c r="U4">
         <v>-103.6966666667</v>
       </c>
       <c r="V4">
-        <v>5842</v>
+        <v>5773</v>
       </c>
       <c r="W4">
-        <v>38.8918333333</v>
+        <v>38.9131666667</v>
       </c>
       <c r="X4">
-        <v>-103.6066666667</v>
+        <v>-103.65</v>
       </c>
       <c r="Y4">
-        <v>24.29</v>
+        <v>22.46</v>
       </c>
       <c r="Z4">
-        <v>5136</v>
+        <v>5263</v>
       </c>
     </row>
     <row r="5" spans="1:26">
@@ -3327,79 +3360,79 @@
         <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C5" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D5" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E5" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F5" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G5" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="H5">
-        <v>89886</v>
+        <v>87039</v>
       </c>
       <c r="I5">
-        <v>421</v>
+        <v>670</v>
       </c>
       <c r="J5" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K5">
-        <v>7060</v>
+        <v>7026</v>
       </c>
       <c r="L5">
-        <v>25.06</v>
+        <v>24.29</v>
       </c>
       <c r="M5" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="N5" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="O5" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="P5" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="Q5" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="R5" t="s">
-        <v>722</v>
+        <v>731</v>
       </c>
       <c r="S5" t="s">
-        <v>801</v>
+        <v>811</v>
       </c>
       <c r="T5">
-        <v>39.2365</v>
+        <v>39.2366666667</v>
       </c>
       <c r="U5">
-        <v>-103.697</v>
+        <v>-103.6966666667</v>
       </c>
       <c r="V5">
-        <v>5795</v>
+        <v>5842</v>
       </c>
       <c r="W5">
-        <v>38.8808333333</v>
+        <v>38.8918333333</v>
       </c>
       <c r="X5">
-        <v>-103.6038333333</v>
+        <v>-103.6066666667</v>
       </c>
       <c r="Y5">
-        <v>25.06</v>
+        <v>24.29</v>
       </c>
       <c r="Z5">
-        <v>5319</v>
+        <v>5136</v>
       </c>
     </row>
     <row r="6" spans="1:26">
@@ -3407,79 +3440,79 @@
         <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D6" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E6" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F6" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="G6" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="H6">
-        <v>99763</v>
+        <v>89886</v>
       </c>
       <c r="I6">
-        <v>443</v>
+        <v>421</v>
       </c>
       <c r="J6" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="K6">
-        <v>7090</v>
+        <v>7060</v>
       </c>
       <c r="L6">
-        <v>40.62</v>
+        <v>25.06</v>
       </c>
       <c r="M6" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="N6" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="O6" t="s">
-        <v>624</v>
+        <v>633</v>
       </c>
       <c r="P6" t="s">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="Q6" t="s">
-        <v>527</v>
+        <v>575</v>
       </c>
       <c r="R6" t="s">
-        <v>723</v>
+        <v>732</v>
       </c>
       <c r="S6" t="s">
-        <v>802</v>
+        <v>812</v>
       </c>
       <c r="T6">
-        <v>39.6081666667</v>
+        <v>39.2365</v>
       </c>
       <c r="U6">
-        <v>-104.0423333333</v>
+        <v>-103.697</v>
       </c>
       <c r="V6">
-        <v>5284</v>
+        <v>5795</v>
       </c>
       <c r="W6">
-        <v>39.5006666667</v>
+        <v>38.8808333333</v>
       </c>
       <c r="X6">
-        <v>-103.2921666667</v>
+        <v>-103.6038333333</v>
       </c>
       <c r="Y6">
-        <v>40.62</v>
+        <v>25.06</v>
       </c>
       <c r="Z6">
-        <v>5099</v>
+        <v>5319</v>
       </c>
     </row>
     <row r="7" spans="1:26">
@@ -3490,76 +3523,76 @@
         <v>116</v>
       </c>
       <c r="C7" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D7" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E7" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F7" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="G7" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="H7">
-        <v>91254</v>
+        <v>99763</v>
       </c>
       <c r="I7">
-        <v>488</v>
+        <v>443</v>
       </c>
       <c r="J7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="K7">
-        <v>7500</v>
+        <v>7090</v>
       </c>
       <c r="L7">
-        <v>54.27</v>
+        <v>40.62</v>
       </c>
       <c r="M7" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="N7" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="O7" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="P7" t="s">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="Q7" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="R7" t="s">
-        <v>724</v>
+        <v>733</v>
       </c>
       <c r="S7" t="s">
-        <v>803</v>
+        <v>813</v>
       </c>
       <c r="T7">
-        <v>39.6085166667</v>
+        <v>39.6081666667</v>
       </c>
       <c r="U7">
-        <v>-104.0418833333</v>
+        <v>-104.0423333333</v>
       </c>
       <c r="V7">
-        <v>5414</v>
+        <v>5284</v>
       </c>
       <c r="W7">
-        <v>39.4465666667</v>
+        <v>39.5006666667</v>
       </c>
       <c r="X7">
-        <v>-103.0447833333</v>
+        <v>-103.2921666667</v>
       </c>
       <c r="Y7">
-        <v>54.27</v>
+        <v>40.62</v>
       </c>
       <c r="Z7">
-        <v>4768</v>
+        <v>5099</v>
       </c>
     </row>
     <row r="8" spans="1:26">
@@ -3567,79 +3600,79 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D8" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E8" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F8" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="G8" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="H8">
-        <v>94074</v>
+        <v>91254</v>
       </c>
       <c r="I8">
-        <v>619</v>
+        <v>488</v>
       </c>
       <c r="J8" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="K8">
-        <v>6490</v>
+        <v>7500</v>
       </c>
       <c r="L8">
-        <v>25.82</v>
+        <v>54.27</v>
       </c>
       <c r="M8" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="N8" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="O8" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="P8" t="s">
-        <v>641</v>
+        <v>649</v>
       </c>
       <c r="Q8" t="s">
-        <v>527</v>
+        <v>575</v>
       </c>
       <c r="R8" t="s">
-        <v>725</v>
+        <v>734</v>
       </c>
       <c r="S8" t="s">
-        <v>804</v>
+        <v>814</v>
       </c>
       <c r="T8">
-        <v>39.6083333333</v>
+        <v>39.6085166667</v>
       </c>
       <c r="U8">
-        <v>-104.042</v>
+        <v>-104.0418833333</v>
       </c>
       <c r="V8">
-        <v>5418</v>
+        <v>5414</v>
       </c>
       <c r="W8">
-        <v>39.2358333333</v>
+        <v>39.4465666667</v>
       </c>
       <c r="X8">
-        <v>-103.9986666667</v>
+        <v>-103.0447833333</v>
       </c>
       <c r="Y8">
-        <v>25.82</v>
+        <v>54.27</v>
       </c>
       <c r="Z8">
-        <v>6011</v>
+        <v>4768</v>
       </c>
     </row>
     <row r="9" spans="1:26">
@@ -3647,79 +3680,79 @@
         <v>33</v>
       </c>
       <c r="B9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C9" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D9" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E9" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F9" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="G9" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="H9">
-        <v>93949</v>
+        <v>94074</v>
       </c>
       <c r="I9">
-        <v>694</v>
+        <v>619</v>
       </c>
       <c r="J9" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="K9">
-        <v>7037</v>
+        <v>6490</v>
       </c>
       <c r="L9">
-        <v>29.96</v>
+        <v>25.82</v>
       </c>
       <c r="M9" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="N9" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="O9" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="P9" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="Q9" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="R9" t="s">
-        <v>726</v>
+        <v>735</v>
       </c>
       <c r="S9" t="s">
-        <v>805</v>
+        <v>815</v>
       </c>
       <c r="T9">
-        <v>39.6083</v>
+        <v>39.6083333333</v>
       </c>
       <c r="U9">
-        <v>-104.0423</v>
+        <v>-104.042</v>
       </c>
       <c r="V9">
-        <v>5289</v>
+        <v>5418</v>
       </c>
       <c r="W9">
-        <v>39.1748333333</v>
+        <v>39.2358333333</v>
       </c>
       <c r="X9">
-        <v>-104.0171666667</v>
+        <v>-103.9986666667</v>
       </c>
       <c r="Y9">
-        <v>29.96</v>
+        <v>25.82</v>
       </c>
       <c r="Z9">
-        <v>5847</v>
+        <v>6011</v>
       </c>
     </row>
     <row r="10" spans="1:26">
@@ -3727,79 +3760,79 @@
         <v>34</v>
       </c>
       <c r="B10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C10" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D10" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F10" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="G10" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="H10">
-        <v>95515</v>
+        <v>93949</v>
       </c>
       <c r="I10">
-        <v>258</v>
+        <v>694</v>
       </c>
       <c r="J10" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="K10">
-        <v>6566</v>
+        <v>7037</v>
       </c>
       <c r="L10">
-        <v>60.91</v>
+        <v>29.96</v>
       </c>
       <c r="M10" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="N10" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="O10" t="s">
-        <v>625</v>
+        <v>632</v>
       </c>
       <c r="P10" t="s">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="Q10" t="s">
-        <v>718</v>
+        <v>534</v>
       </c>
       <c r="R10" t="s">
-        <v>727</v>
+        <v>736</v>
       </c>
       <c r="S10" t="s">
-        <v>806</v>
+        <v>816</v>
       </c>
       <c r="T10">
-        <v>39.6081666667</v>
+        <v>39.6083</v>
       </c>
       <c r="U10">
-        <v>-104.0421666667</v>
+        <v>-104.0423</v>
       </c>
       <c r="V10">
-        <v>5235</v>
+        <v>5289</v>
       </c>
       <c r="W10">
-        <v>39.0996666667</v>
+        <v>39.1748333333</v>
       </c>
       <c r="X10">
-        <v>-103.1098333333</v>
+        <v>-104.0171666667</v>
       </c>
       <c r="Y10">
-        <v>60.91</v>
+        <v>29.96</v>
       </c>
       <c r="Z10">
-        <v>5131</v>
+        <v>5847</v>
       </c>
     </row>
     <row r="11" spans="1:26">
@@ -3807,79 +3840,79 @@
         <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C11" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D11" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E11" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F11" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="G11" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="H11">
-        <v>91544</v>
+        <v>95515</v>
       </c>
       <c r="I11">
-        <v>501</v>
+        <v>258</v>
       </c>
       <c r="J11" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="K11">
-        <v>7740</v>
+        <v>6566</v>
       </c>
       <c r="L11">
-        <v>87.26000000000001</v>
+        <v>60.91</v>
       </c>
       <c r="M11" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="N11" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="O11" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="P11" t="s">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="Q11" t="s">
-        <v>567</v>
+        <v>727</v>
       </c>
       <c r="R11" t="s">
-        <v>653</v>
+        <v>737</v>
       </c>
       <c r="S11" t="s">
-        <v>807</v>
+        <v>817</v>
       </c>
       <c r="T11">
-        <v>39.6083333333</v>
+        <v>39.6081666667</v>
       </c>
       <c r="U11">
         <v>-104.0421666667</v>
       </c>
       <c r="V11">
-        <v>5423</v>
+        <v>5235</v>
       </c>
       <c r="W11">
-        <v>39.3553333333</v>
+        <v>39.0996666667</v>
       </c>
       <c r="X11">
-        <v>-102.4378333333</v>
+        <v>-103.1098333333</v>
       </c>
       <c r="Y11">
-        <v>87.26000000000001</v>
+        <v>60.91</v>
       </c>
       <c r="Z11">
-        <v>4181</v>
+        <v>5131</v>
       </c>
     </row>
     <row r="12" spans="1:26">
@@ -3887,79 +3920,79 @@
         <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D12" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E12" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F12" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="G12" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="H12">
-        <v>89245</v>
+        <v>91544</v>
       </c>
       <c r="I12">
-        <v>308</v>
+        <v>501</v>
       </c>
       <c r="J12" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="K12">
-        <v>7294</v>
+        <v>7740</v>
       </c>
       <c r="L12">
-        <v>81.78</v>
+        <v>87.26000000000001</v>
       </c>
       <c r="M12" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="N12" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="O12" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="P12" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="Q12" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="R12" t="s">
-        <v>728</v>
+        <v>662</v>
       </c>
       <c r="S12" t="s">
-        <v>808</v>
+        <v>818</v>
       </c>
       <c r="T12">
-        <v>39.608</v>
+        <v>39.6083333333</v>
       </c>
       <c r="U12">
-        <v>-104.042</v>
+        <v>-104.0421666667</v>
       </c>
       <c r="V12">
-        <v>5664</v>
+        <v>5423</v>
       </c>
       <c r="W12">
-        <v>39.3813333333</v>
+        <v>39.3553333333</v>
       </c>
       <c r="X12">
-        <v>-102.5355</v>
+        <v>-102.4378333333</v>
       </c>
       <c r="Y12">
-        <v>81.78</v>
+        <v>87.26000000000001</v>
       </c>
       <c r="Z12">
-        <v>4273</v>
+        <v>4181</v>
       </c>
     </row>
     <row r="13" spans="1:26">
@@ -3967,79 +4000,79 @@
         <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="C13" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D13" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E13" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F13" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="G13" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="H13">
-        <v>88137</v>
+        <v>89245</v>
       </c>
       <c r="I13">
-        <v>374</v>
+        <v>308</v>
       </c>
       <c r="J13" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="K13">
-        <v>6930</v>
+        <v>7294</v>
       </c>
       <c r="L13">
-        <v>32.86</v>
+        <v>81.78</v>
       </c>
       <c r="M13" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="N13" t="s">
-        <v>562</v>
+        <v>575</v>
       </c>
       <c r="O13" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="P13" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="Q13" t="s">
-        <v>527</v>
+        <v>575</v>
       </c>
       <c r="R13" t="s">
-        <v>729</v>
+        <v>738</v>
       </c>
       <c r="S13" t="s">
-        <v>809</v>
+        <v>819</v>
       </c>
       <c r="T13">
-        <v>39.6085</v>
+        <v>39.608</v>
       </c>
       <c r="U13">
-        <v>-104.0421666667</v>
+        <v>-104.042</v>
       </c>
       <c r="V13">
-        <v>5444</v>
+        <v>5664</v>
       </c>
       <c r="W13">
-        <v>39.1426666667</v>
+        <v>39.3813333333</v>
       </c>
       <c r="X13">
-        <v>-103.9161666667</v>
+        <v>-102.5355</v>
       </c>
       <c r="Y13">
-        <v>32.86</v>
+        <v>81.78</v>
       </c>
       <c r="Z13">
-        <v>6013</v>
+        <v>4273</v>
       </c>
     </row>
     <row r="14" spans="1:26">
@@ -4047,79 +4080,79 @@
         <v>38</v>
       </c>
       <c r="B14" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C14" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D14" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E14" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F14" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="G14" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="H14">
-        <v>90615</v>
+        <v>88137</v>
       </c>
       <c r="I14">
-        <v>424</v>
+        <v>374</v>
       </c>
       <c r="J14" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="K14">
-        <v>6990</v>
+        <v>6930</v>
       </c>
       <c r="L14">
-        <v>35.75</v>
+        <v>32.86</v>
       </c>
       <c r="M14" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="N14" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="O14" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="P14" t="s">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="Q14" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="R14" t="s">
-        <v>730</v>
+        <v>739</v>
       </c>
       <c r="S14" t="s">
-        <v>810</v>
+        <v>820</v>
       </c>
       <c r="T14">
         <v>39.6085</v>
       </c>
       <c r="U14">
-        <v>-104.0418333333</v>
+        <v>-104.0421666667</v>
       </c>
       <c r="V14">
-        <v>5514</v>
+        <v>5444</v>
       </c>
       <c r="W14">
-        <v>39.0968333333</v>
+        <v>39.1426666667</v>
       </c>
       <c r="X14">
-        <v>-103.9398333333</v>
+        <v>-103.9161666667</v>
       </c>
       <c r="Y14">
-        <v>35.75</v>
+        <v>32.86</v>
       </c>
       <c r="Z14">
-        <v>6055</v>
+        <v>6013</v>
       </c>
     </row>
     <row r="15" spans="1:26">
@@ -4127,79 +4160,79 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C15" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D15" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E15" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F15" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="G15" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="H15">
-        <v>84498</v>
+        <v>90615</v>
       </c>
       <c r="I15">
-        <v>283</v>
+        <v>424</v>
       </c>
       <c r="J15" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="K15">
-        <v>5160</v>
+        <v>6990</v>
       </c>
       <c r="L15">
-        <v>83.91</v>
+        <v>35.75</v>
       </c>
       <c r="M15" t="s">
-        <v>484</v>
+        <v>497</v>
       </c>
       <c r="N15" t="s">
-        <v>562</v>
+        <v>575</v>
       </c>
       <c r="O15" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="P15" t="s">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="Q15" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="R15" t="s">
-        <v>731</v>
+        <v>740</v>
       </c>
       <c r="S15" t="s">
-        <v>811</v>
+        <v>821</v>
       </c>
       <c r="T15">
         <v>39.6085</v>
       </c>
       <c r="U15">
-        <v>-104.042</v>
+        <v>-104.0418333333</v>
       </c>
       <c r="V15">
-        <v>5322</v>
+        <v>5514</v>
       </c>
       <c r="W15">
-        <v>40.3986666667</v>
+        <v>39.0968333333</v>
       </c>
       <c r="X15">
-        <v>-102.8365</v>
+        <v>-103.9398333333</v>
       </c>
       <c r="Y15">
-        <v>83.91</v>
+        <v>35.75</v>
       </c>
       <c r="Z15">
-        <v>4698</v>
+        <v>6055</v>
       </c>
     </row>
     <row r="16" spans="1:26">
@@ -4207,79 +4240,79 @@
         <v>40</v>
       </c>
       <c r="B16" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C16" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D16" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E16" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F16" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="G16" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="H16">
-        <v>106085</v>
+        <v>84498</v>
       </c>
       <c r="I16">
-        <v>487</v>
+        <v>283</v>
       </c>
       <c r="J16" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="K16">
-        <v>7924</v>
+        <v>5160</v>
       </c>
       <c r="L16">
-        <v>97.72</v>
+        <v>83.91</v>
       </c>
       <c r="M16" t="s">
         <v>491</v>
       </c>
       <c r="N16" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="O16" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="P16" t="s">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="Q16" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="R16" t="s">
-        <v>732</v>
+        <v>741</v>
       </c>
       <c r="S16" t="s">
-        <v>812</v>
+        <v>822</v>
       </c>
       <c r="T16">
-        <v>39.6091666667</v>
+        <v>39.6085</v>
       </c>
       <c r="U16">
         <v>-104.042</v>
       </c>
       <c r="V16">
-        <v>5431</v>
+        <v>5322</v>
       </c>
       <c r="W16">
-        <v>40.4661666667</v>
+        <v>40.3986666667</v>
       </c>
       <c r="X16">
-        <v>-102.5708333333</v>
+        <v>-102.8365</v>
       </c>
       <c r="Y16">
-        <v>97.72</v>
+        <v>83.91</v>
       </c>
       <c r="Z16">
-        <v>3969</v>
+        <v>4698</v>
       </c>
     </row>
     <row r="17" spans="1:26">
@@ -4290,76 +4323,76 @@
         <v>121</v>
       </c>
       <c r="C17" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D17" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E17" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F17" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G17" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="H17">
-        <v>98987</v>
+        <v>106085</v>
       </c>
       <c r="I17">
-        <v>427</v>
+        <v>487</v>
       </c>
       <c r="J17" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="K17">
-        <v>6035</v>
+        <v>7924</v>
       </c>
       <c r="L17">
-        <v>38.68</v>
+        <v>97.72</v>
       </c>
       <c r="M17" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="N17" t="s">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="O17" t="s">
-        <v>625</v>
+        <v>632</v>
       </c>
       <c r="P17" t="s">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="Q17" t="s">
-        <v>718</v>
+        <v>534</v>
       </c>
       <c r="R17" t="s">
-        <v>733</v>
+        <v>742</v>
       </c>
       <c r="S17" t="s">
-        <v>813</v>
+        <v>823</v>
       </c>
       <c r="T17">
-        <v>39.6083333333</v>
+        <v>39.6091666667</v>
       </c>
       <c r="U17">
-        <v>-104.0418333333</v>
+        <v>-104.042</v>
       </c>
       <c r="V17">
-        <v>5351</v>
+        <v>5431</v>
       </c>
       <c r="W17">
-        <v>40.077</v>
+        <v>40.4661666667</v>
       </c>
       <c r="X17">
-        <v>-103.642</v>
+        <v>-102.5708333333</v>
       </c>
       <c r="Y17">
-        <v>38.68</v>
+        <v>97.72</v>
       </c>
       <c r="Z17">
-        <v>11560</v>
+        <v>3969</v>
       </c>
     </row>
     <row r="18" spans="1:26">
@@ -4367,79 +4400,79 @@
         <v>42</v>
       </c>
       <c r="B18" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C18" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D18" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E18" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F18" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="G18" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="H18">
-        <v>99136</v>
+        <v>98987</v>
       </c>
       <c r="I18">
-        <v>495</v>
+        <v>427</v>
       </c>
       <c r="J18" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="K18">
-        <v>5730</v>
+        <v>6035</v>
       </c>
       <c r="L18">
-        <v>27.05</v>
+        <v>38.68</v>
       </c>
       <c r="M18" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="N18" t="s">
-        <v>522</v>
+        <v>576</v>
       </c>
       <c r="O18" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="P18" t="s">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="Q18" t="s">
-        <v>527</v>
+        <v>727</v>
       </c>
       <c r="R18" t="s">
-        <v>734</v>
+        <v>743</v>
       </c>
       <c r="S18" t="s">
-        <v>814</v>
+        <v>824</v>
       </c>
       <c r="T18">
-        <v>39.1458333333</v>
+        <v>39.6083333333</v>
       </c>
       <c r="U18">
-        <v>-103.689</v>
+        <v>-104.0418333333</v>
       </c>
       <c r="V18">
-        <v>28567</v>
+        <v>5351</v>
       </c>
       <c r="W18">
-        <v>38.8186666667</v>
+        <v>40.077</v>
       </c>
       <c r="X18">
-        <v>-103.9661666667</v>
+        <v>-103.642</v>
       </c>
       <c r="Y18">
-        <v>27.05</v>
+        <v>38.68</v>
       </c>
       <c r="Z18">
-        <v>5621</v>
+        <v>11560</v>
       </c>
     </row>
     <row r="19" spans="1:26">
@@ -4447,79 +4480,79 @@
         <v>43</v>
       </c>
       <c r="B19" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C19" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D19" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E19" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F19" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="G19" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="H19">
-        <v>99980</v>
+        <v>99136</v>
       </c>
       <c r="I19">
-        <v>625</v>
+        <v>495</v>
       </c>
       <c r="J19" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="K19">
-        <v>6431</v>
+        <v>5730</v>
       </c>
       <c r="L19">
-        <v>32.74</v>
+        <v>27.05</v>
       </c>
       <c r="M19" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="N19" t="s">
-        <v>569</v>
+        <v>529</v>
       </c>
       <c r="O19" t="s">
-        <v>624</v>
+        <v>633</v>
       </c>
       <c r="P19" t="s">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="Q19" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="R19" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
       <c r="S19" t="s">
-        <v>815</v>
+        <v>825</v>
       </c>
       <c r="T19">
-        <v>39.6076666667</v>
+        <v>39.1458333333</v>
       </c>
       <c r="U19">
-        <v>-104.0425</v>
+        <v>-103.689</v>
       </c>
       <c r="V19">
-        <v>5394</v>
+        <v>28567</v>
       </c>
       <c r="W19">
-        <v>39.7298333333</v>
+        <v>38.8186666667</v>
       </c>
       <c r="X19">
-        <v>-103.4473333333</v>
+        <v>-103.9661666667</v>
       </c>
       <c r="Y19">
-        <v>32.74</v>
+        <v>27.05</v>
       </c>
       <c r="Z19">
-        <v>5285</v>
+        <v>5621</v>
       </c>
     </row>
     <row r="20" spans="1:26">
@@ -4527,79 +4560,79 @@
         <v>44</v>
       </c>
       <c r="B20" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C20" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D20" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E20" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F20" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="G20" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="H20">
-        <v>101911</v>
+        <v>99980</v>
       </c>
       <c r="I20">
-        <v>526</v>
+        <v>625</v>
       </c>
       <c r="J20" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="K20">
-        <v>6510</v>
+        <v>6431</v>
       </c>
       <c r="L20">
-        <v>37.42</v>
+        <v>32.74</v>
       </c>
       <c r="M20" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="N20" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="O20" t="s">
-        <v>624</v>
+        <v>633</v>
       </c>
       <c r="P20" t="s">
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="Q20" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="R20" t="s">
-        <v>736</v>
+        <v>745</v>
       </c>
       <c r="S20" t="s">
-        <v>816</v>
+        <v>826</v>
       </c>
       <c r="T20">
-        <v>39.6083333333</v>
+        <v>39.6076666667</v>
       </c>
       <c r="U20">
-        <v>-104.0421666667</v>
+        <v>-104.0425</v>
       </c>
       <c r="V20">
-        <v>5519</v>
+        <v>5394</v>
       </c>
       <c r="W20">
-        <v>39.7598333333</v>
+        <v>39.7298333333</v>
       </c>
       <c r="X20">
-        <v>-103.366</v>
+        <v>-103.4473333333</v>
       </c>
       <c r="Y20">
-        <v>37.42</v>
+        <v>32.74</v>
       </c>
       <c r="Z20">
-        <v>34398</v>
+        <v>5285</v>
       </c>
     </row>
     <row r="21" spans="1:26">
@@ -4607,79 +4640,79 @@
         <v>45</v>
       </c>
       <c r="B21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C21" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D21" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E21" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F21" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="G21" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="H21">
-        <v>89485</v>
+        <v>101911</v>
       </c>
       <c r="I21">
-        <v>150</v>
+        <v>526</v>
       </c>
       <c r="J21" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="K21">
-        <v>5269</v>
+        <v>6510</v>
       </c>
       <c r="L21">
-        <v>37.35</v>
+        <v>37.42</v>
       </c>
       <c r="M21" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="N21" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="O21" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="P21" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="Q21" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="R21" t="s">
-        <v>737</v>
+        <v>746</v>
       </c>
       <c r="S21" t="s">
-        <v>766</v>
+        <v>827</v>
       </c>
       <c r="T21">
         <v>39.6083333333</v>
       </c>
       <c r="U21">
-        <v>-104.042</v>
+        <v>-104.0421666667</v>
       </c>
       <c r="V21">
-        <v>5367</v>
+        <v>5519</v>
       </c>
       <c r="W21">
-        <v>39.7646666667</v>
+        <v>39.7598333333</v>
       </c>
       <c r="X21">
-        <v>-103.369</v>
+        <v>-103.366</v>
       </c>
       <c r="Y21">
-        <v>37.35</v>
+        <v>37.42</v>
       </c>
       <c r="Z21">
-        <v>45636</v>
+        <v>34398</v>
       </c>
     </row>
     <row r="22" spans="1:26">
@@ -4687,79 +4720,79 @@
         <v>46</v>
       </c>
       <c r="B22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C22" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D22" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E22" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F22" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="G22" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="H22">
-        <v>89552</v>
+        <v>89485</v>
       </c>
       <c r="I22">
-        <v>224</v>
+        <v>150</v>
       </c>
       <c r="J22" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="K22">
-        <v>6707</v>
+        <v>5269</v>
       </c>
       <c r="L22">
-        <v>71.97</v>
+        <v>37.35</v>
       </c>
       <c r="M22" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="N22" t="s">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="O22" t="s">
-        <v>625</v>
+        <v>632</v>
       </c>
       <c r="P22" t="s">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="Q22" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="R22" t="s">
-        <v>738</v>
+        <v>747</v>
       </c>
       <c r="S22" t="s">
-        <v>817</v>
+        <v>776</v>
       </c>
       <c r="T22">
-        <v>39.608</v>
+        <v>39.6083333333</v>
       </c>
       <c r="U22">
-        <v>-104.0423333333</v>
+        <v>-104.042</v>
       </c>
       <c r="V22">
-        <v>5421</v>
+        <v>5367</v>
       </c>
       <c r="W22">
-        <v>38.9500166667</v>
+        <v>39.7646666667</v>
       </c>
       <c r="X22">
-        <v>-102.998</v>
+        <v>-103.369</v>
       </c>
       <c r="Y22">
-        <v>71.97</v>
+        <v>37.35</v>
       </c>
       <c r="Z22">
-        <v>6746</v>
+        <v>45636</v>
       </c>
     </row>
     <row r="23" spans="1:26">
@@ -4767,79 +4800,79 @@
         <v>47</v>
       </c>
       <c r="B23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C23" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D23" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E23" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F23" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="G23" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="H23">
-        <v>90473</v>
+        <v>89552</v>
       </c>
       <c r="I23">
-        <v>380</v>
+        <v>224</v>
       </c>
       <c r="J23" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="K23">
-        <v>6840</v>
+        <v>6707</v>
       </c>
       <c r="L23">
-        <v>74.36</v>
+        <v>71.97</v>
       </c>
       <c r="M23" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="N23" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="O23" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="P23" t="s">
-        <v>656</v>
+        <v>664</v>
       </c>
       <c r="Q23" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="R23" t="s">
-        <v>739</v>
+        <v>748</v>
       </c>
       <c r="S23" t="s">
-        <v>818</v>
+        <v>828</v>
       </c>
       <c r="T23">
-        <v>39.6081666667</v>
+        <v>39.608</v>
       </c>
       <c r="U23">
-        <v>-104.0426666667</v>
+        <v>-104.0423333333</v>
       </c>
       <c r="V23">
-        <v>5594</v>
+        <v>5421</v>
       </c>
       <c r="W23">
-        <v>38.9375</v>
+        <v>38.9500166667</v>
       </c>
       <c r="X23">
-        <v>-102.9541666667</v>
+        <v>-102.998</v>
       </c>
       <c r="Y23">
-        <v>74.36</v>
+        <v>71.97</v>
       </c>
       <c r="Z23">
-        <v>5134</v>
+        <v>6746</v>
       </c>
     </row>
     <row r="24" spans="1:26">
@@ -4847,79 +4880,79 @@
         <v>48</v>
       </c>
       <c r="B24" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C24" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D24" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E24" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F24" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="G24" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="H24">
-        <v>109752</v>
+        <v>90473</v>
       </c>
       <c r="I24">
-        <v>477</v>
+        <v>380</v>
       </c>
       <c r="J24" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="K24">
-        <v>8221</v>
+        <v>6840</v>
       </c>
       <c r="L24">
-        <v>81.86</v>
+        <v>74.36</v>
       </c>
       <c r="M24" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="N24" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="O24" t="s">
-        <v>624</v>
+        <v>633</v>
       </c>
       <c r="P24" t="s">
-        <v>657</v>
+        <v>665</v>
       </c>
       <c r="Q24" t="s">
-        <v>527</v>
+        <v>575</v>
       </c>
       <c r="R24" t="s">
-        <v>740</v>
+        <v>749</v>
       </c>
       <c r="S24" t="s">
-        <v>819</v>
+        <v>829</v>
       </c>
       <c r="T24">
-        <v>39.608</v>
+        <v>39.6081666667</v>
       </c>
       <c r="U24">
-        <v>-104.0423333333</v>
+        <v>-104.0426666667</v>
       </c>
       <c r="V24">
-        <v>5281</v>
+        <v>5594</v>
       </c>
       <c r="W24">
-        <v>38.9566666667</v>
+        <v>38.9375</v>
       </c>
       <c r="X24">
-        <v>-102.7625</v>
+        <v>-102.9541666667</v>
       </c>
       <c r="Y24">
-        <v>81.86</v>
+        <v>74.36</v>
       </c>
       <c r="Z24">
-        <v>4489</v>
+        <v>5134</v>
       </c>
     </row>
     <row r="25" spans="1:26">
@@ -4927,79 +4960,79 @@
         <v>49</v>
       </c>
       <c r="B25" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C25" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D25" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E25" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F25" t="s">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="G25" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="H25">
-        <v>98821</v>
+        <v>109752</v>
       </c>
       <c r="I25">
-        <v>418</v>
+        <v>477</v>
       </c>
       <c r="J25" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="K25">
-        <v>6557</v>
+        <v>8221</v>
       </c>
       <c r="L25">
-        <v>21.94</v>
+        <v>81.86</v>
       </c>
       <c r="M25" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="N25" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="O25" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="P25" t="s">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="Q25" t="s">
-        <v>718</v>
+        <v>534</v>
       </c>
       <c r="R25" t="s">
-        <v>741</v>
+        <v>750</v>
       </c>
       <c r="S25" t="s">
-        <v>820</v>
+        <v>830</v>
       </c>
       <c r="T25">
         <v>39.608</v>
       </c>
       <c r="U25">
-        <v>-104.0418333333</v>
+        <v>-104.0423333333</v>
       </c>
       <c r="V25">
-        <v>5391</v>
+        <v>5281</v>
       </c>
       <c r="W25">
-        <v>39.3363</v>
+        <v>38.9566666667</v>
       </c>
       <c r="X25">
-        <v>-103.8284666667</v>
+        <v>-102.7625</v>
       </c>
       <c r="Y25">
-        <v>21.94</v>
+        <v>81.86</v>
       </c>
       <c r="Z25">
-        <v>6175</v>
+        <v>4489</v>
       </c>
     </row>
     <row r="26" spans="1:26">
@@ -5007,79 +5040,79 @@
         <v>50</v>
       </c>
       <c r="B26" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C26" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D26" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E26" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F26" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="G26" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="H26">
-        <v>72421</v>
+        <v>98821</v>
       </c>
       <c r="I26">
-        <v>280</v>
+        <v>418</v>
       </c>
       <c r="J26" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="K26">
-        <v>5921</v>
+        <v>6557</v>
       </c>
       <c r="L26">
-        <v>48.27</v>
+        <v>21.94</v>
       </c>
       <c r="M26" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="N26" t="s">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="O26" t="s">
-        <v>625</v>
+        <v>632</v>
       </c>
       <c r="P26" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="Q26" t="s">
-        <v>567</v>
+        <v>727</v>
       </c>
       <c r="R26" t="s">
-        <v>742</v>
+        <v>751</v>
       </c>
       <c r="S26" t="s">
-        <v>821</v>
+        <v>831</v>
       </c>
       <c r="T26">
-        <v>39.6083166667</v>
+        <v>39.608</v>
       </c>
       <c r="U26">
-        <v>-104.0419333333</v>
+        <v>-104.0418333333</v>
       </c>
       <c r="V26">
-        <v>5230</v>
+        <v>5391</v>
       </c>
       <c r="W26">
-        <v>39.7446666667</v>
+        <v>39.3363</v>
       </c>
       <c r="X26">
-        <v>-103.151</v>
+        <v>-103.8284666667</v>
       </c>
       <c r="Y26">
-        <v>48.27</v>
+        <v>21.94</v>
       </c>
       <c r="Z26">
-        <v>4812</v>
+        <v>6175</v>
       </c>
     </row>
     <row r="27" spans="1:26">
@@ -5087,79 +5120,79 @@
         <v>51</v>
       </c>
       <c r="B27" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C27" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D27" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E27" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F27" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G27" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="H27">
-        <v>72356</v>
+        <v>72421</v>
       </c>
       <c r="I27">
-        <v>362</v>
+        <v>280</v>
       </c>
       <c r="J27" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="K27">
-        <v>5470</v>
+        <v>5921</v>
       </c>
       <c r="L27">
-        <v>44.44</v>
+        <v>48.27</v>
       </c>
       <c r="M27" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="N27" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="O27" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="P27" t="s">
-        <v>660</v>
+        <v>668</v>
       </c>
       <c r="Q27" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="R27" t="s">
-        <v>743</v>
+        <v>752</v>
       </c>
       <c r="S27" t="s">
-        <v>822</v>
+        <v>832</v>
       </c>
       <c r="T27">
-        <v>39.6083333333</v>
+        <v>39.6083166667</v>
       </c>
       <c r="U27">
-        <v>-104.0418333333</v>
+        <v>-104.0419333333</v>
       </c>
       <c r="V27">
-        <v>5320</v>
+        <v>5230</v>
       </c>
       <c r="W27">
-        <v>39.7373333333</v>
+        <v>39.7446666667</v>
       </c>
       <c r="X27">
-        <v>-103.2226666667</v>
+        <v>-103.151</v>
       </c>
       <c r="Y27">
-        <v>44.44</v>
+        <v>48.27</v>
       </c>
       <c r="Z27">
-        <v>4897</v>
+        <v>4812</v>
       </c>
     </row>
     <row r="28" spans="1:26">
@@ -5167,58 +5200,58 @@
         <v>52</v>
       </c>
       <c r="B28" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C28" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D28" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E28" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F28" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="G28" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="H28">
-        <v>67108</v>
+        <v>72356</v>
       </c>
       <c r="I28">
-        <v>293</v>
+        <v>362</v>
       </c>
       <c r="J28" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="K28">
-        <v>4950</v>
+        <v>5470</v>
       </c>
       <c r="L28">
-        <v>40.84</v>
+        <v>44.44</v>
       </c>
       <c r="M28" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="N28" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="O28" t="s">
-        <v>624</v>
+        <v>633</v>
       </c>
       <c r="P28" t="s">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="Q28" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="R28" t="s">
-        <v>744</v>
+        <v>753</v>
       </c>
       <c r="S28" t="s">
-        <v>823</v>
+        <v>833</v>
       </c>
       <c r="T28">
         <v>39.6083333333</v>
@@ -5227,19 +5260,19 @@
         <v>-104.0418333333</v>
       </c>
       <c r="V28">
-        <v>5368</v>
+        <v>5320</v>
       </c>
       <c r="W28">
-        <v>39.735</v>
+        <v>39.7373333333</v>
       </c>
       <c r="X28">
-        <v>-103.2911666667</v>
+        <v>-103.2226666667</v>
       </c>
       <c r="Y28">
-        <v>40.84</v>
+        <v>44.44</v>
       </c>
       <c r="Z28">
-        <v>4971</v>
+        <v>4897</v>
       </c>
     </row>
     <row r="29" spans="1:26">
@@ -5247,79 +5280,79 @@
         <v>53</v>
       </c>
       <c r="B29" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C29" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D29" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E29" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F29" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="G29" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="H29">
-        <v>79183</v>
+        <v>67108</v>
       </c>
       <c r="I29">
-        <v>387</v>
+        <v>293</v>
       </c>
       <c r="J29" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="K29">
-        <v>6168</v>
+        <v>4950</v>
       </c>
       <c r="L29">
-        <v>56.25</v>
+        <v>40.84</v>
       </c>
       <c r="M29" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="N29" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="O29" t="s">
-        <v>624</v>
+        <v>633</v>
       </c>
       <c r="P29" t="s">
-        <v>635</v>
+        <v>670</v>
       </c>
       <c r="Q29" t="s">
-        <v>527</v>
+        <v>575</v>
       </c>
       <c r="R29" t="s">
-        <v>745</v>
+        <v>754</v>
       </c>
       <c r="S29" t="s">
-        <v>824</v>
+        <v>834</v>
       </c>
       <c r="T29">
-        <v>39.6085166667</v>
+        <v>39.6083333333</v>
       </c>
       <c r="U29">
-        <v>-104.0422166667</v>
+        <v>-104.0418333333</v>
       </c>
       <c r="V29">
-        <v>5434</v>
+        <v>5368</v>
       </c>
       <c r="W29">
-        <v>39.5215</v>
+        <v>39.735</v>
       </c>
       <c r="X29">
-        <v>-102.9915</v>
+        <v>-103.2911666667</v>
       </c>
       <c r="Y29">
-        <v>56.25</v>
+        <v>40.84</v>
       </c>
       <c r="Z29">
-        <v>4713</v>
+        <v>4971</v>
       </c>
     </row>
     <row r="30" spans="1:26">
@@ -5327,79 +5360,79 @@
         <v>54</v>
       </c>
       <c r="B30" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C30" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D30" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E30" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F30" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G30" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="H30">
-        <v>100589</v>
+        <v>79183</v>
       </c>
       <c r="I30">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="J30" t="s">
-        <v>405</v>
+        <v>426</v>
       </c>
       <c r="K30">
-        <v>6990</v>
+        <v>6168</v>
       </c>
       <c r="L30">
-        <v>80.22</v>
+        <v>56.25</v>
       </c>
       <c r="M30" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="N30" t="s">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="O30" t="s">
-        <v>624</v>
+        <v>633</v>
       </c>
       <c r="P30" t="s">
-        <v>662</v>
+        <v>644</v>
       </c>
       <c r="Q30" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="R30" t="s">
-        <v>746</v>
+        <v>755</v>
       </c>
       <c r="S30" t="s">
-        <v>825</v>
+        <v>835</v>
       </c>
       <c r="T30">
-        <v>39.6078333333</v>
+        <v>39.6085166667</v>
       </c>
       <c r="U30">
-        <v>-104.0415</v>
+        <v>-104.0422166667</v>
       </c>
       <c r="V30">
-        <v>5366</v>
+        <v>5434</v>
       </c>
       <c r="W30">
-        <v>38.8346666667</v>
+        <v>39.5215</v>
       </c>
       <c r="X30">
-        <v>-102.922</v>
+        <v>-102.9915</v>
       </c>
       <c r="Y30">
-        <v>80.22</v>
+        <v>56.25</v>
       </c>
       <c r="Z30">
-        <v>5042</v>
+        <v>4713</v>
       </c>
     </row>
     <row r="31" spans="1:26">
@@ -5407,58 +5440,58 @@
         <v>55</v>
       </c>
       <c r="B31" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C31" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D31" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E31" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F31" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="G31" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="H31">
-        <v>74803</v>
+        <v>100589</v>
       </c>
       <c r="I31">
-        <v>486</v>
+        <v>394</v>
       </c>
       <c r="J31" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="K31">
-        <v>5052</v>
+        <v>6990</v>
       </c>
       <c r="L31">
-        <v>64.63</v>
+        <v>80.22</v>
       </c>
       <c r="M31" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="N31" t="s">
-        <v>579</v>
+        <v>588</v>
       </c>
       <c r="O31" t="s">
-        <v>624</v>
+        <v>633</v>
       </c>
       <c r="P31" t="s">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="Q31" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="R31" t="s">
-        <v>747</v>
+        <v>756</v>
       </c>
       <c r="S31" t="s">
-        <v>774</v>
+        <v>836</v>
       </c>
       <c r="T31">
         <v>39.6078333333</v>
@@ -5467,19 +5500,19 @@
         <v>-104.0415</v>
       </c>
       <c r="V31">
-        <v>5285</v>
+        <v>5366</v>
       </c>
       <c r="W31">
-        <v>38.9044166667</v>
+        <v>38.8346666667</v>
       </c>
       <c r="X31">
-        <v>-103.2439</v>
+        <v>-102.922</v>
       </c>
       <c r="Y31">
-        <v>64.63</v>
+        <v>80.22</v>
       </c>
       <c r="Z31">
-        <v>4689</v>
+        <v>5042</v>
       </c>
     </row>
     <row r="32" spans="1:26">
@@ -5487,79 +5520,79 @@
         <v>56</v>
       </c>
       <c r="B32" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C32" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D32" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E32" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F32" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="G32" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="H32">
-        <v>86937</v>
+        <v>74803</v>
       </c>
       <c r="I32">
-        <v>376</v>
+        <v>486</v>
       </c>
       <c r="J32" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="K32">
-        <v>6671</v>
+        <v>5052</v>
       </c>
       <c r="L32">
-        <v>47.85</v>
+        <v>64.63</v>
       </c>
       <c r="M32" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="N32" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="O32" t="s">
-        <v>624</v>
+        <v>633</v>
       </c>
       <c r="P32" t="s">
-        <v>664</v>
+        <v>672</v>
       </c>
       <c r="Q32" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="R32" t="s">
-        <v>748</v>
+        <v>757</v>
       </c>
       <c r="S32" t="s">
-        <v>826</v>
+        <v>784</v>
       </c>
       <c r="T32">
-        <v>39.6085</v>
+        <v>39.6078333333</v>
       </c>
       <c r="U32">
-        <v>-104.042</v>
+        <v>-104.0415</v>
       </c>
       <c r="V32">
-        <v>5396</v>
+        <v>5285</v>
       </c>
       <c r="W32">
-        <v>39.6008166667</v>
+        <v>38.9044166667</v>
       </c>
       <c r="X32">
-        <v>-103.1426166667</v>
+        <v>-103.2439</v>
       </c>
       <c r="Y32">
-        <v>47.85</v>
+        <v>64.63</v>
       </c>
       <c r="Z32">
-        <v>5460</v>
+        <v>4689</v>
       </c>
     </row>
     <row r="33" spans="1:26">
@@ -5570,76 +5603,76 @@
         <v>134</v>
       </c>
       <c r="C33" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D33" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E33" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F33" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="G33" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="H33">
-        <v>96229</v>
+        <v>86937</v>
       </c>
       <c r="I33">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="J33" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="K33">
-        <v>7721</v>
+        <v>6671</v>
       </c>
       <c r="L33">
-        <v>38.55</v>
+        <v>47.85</v>
       </c>
       <c r="M33" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="N33" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="O33" t="s">
-        <v>624</v>
+        <v>633</v>
       </c>
       <c r="P33" t="s">
-        <v>665</v>
+        <v>673</v>
       </c>
       <c r="Q33" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="R33" t="s">
-        <v>749</v>
+        <v>758</v>
       </c>
       <c r="S33" t="s">
-        <v>827</v>
+        <v>837</v>
       </c>
       <c r="T33">
-        <v>39.6073333333</v>
+        <v>39.6085</v>
       </c>
       <c r="U33">
-        <v>-104.0398333333</v>
+        <v>-104.042</v>
       </c>
       <c r="V33">
-        <v>5417</v>
+        <v>5396</v>
       </c>
       <c r="W33">
-        <v>39.3150333333</v>
+        <v>39.6008166667</v>
       </c>
       <c r="X33">
-        <v>-103.4237666667</v>
+        <v>-103.1426166667</v>
       </c>
       <c r="Y33">
-        <v>38.55</v>
+        <v>47.85</v>
       </c>
       <c r="Z33">
-        <v>6287</v>
+        <v>5460</v>
       </c>
     </row>
     <row r="34" spans="1:26">
@@ -5647,79 +5680,79 @@
         <v>58</v>
       </c>
       <c r="B34" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C34" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D34" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E34" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G34" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="H34">
-        <v>102087</v>
+        <v>96229</v>
       </c>
       <c r="I34">
-        <v>390</v>
+        <v>374</v>
       </c>
       <c r="J34" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="K34">
-        <v>5936</v>
+        <v>7721</v>
       </c>
       <c r="L34">
-        <v>7.52</v>
+        <v>38.55</v>
       </c>
       <c r="M34" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="N34" t="s">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="O34" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="P34" t="s">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="Q34" t="s">
-        <v>527</v>
+        <v>575</v>
       </c>
       <c r="R34" t="s">
-        <v>750</v>
+        <v>759</v>
       </c>
       <c r="S34" t="s">
-        <v>828</v>
+        <v>838</v>
       </c>
       <c r="T34">
-        <v>39.236</v>
+        <v>39.6073333333</v>
       </c>
       <c r="U34">
-        <v>-103.697</v>
+        <v>-104.0398333333</v>
       </c>
       <c r="V34">
-        <v>5391</v>
+        <v>5417</v>
       </c>
       <c r="W34">
-        <v>39.1517833333</v>
+        <v>39.3150333333</v>
       </c>
       <c r="X34">
-        <v>-103.6078666667</v>
+        <v>-103.4237666667</v>
       </c>
       <c r="Y34">
-        <v>7.52</v>
+        <v>38.55</v>
       </c>
       <c r="Z34">
-        <v>5496</v>
+        <v>6287</v>
       </c>
     </row>
     <row r="35" spans="1:26">
@@ -5727,79 +5760,79 @@
         <v>59</v>
       </c>
       <c r="B35" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C35" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D35" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E35" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F35" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G35" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="H35">
-        <v>103257</v>
+        <v>102087</v>
       </c>
       <c r="I35">
-        <v>433</v>
+        <v>390</v>
       </c>
       <c r="J35" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="K35">
-        <v>6600</v>
+        <v>5936</v>
       </c>
       <c r="L35">
-        <v>32.05</v>
+        <v>7.52</v>
       </c>
       <c r="M35" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="N35" t="s">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="O35" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="P35" t="s">
-        <v>667</v>
+        <v>675</v>
       </c>
       <c r="Q35" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="R35" t="s">
-        <v>751</v>
+        <v>760</v>
       </c>
       <c r="S35" t="s">
-        <v>829</v>
+        <v>839</v>
       </c>
       <c r="T35">
-        <v>39.2783666667</v>
+        <v>39.236</v>
       </c>
       <c r="U35">
-        <v>-103.4952333333</v>
+        <v>-103.697</v>
       </c>
       <c r="V35">
-        <v>5713</v>
+        <v>5391</v>
       </c>
       <c r="W35">
-        <v>38.8373</v>
+        <v>39.1517833333</v>
       </c>
       <c r="X35">
-        <v>-103.30915</v>
+        <v>-103.6078666667</v>
       </c>
       <c r="Y35">
-        <v>32.05</v>
+        <v>7.52</v>
       </c>
       <c r="Z35">
-        <v>9506</v>
+        <v>5496</v>
       </c>
     </row>
     <row r="36" spans="1:26">
@@ -5807,79 +5840,79 @@
         <v>60</v>
       </c>
       <c r="B36" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C36" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D36" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E36" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F36" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G36" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="H36">
-        <v>78749</v>
+        <v>103257</v>
       </c>
       <c r="I36">
-        <v>192</v>
+        <v>433</v>
       </c>
       <c r="J36" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="K36">
-        <v>6319</v>
+        <v>6600</v>
       </c>
       <c r="L36">
-        <v>37.98</v>
+        <v>32.05</v>
       </c>
       <c r="M36" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="N36" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="O36" t="s">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="P36" t="s">
-        <v>668</v>
+        <v>676</v>
       </c>
       <c r="Q36" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="R36" t="s">
-        <v>752</v>
+        <v>761</v>
       </c>
       <c r="S36" t="s">
-        <v>830</v>
+        <v>840</v>
       </c>
       <c r="T36">
-        <v>34.7251666667</v>
+        <v>39.2783666667</v>
       </c>
       <c r="U36">
-        <v>-86.64700000000001</v>
+        <v>-103.4952333333</v>
       </c>
       <c r="V36">
-        <v>741</v>
+        <v>5713</v>
       </c>
       <c r="W36">
-        <v>34.4031166667</v>
+        <v>38.8373</v>
       </c>
       <c r="X36">
-        <v>-86.1054833333</v>
+        <v>-103.30915</v>
       </c>
       <c r="Y36">
-        <v>37.98</v>
+        <v>32.05</v>
       </c>
       <c r="Z36">
-        <v>14794</v>
+        <v>9506</v>
       </c>
     </row>
     <row r="37" spans="1:26">
@@ -5887,79 +5920,79 @@
         <v>61</v>
       </c>
       <c r="B37" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C37" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D37" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E37" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F37" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="G37" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="H37">
-        <v>101223</v>
+        <v>78749</v>
       </c>
       <c r="I37">
-        <v>412</v>
+        <v>192</v>
       </c>
       <c r="J37" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="K37">
-        <v>6390</v>
+        <v>6319</v>
       </c>
       <c r="L37">
-        <v>41.2</v>
+        <v>37.98</v>
       </c>
       <c r="M37" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="N37" t="s">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="O37" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="P37" t="s">
-        <v>669</v>
+        <v>677</v>
       </c>
       <c r="Q37" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="R37" t="s">
-        <v>753</v>
+        <v>762</v>
       </c>
       <c r="S37" t="s">
-        <v>831</v>
+        <v>841</v>
       </c>
       <c r="T37">
-        <v>40.2265</v>
+        <v>34.7251666667</v>
       </c>
       <c r="U37">
-        <v>-104.0778333333</v>
+        <v>-86.64700000000001</v>
       </c>
       <c r="V37">
-        <v>4721</v>
+        <v>741</v>
       </c>
       <c r="W37">
-        <v>40.5656666667</v>
+        <v>34.4031166667</v>
       </c>
       <c r="X37">
-        <v>-104.7225</v>
+        <v>-86.1054833333</v>
       </c>
       <c r="Y37">
-        <v>41.2</v>
+        <v>37.98</v>
       </c>
       <c r="Z37">
-        <v>4915</v>
+        <v>14794</v>
       </c>
     </row>
     <row r="38" spans="1:26">
@@ -5967,79 +6000,79 @@
         <v>62</v>
       </c>
       <c r="B38" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C38" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D38" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E38" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F38" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="G38" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="H38">
-        <v>84841</v>
+        <v>101223</v>
       </c>
       <c r="I38">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="J38" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="K38">
-        <v>7710</v>
+        <v>6390</v>
       </c>
       <c r="L38">
-        <v>37.69</v>
+        <v>41.2</v>
       </c>
       <c r="M38" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="N38" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="O38" t="s">
-        <v>626</v>
+        <v>636</v>
       </c>
       <c r="P38" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="Q38" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="R38" t="s">
-        <v>754</v>
+        <v>763</v>
       </c>
       <c r="S38" t="s">
-        <v>832</v>
+        <v>842</v>
       </c>
       <c r="T38">
-        <v>39.7588166667</v>
+        <v>40.2265</v>
       </c>
       <c r="U38">
-        <v>-104.9900666667</v>
+        <v>-104.0778333333</v>
       </c>
       <c r="V38">
-        <v>6661</v>
+        <v>4721</v>
       </c>
       <c r="W38">
-        <v>40.07435</v>
+        <v>40.5656666667</v>
       </c>
       <c r="X38">
-        <v>-104.4093666667</v>
+        <v>-104.7225</v>
       </c>
       <c r="Y38">
-        <v>37.69</v>
+        <v>41.2</v>
       </c>
       <c r="Z38">
-        <v>4837</v>
+        <v>4915</v>
       </c>
     </row>
     <row r="39" spans="1:26">
@@ -6047,79 +6080,79 @@
         <v>63</v>
       </c>
       <c r="B39" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C39" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D39" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E39" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="F39" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="G39" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="H39">
-        <v>92029</v>
+        <v>84841</v>
       </c>
       <c r="I39">
-        <v>458</v>
+        <v>425</v>
       </c>
       <c r="J39" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="K39">
-        <v>7440</v>
+        <v>7710</v>
       </c>
       <c r="L39">
-        <v>71.73</v>
+        <v>37.69</v>
       </c>
       <c r="M39" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="N39" t="s">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="O39" t="s">
-        <v>624</v>
+        <v>634</v>
       </c>
       <c r="P39" t="s">
-        <v>671</v>
+        <v>679</v>
       </c>
       <c r="Q39" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="R39" t="s">
-        <v>755</v>
+        <v>764</v>
       </c>
       <c r="S39" t="s">
-        <v>833</v>
+        <v>843</v>
       </c>
       <c r="T39">
-        <v>39.6075</v>
+        <v>39.7588166667</v>
       </c>
       <c r="U39">
-        <v>-104.0411666667</v>
+        <v>-104.9900666667</v>
       </c>
       <c r="V39">
-        <v>5443</v>
+        <v>6661</v>
       </c>
       <c r="W39">
-        <v>39.1121666667</v>
+        <v>40.07435</v>
       </c>
       <c r="X39">
-        <v>-102.86</v>
+        <v>-104.4093666667</v>
       </c>
       <c r="Y39">
-        <v>71.73</v>
+        <v>37.69</v>
       </c>
       <c r="Z39">
-        <v>5143</v>
+        <v>4837</v>
       </c>
     </row>
     <row r="40" spans="1:26">
@@ -6127,79 +6160,79 @@
         <v>64</v>
       </c>
       <c r="B40" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C40" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D40" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E40" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F40" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="G40" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="H40">
-        <v>97223</v>
+        <v>92029</v>
       </c>
       <c r="I40">
-        <v>507</v>
+        <v>458</v>
       </c>
       <c r="J40" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="K40">
-        <v>7980</v>
+        <v>7440</v>
       </c>
       <c r="L40">
-        <v>76.06</v>
+        <v>71.73</v>
       </c>
       <c r="M40" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="N40" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="O40" t="s">
-        <v>624</v>
+        <v>633</v>
       </c>
       <c r="P40" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
       <c r="Q40" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="R40" t="s">
-        <v>756</v>
+        <v>765</v>
       </c>
       <c r="S40" t="s">
-        <v>834</v>
+        <v>844</v>
       </c>
       <c r="T40">
-        <v>39.6075833333</v>
+        <v>39.6075</v>
       </c>
       <c r="U40">
-        <v>-104.0413166667</v>
+        <v>-104.0411666667</v>
       </c>
       <c r="V40">
-        <v>5335</v>
+        <v>5443</v>
       </c>
       <c r="W40">
-        <v>39.0711</v>
+        <v>39.1121666667</v>
       </c>
       <c r="X40">
-        <v>-102.7973166667</v>
+        <v>-102.86</v>
       </c>
       <c r="Y40">
-        <v>76.06</v>
+        <v>71.73</v>
       </c>
       <c r="Z40">
-        <v>4761</v>
+        <v>5143</v>
       </c>
     </row>
     <row r="41" spans="1:26">
@@ -6207,79 +6240,79 @@
         <v>65</v>
       </c>
       <c r="B41" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C41" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D41" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E41" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F41" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G41" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="H41">
-        <v>105170</v>
+        <v>97223</v>
       </c>
       <c r="I41">
-        <v>459</v>
+        <v>507</v>
       </c>
       <c r="J41" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="K41">
-        <v>7050</v>
+        <v>7980</v>
       </c>
       <c r="L41">
-        <v>54.25</v>
+        <v>76.06</v>
       </c>
       <c r="M41" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="N41" t="s">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="O41" t="s">
-        <v>224</v>
+        <v>633</v>
       </c>
       <c r="P41" t="s">
-        <v>673</v>
+        <v>681</v>
       </c>
       <c r="Q41" t="s">
-        <v>527</v>
+        <v>575</v>
       </c>
       <c r="R41" t="s">
-        <v>757</v>
+        <v>766</v>
       </c>
       <c r="S41" t="s">
-        <v>835</v>
+        <v>845</v>
       </c>
       <c r="T41">
-        <v>39.6085</v>
+        <v>39.6075833333</v>
       </c>
       <c r="U41">
-        <v>-104.0425</v>
+        <v>-104.0413166667</v>
       </c>
       <c r="V41">
-        <v>5334</v>
+        <v>5335</v>
       </c>
       <c r="W41">
-        <v>39.2156666667</v>
+        <v>39.0711</v>
       </c>
       <c r="X41">
-        <v>-103.1618333333</v>
+        <v>-102.7973166667</v>
       </c>
       <c r="Y41">
-        <v>54.25</v>
+        <v>76.06</v>
       </c>
       <c r="Z41">
-        <v>5740</v>
+        <v>4761</v>
       </c>
     </row>
     <row r="42" spans="1:26">
@@ -6287,79 +6320,79 @@
         <v>66</v>
       </c>
       <c r="B42" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C42" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D42" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E42" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F42" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G42" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="H42">
-        <v>63158</v>
+        <v>105170</v>
       </c>
       <c r="I42">
-        <v>329</v>
+        <v>459</v>
       </c>
       <c r="J42" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="K42">
-        <v>5231</v>
+        <v>7050</v>
       </c>
       <c r="L42">
-        <v>81.72</v>
+        <v>54.25</v>
       </c>
       <c r="M42" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="N42" t="s">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="O42" t="s">
-        <v>624</v>
+        <v>227</v>
       </c>
       <c r="P42" t="s">
-        <v>674</v>
+        <v>682</v>
       </c>
       <c r="Q42" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="R42" t="s">
-        <v>478</v>
+        <v>767</v>
       </c>
       <c r="S42" t="s">
-        <v>836</v>
+        <v>846</v>
       </c>
       <c r="T42">
-        <v>39.6083333333</v>
+        <v>39.6085</v>
       </c>
       <c r="U42">
         <v>-104.0425</v>
       </c>
       <c r="V42">
-        <v>5367</v>
+        <v>5334</v>
       </c>
       <c r="W42">
-        <v>39.48805</v>
+        <v>39.2156666667</v>
       </c>
       <c r="X42">
-        <v>-102.51555</v>
+        <v>-103.1618333333</v>
       </c>
       <c r="Y42">
-        <v>81.72</v>
+        <v>54.25</v>
       </c>
       <c r="Z42">
-        <v>4075</v>
+        <v>5740</v>
       </c>
     </row>
     <row r="43" spans="1:26">
@@ -6367,79 +6400,79 @@
         <v>67</v>
       </c>
       <c r="B43" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C43" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D43" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E43" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F43" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G43" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="H43">
-        <v>107700</v>
+        <v>63158</v>
       </c>
       <c r="I43">
-        <v>472</v>
+        <v>329</v>
       </c>
       <c r="J43" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="K43">
-        <v>7323</v>
+        <v>5231</v>
       </c>
       <c r="L43">
-        <v>80.5</v>
+        <v>81.72</v>
       </c>
       <c r="M43" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="N43" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="O43" t="s">
-        <v>224</v>
+        <v>633</v>
       </c>
       <c r="P43" t="s">
-        <v>675</v>
+        <v>683</v>
       </c>
       <c r="Q43" t="s">
-        <v>527</v>
+        <v>575</v>
       </c>
       <c r="R43" t="s">
-        <v>758</v>
+        <v>485</v>
       </c>
       <c r="S43" t="s">
-        <v>837</v>
+        <v>847</v>
       </c>
       <c r="T43">
-        <v>39.6083</v>
+        <v>39.6083333333</v>
       </c>
       <c r="U43">
-        <v>-104.0426666667</v>
+        <v>-104.0425</v>
       </c>
       <c r="V43">
-        <v>5234</v>
+        <v>5367</v>
       </c>
       <c r="W43">
-        <v>39.4588333333</v>
+        <v>39.48805</v>
       </c>
       <c r="X43">
-        <v>-102.5435</v>
+        <v>-102.51555</v>
       </c>
       <c r="Y43">
-        <v>80.5</v>
+        <v>81.72</v>
       </c>
       <c r="Z43">
-        <v>4646</v>
+        <v>4075</v>
       </c>
     </row>
     <row r="44" spans="1:26">
@@ -6447,79 +6480,79 @@
         <v>68</v>
       </c>
       <c r="B44" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C44" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D44" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E44" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F44" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="G44" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="H44">
-        <v>103639</v>
+        <v>107700</v>
       </c>
       <c r="I44">
-        <v>382</v>
+        <v>472</v>
       </c>
       <c r="J44" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="K44">
-        <v>6371</v>
+        <v>7323</v>
       </c>
       <c r="L44">
-        <v>56.46</v>
+        <v>80.5</v>
       </c>
       <c r="M44" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="N44" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="O44" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="P44" t="s">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="Q44" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="R44" t="s">
-        <v>759</v>
+        <v>768</v>
       </c>
       <c r="S44" t="s">
-        <v>838</v>
+        <v>848</v>
       </c>
       <c r="T44">
-        <v>39.608</v>
+        <v>39.6083</v>
       </c>
       <c r="U44">
-        <v>-104.0421666667</v>
+        <v>-104.0426666667</v>
       </c>
       <c r="V44">
-        <v>5388</v>
+        <v>5234</v>
       </c>
       <c r="W44">
-        <v>39.8818166667</v>
+        <v>39.4588333333</v>
       </c>
       <c r="X44">
-        <v>-103.0400833333</v>
+        <v>-102.5435</v>
       </c>
       <c r="Y44">
-        <v>56.46</v>
+        <v>80.5</v>
       </c>
       <c r="Z44">
-        <v>6891</v>
+        <v>4646</v>
       </c>
     </row>
     <row r="45" spans="1:26">
@@ -6527,79 +6560,79 @@
         <v>69</v>
       </c>
       <c r="B45" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C45" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D45" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E45" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F45" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="G45" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="H45">
-        <v>86211</v>
+        <v>103639</v>
       </c>
       <c r="I45">
-        <v>211</v>
+        <v>382</v>
       </c>
       <c r="J45" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="K45">
-        <v>7168</v>
+        <v>6371</v>
       </c>
       <c r="L45">
-        <v>75.56999999999999</v>
+        <v>56.46</v>
       </c>
       <c r="M45" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="N45" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="O45" t="s">
-        <v>629</v>
+        <v>227</v>
       </c>
       <c r="P45" t="s">
-        <v>677</v>
+        <v>685</v>
       </c>
       <c r="Q45" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="R45" t="s">
-        <v>760</v>
+        <v>769</v>
       </c>
       <c r="S45" t="s">
-        <v>839</v>
+        <v>849</v>
       </c>
       <c r="T45">
-        <v>39.6083333333</v>
+        <v>39.608</v>
       </c>
       <c r="U45">
-        <v>-104.0423333333</v>
+        <v>-104.0421666667</v>
       </c>
       <c r="V45">
-        <v>5251</v>
+        <v>5388</v>
       </c>
       <c r="W45">
-        <v>39.7735</v>
+        <v>39.8818166667</v>
       </c>
       <c r="X45">
-        <v>-102.6361666667</v>
+        <v>-103.0400833333</v>
       </c>
       <c r="Y45">
-        <v>75.56999999999999</v>
+        <v>56.46</v>
       </c>
       <c r="Z45">
-        <v>5519</v>
+        <v>6891</v>
       </c>
     </row>
     <row r="46" spans="1:26">
@@ -6607,79 +6640,79 @@
         <v>70</v>
       </c>
       <c r="B46" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="C46" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D46" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E46" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F46" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="G46" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="H46">
-        <v>92213</v>
+        <v>86211</v>
       </c>
       <c r="I46">
-        <v>365</v>
+        <v>211</v>
       </c>
       <c r="J46" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="K46">
-        <v>6521</v>
+        <v>7168</v>
       </c>
       <c r="L46">
-        <v>62.99</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="M46" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="N46" t="s">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="O46" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="P46" t="s">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="Q46" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="R46" t="s">
-        <v>756</v>
+        <v>770</v>
       </c>
       <c r="S46" t="s">
-        <v>840</v>
+        <v>850</v>
       </c>
       <c r="T46">
-        <v>39.6086666667</v>
+        <v>39.6083333333</v>
       </c>
       <c r="U46">
         <v>-104.0423333333</v>
       </c>
       <c r="V46">
-        <v>5389</v>
+        <v>5251</v>
       </c>
       <c r="W46">
-        <v>39.6407833333</v>
+        <v>39.7735</v>
       </c>
       <c r="X46">
-        <v>-102.8586666667</v>
+        <v>-102.6361666667</v>
       </c>
       <c r="Y46">
-        <v>62.99</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="Z46">
-        <v>5713</v>
+        <v>5519</v>
       </c>
     </row>
     <row r="47" spans="1:26">
@@ -6687,79 +6720,79 @@
         <v>71</v>
       </c>
       <c r="B47" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C47" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D47" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E47" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F47" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G47" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="H47">
-        <v>95303</v>
+        <v>92213</v>
       </c>
       <c r="I47">
-        <v>468</v>
+        <v>365</v>
       </c>
       <c r="J47" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="K47">
-        <v>7413</v>
+        <v>6521</v>
       </c>
       <c r="L47">
-        <v>70.08</v>
+        <v>62.99</v>
       </c>
       <c r="M47" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="N47" t="s">
-        <v>586</v>
+        <v>600</v>
       </c>
       <c r="O47" t="s">
-        <v>628</v>
+        <v>638</v>
       </c>
       <c r="P47" t="s">
-        <v>679</v>
+        <v>687</v>
       </c>
       <c r="Q47" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="R47" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="S47" t="s">
-        <v>841</v>
+        <v>851</v>
       </c>
       <c r="T47">
-        <v>39.6087666667</v>
+        <v>39.6086666667</v>
       </c>
       <c r="U47">
-        <v>-104.0423166667</v>
+        <v>-104.0423333333</v>
       </c>
       <c r="V47">
-        <v>5312</v>
+        <v>5389</v>
       </c>
       <c r="W47">
-        <v>39.6068333333</v>
+        <v>39.6407833333</v>
       </c>
       <c r="X47">
-        <v>-102.7248333333</v>
+        <v>-102.8586666667</v>
       </c>
       <c r="Y47">
-        <v>70.08</v>
+        <v>62.99</v>
       </c>
       <c r="Z47">
-        <v>4310</v>
+        <v>5713</v>
       </c>
     </row>
     <row r="48" spans="1:26">
@@ -6767,79 +6800,79 @@
         <v>72</v>
       </c>
       <c r="B48" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C48" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D48" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E48" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F48" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="G48" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="H48">
-        <v>111177</v>
+        <v>95303</v>
       </c>
       <c r="I48">
-        <v>571</v>
+        <v>468</v>
       </c>
       <c r="J48" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="K48">
-        <v>7512</v>
+        <v>7413</v>
       </c>
       <c r="L48">
-        <v>76.73</v>
+        <v>70.08</v>
       </c>
       <c r="M48" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="N48" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="O48" t="s">
-        <v>224</v>
+        <v>636</v>
       </c>
       <c r="P48" t="s">
-        <v>680</v>
+        <v>688</v>
       </c>
       <c r="Q48" t="s">
-        <v>527</v>
+        <v>575</v>
       </c>
       <c r="R48" t="s">
-        <v>762</v>
+        <v>771</v>
       </c>
       <c r="S48" t="s">
-        <v>842</v>
+        <v>852</v>
       </c>
       <c r="T48">
-        <v>39.6078333333</v>
+        <v>39.6087666667</v>
       </c>
       <c r="U48">
-        <v>-104.0413333333</v>
+        <v>-104.0423166667</v>
       </c>
       <c r="V48">
-        <v>5340</v>
+        <v>5312</v>
       </c>
       <c r="W48">
-        <v>39.1830333333</v>
+        <v>39.6068333333</v>
       </c>
       <c r="X48">
-        <v>-102.7124166667</v>
+        <v>-102.7248333333</v>
       </c>
       <c r="Y48">
-        <v>76.73</v>
+        <v>70.08</v>
       </c>
       <c r="Z48">
-        <v>5060</v>
+        <v>4310</v>
       </c>
     </row>
     <row r="49" spans="1:26">
@@ -6847,79 +6880,79 @@
         <v>73</v>
       </c>
       <c r="B49" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C49" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D49" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E49" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F49" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="G49" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="H49">
-        <v>101899</v>
+        <v>111177</v>
       </c>
       <c r="I49">
-        <v>418</v>
+        <v>571</v>
       </c>
       <c r="J49" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="K49">
-        <v>6507</v>
+        <v>7512</v>
       </c>
       <c r="L49">
-        <v>34.24</v>
+        <v>76.73</v>
       </c>
       <c r="M49" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="N49" t="s">
-        <v>594</v>
+        <v>601</v>
       </c>
       <c r="O49" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="P49" t="s">
-        <v>681</v>
+        <v>689</v>
       </c>
       <c r="Q49" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="R49" t="s">
-        <v>763</v>
+        <v>772</v>
       </c>
       <c r="S49" t="s">
-        <v>843</v>
+        <v>853</v>
       </c>
       <c r="T49">
-        <v>39.6083333333</v>
+        <v>39.6078333333</v>
       </c>
       <c r="U49">
-        <v>-104.042</v>
+        <v>-104.0413333333</v>
       </c>
       <c r="V49">
-        <v>5284</v>
+        <v>5340</v>
       </c>
       <c r="W49">
-        <v>39.8047333333</v>
+        <v>39.1830333333</v>
       </c>
       <c r="X49">
-        <v>-103.4500166667</v>
+        <v>-102.7124166667</v>
       </c>
       <c r="Y49">
-        <v>34.24</v>
+        <v>76.73</v>
       </c>
       <c r="Z49">
-        <v>4718</v>
+        <v>5060</v>
       </c>
     </row>
     <row r="50" spans="1:26">
@@ -6927,79 +6960,79 @@
         <v>74</v>
       </c>
       <c r="B50" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C50" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D50" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E50" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F50" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="G50" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H50">
-        <v>93012</v>
+        <v>101899</v>
       </c>
       <c r="I50">
-        <v>677</v>
+        <v>418</v>
       </c>
       <c r="J50" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="K50">
-        <v>6885</v>
+        <v>6507</v>
       </c>
       <c r="L50">
-        <v>51.37</v>
+        <v>34.24</v>
       </c>
       <c r="M50" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="N50" t="s">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="O50" t="s">
-        <v>624</v>
+        <v>227</v>
       </c>
       <c r="P50" t="s">
-        <v>682</v>
+        <v>690</v>
       </c>
       <c r="Q50" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="R50" t="s">
-        <v>764</v>
+        <v>773</v>
       </c>
       <c r="S50" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="T50">
-        <v>39.6081666667</v>
+        <v>39.6083333333</v>
       </c>
       <c r="U50">
-        <v>-104.0421666667</v>
+        <v>-104.042</v>
       </c>
       <c r="V50">
-        <v>5246</v>
+        <v>5284</v>
       </c>
       <c r="W50">
-        <v>39.412</v>
+        <v>39.8047333333</v>
       </c>
       <c r="X50">
-        <v>-103.112</v>
+        <v>-103.4500166667</v>
       </c>
       <c r="Y50">
-        <v>51.37</v>
+        <v>34.24</v>
       </c>
       <c r="Z50">
-        <v>4911</v>
+        <v>4718</v>
       </c>
     </row>
     <row r="51" spans="1:26">
@@ -7007,79 +7040,79 @@
         <v>75</v>
       </c>
       <c r="B51" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C51" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D51" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E51" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F51" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="G51" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="H51">
-        <v>88369</v>
+        <v>93012</v>
       </c>
       <c r="I51">
-        <v>354</v>
+        <v>677</v>
       </c>
       <c r="J51" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="K51">
-        <v>9683</v>
+        <v>6885</v>
       </c>
       <c r="L51">
-        <v>19</v>
+        <v>51.37</v>
       </c>
       <c r="M51" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="N51" t="s">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="O51" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="P51" t="s">
-        <v>683</v>
+        <v>691</v>
       </c>
       <c r="Q51" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="R51" t="s">
-        <v>765</v>
+        <v>774</v>
       </c>
       <c r="S51" t="s">
-        <v>701</v>
+        <v>855</v>
       </c>
       <c r="T51">
-        <v>39.2788333333</v>
+        <v>39.6081666667</v>
       </c>
       <c r="U51">
-        <v>-103.4953333333</v>
+        <v>-104.0421666667</v>
       </c>
       <c r="V51">
-        <v>5830</v>
+        <v>5246</v>
       </c>
       <c r="W51">
-        <v>39.0613333333</v>
+        <v>39.412</v>
       </c>
       <c r="X51">
-        <v>-103.2778333333</v>
+        <v>-103.112</v>
       </c>
       <c r="Y51">
-        <v>19</v>
+        <v>51.37</v>
       </c>
       <c r="Z51">
-        <v>5119</v>
+        <v>4911</v>
       </c>
     </row>
     <row r="52" spans="1:26">
@@ -7087,79 +7120,79 @@
         <v>76</v>
       </c>
       <c r="B52" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C52" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D52" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E52" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F52" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="G52" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="H52">
-        <v>91544</v>
+        <v>88369</v>
       </c>
       <c r="I52">
-        <v>480</v>
+        <v>354</v>
       </c>
       <c r="J52" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="K52">
-        <v>8340</v>
+        <v>9683</v>
       </c>
       <c r="L52">
-        <v>13.41</v>
+        <v>19</v>
       </c>
       <c r="M52" t="s">
-        <v>481</v>
+        <v>533</v>
       </c>
       <c r="N52" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="O52" t="s">
-        <v>224</v>
+        <v>637</v>
       </c>
       <c r="P52" t="s">
-        <v>672</v>
+        <v>692</v>
       </c>
       <c r="Q52" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="R52" t="s">
-        <v>766</v>
+        <v>775</v>
       </c>
       <c r="S52" t="s">
-        <v>845</v>
+        <v>710</v>
       </c>
       <c r="T52">
-        <v>39.2779</v>
+        <v>39.2788333333</v>
       </c>
       <c r="U52">
-        <v>-103.4955333333</v>
+        <v>-103.4953333333</v>
       </c>
       <c r="V52">
-        <v>5677</v>
+        <v>5830</v>
       </c>
       <c r="W52">
-        <v>39.0890666667</v>
+        <v>39.0613333333</v>
       </c>
       <c r="X52">
-        <v>-103.43705</v>
+        <v>-103.2778333333</v>
       </c>
       <c r="Y52">
-        <v>13.41</v>
+        <v>19</v>
       </c>
       <c r="Z52">
-        <v>4968</v>
+        <v>5119</v>
       </c>
     </row>
     <row r="53" spans="1:26">
@@ -7170,76 +7203,76 @@
         <v>143</v>
       </c>
       <c r="C53" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D53" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E53" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F53" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="G53" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="H53">
-        <v>91973</v>
+        <v>91544</v>
       </c>
       <c r="I53">
-        <v>432</v>
+        <v>480</v>
       </c>
       <c r="J53" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="K53">
-        <v>7661</v>
+        <v>8340</v>
       </c>
       <c r="L53">
-        <v>11.38</v>
+        <v>13.41</v>
       </c>
       <c r="M53" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
       <c r="N53" t="s">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="O53" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="P53" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="Q53" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="R53" t="s">
-        <v>767</v>
+        <v>776</v>
       </c>
       <c r="S53" t="s">
-        <v>846</v>
+        <v>856</v>
       </c>
       <c r="T53">
-        <v>39.2786666667</v>
+        <v>39.2779</v>
       </c>
       <c r="U53">
-        <v>-103.4953333333</v>
+        <v>-103.4955333333</v>
       </c>
       <c r="V53">
-        <v>5774</v>
+        <v>5677</v>
       </c>
       <c r="W53">
-        <v>39.1167166667</v>
+        <v>39.0890666667</v>
       </c>
       <c r="X53">
-        <v>-103.4558666667</v>
+        <v>-103.43705</v>
       </c>
       <c r="Y53">
-        <v>11.38</v>
+        <v>13.41</v>
       </c>
       <c r="Z53">
-        <v>5020</v>
+        <v>4968</v>
       </c>
     </row>
     <row r="54" spans="1:26">
@@ -7247,79 +7280,79 @@
         <v>78</v>
       </c>
       <c r="B54" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C54" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D54" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E54" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F54" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="G54" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="H54">
-        <v>93170</v>
+        <v>91973</v>
       </c>
       <c r="I54">
-        <v>491</v>
+        <v>432</v>
       </c>
       <c r="J54" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="K54">
-        <v>7590</v>
+        <v>7661</v>
       </c>
       <c r="L54">
-        <v>35.52</v>
+        <v>11.38</v>
       </c>
       <c r="M54" t="s">
-        <v>509</v>
+        <v>534</v>
       </c>
       <c r="N54" t="s">
-        <v>597</v>
+        <v>606</v>
       </c>
       <c r="O54" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="P54" t="s">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="Q54" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="R54" t="s">
-        <v>768</v>
+        <v>777</v>
       </c>
       <c r="S54" t="s">
-        <v>847</v>
+        <v>857</v>
       </c>
       <c r="T54">
-        <v>39.6083166667</v>
+        <v>39.2786666667</v>
       </c>
       <c r="U54">
-        <v>-104.0420166667</v>
+        <v>-103.4953333333</v>
       </c>
       <c r="V54">
-        <v>5289</v>
+        <v>5774</v>
       </c>
       <c r="W54">
-        <v>39.7067</v>
+        <v>39.1167166667</v>
       </c>
       <c r="X54">
-        <v>-103.3860333333</v>
+        <v>-103.4558666667</v>
       </c>
       <c r="Y54">
-        <v>35.52</v>
+        <v>11.38</v>
       </c>
       <c r="Z54">
-        <v>4701</v>
+        <v>5020</v>
       </c>
     </row>
     <row r="55" spans="1:26">
@@ -7327,79 +7360,79 @@
         <v>79</v>
       </c>
       <c r="B55" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C55" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D55" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E55" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F55" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="G55" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="H55">
-        <v>92462</v>
+        <v>93170</v>
       </c>
       <c r="I55">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J55" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="K55">
-        <v>7792</v>
+        <v>7590</v>
       </c>
       <c r="L55">
-        <v>51.96</v>
+        <v>35.52</v>
       </c>
       <c r="M55" t="s">
-        <v>528</v>
+        <v>516</v>
       </c>
       <c r="N55" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="O55" t="s">
-        <v>629</v>
+        <v>227</v>
       </c>
       <c r="P55" t="s">
-        <v>686</v>
+        <v>694</v>
       </c>
       <c r="Q55" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="R55" t="s">
-        <v>717</v>
+        <v>778</v>
       </c>
       <c r="S55" t="s">
-        <v>848</v>
+        <v>858</v>
       </c>
       <c r="T55">
-        <v>39.6088333333</v>
+        <v>39.6083166667</v>
       </c>
       <c r="U55">
-        <v>-104.04</v>
+        <v>-104.0420166667</v>
       </c>
       <c r="V55">
-        <v>5691</v>
+        <v>5289</v>
       </c>
       <c r="W55">
-        <v>39.3678333333</v>
+        <v>39.7067</v>
       </c>
       <c r="X55">
-        <v>-103.1161666667</v>
+        <v>-103.3860333333</v>
       </c>
       <c r="Y55">
-        <v>51.96</v>
+        <v>35.52</v>
       </c>
       <c r="Z55">
-        <v>5425</v>
+        <v>4701</v>
       </c>
     </row>
     <row r="56" spans="1:26">
@@ -7407,79 +7440,79 @@
         <v>80</v>
       </c>
       <c r="B56" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C56" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D56" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E56" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F56" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G56" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H56">
-        <v>67670</v>
+        <v>92462</v>
       </c>
       <c r="I56">
-        <v>336</v>
+        <v>490</v>
       </c>
       <c r="J56" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="K56">
-        <v>5580</v>
+        <v>7792</v>
       </c>
       <c r="L56">
-        <v>51.6</v>
+        <v>51.96</v>
       </c>
       <c r="M56" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="N56" t="s">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="O56" t="s">
-        <v>624</v>
+        <v>637</v>
       </c>
       <c r="P56" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
       <c r="Q56" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="R56" t="s">
-        <v>769</v>
+        <v>726</v>
       </c>
       <c r="S56" t="s">
-        <v>849</v>
+        <v>859</v>
       </c>
       <c r="T56">
-        <v>39.608</v>
+        <v>39.6088333333</v>
       </c>
       <c r="U56">
-        <v>-104.0413333333</v>
+        <v>-104.04</v>
       </c>
       <c r="V56">
-        <v>5270</v>
+        <v>5691</v>
       </c>
       <c r="W56">
-        <v>39.4133333333</v>
+        <v>39.3678333333</v>
       </c>
       <c r="X56">
-        <v>-103.106</v>
+        <v>-103.1161666667</v>
       </c>
       <c r="Y56">
-        <v>51.6</v>
+        <v>51.96</v>
       </c>
       <c r="Z56">
-        <v>4921</v>
+        <v>5425</v>
       </c>
     </row>
     <row r="57" spans="1:26">
@@ -7487,79 +7520,79 @@
         <v>81</v>
       </c>
       <c r="B57" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C57" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D57" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E57" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F57" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="G57" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="H57">
-        <v>91878</v>
+        <v>67670</v>
       </c>
       <c r="I57">
-        <v>426</v>
+        <v>336</v>
       </c>
       <c r="J57" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="K57">
-        <v>7230</v>
+        <v>5580</v>
       </c>
       <c r="L57">
-        <v>48.14</v>
+        <v>51.6</v>
       </c>
       <c r="M57" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="N57" t="s">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="O57" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="P57" t="s">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="Q57" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="R57" t="s">
-        <v>770</v>
+        <v>779</v>
       </c>
       <c r="S57" t="s">
-        <v>850</v>
+        <v>860</v>
       </c>
       <c r="T57">
-        <v>39.6086333333</v>
+        <v>39.608</v>
       </c>
       <c r="U57">
-        <v>-104.0395833333</v>
+        <v>-104.0413333333</v>
       </c>
       <c r="V57">
-        <v>5673</v>
+        <v>5270</v>
       </c>
       <c r="W57">
-        <v>39.3669166667</v>
+        <v>39.4133333333</v>
       </c>
       <c r="X57">
-        <v>-103.1921333333</v>
+        <v>-103.106</v>
       </c>
       <c r="Y57">
-        <v>48.14</v>
+        <v>51.6</v>
       </c>
       <c r="Z57">
-        <v>5436</v>
+        <v>4921</v>
       </c>
     </row>
     <row r="58" spans="1:26">
@@ -7567,79 +7600,79 @@
         <v>82</v>
       </c>
       <c r="B58" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="C58" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D58" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E58" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F58" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="G58" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="H58">
-        <v>94959</v>
+        <v>91878</v>
       </c>
       <c r="I58">
-        <v>563</v>
+        <v>426</v>
       </c>
       <c r="J58" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="K58">
-        <v>5850</v>
+        <v>7230</v>
       </c>
       <c r="L58">
-        <v>39.35</v>
+        <v>48.14</v>
       </c>
       <c r="M58" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="N58" t="s">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="O58" t="s">
-        <v>224</v>
+        <v>634</v>
       </c>
       <c r="P58" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
       <c r="Q58" t="s">
-        <v>527</v>
+        <v>575</v>
       </c>
       <c r="R58" t="s">
-        <v>771</v>
+        <v>780</v>
       </c>
       <c r="S58" t="s">
-        <v>851</v>
+        <v>861</v>
       </c>
       <c r="T58">
-        <v>39.6091666667</v>
+        <v>39.6086333333</v>
       </c>
       <c r="U58">
-        <v>-104.042</v>
+        <v>-104.0395833333</v>
       </c>
       <c r="V58">
-        <v>5646</v>
+        <v>5673</v>
       </c>
       <c r="W58">
-        <v>39.2631666667</v>
+        <v>39.3669166667</v>
       </c>
       <c r="X58">
-        <v>-103.4556666667</v>
+        <v>-103.1921333333</v>
       </c>
       <c r="Y58">
-        <v>39.35</v>
+        <v>48.14</v>
       </c>
       <c r="Z58">
-        <v>8248</v>
+        <v>5436</v>
       </c>
     </row>
     <row r="59" spans="1:26">
@@ -7647,79 +7680,79 @@
         <v>83</v>
       </c>
       <c r="B59" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="C59" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D59" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E59" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F59" t="s">
-        <v>248</v>
+        <v>286</v>
       </c>
       <c r="G59" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="H59">
-        <v>93155</v>
+        <v>94959</v>
       </c>
       <c r="I59">
-        <v>435</v>
+        <v>563</v>
       </c>
       <c r="J59" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="K59">
-        <v>6960</v>
+        <v>5850</v>
       </c>
       <c r="L59">
-        <v>77.23</v>
+        <v>39.35</v>
       </c>
       <c r="M59" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="N59" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="O59" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="P59" t="s">
-        <v>478</v>
+        <v>698</v>
       </c>
       <c r="Q59" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="R59" t="s">
-        <v>772</v>
+        <v>781</v>
       </c>
       <c r="S59" t="s">
-        <v>852</v>
+        <v>862</v>
       </c>
       <c r="T59">
-        <v>39.6080166667</v>
+        <v>39.6091666667</v>
       </c>
       <c r="U59">
-        <v>-104.0423</v>
+        <v>-104.042</v>
       </c>
       <c r="V59">
-        <v>5306</v>
+        <v>5646</v>
       </c>
       <c r="W59">
-        <v>38.6113</v>
+        <v>39.2631666667</v>
       </c>
       <c r="X59">
-        <v>-103.3882</v>
+        <v>-103.4556666667</v>
       </c>
       <c r="Y59">
-        <v>77.23</v>
+        <v>39.35</v>
       </c>
       <c r="Z59">
-        <v>5141</v>
+        <v>8248</v>
       </c>
     </row>
     <row r="60" spans="1:26">
@@ -7727,79 +7760,79 @@
         <v>84</v>
       </c>
       <c r="B60" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C60" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D60" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E60" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F60" t="s">
-        <v>283</v>
+        <v>252</v>
       </c>
       <c r="G60" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="H60">
-        <v>95810</v>
+        <v>93155</v>
       </c>
       <c r="I60">
-        <v>450</v>
+        <v>435</v>
       </c>
       <c r="J60" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="K60">
-        <v>6963</v>
+        <v>6960</v>
       </c>
       <c r="L60">
-        <v>78.61</v>
+        <v>77.23</v>
       </c>
       <c r="M60" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="N60" t="s">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="O60" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="P60" t="s">
-        <v>690</v>
+        <v>485</v>
       </c>
       <c r="Q60" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="R60" t="s">
-        <v>773</v>
+        <v>782</v>
       </c>
       <c r="S60" t="s">
-        <v>853</v>
+        <v>863</v>
       </c>
       <c r="T60">
-        <v>39.6082</v>
+        <v>39.6080166667</v>
       </c>
       <c r="U60">
-        <v>-104.04225</v>
+        <v>-104.0423</v>
       </c>
       <c r="V60">
-        <v>5296</v>
+        <v>5306</v>
       </c>
       <c r="W60">
-        <v>38.5923333333</v>
+        <v>38.6113</v>
       </c>
       <c r="X60">
-        <v>-103.38</v>
+        <v>-103.3882</v>
       </c>
       <c r="Y60">
-        <v>78.61</v>
+        <v>77.23</v>
       </c>
       <c r="Z60">
-        <v>5405</v>
+        <v>5141</v>
       </c>
     </row>
     <row r="61" spans="1:26">
@@ -7807,79 +7840,79 @@
         <v>85</v>
       </c>
       <c r="B61" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C61" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D61" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E61" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F61" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="G61" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="H61">
-        <v>105972</v>
+        <v>95810</v>
       </c>
       <c r="I61">
-        <v>507</v>
+        <v>450</v>
       </c>
       <c r="J61" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="K61">
-        <v>8130</v>
+        <v>6963</v>
       </c>
       <c r="L61">
-        <v>83.86</v>
+        <v>78.61</v>
       </c>
       <c r="M61" t="s">
+        <v>540</v>
+      </c>
+      <c r="N61" t="s">
+        <v>612</v>
+      </c>
+      <c r="O61" t="s">
+        <v>227</v>
+      </c>
+      <c r="P61" t="s">
+        <v>699</v>
+      </c>
+      <c r="Q61" t="s">
         <v>534</v>
       </c>
-      <c r="N61" t="s">
-        <v>561</v>
-      </c>
-      <c r="O61" t="s">
-        <v>624</v>
-      </c>
-      <c r="P61" t="s">
-        <v>691</v>
-      </c>
-      <c r="Q61" t="s">
-        <v>527</v>
-      </c>
       <c r="R61" t="s">
-        <v>774</v>
+        <v>783</v>
       </c>
       <c r="S61" t="s">
-        <v>854</v>
+        <v>864</v>
       </c>
       <c r="T61">
-        <v>39.6083333333</v>
+        <v>39.6082</v>
       </c>
       <c r="U61">
-        <v>-104.0418333333</v>
+        <v>-104.04225</v>
       </c>
       <c r="V61">
-        <v>5205</v>
+        <v>5296</v>
       </c>
       <c r="W61">
-        <v>39.6491666667</v>
+        <v>38.5923333333</v>
       </c>
       <c r="X61">
-        <v>-102.4658333333</v>
+        <v>-103.38</v>
       </c>
       <c r="Y61">
-        <v>83.86</v>
+        <v>78.61</v>
       </c>
       <c r="Z61">
-        <v>4139</v>
+        <v>5405</v>
       </c>
     </row>
     <row r="62" spans="1:26">
@@ -7887,79 +7920,79 @@
         <v>86</v>
       </c>
       <c r="B62" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="C62" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D62" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E62" t="s">
         <v>224</v>
       </c>
       <c r="F62" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="G62" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="H62">
-        <v>98296</v>
+        <v>105972</v>
       </c>
       <c r="I62">
-        <v>731</v>
+        <v>507</v>
       </c>
       <c r="J62" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="K62">
-        <v>7635</v>
+        <v>8130</v>
       </c>
       <c r="L62">
-        <v>41.86</v>
+        <v>83.86</v>
       </c>
       <c r="M62" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="N62" t="s">
-        <v>605</v>
+        <v>569</v>
       </c>
       <c r="O62" t="s">
-        <v>224</v>
+        <v>633</v>
       </c>
       <c r="P62" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="Q62" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="R62" t="s">
-        <v>775</v>
+        <v>784</v>
       </c>
       <c r="S62" t="s">
-        <v>855</v>
+        <v>865</v>
       </c>
       <c r="T62">
-        <v>40.4735</v>
+        <v>39.6083333333</v>
       </c>
       <c r="U62">
-        <v>-104.9626666667</v>
+        <v>-104.0418333333</v>
       </c>
       <c r="V62">
-        <v>5042</v>
+        <v>5205</v>
       </c>
       <c r="W62">
-        <v>40.4116666667</v>
+        <v>39.6491666667</v>
       </c>
       <c r="X62">
-        <v>-104.1701666667</v>
+        <v>-102.4658333333</v>
       </c>
       <c r="Y62">
-        <v>41.86</v>
+        <v>83.86</v>
       </c>
       <c r="Z62">
-        <v>4695</v>
+        <v>4139</v>
       </c>
     </row>
     <row r="63" spans="1:26">
@@ -7967,79 +8000,79 @@
         <v>87</v>
       </c>
       <c r="B63" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C63" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D63" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E63" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F63" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="G63" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="H63">
-        <v>108310</v>
+        <v>98296</v>
       </c>
       <c r="I63">
-        <v>376</v>
+        <v>731</v>
       </c>
       <c r="J63" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="K63">
-        <v>6229</v>
+        <v>7635</v>
       </c>
       <c r="L63">
-        <v>22.8</v>
+        <v>41.86</v>
       </c>
       <c r="M63" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="N63" t="s">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="O63" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="P63" t="s">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="Q63" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="R63" t="s">
-        <v>776</v>
+        <v>785</v>
       </c>
       <c r="S63" t="s">
-        <v>856</v>
+        <v>866</v>
       </c>
       <c r="T63">
-        <v>39.6082333333</v>
+        <v>40.4735</v>
       </c>
       <c r="U63">
-        <v>-104.0421</v>
+        <v>-104.9626666667</v>
       </c>
       <c r="V63">
-        <v>5312</v>
+        <v>5042</v>
       </c>
       <c r="W63">
-        <v>39.5823333333</v>
+        <v>40.4116666667</v>
       </c>
       <c r="X63">
-        <v>-103.6148333333</v>
+        <v>-104.1701666667</v>
       </c>
       <c r="Y63">
-        <v>22.8</v>
+        <v>41.86</v>
       </c>
       <c r="Z63">
-        <v>5248</v>
+        <v>4695</v>
       </c>
     </row>
     <row r="64" spans="1:26">
@@ -8047,79 +8080,79 @@
         <v>88</v>
       </c>
       <c r="B64" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="C64" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D64" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E64" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="F64" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="G64" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="H64">
-        <v>92928</v>
+        <v>108310</v>
       </c>
       <c r="I64">
-        <v>430</v>
+        <v>376</v>
       </c>
       <c r="J64" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="K64">
-        <v>6870</v>
+        <v>6229</v>
       </c>
       <c r="L64">
-        <v>31.8</v>
+        <v>22.8</v>
       </c>
       <c r="M64" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="N64" t="s">
-        <v>607</v>
+        <v>614</v>
       </c>
       <c r="O64" t="s">
-        <v>631</v>
+        <v>227</v>
       </c>
       <c r="P64" t="s">
-        <v>694</v>
+        <v>702</v>
       </c>
       <c r="Q64" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="R64" t="s">
-        <v>767</v>
+        <v>786</v>
       </c>
       <c r="S64" t="s">
-        <v>857</v>
+        <v>867</v>
       </c>
       <c r="T64">
-        <v>39.6084333333</v>
+        <v>39.6082333333</v>
       </c>
       <c r="U64">
-        <v>-104.0421333333</v>
+        <v>-104.0421</v>
       </c>
       <c r="V64">
-        <v>5280</v>
+        <v>5312</v>
       </c>
       <c r="W64">
-        <v>39.6995666667</v>
+        <v>39.5823333333</v>
       </c>
       <c r="X64">
-        <v>-103.4557333333</v>
+        <v>-103.6148333333</v>
       </c>
       <c r="Y64">
-        <v>31.8</v>
+        <v>22.8</v>
       </c>
       <c r="Z64">
-        <v>5526</v>
+        <v>5248</v>
       </c>
     </row>
     <row r="65" spans="1:26">
@@ -8127,79 +8160,79 @@
         <v>89</v>
       </c>
       <c r="B65" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="C65" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D65" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E65" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F65" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="G65" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="H65">
-        <v>97198</v>
+        <v>92928</v>
       </c>
       <c r="I65">
-        <v>503</v>
+        <v>430</v>
       </c>
       <c r="J65" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="K65">
-        <v>8010</v>
+        <v>6870</v>
       </c>
       <c r="L65">
-        <v>22.69</v>
+        <v>31.8</v>
       </c>
       <c r="M65" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="N65" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="O65" t="s">
-        <v>224</v>
+        <v>639</v>
       </c>
       <c r="P65" t="s">
-        <v>695</v>
+        <v>703</v>
       </c>
       <c r="Q65" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="R65" t="s">
         <v>777</v>
       </c>
       <c r="S65" t="s">
-        <v>659</v>
+        <v>868</v>
       </c>
       <c r="T65">
-        <v>39.278</v>
+        <v>39.6084333333</v>
       </c>
       <c r="U65">
-        <v>-103.4955</v>
+        <v>-104.0421333333</v>
       </c>
       <c r="V65">
-        <v>5806</v>
+        <v>5280</v>
       </c>
       <c r="W65">
-        <v>38.9785</v>
+        <v>39.6995666667</v>
       </c>
       <c r="X65">
-        <v>-103.6698333333</v>
+        <v>-103.4557333333</v>
       </c>
       <c r="Y65">
-        <v>22.69</v>
+        <v>31.8</v>
       </c>
       <c r="Z65">
-        <v>5501</v>
+        <v>5526</v>
       </c>
     </row>
     <row r="66" spans="1:26">
@@ -8207,79 +8240,79 @@
         <v>90</v>
       </c>
       <c r="B66" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C66" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D66" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E66" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F66" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="G66" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="H66">
-        <v>98738</v>
+        <v>97198</v>
       </c>
       <c r="I66">
-        <v>335</v>
+        <v>503</v>
       </c>
       <c r="J66" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="K66">
-        <v>7890</v>
+        <v>8010</v>
       </c>
       <c r="L66">
-        <v>21.96</v>
+        <v>22.69</v>
       </c>
       <c r="M66" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="N66" t="s">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="O66" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="P66" t="s">
-        <v>696</v>
+        <v>704</v>
       </c>
       <c r="Q66" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="R66" t="s">
-        <v>778</v>
+        <v>787</v>
       </c>
       <c r="S66" t="s">
-        <v>858</v>
+        <v>668</v>
       </c>
       <c r="T66">
-        <v>39.2780833333</v>
+        <v>39.278</v>
       </c>
       <c r="U66">
-        <v>-103.4953</v>
+        <v>-103.4955</v>
       </c>
       <c r="V66">
-        <v>5724</v>
+        <v>5806</v>
       </c>
       <c r="W66">
-        <v>38.9941666667</v>
+        <v>38.9785</v>
       </c>
       <c r="X66">
-        <v>-103.6801166667</v>
+        <v>-103.6698333333</v>
       </c>
       <c r="Y66">
-        <v>21.96</v>
+        <v>22.69</v>
       </c>
       <c r="Z66">
-        <v>5424</v>
+        <v>5501</v>
       </c>
     </row>
     <row r="67" spans="1:26">
@@ -8287,79 +8320,79 @@
         <v>91</v>
       </c>
       <c r="B67" t="s">
-        <v>116</v>
+        <v>150</v>
       </c>
       <c r="C67" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D67" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E67" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F67" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="G67" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H67">
-        <v>98726</v>
+        <v>98738</v>
       </c>
       <c r="I67">
-        <v>463</v>
+        <v>335</v>
       </c>
       <c r="J67" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="K67">
-        <v>8070</v>
+        <v>7890</v>
       </c>
       <c r="L67">
-        <v>22.81</v>
+        <v>21.96</v>
       </c>
       <c r="M67" t="s">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="N67" t="s">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="O67" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="P67" t="s">
-        <v>696</v>
+        <v>705</v>
       </c>
       <c r="Q67" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="R67" t="s">
-        <v>778</v>
+        <v>788</v>
       </c>
       <c r="S67" t="s">
-        <v>858</v>
+        <v>869</v>
       </c>
       <c r="T67">
-        <v>39.278</v>
+        <v>39.2780833333</v>
       </c>
       <c r="U67">
-        <v>-103.4953333333</v>
+        <v>-103.4953</v>
       </c>
       <c r="V67">
-        <v>5842</v>
+        <v>5724</v>
       </c>
       <c r="W67">
-        <v>38.9778333333</v>
+        <v>38.9941666667</v>
       </c>
       <c r="X67">
-        <v>-103.6733333333</v>
+        <v>-103.6801166667</v>
       </c>
       <c r="Y67">
-        <v>22.81</v>
+        <v>21.96</v>
       </c>
       <c r="Z67">
-        <v>5392</v>
+        <v>5424</v>
       </c>
     </row>
     <row r="68" spans="1:26">
@@ -8367,79 +8400,79 @@
         <v>92</v>
       </c>
       <c r="B68" t="s">
-        <v>149</v>
+        <v>118</v>
       </c>
       <c r="C68" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D68" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E68" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F68" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="G68" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="H68">
-        <v>94192</v>
+        <v>98726</v>
       </c>
       <c r="I68">
-        <v>378</v>
+        <v>463</v>
       </c>
       <c r="J68" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="K68">
-        <v>5952</v>
+        <v>8070</v>
       </c>
       <c r="L68">
-        <v>14.87</v>
+        <v>22.81</v>
       </c>
       <c r="M68" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="N68" t="s">
-        <v>540</v>
+        <v>617</v>
       </c>
       <c r="O68" t="s">
-        <v>626</v>
+        <v>227</v>
       </c>
       <c r="P68" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="Q68" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="R68" t="s">
-        <v>779</v>
+        <v>788</v>
       </c>
       <c r="S68" t="s">
-        <v>859</v>
+        <v>869</v>
       </c>
       <c r="T68">
-        <v>39.2153333333</v>
+        <v>39.278</v>
       </c>
       <c r="U68">
-        <v>-103.7201666667</v>
+        <v>-103.4953333333</v>
       </c>
       <c r="V68">
-        <v>18606</v>
+        <v>5842</v>
       </c>
       <c r="W68">
-        <v>39.23415</v>
+        <v>38.9778333333</v>
       </c>
       <c r="X68">
-        <v>-103.99705</v>
+        <v>-103.6733333333</v>
       </c>
       <c r="Y68">
-        <v>14.87</v>
+        <v>22.81</v>
       </c>
       <c r="Z68">
-        <v>6421</v>
+        <v>5392</v>
       </c>
     </row>
     <row r="69" spans="1:26">
@@ -8447,79 +8480,79 @@
         <v>93</v>
       </c>
       <c r="B69" t="s">
-        <v>116</v>
+        <v>151</v>
       </c>
       <c r="C69" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D69" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E69" t="s">
         <v>225</v>
       </c>
       <c r="F69" t="s">
-        <v>243</v>
+        <v>294</v>
       </c>
       <c r="G69" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="H69">
-        <v>105633</v>
+        <v>94192</v>
       </c>
       <c r="I69">
-        <v>202</v>
+        <v>378</v>
       </c>
       <c r="J69" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="K69">
-        <v>7578</v>
+        <v>5952</v>
       </c>
       <c r="L69">
-        <v>52.07</v>
+        <v>14.87</v>
       </c>
       <c r="M69" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="N69" t="s">
-        <v>564</v>
+        <v>547</v>
       </c>
       <c r="O69" t="s">
-        <v>224</v>
+        <v>634</v>
       </c>
       <c r="P69" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="Q69" t="s">
-        <v>527</v>
+        <v>575</v>
       </c>
       <c r="R69" t="s">
-        <v>780</v>
+        <v>789</v>
       </c>
       <c r="S69" t="s">
-        <v>811</v>
+        <v>870</v>
       </c>
       <c r="T69">
-        <v>39.6066833333</v>
+        <v>39.2153333333</v>
       </c>
       <c r="U69">
-        <v>-104.0389666667</v>
+        <v>-103.7201666667</v>
       </c>
       <c r="V69">
-        <v>5795</v>
+        <v>18606</v>
       </c>
       <c r="W69">
-        <v>39.242</v>
+        <v>39.23415</v>
       </c>
       <c r="X69">
-        <v>-103.1845</v>
+        <v>-103.99705</v>
       </c>
       <c r="Y69">
-        <v>52.07</v>
+        <v>14.87</v>
       </c>
       <c r="Z69">
-        <v>6623</v>
+        <v>6421</v>
       </c>
     </row>
     <row r="70" spans="1:26">
@@ -8527,79 +8560,79 @@
         <v>94</v>
       </c>
       <c r="B70" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="C70" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D70" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E70" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F70" t="s">
-        <v>291</v>
+        <v>247</v>
       </c>
       <c r="G70" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="H70">
-        <v>99651</v>
+        <v>105633</v>
       </c>
       <c r="I70">
-        <v>423</v>
+        <v>202</v>
       </c>
       <c r="J70" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="K70">
-        <v>6694</v>
+        <v>7578</v>
       </c>
       <c r="L70">
-        <v>46.57</v>
+        <v>52.07</v>
       </c>
       <c r="M70" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="N70" t="s">
-        <v>602</v>
+        <v>572</v>
       </c>
       <c r="O70" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="P70" t="s">
-        <v>699</v>
+        <v>707</v>
       </c>
       <c r="Q70" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="R70" t="s">
-        <v>781</v>
+        <v>790</v>
       </c>
       <c r="S70" t="s">
-        <v>860</v>
+        <v>822</v>
       </c>
       <c r="T70">
-        <v>40.2258833333</v>
+        <v>39.6066833333</v>
       </c>
       <c r="U70">
-        <v>-104.0762666667</v>
+        <v>-104.0389666667</v>
       </c>
       <c r="V70">
-        <v>5001</v>
+        <v>5795</v>
       </c>
       <c r="W70">
-        <v>39.8741666667</v>
+        <v>39.242</v>
       </c>
       <c r="X70">
-        <v>-103.3245</v>
+        <v>-103.1845</v>
       </c>
       <c r="Y70">
-        <v>46.57</v>
+        <v>52.07</v>
       </c>
       <c r="Z70">
-        <v>5807</v>
+        <v>6623</v>
       </c>
     </row>
     <row r="71" spans="1:26">
@@ -8607,79 +8640,79 @@
         <v>95</v>
       </c>
       <c r="B71" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="C71" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D71" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E71" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="F71" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="G71" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="H71">
-        <v>98291</v>
+        <v>99651</v>
       </c>
       <c r="I71">
-        <v>209</v>
+        <v>423</v>
       </c>
       <c r="J71" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="K71">
-        <v>5790</v>
+        <v>6694</v>
       </c>
       <c r="L71">
-        <v>41.89</v>
+        <v>46.57</v>
       </c>
       <c r="M71" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="N71" t="s">
-        <v>564</v>
+        <v>610</v>
       </c>
       <c r="O71" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="P71" t="s">
-        <v>700</v>
+        <v>708</v>
       </c>
       <c r="Q71" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="R71" t="s">
-        <v>775</v>
+        <v>791</v>
       </c>
       <c r="S71" t="s">
-        <v>861</v>
+        <v>871</v>
       </c>
       <c r="T71">
-        <v>39.6076333333</v>
+        <v>40.2258833333</v>
       </c>
       <c r="U71">
-        <v>-104.0412666667</v>
+        <v>-104.0762666667</v>
       </c>
       <c r="V71">
-        <v>5204</v>
+        <v>5001</v>
       </c>
       <c r="W71">
-        <v>39.4219166667</v>
+        <v>39.8741666667</v>
       </c>
       <c r="X71">
-        <v>-103.2925833333</v>
+        <v>-103.3245</v>
       </c>
       <c r="Y71">
-        <v>41.89</v>
+        <v>46.57</v>
       </c>
       <c r="Z71">
-        <v>5115</v>
+        <v>5807</v>
       </c>
     </row>
     <row r="72" spans="1:26">
@@ -8687,79 +8720,79 @@
         <v>96</v>
       </c>
       <c r="B72" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
       <c r="C72" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D72" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E72" t="s">
         <v>224</v>
       </c>
       <c r="F72" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="G72" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="H72">
-        <v>104708</v>
+        <v>98291</v>
       </c>
       <c r="I72">
-        <v>724</v>
+        <v>209</v>
       </c>
       <c r="J72" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="K72">
-        <v>6000</v>
+        <v>5790</v>
       </c>
       <c r="L72">
-        <v>56</v>
+        <v>41.89</v>
       </c>
       <c r="M72" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="N72" t="s">
-        <v>610</v>
+        <v>572</v>
       </c>
       <c r="O72" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="P72" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="Q72" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="R72" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="S72" t="s">
-        <v>862</v>
+        <v>872</v>
       </c>
       <c r="T72">
-        <v>39.6084833333</v>
+        <v>39.6076333333</v>
       </c>
       <c r="U72">
-        <v>-104.0404333333</v>
+        <v>-104.0412666667</v>
       </c>
       <c r="V72">
-        <v>5257</v>
+        <v>5204</v>
       </c>
       <c r="W72">
-        <v>39.78105</v>
+        <v>39.4219166667</v>
       </c>
       <c r="X72">
-        <v>-103.01055</v>
+        <v>-103.2925833333</v>
       </c>
       <c r="Y72">
-        <v>56</v>
+        <v>41.89</v>
       </c>
       <c r="Z72">
-        <v>4571</v>
+        <v>5115</v>
       </c>
     </row>
     <row r="73" spans="1:26">
@@ -8767,79 +8800,79 @@
         <v>97</v>
       </c>
       <c r="B73" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C73" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D73" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E73" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="F73" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="G73" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="H73">
-        <v>89770</v>
+        <v>104708</v>
       </c>
       <c r="I73">
-        <v>478</v>
+        <v>724</v>
       </c>
       <c r="J73" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="K73">
-        <v>6750</v>
+        <v>6000</v>
       </c>
       <c r="L73">
-        <v>57.99</v>
+        <v>56</v>
       </c>
       <c r="M73" t="s">
-        <v>487</v>
+        <v>551</v>
       </c>
       <c r="N73" t="s">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="O73" t="s">
-        <v>628</v>
+        <v>227</v>
       </c>
       <c r="P73" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="Q73" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="R73" t="s">
-        <v>783</v>
+        <v>792</v>
       </c>
       <c r="S73" t="s">
-        <v>863</v>
+        <v>873</v>
       </c>
       <c r="T73">
-        <v>39.6073333333</v>
+        <v>39.6084833333</v>
       </c>
       <c r="U73">
-        <v>-104.0408333333</v>
+        <v>-104.0404333333</v>
       </c>
       <c r="V73">
-        <v>5673</v>
+        <v>5257</v>
       </c>
       <c r="W73">
-        <v>38.8768333333</v>
+        <v>39.78105</v>
       </c>
       <c r="X73">
-        <v>-103.5055</v>
+        <v>-103.01055</v>
       </c>
       <c r="Y73">
-        <v>57.99</v>
+        <v>56</v>
       </c>
       <c r="Z73">
-        <v>5811</v>
+        <v>4571</v>
       </c>
     </row>
     <row r="74" spans="1:26">
@@ -8847,79 +8880,79 @@
         <v>98</v>
       </c>
       <c r="B74" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C74" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D74" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E74" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F74" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="G74" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="H74">
-        <v>89651</v>
+        <v>89770</v>
       </c>
       <c r="I74">
-        <v>432</v>
+        <v>478</v>
       </c>
       <c r="J74" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="K74">
-        <v>7519</v>
+        <v>6750</v>
       </c>
       <c r="L74">
-        <v>75.94</v>
+        <v>57.99</v>
       </c>
       <c r="M74" t="s">
-        <v>545</v>
+        <v>494</v>
       </c>
       <c r="N74" t="s">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="O74" t="s">
-        <v>224</v>
+        <v>636</v>
       </c>
       <c r="P74" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="Q74" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="R74" t="s">
-        <v>784</v>
+        <v>793</v>
       </c>
       <c r="S74" t="s">
-        <v>864</v>
+        <v>874</v>
       </c>
       <c r="T74">
-        <v>40.22645</v>
+        <v>39.6073333333</v>
       </c>
       <c r="U74">
-        <v>-104.0757</v>
+        <v>-104.0408333333</v>
       </c>
       <c r="V74">
-        <v>5115</v>
+        <v>5673</v>
       </c>
       <c r="W74">
-        <v>41.0114</v>
+        <v>38.8768333333</v>
       </c>
       <c r="X74">
-        <v>-103.0606333333</v>
+        <v>-103.5055</v>
       </c>
       <c r="Y74">
-        <v>75.94</v>
+        <v>57.99</v>
       </c>
       <c r="Z74">
-        <v>4394</v>
+        <v>5811</v>
       </c>
     </row>
     <row r="75" spans="1:26">
@@ -8927,79 +8960,79 @@
         <v>99</v>
       </c>
       <c r="B75" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C75" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D75" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E75" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="F75" t="s">
-        <v>240</v>
+        <v>298</v>
       </c>
       <c r="G75" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="H75">
-        <v>90386</v>
+        <v>89651</v>
       </c>
       <c r="I75">
-        <v>512</v>
+        <v>432</v>
       </c>
       <c r="J75" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="K75">
-        <v>8404</v>
+        <v>7519</v>
       </c>
       <c r="L75">
-        <v>86</v>
+        <v>75.94</v>
       </c>
       <c r="M75" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="N75" t="s">
-        <v>613</v>
+        <v>620</v>
       </c>
       <c r="O75" t="s">
-        <v>632</v>
+        <v>227</v>
       </c>
       <c r="P75" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="Q75" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="R75" t="s">
-        <v>785</v>
+        <v>794</v>
       </c>
       <c r="S75" t="s">
-        <v>865</v>
+        <v>875</v>
       </c>
       <c r="T75">
-        <v>40.22565</v>
+        <v>40.22645</v>
       </c>
       <c r="U75">
-        <v>-104.0767333333</v>
+        <v>-104.0757</v>
       </c>
       <c r="V75">
-        <v>4633</v>
+        <v>5115</v>
       </c>
       <c r="W75">
-        <v>41.1266666667</v>
+        <v>41.0114</v>
       </c>
       <c r="X75">
-        <v>-102.9426666667</v>
+        <v>-103.0606333333</v>
       </c>
       <c r="Y75">
-        <v>86</v>
+        <v>75.94</v>
       </c>
       <c r="Z75">
-        <v>4150</v>
+        <v>4394</v>
       </c>
     </row>
     <row r="76" spans="1:26">
@@ -9007,79 +9040,79 @@
         <v>100</v>
       </c>
       <c r="B76" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C76" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D76" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E76" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="F76" t="s">
-        <v>295</v>
+        <v>244</v>
       </c>
       <c r="G76" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="H76">
-        <v>100372</v>
+        <v>90386</v>
       </c>
       <c r="I76">
-        <v>627</v>
+        <v>512</v>
       </c>
       <c r="J76" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="K76">
-        <v>7076</v>
+        <v>8404</v>
       </c>
       <c r="L76">
-        <v>63.56</v>
+        <v>86</v>
       </c>
       <c r="M76" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="N76" t="s">
-        <v>614</v>
+        <v>621</v>
       </c>
       <c r="O76" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="P76" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="Q76" t="s">
-        <v>527</v>
+        <v>575</v>
       </c>
       <c r="R76" t="s">
-        <v>786</v>
+        <v>795</v>
       </c>
       <c r="S76" t="s">
-        <v>866</v>
+        <v>876</v>
       </c>
       <c r="T76">
-        <v>40.2258333333</v>
+        <v>40.22565</v>
       </c>
       <c r="U76">
-        <v>-104.0761666667</v>
+        <v>-104.0767333333</v>
       </c>
       <c r="V76">
-        <v>4712</v>
+        <v>4633</v>
       </c>
       <c r="W76">
-        <v>39.7649</v>
+        <v>41.1266666667</v>
       </c>
       <c r="X76">
-        <v>-103.036</v>
+        <v>-102.9426666667</v>
       </c>
       <c r="Y76">
-        <v>63.56</v>
+        <v>86</v>
       </c>
       <c r="Z76">
-        <v>4597</v>
+        <v>4150</v>
       </c>
     </row>
     <row r="77" spans="1:26">
@@ -9087,79 +9120,79 @@
         <v>101</v>
       </c>
       <c r="B77" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="C77" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D77" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E77" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="F77" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="G77" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="H77">
-        <v>110090</v>
+        <v>100372</v>
       </c>
       <c r="I77">
-        <v>423</v>
+        <v>627</v>
       </c>
       <c r="J77" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="K77">
-        <v>6618</v>
+        <v>7076</v>
       </c>
       <c r="L77">
-        <v>66.95</v>
+        <v>63.56</v>
       </c>
       <c r="M77" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="N77" t="s">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="O77" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="P77" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="Q77" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="R77" t="s">
-        <v>787</v>
+        <v>796</v>
       </c>
       <c r="S77" t="s">
-        <v>867</v>
+        <v>877</v>
       </c>
       <c r="T77">
-        <v>39.6082</v>
+        <v>40.2258333333</v>
       </c>
       <c r="U77">
-        <v>-104.0416833333</v>
+        <v>-104.0761666667</v>
       </c>
       <c r="V77">
-        <v>5398</v>
+        <v>4712</v>
       </c>
       <c r="W77">
-        <v>38.7788333333</v>
+        <v>39.7649</v>
       </c>
       <c r="X77">
-        <v>-103.3933333333</v>
+        <v>-103.036</v>
       </c>
       <c r="Y77">
-        <v>66.95</v>
+        <v>63.56</v>
       </c>
       <c r="Z77">
-        <v>4798</v>
+        <v>4597</v>
       </c>
     </row>
     <row r="78" spans="1:26">
@@ -9167,79 +9200,79 @@
         <v>102</v>
       </c>
       <c r="B78" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="C78" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D78" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E78" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F78" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="G78" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="H78">
-        <v>98451</v>
+        <v>110090</v>
       </c>
       <c r="I78">
-        <v>863</v>
+        <v>423</v>
       </c>
       <c r="J78" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="K78">
-        <v>9360</v>
+        <v>6618</v>
       </c>
       <c r="L78">
-        <v>55.13</v>
+        <v>66.95</v>
       </c>
       <c r="M78" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="N78" t="s">
-        <v>522</v>
+        <v>623</v>
       </c>
       <c r="O78" t="s">
-        <v>626</v>
+        <v>636</v>
       </c>
       <c r="P78" t="s">
-        <v>707</v>
+        <v>715</v>
       </c>
       <c r="Q78" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="R78" t="s">
-        <v>788</v>
+        <v>797</v>
       </c>
       <c r="S78" t="s">
-        <v>868</v>
+        <v>878</v>
       </c>
       <c r="T78">
-        <v>39.6086666667</v>
+        <v>39.6082</v>
       </c>
       <c r="U78">
-        <v>-104.0421666667</v>
+        <v>-104.0416833333</v>
       </c>
       <c r="V78">
-        <v>5250</v>
+        <v>5398</v>
       </c>
       <c r="W78">
-        <v>38.8388333333</v>
+        <v>38.7788333333</v>
       </c>
       <c r="X78">
-        <v>-104.316</v>
+        <v>-103.3933333333</v>
       </c>
       <c r="Y78">
-        <v>55.13</v>
+        <v>66.95</v>
       </c>
       <c r="Z78">
-        <v>6134</v>
+        <v>4798</v>
       </c>
     </row>
     <row r="79" spans="1:26">
@@ -9247,79 +9280,79 @@
         <v>103</v>
       </c>
       <c r="B79" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C79" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D79" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E79" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="F79" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="G79" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="H79">
-        <v>11223</v>
+        <v>98451</v>
       </c>
       <c r="I79">
-        <v>94</v>
+        <v>863</v>
       </c>
       <c r="J79" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="K79">
-        <v>1496</v>
+        <v>9360</v>
       </c>
       <c r="L79">
-        <v>4.32</v>
+        <v>55.13</v>
       </c>
       <c r="M79" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="N79" t="s">
-        <v>616</v>
+        <v>529</v>
       </c>
       <c r="O79" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="P79" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="Q79" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="R79" t="s">
-        <v>789</v>
+        <v>798</v>
       </c>
       <c r="S79" t="s">
-        <v>869</v>
+        <v>879</v>
       </c>
       <c r="T79">
-        <v>40.6483166667</v>
+        <v>39.6086666667</v>
       </c>
       <c r="U79">
-        <v>-104.3849333333</v>
+        <v>-104.0421666667</v>
       </c>
       <c r="V79">
-        <v>5109</v>
+        <v>5250</v>
       </c>
       <c r="W79">
-        <v>40.6065166667</v>
+        <v>38.8388333333</v>
       </c>
       <c r="X79">
-        <v>-104.3236833333</v>
+        <v>-104.316</v>
       </c>
       <c r="Y79">
-        <v>4.32</v>
+        <v>55.13</v>
       </c>
       <c r="Z79">
-        <v>4866</v>
+        <v>6134</v>
       </c>
     </row>
     <row r="80" spans="1:26">
@@ -9327,79 +9360,79 @@
         <v>104</v>
       </c>
       <c r="B80" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C80" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D80" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E80" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="F80" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="G80" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="H80">
-        <v>93102</v>
+        <v>11223</v>
       </c>
       <c r="I80">
-        <v>399</v>
+        <v>94</v>
       </c>
       <c r="J80" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="K80">
-        <v>6297</v>
+        <v>1496</v>
       </c>
       <c r="L80">
-        <v>11.64</v>
+        <v>4.32</v>
       </c>
       <c r="M80" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="N80" t="s">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="O80" t="s">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="P80" t="s">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="Q80" t="s">
-        <v>527</v>
+        <v>575</v>
       </c>
       <c r="R80" t="s">
-        <v>790</v>
+        <v>799</v>
       </c>
       <c r="S80" t="s">
-        <v>870</v>
+        <v>880</v>
       </c>
       <c r="T80">
-        <v>39.6083833333</v>
+        <v>40.6483166667</v>
       </c>
       <c r="U80">
-        <v>-104.04185</v>
+        <v>-104.3849333333</v>
       </c>
       <c r="V80">
-        <v>5316</v>
+        <v>5109</v>
       </c>
       <c r="W80">
-        <v>39.4658666667</v>
+        <v>40.6065166667</v>
       </c>
       <c r="X80">
-        <v>-103.92525</v>
+        <v>-104.3236833333</v>
       </c>
       <c r="Y80">
-        <v>11.64</v>
+        <v>4.32</v>
       </c>
       <c r="Z80">
-        <v>5483</v>
+        <v>4866</v>
       </c>
     </row>
     <row r="81" spans="1:26">
@@ -9407,79 +9440,79 @@
         <v>105</v>
       </c>
       <c r="B81" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="C81" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D81" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E81" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="F81" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="G81" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="H81">
-        <v>84358</v>
+        <v>93102</v>
       </c>
       <c r="I81">
-        <v>450</v>
+        <v>399</v>
       </c>
       <c r="J81" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="K81">
-        <v>8130</v>
+        <v>6297</v>
       </c>
       <c r="L81">
-        <v>129.41</v>
+        <v>11.64</v>
       </c>
       <c r="M81" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="N81" t="s">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="O81" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="P81" t="s">
-        <v>710</v>
+        <v>718</v>
       </c>
       <c r="Q81" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="R81" t="s">
-        <v>791</v>
+        <v>800</v>
       </c>
       <c r="S81" t="s">
-        <v>871</v>
+        <v>881</v>
       </c>
       <c r="T81">
-        <v>40.4736666667</v>
+        <v>39.6083833333</v>
       </c>
       <c r="U81">
-        <v>-104.9626666667</v>
+        <v>-104.04185</v>
       </c>
       <c r="V81">
-        <v>5198</v>
+        <v>5316</v>
       </c>
       <c r="W81">
-        <v>40.8561666667</v>
+        <v>39.4658666667</v>
       </c>
       <c r="X81">
-        <v>-102.5436666667</v>
+        <v>-103.92525</v>
       </c>
       <c r="Y81">
-        <v>129.41</v>
+        <v>11.64</v>
       </c>
       <c r="Z81">
-        <v>4815</v>
+        <v>5483</v>
       </c>
     </row>
     <row r="82" spans="1:26">
@@ -9487,79 +9520,79 @@
         <v>106</v>
       </c>
       <c r="B82" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="C82" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D82" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E82" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F82" t="s">
-        <v>280</v>
+        <v>304</v>
       </c>
       <c r="G82" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="H82">
-        <v>85332</v>
+        <v>84358</v>
       </c>
       <c r="I82">
-        <v>224</v>
+        <v>450</v>
       </c>
       <c r="J82" t="s">
-        <v>471</v>
+        <v>457</v>
       </c>
       <c r="K82">
-        <v>7055</v>
+        <v>8130</v>
       </c>
       <c r="L82">
-        <v>109.12</v>
+        <v>129.41</v>
       </c>
       <c r="M82" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="N82" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="O82" t="s">
-        <v>634</v>
+        <v>641</v>
       </c>
       <c r="P82" t="s">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="Q82" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="R82" t="s">
-        <v>716</v>
+        <v>801</v>
       </c>
       <c r="S82" t="s">
-        <v>872</v>
+        <v>882</v>
       </c>
       <c r="T82">
-        <v>40.4736</v>
+        <v>40.4736666667</v>
       </c>
       <c r="U82">
-        <v>-104.9627166667</v>
+        <v>-104.9626666667</v>
       </c>
       <c r="V82">
-        <v>5181</v>
+        <v>5198</v>
       </c>
       <c r="W82">
-        <v>40.8481</v>
+        <v>40.8561666667</v>
       </c>
       <c r="X82">
-        <v>-102.9386833333</v>
+        <v>-102.5436666667</v>
       </c>
       <c r="Y82">
-        <v>109.12</v>
+        <v>129.41</v>
       </c>
       <c r="Z82">
-        <v>3780</v>
+        <v>4815</v>
       </c>
     </row>
     <row r="83" spans="1:26">
@@ -9567,79 +9600,79 @@
         <v>107</v>
       </c>
       <c r="B83" t="s">
-        <v>131</v>
+        <v>158</v>
       </c>
       <c r="C83" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D83" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E83" t="s">
+        <v>223</v>
+      </c>
+      <c r="F83" t="s">
+        <v>284</v>
+      </c>
+      <c r="G83" t="s">
+        <v>391</v>
+      </c>
+      <c r="H83">
+        <v>85332</v>
+      </c>
+      <c r="I83">
         <v>224</v>
       </c>
-      <c r="F83" t="s">
-        <v>301</v>
-      </c>
-      <c r="G83" t="s">
-        <v>387</v>
-      </c>
-      <c r="H83">
-        <v>104023</v>
-      </c>
-      <c r="I83">
-        <v>475</v>
-      </c>
       <c r="J83" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="K83">
-        <v>7395</v>
+        <v>7055</v>
       </c>
       <c r="L83">
-        <v>80.27</v>
+        <v>109.12</v>
       </c>
       <c r="M83" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="N83" t="s">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="O83" t="s">
-        <v>224</v>
+        <v>642</v>
       </c>
       <c r="P83" t="s">
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="Q83" t="s">
-        <v>527</v>
+        <v>575</v>
       </c>
       <c r="R83" t="s">
-        <v>792</v>
+        <v>725</v>
       </c>
       <c r="S83" t="s">
-        <v>873</v>
+        <v>883</v>
       </c>
       <c r="T83">
-        <v>40.5265</v>
+        <v>40.4736</v>
       </c>
       <c r="U83">
-        <v>-104.7233333333</v>
+        <v>-104.9627166667</v>
       </c>
       <c r="V83">
-        <v>4894</v>
+        <v>5181</v>
       </c>
       <c r="W83">
-        <v>40.0466333333</v>
+        <v>40.8481</v>
       </c>
       <c r="X83">
-        <v>-103.3351666667</v>
+        <v>-102.9386833333</v>
       </c>
       <c r="Y83">
-        <v>80.27</v>
+        <v>109.12</v>
       </c>
       <c r="Z83">
-        <v>4774</v>
+        <v>3780</v>
       </c>
     </row>
     <row r="84" spans="1:26">
@@ -9647,79 +9680,79 @@
         <v>108</v>
       </c>
       <c r="B84" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C84" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D84" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E84" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F84" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="G84" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="H84">
-        <v>110101</v>
+        <v>104023</v>
       </c>
       <c r="I84">
-        <v>355</v>
+        <v>475</v>
       </c>
       <c r="J84" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="K84">
-        <v>7800</v>
+        <v>7395</v>
       </c>
       <c r="L84">
-        <v>88.25</v>
+        <v>80.27</v>
       </c>
       <c r="M84" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="N84" t="s">
-        <v>511</v>
+        <v>628</v>
       </c>
       <c r="O84" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="P84" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="Q84" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="R84" t="s">
-        <v>793</v>
+        <v>802</v>
       </c>
       <c r="S84" t="s">
-        <v>874</v>
+        <v>884</v>
       </c>
       <c r="T84">
-        <v>40.5265166667</v>
+        <v>40.5265</v>
       </c>
       <c r="U84">
-        <v>-104.7232333333</v>
+        <v>-104.7233333333</v>
       </c>
       <c r="V84">
-        <v>4968</v>
+        <v>4894</v>
       </c>
       <c r="W84">
-        <v>40.0466833333</v>
+        <v>40.0466333333</v>
       </c>
       <c r="X84">
-        <v>-103.1701333333</v>
+        <v>-103.3351666667</v>
       </c>
       <c r="Y84">
-        <v>88.25</v>
+        <v>80.27</v>
       </c>
       <c r="Z84">
-        <v>4971</v>
+        <v>4774</v>
       </c>
     </row>
     <row r="85" spans="1:26">
@@ -9727,79 +9760,79 @@
         <v>109</v>
       </c>
       <c r="B85" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C85" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D85" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E85" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F85" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="G85" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="H85">
-        <v>88956</v>
+        <v>110101</v>
       </c>
       <c r="I85">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="J85" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="K85">
-        <v>6495</v>
+        <v>7800</v>
       </c>
       <c r="L85">
-        <v>94.23999999999999</v>
+        <v>88.25</v>
       </c>
       <c r="M85" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="N85" t="s">
-        <v>621</v>
+        <v>518</v>
       </c>
       <c r="O85" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="P85" t="s">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="Q85" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="R85" t="s">
-        <v>794</v>
+        <v>803</v>
       </c>
       <c r="S85" t="s">
-        <v>776</v>
+        <v>885</v>
       </c>
       <c r="T85">
-        <v>40.2255</v>
+        <v>40.5265166667</v>
       </c>
       <c r="U85">
-        <v>-104.0765</v>
+        <v>-104.7232333333</v>
       </c>
       <c r="V85">
-        <v>4752</v>
+        <v>4968</v>
       </c>
       <c r="W85">
-        <v>39.6237333333</v>
+        <v>40.0466833333</v>
       </c>
       <c r="X85">
-        <v>-102.479</v>
+        <v>-103.1701333333</v>
       </c>
       <c r="Y85">
-        <v>94.23999999999999</v>
+        <v>88.25</v>
       </c>
       <c r="Z85">
-        <v>4111</v>
+        <v>4971</v>
       </c>
     </row>
     <row r="86" spans="1:26">
@@ -9807,79 +9840,79 @@
         <v>110</v>
       </c>
       <c r="B86" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C86" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D86" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E86" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="F86" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="G86" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="H86">
-        <v>92625</v>
+        <v>88956</v>
       </c>
       <c r="I86">
-        <v>487</v>
+        <v>365</v>
       </c>
       <c r="J86" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="K86">
-        <v>7855</v>
+        <v>6495</v>
       </c>
       <c r="L86">
-        <v>87.38</v>
+        <v>94.23999999999999</v>
       </c>
       <c r="M86" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="N86" t="s">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="O86" t="s">
-        <v>632</v>
+        <v>227</v>
       </c>
       <c r="P86" t="s">
-        <v>715</v>
+        <v>723</v>
       </c>
       <c r="Q86" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="R86" t="s">
-        <v>795</v>
+        <v>804</v>
       </c>
       <c r="S86" t="s">
-        <v>721</v>
+        <v>786</v>
       </c>
       <c r="T86">
-        <v>39.61065</v>
+        <v>40.2255</v>
       </c>
       <c r="U86">
-        <v>-104.0421666667</v>
+        <v>-104.0765</v>
       </c>
       <c r="V86">
-        <v>5326</v>
+        <v>4752</v>
       </c>
       <c r="W86">
-        <v>39.43295</v>
+        <v>39.6237333333</v>
       </c>
       <c r="X86">
-        <v>-102.4176833333</v>
+        <v>-102.479</v>
       </c>
       <c r="Y86">
-        <v>87.38</v>
+        <v>94.23999999999999</v>
       </c>
       <c r="Z86">
-        <v>4164</v>
+        <v>4111</v>
       </c>
     </row>
     <row r="87" spans="1:26">
@@ -9887,79 +9920,79 @@
         <v>111</v>
       </c>
       <c r="B87" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="C87" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D87" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E87" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F87" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="G87" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="H87">
-        <v>107050</v>
+        <v>92625</v>
       </c>
       <c r="I87">
-        <v>781</v>
+        <v>487</v>
       </c>
       <c r="J87" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="K87">
-        <v>8875</v>
+        <v>7855</v>
       </c>
       <c r="L87">
-        <v>19.02</v>
+        <v>87.38</v>
       </c>
       <c r="M87" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="N87" t="s">
-        <v>588</v>
+        <v>630</v>
       </c>
       <c r="O87" t="s">
-        <v>224</v>
+        <v>640</v>
       </c>
       <c r="P87" t="s">
-        <v>716</v>
+        <v>724</v>
       </c>
       <c r="Q87" t="s">
-        <v>527</v>
+        <v>575</v>
       </c>
       <c r="R87" t="s">
-        <v>796</v>
+        <v>805</v>
       </c>
       <c r="S87" t="s">
-        <v>875</v>
+        <v>731</v>
       </c>
       <c r="T87">
-        <v>39.2356666667</v>
+        <v>39.61065</v>
       </c>
       <c r="U87">
-        <v>-103.6976666667</v>
+        <v>-104.0421666667</v>
       </c>
       <c r="V87">
-        <v>5746</v>
+        <v>5326</v>
       </c>
       <c r="W87">
-        <v>39.07765</v>
+        <v>39.43295</v>
       </c>
       <c r="X87">
-        <v>-103.9885833333</v>
+        <v>-102.4176833333</v>
       </c>
       <c r="Y87">
-        <v>19.02</v>
+        <v>87.38</v>
       </c>
       <c r="Z87">
-        <v>6441</v>
+        <v>4164</v>
       </c>
     </row>
     <row r="88" spans="1:26">
@@ -9967,78 +10000,158 @@
         <v>112</v>
       </c>
       <c r="B88" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="C88" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D88" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E88" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F88" t="s">
-        <v>243</v>
+        <v>309</v>
       </c>
       <c r="G88" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="H88">
+        <v>107050</v>
+      </c>
+      <c r="I88">
+        <v>781</v>
+      </c>
+      <c r="J88" t="s">
+        <v>482</v>
+      </c>
+      <c r="K88">
+        <v>8875</v>
+      </c>
+      <c r="L88">
+        <v>19.02</v>
+      </c>
+      <c r="M88" t="s">
+        <v>565</v>
+      </c>
+      <c r="N88" t="s">
+        <v>596</v>
+      </c>
+      <c r="O88" t="s">
+        <v>227</v>
+      </c>
+      <c r="P88" t="s">
+        <v>725</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>534</v>
+      </c>
+      <c r="R88" t="s">
+        <v>806</v>
+      </c>
+      <c r="S88" t="s">
+        <v>886</v>
+      </c>
+      <c r="T88">
+        <v>39.2356666667</v>
+      </c>
+      <c r="U88">
+        <v>-103.6976666667</v>
+      </c>
+      <c r="V88">
+        <v>5746</v>
+      </c>
+      <c r="W88">
+        <v>39.07765</v>
+      </c>
+      <c r="X88">
+        <v>-103.9885833333</v>
+      </c>
+      <c r="Y88">
+        <v>19.02</v>
+      </c>
+      <c r="Z88">
+        <v>6441</v>
+      </c>
+    </row>
+    <row r="89" spans="1:26">
+      <c r="A89" t="s">
+        <v>113</v>
+      </c>
+      <c r="B89" t="s">
+        <v>143</v>
+      </c>
+      <c r="C89" t="s">
+        <v>219</v>
+      </c>
+      <c r="D89" t="s">
+        <v>221</v>
+      </c>
+      <c r="E89" t="s">
+        <v>232</v>
+      </c>
+      <c r="F89" t="s">
+        <v>247</v>
+      </c>
+      <c r="G89" t="s">
+        <v>397</v>
+      </c>
+      <c r="H89">
         <v>102867</v>
       </c>
-      <c r="I88">
+      <c r="I89">
         <v>498</v>
       </c>
-      <c r="J88" t="s">
-        <v>477</v>
-      </c>
-      <c r="K88">
+      <c r="J89" t="s">
+        <v>483</v>
+      </c>
+      <c r="K89">
         <v>7665</v>
       </c>
-      <c r="L88">
+      <c r="L89">
         <v>8.380000000000001</v>
       </c>
-      <c r="M88" t="s">
-        <v>559</v>
-      </c>
-      <c r="N88" t="s">
-        <v>623</v>
-      </c>
-      <c r="O88" t="s">
-        <v>224</v>
-      </c>
-      <c r="P88" t="s">
-        <v>717</v>
-      </c>
-      <c r="Q88" t="s">
-        <v>527</v>
-      </c>
-      <c r="R88" t="s">
-        <v>797</v>
-      </c>
-      <c r="S88" t="s">
-        <v>649</v>
-      </c>
-      <c r="T88">
+      <c r="M89" t="s">
+        <v>566</v>
+      </c>
+      <c r="N89" t="s">
+        <v>631</v>
+      </c>
+      <c r="O89" t="s">
+        <v>227</v>
+      </c>
+      <c r="P89" t="s">
+        <v>726</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>534</v>
+      </c>
+      <c r="R89" t="s">
+        <v>807</v>
+      </c>
+      <c r="S89" t="s">
+        <v>658</v>
+      </c>
+      <c r="T89">
         <v>39.2794333333</v>
       </c>
-      <c r="U88">
+      <c r="U89">
         <v>-103.4946166667</v>
       </c>
-      <c r="V88">
+      <c r="V89">
         <v>5905</v>
       </c>
-      <c r="W88">
+      <c r="W89">
         <v>39.2383333333</v>
       </c>
-      <c r="X88">
+      <c r="X89">
         <v>-103.64215</v>
       </c>
-      <c r="Y88">
+      <c r="Y89">
         <v>8.380000000000001</v>
       </c>
-      <c r="Z88">
+      <c r="Z89">
         <v>5303</v>
       </c>
     </row>

--- a/www/flightdata/xlsx/flights_metadata.xlsx
+++ b/www/flightdata/xlsx/flights_metadata.xlsx
@@ -1345,10 +1345,10 @@
     <t>[{'transition': 'high_to_low', 'altitude_ft': 59923.0, 'altitude_m': 18264.53}]</t>
   </si>
   <si>
-    <t>1hrs 36mins 7secs</t>
-  </si>
-  <si>
-    <t>1hrs 37mins 0secs</t>
+    <t>1hrs 48mins 37secs</t>
+  </si>
+  <si>
+    <t>1hrs 39mins 0secs</t>
   </si>
   <si>
     <t>1hrs 54mins 7secs</t>
@@ -2130,19 +2130,19 @@
         <v>27272.59</v>
       </c>
       <c r="J2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K2" t="s">
         <v>443</v>
       </c>
       <c r="L2">
-        <v>5767</v>
+        <v>6517</v>
       </c>
       <c r="M2">
-        <v>101.55</v>
+        <v>101.7</v>
       </c>
       <c r="N2">
-        <v>163.43</v>
+        <v>163.66</v>
       </c>
       <c r="O2">
         <v>9.630000000000001</v>
@@ -2199,22 +2199,22 @@
         <v>1418.84</v>
       </c>
       <c r="AG2">
-        <v>39.4151666667</v>
+        <v>39.4126666667</v>
       </c>
       <c r="AH2">
-        <v>-102.4776666667</v>
+        <v>-102.4765</v>
       </c>
       <c r="AI2">
-        <v>101.55</v>
+        <v>101.7</v>
       </c>
       <c r="AJ2">
-        <v>163.43</v>
+        <v>163.66</v>
       </c>
       <c r="AK2">
-        <v>5090</v>
+        <v>4206</v>
       </c>
       <c r="AL2">
-        <v>1551.43</v>
+        <v>1281.99</v>
       </c>
     </row>
     <row r="3" spans="1:38">
@@ -2246,19 +2246,19 @@
         <v>30445.86</v>
       </c>
       <c r="J3">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="K3" t="s">
         <v>444</v>
       </c>
       <c r="L3">
-        <v>5820</v>
+        <v>5940</v>
       </c>
       <c r="M3">
-        <v>93.68000000000001</v>
+        <v>93.92</v>
       </c>
       <c r="N3">
-        <v>150.76</v>
+        <v>151.15</v>
       </c>
       <c r="O3">
         <v>7.8</v>
@@ -2303,34 +2303,34 @@
         <v>8.550000000000001</v>
       </c>
       <c r="AC3">
-        <v>40.2245</v>
+        <v>40.2216666667</v>
       </c>
       <c r="AD3">
-        <v>-104.0771666667</v>
+        <v>-104.0768333333</v>
       </c>
       <c r="AE3">
-        <v>4611</v>
+        <v>4964</v>
       </c>
       <c r="AF3">
-        <v>1405.43</v>
+        <v>1513.03</v>
       </c>
       <c r="AG3">
-        <v>39.465</v>
+        <v>39.4601666667</v>
       </c>
       <c r="AH3">
-        <v>-102.6128333333</v>
+        <v>-102.6088333333</v>
       </c>
       <c r="AI3">
-        <v>93.68000000000001</v>
+        <v>93.92</v>
       </c>
       <c r="AJ3">
-        <v>150.76</v>
+        <v>151.15</v>
       </c>
       <c r="AK3">
-        <v>5573</v>
+        <v>4182</v>
       </c>
       <c r="AL3">
-        <v>1698.65</v>
+        <v>1274.67</v>
       </c>
     </row>
     <row r="4" spans="1:38">

--- a/www/flightdata/xlsx/flights_metadata.xlsx
+++ b/www/flightdata/xlsx/flights_metadata.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="535">
   <si>
     <t>flight</t>
   </si>
@@ -1087,7 +1087,7 @@
     <t>[{'transition': 'high_to_low', 'altitude_ft': 54081.0, 'altitude_m': 16483.89}]</t>
   </si>
   <si>
-    <t>[{'transition': 'high_to_low', 'altitude_ft': 43536.0, 'altitude_m': 13269.77}]</t>
+    <t>[{'transition': 'low_to_high', 'altitude_ft': 5773.0, 'altitude_m': 1759.61}, {'transition': 'high_to_low', 'altitude_ft': 43536.0, 'altitude_m': 13269.77}]</t>
   </si>
   <si>
     <t>[{'transition': 'high_to_low', 'altitude_ft': 45552.0, 'altitude_m': 13884.25}]</t>
@@ -1120,10 +1120,10 @@
     <t>[{'transition': 'high_to_low', 'altitude_ft': 52910.0, 'altitude_m': 16126.97}]</t>
   </si>
   <si>
-    <t>[{'transition': 'high_to_low', 'altitude_ft': 59200.0, 'altitude_m': 18044.16}]</t>
-  </si>
-  <si>
-    <t>[{'transition': 'high_to_low', 'altitude_ft': 65939.0, 'altitude_m': 20098.21}]</t>
+    <t>[{'transition': 'low_to_high', 'altitude_ft': 17172.0, 'altitude_m': 5234.03}, {'transition': 'high_to_low', 'altitude_ft': 59200.0, 'altitude_m': 18044.16}]</t>
+  </si>
+  <si>
+    <t>[{'transition': 'low_to_high', 'altitude_ft': 16428.0, 'altitude_m': 5007.25}, {'transition': 'high_to_low', 'altitude_ft': 65939.0, 'altitude_m': 20098.21}]</t>
   </si>
   <si>
     <t>[{'transition': 'low_to_high', 'altitude_ft': 11797.0, 'altitude_m': 3595.73}, {'transition': 'high_to_low', 'altitude_ft': 60694.0, 'altitude_m': 18499.53}]</t>
@@ -1141,7 +1141,7 @@
     <t>[{'transition': 'high_to_low', 'altitude_ft': 58771.0, 'altitude_m': 17913.4}]</t>
   </si>
   <si>
-    <t>[{'transition': 'high_to_low', 'altitude_ft': 66163.0, 'altitude_m': 20166.48}]</t>
+    <t>[{'transition': 'low_to_high', 'altitude_ft': 34239.0, 'altitude_m': 10436.05}, {'transition': 'high_to_low', 'altitude_ft': 66163.0, 'altitude_m': 20166.48}]</t>
   </si>
   <si>
     <t>[{'transition': 'high_to_low', 'altitude_ft': 49662.0, 'altitude_m': 15136.98}]</t>
@@ -1153,19 +1153,19 @@
     <t>[{'transition': 'high_to_low', 'altitude_ft': 68226.0, 'altitude_m': 20795.28}]</t>
   </si>
   <si>
-    <t>[{'transition': 'high_to_low', 'altitude_ft': 55168.0, 'altitude_m': 16815.21}]</t>
-  </si>
-  <si>
-    <t>[{'transition': 'low_to_high', 'altitude_ft': 20498.0, 'altitude_m': 6247.79}, {'transition': 'high_to_low', 'altitude_ft': 46196.0, 'altitude_m': 14080.54}]</t>
-  </si>
-  <si>
-    <t>[{'transition': 'high_to_low', 'altitude_ft': 65571.0, 'altitude_m': 19986.04}]</t>
+    <t>[{'transition': 'low_to_high', 'altitude_ft': 9581.0, 'altitude_m': 2920.29}, {'transition': 'high_to_low', 'altitude_ft': 55168.0, 'altitude_m': 16815.21}]</t>
+  </si>
+  <si>
+    <t>[{'transition': 'low_to_high', 'altitude_ft': 16931.0, 'altitude_m': 5160.57}, {'transition': 'high_to_low', 'altitude_ft': 46196.0, 'altitude_m': 14080.54}]</t>
+  </si>
+  <si>
+    <t>[{'transition': 'low_to_high', 'altitude_ft': 17492.0, 'altitude_m': 5331.56}, {'transition': 'high_to_low', 'altitude_ft': 65571.0, 'altitude_m': 19986.04}]</t>
   </si>
   <si>
     <t>[{'transition': 'low_to_high', 'altitude_ft': 29928.0, 'altitude_m': 9122.05}]</t>
   </si>
   <si>
-    <t>[{'transition': 'high_to_low', 'altitude_ft': 45725.0, 'altitude_m': 13936.98}]</t>
+    <t>[{'transition': 'low_to_high', 'altitude_ft': 10313.0, 'altitude_m': 3143.4}, {'transition': 'high_to_low', 'altitude_ft': 45725.0, 'altitude_m': 13936.98}]</t>
   </si>
   <si>
     <t>[{'transition': 'low_to_high', 'altitude_ft': 16636.0, 'altitude_m': 5070.65}, {'transition': 'high_to_low', 'altitude_ft': 64772.0, 'altitude_m': 19742.51}]</t>
@@ -1180,7 +1180,7 @@
     <t>[{'transition': 'high_to_low', 'altitude_ft': 40575.0, 'altitude_m': 12367.26}]</t>
   </si>
   <si>
-    <t>[{'transition': 'low_to_high', 'altitude_ft': 41108.0, 'altitude_m': 12529.72}]</t>
+    <t>[{'transition': 'low_to_high', 'altitude_ft': 5795.0, 'altitude_m': 1766.32}]</t>
   </si>
   <si>
     <t>[{'transition': 'high_to_low', 'altitude_ft': 52066.0, 'altitude_m': 15869.72}]</t>
@@ -1201,7 +1201,7 @@
     <t>[{'transition': 'low_to_high', 'altitude_ft': 13693.0, 'altitude_m': 4173.63}, {'transition': 'high_to_low', 'altitude_ft': 53644.0, 'altitude_m': 16350.69}]</t>
   </si>
   <si>
-    <t>[{'transition': 'high_to_low', 'altitude_ft': 58636.0, 'altitude_m': 17872.25}]</t>
+    <t>[{'transition': 'low_to_high', 'altitude_ft': 12357.0, 'altitude_m': 3766.41}, {'transition': 'high_to_low', 'altitude_ft': 58636.0, 'altitude_m': 17872.25}]</t>
   </si>
   <si>
     <t>[{'transition': 'low_to_high', 'altitude_ft': 34496.0, 'altitude_m': 10514.38}]</t>
@@ -1213,7 +1213,7 @@
     <t>[{'transition': 'high_to_low', 'altitude_ft': 48301.0, 'altitude_m': 14722.14}]</t>
   </si>
   <si>
-    <t>[{'transition': 'high_to_low', 'altitude_ft': 48669.0, 'altitude_m': 14834.31}]</t>
+    <t>[{'transition': 'low_to_high', 'altitude_ft': 9997.0, 'altitude_m': 3047.09}, {'transition': 'high_to_low', 'altitude_ft': 55507.0, 'altitude_m': 16918.53}]</t>
   </si>
   <si>
     <t>[{'transition': 'high_to_low', 'altitude_ft': 54974.0, 'altitude_m': 16756.08}]</t>
@@ -1231,16 +1231,16 @@
     <t>[{'transition': 'high_to_low', 'altitude_ft': 48805.0, 'altitude_m': 14875.76}]</t>
   </si>
   <si>
-    <t>[{'transition': 'high_to_low', 'altitude_ft': 52295.0, 'altitude_m': 15939.52}]</t>
-  </si>
-  <si>
-    <t>[{'transition': 'low_to_high', 'altitude_ft': 5969.0, 'altitude_m': 1819.35}, {'transition': 'high_to_low', 'altitude_ft': 35049.0, 'altitude_m': 10682.94}]</t>
+    <t>[{'transition': 'high_to_low', 'altitude_ft': 58113.0, 'altitude_m': 17712.84}]</t>
+  </si>
+  <si>
+    <t>[{'transition': 'high_to_low', 'altitude_ft': 35049.0, 'altitude_m': 10682.94}]</t>
   </si>
   <si>
     <t>[{'transition': 'high_to_low', 'altitude_ft': 52446.0, 'altitude_m': 15985.54}]</t>
   </si>
   <si>
-    <t>[{'transition': 'high_to_low', 'altitude_ft': 62431.0, 'altitude_m': 19028.97}]</t>
+    <t>[{'transition': 'low_to_high', 'altitude_ft': 5949.0, 'altitude_m': 1813.26}, {'transition': 'high_to_low', 'altitude_ft': 62431.0, 'altitude_m': 19028.97}]</t>
   </si>
   <si>
     <t>[{'transition': 'high_to_low', 'altitude_ft': 51806.0, 'altitude_m': 15790.47}]</t>
@@ -1252,16 +1252,16 @@
     <t>[{'transition': 'high_to_low', 'altitude_ft': 50361.0, 'altitude_m': 15350.03}]</t>
   </si>
   <si>
-    <t>[{'transition': 'high_to_low', 'altitude_ft': 56579.0, 'altitude_m': 17245.28}]</t>
+    <t>[{'transition': 'low_to_high', 'altitude_ft': 7718.0, 'altitude_m': 2352.45}, {'transition': 'high_to_low', 'altitude_ft': 56579.0, 'altitude_m': 17245.28}]</t>
   </si>
   <si>
     <t>[{'transition': 'high_to_low', 'altitude_ft': 48010.0, 'altitude_m': 14633.45}]</t>
   </si>
   <si>
-    <t>[{'transition': 'high_to_low', 'altitude_ft': 52999.0, 'altitude_m': 16154.1}]</t>
-  </si>
-  <si>
-    <t>[{'transition': 'low_to_high', 'altitude_ft': 5473.0, 'altitude_m': 1668.17}, {'transition': 'high_to_low', 'altitude_ft': 55939.0, 'altitude_m': 17050.21}]</t>
+    <t>[{'transition': 'low_to_high', 'altitude_ft': 10497.0, 'altitude_m': 3199.49}, {'transition': 'high_to_low', 'altitude_ft': 52999.0, 'altitude_m': 16154.1}]</t>
+  </si>
+  <si>
+    <t>[{'transition': 'high_to_low', 'altitude_ft': 55939.0, 'altitude_m': 17050.21}]</t>
   </si>
   <si>
     <t>[{'transition': 'low_to_high', 'altitude_ft': 11534.0, 'altitude_m': 3515.56}, {'transition': 'high_to_low', 'altitude_ft': 61309.0, 'altitude_m': 18686.98}]</t>
@@ -1273,7 +1273,7 @@
     <t>[{'transition': 'high_to_low', 'altitude_ft': 48745.0, 'altitude_m': 14857.48}]</t>
   </si>
   <si>
-    <t>[{'transition': 'high_to_low', 'altitude_ft': 54970.0, 'altitude_m': 16754.86}]</t>
+    <t>[{'transition': 'low_to_high', 'altitude_ft': 27080.0, 'altitude_m': 8253.98}, {'transition': 'high_to_low', 'altitude_ft': 60531.0, 'altitude_m': 18449.85}]</t>
   </si>
   <si>
     <t>[{'transition': 'high_to_low', 'altitude_ft': 51568.0, 'altitude_m': 15717.93}]</t>
@@ -1285,7 +1285,7 @@
     <t>[{'transition': 'high_to_low', 'altitude_ft': 53199.0, 'altitude_m': 16215.06}]</t>
   </si>
   <si>
-    <t>[{'transition': 'high_to_low', 'altitude_ft': 55820.0, 'altitude_m': 17013.94}]</t>
+    <t>[{'transition': 'low_to_high', 'altitude_ft': 8118.0, 'altitude_m': 2474.37}, {'transition': 'high_to_low', 'altitude_ft': 55820.0, 'altitude_m': 17013.94}]</t>
   </si>
   <si>
     <t>[{'transition': 'high_to_low', 'altitude_ft': 66320.0, 'altitude_m': 20214.34}]</t>
@@ -1297,7 +1297,7 @@
     <t>[{'transition': 'low_to_high', 'altitude_ft': 21272.0, 'altitude_m': 6483.71}, {'transition': 'high_to_low', 'altitude_ft': 74152.0, 'altitude_m': 22601.53}]</t>
   </si>
   <si>
-    <t>[{'transition': 'high_to_low', 'altitude_ft': 40581.0, 'altitude_m': 12369.09}]</t>
+    <t>[{'transition': 'low_to_high', 'altitude_ft': 5667.0, 'altitude_m': 1727.3}, {'transition': 'high_to_low', 'altitude_ft': 40581.0, 'altitude_m': 12369.09}]</t>
   </si>
   <si>
     <t>[{'transition': 'high_to_low', 'altitude_ft': 40592.0, 'altitude_m': 12372.44}]</t>
@@ -1309,7 +1309,7 @@
     <t>[{'transition': 'high_to_low', 'altitude_ft': 52415.0, 'altitude_m': 15976.09}]</t>
   </si>
   <si>
-    <t>[{'transition': 'high_to_low', 'altitude_ft': 62268.0, 'altitude_m': 18979.29}]</t>
+    <t>[{'transition': 'low_to_high', 'altitude_ft': 8489.0, 'altitude_m': 2587.45}, {'transition': 'high_to_low', 'altitude_ft': 62268.0, 'altitude_m': 18979.29}]</t>
   </si>
   <si>
     <t>[{'transition': 'low_to_high', 'altitude_ft': 12462.0, 'altitude_m': 3798.42}, {'transition': 'high_to_low', 'altitude_ft': 52124.0, 'altitude_m': 15887.4}]</t>
@@ -1327,7 +1327,7 @@
     <t>[{'transition': 'high_to_low', 'altitude_ft': 32694.0, 'altitude_m': 9965.13}]</t>
   </si>
   <si>
-    <t>[{'transition': 'high_to_low', 'altitude_ft': 48953.0, 'altitude_m': 14920.87}]</t>
+    <t>[{'transition': 'low_to_high', 'altitude_ft': 9847.0, 'altitude_m': 3001.37}, {'transition': 'high_to_low', 'altitude_ft': 48953.0, 'altitude_m': 14920.87}]</t>
   </si>
   <si>
     <t>[{'transition': 'high_to_low', 'altitude_ft': 74746.0, 'altitude_m': 22782.58}]</t>
@@ -1342,289 +1342,283 @@
     <t>[{'transition': 'high_to_low', 'altitude_ft': 50074.0, 'altitude_m': 15262.56}]</t>
   </si>
   <si>
-    <t>[{'transition': 'high_to_low', 'altitude_ft': 59923.0, 'altitude_m': 18264.53}]</t>
-  </si>
-  <si>
-    <t>1hrs 48mins 37secs</t>
-  </si>
-  <si>
-    <t>1hrs 39mins 0secs</t>
-  </si>
-  <si>
-    <t>1hrs 54mins 7secs</t>
-  </si>
-  <si>
-    <t>2hrs 5mins 30secs</t>
-  </si>
-  <si>
-    <t>2hrs 26mins 0secs</t>
-  </si>
-  <si>
-    <t>2hrs 19mins 23secs</t>
-  </si>
-  <si>
-    <t>2hrs 20mins 0secs</t>
-  </si>
-  <si>
-    <t>1hrs 38mins 50secs</t>
-  </si>
-  <si>
-    <t>2hrs 36mins 0secs</t>
+    <t>[{'transition': 'low_to_high', 'altitude_ft': 13128.0, 'altitude_m': 4001.41}, {'transition': 'high_to_low', 'altitude_ft': 59923.0, 'altitude_m': 18264.53}]</t>
+  </si>
+  <si>
+    <t>1hrs 37mins 7secs</t>
+  </si>
+  <si>
+    <t>1hrs 37mins 50secs</t>
+  </si>
+  <si>
+    <t>1hrs 54mins 23secs</t>
+  </si>
+  <si>
+    <t>2hrs 6mins 0secs</t>
+  </si>
+  <si>
+    <t>2hrs 26mins 30secs</t>
+  </si>
+  <si>
+    <t>2hrs 19mins 53secs</t>
+  </si>
+  <si>
+    <t>2hrs 20mins 20secs</t>
+  </si>
+  <si>
+    <t>1hrs 38mins 0secs</t>
+  </si>
+  <si>
+    <t>2hrs 36mins 10secs</t>
   </si>
   <si>
     <t>2hrs 27mins 30secs</t>
   </si>
   <si>
-    <t>1hrs 15mins 23secs</t>
-  </si>
-  <si>
-    <t>2hrs 7mins 40secs</t>
-  </si>
-  <si>
-    <t>1hrs 57mins 6secs</t>
-  </si>
-  <si>
-    <t>1hrs 57mins 40secs</t>
-  </si>
-  <si>
-    <t>1hrs 58mins 10secs</t>
-  </si>
-  <si>
-    <t>2hrs 5mins 0secs</t>
-  </si>
-  <si>
-    <t>1hrs 48mins 10secs</t>
-  </si>
-  <si>
-    <t>1hrs 57mins 17secs</t>
-  </si>
-  <si>
-    <t>1hrs 49mins 26secs</t>
-  </si>
-  <si>
-    <t>2hrs 9mins 0secs</t>
-  </si>
-  <si>
-    <t>2hrs 1mins 34secs</t>
-  </si>
-  <si>
-    <t>1hrs 55mins 30secs</t>
+    <t>1hrs 15mins 38secs</t>
+  </si>
+  <si>
+    <t>2hrs 8mins 20secs</t>
+  </si>
+  <si>
+    <t>1hrs 57mins 36secs</t>
+  </si>
+  <si>
+    <t>1hrs 59mins 30secs</t>
+  </si>
+  <si>
+    <t>1hrs 55mins 20secs</t>
+  </si>
+  <si>
+    <t>2hrs 4mins 47secs</t>
+  </si>
+  <si>
+    <t>1hrs 48mins 0secs</t>
+  </si>
+  <si>
+    <t>1hrs 57mins 30secs</t>
+  </si>
+  <si>
+    <t>1hrs 49mins 4secs</t>
+  </si>
+  <si>
+    <t>2hrs 9mins 30secs</t>
+  </si>
+  <si>
+    <t>2hrs 1mins 30secs</t>
+  </si>
+  <si>
+    <t>1hrs 55mins 0secs</t>
+  </si>
+  <si>
+    <t>1hrs 57mins 34secs</t>
+  </si>
+  <si>
+    <t>1hrs 26mins 40secs</t>
+  </si>
+  <si>
+    <t>2hrs 11mins 26secs</t>
+  </si>
+  <si>
+    <t>1hrs 40mins 45secs</t>
+  </si>
+  <si>
+    <t>1hrs 34mins 53secs</t>
+  </si>
+  <si>
+    <t>1hrs 47mins 30secs</t>
+  </si>
+  <si>
+    <t>1hrs 48mins 59secs</t>
+  </si>
+  <si>
+    <t>1hrs 28mins 19secs</t>
+  </si>
+  <si>
+    <t>1hrs 52mins 17secs</t>
+  </si>
+  <si>
+    <t>1hrs 54mins 26secs</t>
+  </si>
+  <si>
+    <t>2hrs 18mins 0secs</t>
+  </si>
+  <si>
+    <t>1hrs 49mins 47secs</t>
+  </si>
+  <si>
+    <t>1hrs 36mins 48secs</t>
+  </si>
+  <si>
+    <t>1hrs 31mins 20secs</t>
+  </si>
+  <si>
+    <t>1hrs 23mins 18secs</t>
+  </si>
+  <si>
+    <t>1hrs 42mins 48secs</t>
+  </si>
+  <si>
+    <t>1hrs 56mins 49secs</t>
+  </si>
+  <si>
+    <t>1hrs 24mins 15secs</t>
+  </si>
+  <si>
+    <t>1hrs 52mins 0secs</t>
+  </si>
+  <si>
+    <t>2hrs 6mins 34secs</t>
+  </si>
+  <si>
+    <t>1hrs 50mins 26secs</t>
+  </si>
+  <si>
+    <t>1hrs 55mins 15secs</t>
+  </si>
+  <si>
+    <t>1hrs 46mins 30secs</t>
+  </si>
+  <si>
+    <t>2hrs 4mins 57secs</t>
+  </si>
+  <si>
+    <t>2hrs 4mins 30secs</t>
+  </si>
+  <si>
+    <t>2hrs 12mins 27secs</t>
+  </si>
+  <si>
+    <t>1hrs 58mins 0secs</t>
+  </si>
+  <si>
+    <t>1hrs 27mins 19secs</t>
+  </si>
+  <si>
+    <t>2hrs 2mins 0secs</t>
+  </si>
+  <si>
+    <t>1hrs 59mins 52secs</t>
+  </si>
+  <si>
+    <t>1hrs 49mins 19secs</t>
+  </si>
+  <si>
+    <t>2hrs 5mins 45secs</t>
+  </si>
+  <si>
+    <t>1hrs 49mins 0secs</t>
+  </si>
+  <si>
+    <t>1hrs 54mins 30secs</t>
+  </si>
+  <si>
+    <t>2hrs 36mins 5secs</t>
+  </si>
+  <si>
+    <t>2hrs 7mins 49secs</t>
+  </si>
+  <si>
+    <t>2hrs 8mins 0secs</t>
+  </si>
+  <si>
+    <t>2hrs 10mins 24secs</t>
+  </si>
+  <si>
+    <t>1hrs 33mins 19secs</t>
+  </si>
+  <si>
+    <t>2hrs 1mins 12secs</t>
+  </si>
+  <si>
+    <t>1hrs 38mins 18secs</t>
+  </si>
+  <si>
+    <t>1hrs 56mins 4secs</t>
   </si>
   <si>
     <t>1hrs 56mins 30secs</t>
   </si>
   <si>
-    <t>1hrs 26mins 0secs</t>
-  </si>
-  <si>
-    <t>2hrs 12mins 4secs</t>
-  </si>
-  <si>
-    <t>1hrs 40mins 35secs</t>
-  </si>
-  <si>
-    <t>1hrs 35mins 30secs</t>
-  </si>
-  <si>
-    <t>1hrs 47mins 11secs</t>
-  </si>
-  <si>
-    <t>1hrs 48mins 30secs</t>
-  </si>
-  <si>
-    <t>1hrs 27mins 49secs</t>
-  </si>
-  <si>
-    <t>1hrs 51mins 47secs</t>
-  </si>
-  <si>
-    <t>1hrs 54mins 0secs</t>
-  </si>
-  <si>
-    <t>2hrs 17mins 1secs</t>
-  </si>
-  <si>
-    <t>1hrs 49mins 17secs</t>
-  </si>
-  <si>
-    <t>1hrs 38mins 41secs</t>
-  </si>
-  <si>
-    <t>1hrs 31mins 10secs</t>
-  </si>
-  <si>
-    <t>1hrs 22mins 30secs</t>
-  </si>
-  <si>
-    <t>1hrs 42mins 48secs</t>
-  </si>
-  <si>
-    <t>1hrs 24mins 12secs</t>
-  </si>
-  <si>
-    <t>1hrs 51mins 11secs</t>
-  </si>
-  <si>
-    <t>2hrs 8mins 41secs</t>
-  </si>
-  <si>
-    <t>1hrs 38mins 56secs</t>
-  </si>
-  <si>
-    <t>1hrs 50mins 0secs</t>
-  </si>
-  <si>
-    <t>1hrs 45mins 19secs</t>
-  </si>
-  <si>
-    <t>1hrs 46mins 30secs</t>
-  </si>
-  <si>
-    <t>2hrs 8mins 30secs</t>
-  </si>
-  <si>
-    <t>2hrs 4mins 0secs</t>
-  </si>
-  <si>
-    <t>2hrs 13mins 0secs</t>
-  </si>
-  <si>
-    <t>1hrs 57mins 30secs</t>
-  </si>
-  <si>
-    <t>1hrs 27mins 11secs</t>
-  </si>
-  <si>
-    <t>2hrs 2mins 3secs</t>
-  </si>
-  <si>
-    <t>1hrs 46mins 11secs</t>
-  </si>
-  <si>
-    <t>1hrs 59mins 28secs</t>
-  </si>
-  <si>
-    <t>1hrs 48mins 41secs</t>
-  </si>
-  <si>
-    <t>2hrs 3mins 33secs</t>
-  </si>
-  <si>
-    <t>2hrs 5mins 12secs</t>
-  </si>
-  <si>
-    <t>1hrs 48mins 27secs</t>
-  </si>
-  <si>
-    <t>1hrs 54mins 45secs</t>
-  </si>
-  <si>
-    <t>2hrs 41mins 23secs</t>
-  </si>
-  <si>
-    <t>2hrs 19mins 0secs</t>
-  </si>
-  <si>
-    <t>2hrs 7mins 41secs</t>
-  </si>
-  <si>
-    <t>2hrs 6mins 30secs</t>
-  </si>
-  <si>
-    <t>2hrs 9mins 52secs</t>
-  </si>
-  <si>
-    <t>1hrs 33mins 0secs</t>
-  </si>
-  <si>
-    <t>2hrs 0mins 30secs</t>
-  </si>
-  <si>
-    <t>1hrs 37mins 30secs</t>
-  </si>
-  <si>
-    <t>1hrs 56mins 0secs</t>
-  </si>
-  <si>
-    <t>1hrs 56mins 3secs</t>
-  </si>
-  <si>
-    <t>2hrs 15mins 30secs</t>
-  </si>
-  <si>
-    <t>2hrs 7mins 15secs</t>
-  </si>
-  <si>
-    <t>1hrs 43mins 49secs</t>
-  </si>
-  <si>
-    <t>1hrs 54mins 30secs</t>
-  </si>
-  <si>
-    <t>2hrs 13mins 30secs</t>
-  </si>
-  <si>
-    <t>2hrs 11mins 30secs</t>
-  </si>
-  <si>
-    <t>2hrs 14mins 30secs</t>
-  </si>
-  <si>
-    <t>1hrs 39mins 12secs</t>
-  </si>
-  <si>
-    <t>2hrs 6mins 18secs</t>
-  </si>
-  <si>
-    <t>1hrs 51mins 34secs</t>
-  </si>
-  <si>
-    <t>1hrs 36mins 30secs</t>
-  </si>
-  <si>
-    <t>1hrs 40mins 0secs</t>
+    <t>2hrs 14mins 57secs</t>
+  </si>
+  <si>
+    <t>2hrs 7mins 48secs</t>
+  </si>
+  <si>
+    <t>1hrs 44mins 0secs</t>
+  </si>
+  <si>
+    <t>1hrs 54mins 42secs</t>
+  </si>
+  <si>
+    <t>2hrs 14mins 0secs</t>
+  </si>
+  <si>
+    <t>2hrs 12mins 0secs</t>
+  </si>
+  <si>
+    <t>2hrs 14mins 48secs</t>
+  </si>
+  <si>
+    <t>1hrs 48mins 12secs</t>
+  </si>
+  <si>
+    <t>2hrs 7mins 18secs</t>
   </si>
   <si>
     <t>1hrs 52mins 30secs</t>
   </si>
   <si>
-    <t>2hrs 5mins 19secs</t>
-  </si>
-  <si>
-    <t>2hrs 20mins 4secs</t>
-  </si>
-  <si>
-    <t>1hrs 57mins 56secs</t>
-  </si>
-  <si>
-    <t>1hrs 50mins 18secs</t>
-  </si>
-  <si>
-    <t>0hrs 24mins 56secs</t>
-  </si>
-  <si>
-    <t>1hrs 44mins 57secs</t>
-  </si>
-  <si>
-    <t>1hrs 57mins 35secs</t>
-  </si>
-  <si>
-    <t>2hrs 3mins 15secs</t>
-  </si>
-  <si>
-    <t>2hrs 10mins 0secs</t>
+    <t>1hrs 35mins 18secs</t>
+  </si>
+  <si>
+    <t>1hrs 39mins 44secs</t>
+  </si>
+  <si>
+    <t>1hrs 53mins 30secs</t>
+  </si>
+  <si>
+    <t>2hrs 5mins 33secs</t>
+  </si>
+  <si>
+    <t>2hrs 19mins 56secs</t>
+  </si>
+  <si>
+    <t>1hrs 57mins 23secs</t>
+  </si>
+  <si>
+    <t>1hrs 50mins 30secs</t>
+  </si>
+  <si>
+    <t>2hrs 36mins 30secs</t>
+  </si>
+  <si>
+    <t>0hrs 25mins 26secs</t>
+  </si>
+  <si>
+    <t>1hrs 45mins 0secs</t>
+  </si>
+  <si>
+    <t>2hrs 16mins 30secs</t>
+  </si>
+  <si>
+    <t>1hrs 58mins 33secs</t>
+  </si>
+  <si>
+    <t>2hrs 3mins 0secs</t>
+  </si>
+  <si>
+    <t>2hrs 10mins 30secs</t>
   </si>
   <si>
     <t>1hrs 48mins 15secs</t>
   </si>
   <si>
-    <t>2hrs 10mins 55secs</t>
-  </si>
-  <si>
-    <t>2hrs 27mins 55secs</t>
-  </si>
-  <si>
-    <t>2hrs 7mins 45secs</t>
+    <t>2hrs 28mins 30secs</t>
+  </si>
+  <si>
+    <t>2hrs 8mins 15secs</t>
   </si>
 </sst>
 </file>
@@ -2130,19 +2124,19 @@
         <v>27272.59</v>
       </c>
       <c r="J2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K2" t="s">
         <v>443</v>
       </c>
       <c r="L2">
-        <v>6517</v>
+        <v>5827</v>
       </c>
       <c r="M2">
-        <v>101.7</v>
+        <v>101.65</v>
       </c>
       <c r="N2">
-        <v>163.66</v>
+        <v>163.59</v>
       </c>
       <c r="O2">
         <v>9.630000000000001</v>
@@ -2187,34 +2181,34 @@
         <v>8.529999999999999</v>
       </c>
       <c r="AC2">
-        <v>40.2238333333</v>
+        <v>40.2248333333</v>
       </c>
       <c r="AD2">
         <v>-104.0771666667</v>
       </c>
       <c r="AE2">
-        <v>4655</v>
+        <v>4564</v>
       </c>
       <c r="AF2">
-        <v>1418.84</v>
+        <v>1391.11</v>
       </c>
       <c r="AG2">
-        <v>39.4126666667</v>
+        <v>39.414</v>
       </c>
       <c r="AH2">
-        <v>-102.4765</v>
+        <v>-102.4771666667</v>
       </c>
       <c r="AI2">
-        <v>101.7</v>
+        <v>101.65</v>
       </c>
       <c r="AJ2">
-        <v>163.66</v>
+        <v>163.59</v>
       </c>
       <c r="AK2">
-        <v>4206</v>
+        <v>4606</v>
       </c>
       <c r="AL2">
-        <v>1281.99</v>
+        <v>1403.91</v>
       </c>
     </row>
     <row r="3" spans="1:38">
@@ -2246,19 +2240,19 @@
         <v>30445.86</v>
       </c>
       <c r="J3">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="K3" t="s">
         <v>444</v>
       </c>
       <c r="L3">
-        <v>5940</v>
+        <v>5870</v>
       </c>
       <c r="M3">
-        <v>93.92</v>
+        <v>93.79000000000001</v>
       </c>
       <c r="N3">
-        <v>151.15</v>
+        <v>150.94</v>
       </c>
       <c r="O3">
         <v>7.8</v>
@@ -2303,34 +2297,34 @@
         <v>8.550000000000001</v>
       </c>
       <c r="AC3">
-        <v>40.2216666667</v>
+        <v>40.2246666667</v>
       </c>
       <c r="AD3">
-        <v>-104.0768333333</v>
+        <v>-104.0771666667</v>
       </c>
       <c r="AE3">
-        <v>4964</v>
+        <v>4567</v>
       </c>
       <c r="AF3">
-        <v>1513.03</v>
+        <v>1392.02</v>
       </c>
       <c r="AG3">
-        <v>39.4601666667</v>
+        <v>39.4631666667</v>
       </c>
       <c r="AH3">
-        <v>-102.6088333333</v>
+        <v>-102.612</v>
       </c>
       <c r="AI3">
-        <v>93.92</v>
+        <v>93.79000000000001</v>
       </c>
       <c r="AJ3">
-        <v>151.15</v>
+        <v>150.94</v>
       </c>
       <c r="AK3">
-        <v>4182</v>
+        <v>5140</v>
       </c>
       <c r="AL3">
-        <v>1274.67</v>
+        <v>1566.67</v>
       </c>
     </row>
     <row r="4" spans="1:38">
@@ -2368,13 +2362,13 @@
         <v>445</v>
       </c>
       <c r="L4">
-        <v>6847</v>
+        <v>6863</v>
       </c>
       <c r="M4">
-        <v>56.07</v>
+        <v>56.11</v>
       </c>
       <c r="N4">
-        <v>90.23999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="O4">
         <v>10.16</v>
@@ -2419,34 +2413,34 @@
         <v>8.93</v>
       </c>
       <c r="AC4">
-        <v>40.2245</v>
+        <v>40.2248333333</v>
       </c>
       <c r="AD4">
-        <v>-104.0768333333</v>
+        <v>-104.0773333333</v>
       </c>
       <c r="AE4">
-        <v>4685</v>
+        <v>4557</v>
       </c>
       <c r="AF4">
-        <v>1427.99</v>
+        <v>1388.97</v>
       </c>
       <c r="AG4">
-        <v>39.742</v>
+        <v>39.7418333333</v>
       </c>
       <c r="AH4">
         <v>-103.2243333333</v>
       </c>
       <c r="AI4">
-        <v>56.07</v>
+        <v>56.11</v>
       </c>
       <c r="AJ4">
-        <v>90.23999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="AK4">
-        <v>4857</v>
+        <v>4868</v>
       </c>
       <c r="AL4">
-        <v>1480.41</v>
+        <v>1483.77</v>
       </c>
     </row>
     <row r="5" spans="1:38">
@@ -2478,19 +2472,19 @@
         <v>31019.5</v>
       </c>
       <c r="J5">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K5" t="s">
         <v>446</v>
       </c>
       <c r="L5">
-        <v>7530</v>
+        <v>7560</v>
       </c>
       <c r="M5">
-        <v>59.95</v>
+        <v>59.97</v>
       </c>
       <c r="N5">
-        <v>96.48</v>
+        <v>96.51000000000001</v>
       </c>
       <c r="O5">
         <v>9.42</v>
@@ -2535,16 +2529,16 @@
         <v>8.65</v>
       </c>
       <c r="AC5">
-        <v>40.2246666667</v>
+        <v>40.2248333333</v>
       </c>
       <c r="AD5">
-        <v>-104.0768333333</v>
+        <v>-104.0771666667</v>
       </c>
       <c r="AE5">
-        <v>4802</v>
+        <v>4563</v>
       </c>
       <c r="AF5">
-        <v>1463.65</v>
+        <v>1390.8</v>
       </c>
       <c r="AG5">
         <v>39.7071666667</v>
@@ -2553,10 +2547,10 @@
         <v>-103.1671666667</v>
       </c>
       <c r="AI5">
-        <v>59.95</v>
+        <v>59.97</v>
       </c>
       <c r="AJ5">
-        <v>96.48</v>
+        <v>96.51000000000001</v>
       </c>
       <c r="AK5">
         <v>4828</v>
@@ -2594,19 +2588,19 @@
         <v>29367.48</v>
       </c>
       <c r="J6">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="K6" t="s">
         <v>447</v>
       </c>
       <c r="L6">
-        <v>8760</v>
+        <v>8790</v>
       </c>
       <c r="M6">
-        <v>75.51000000000001</v>
+        <v>75.62</v>
       </c>
       <c r="N6">
-        <v>121.52</v>
+        <v>121.7</v>
       </c>
       <c r="O6">
         <v>3.54</v>
@@ -2651,16 +2645,16 @@
         <v>5.84</v>
       </c>
       <c r="AC6">
-        <v>39.235</v>
+        <v>39.236</v>
       </c>
       <c r="AD6">
-        <v>-103.6948333333</v>
+        <v>-103.6966666667</v>
       </c>
       <c r="AE6">
-        <v>5711</v>
+        <v>5420</v>
       </c>
       <c r="AF6">
-        <v>1740.71</v>
+        <v>1652.02</v>
       </c>
       <c r="AG6">
         <v>38.9201666667</v>
@@ -2669,10 +2663,10 @@
         <v>-102.3456666667</v>
       </c>
       <c r="AI6">
-        <v>75.51000000000001</v>
+        <v>75.62</v>
       </c>
       <c r="AJ6">
-        <v>121.52</v>
+        <v>121.7</v>
       </c>
       <c r="AK6">
         <v>4276</v>
@@ -2710,19 +2704,19 @@
         <v>29403.45</v>
       </c>
       <c r="J7">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="K7" t="s">
         <v>448</v>
       </c>
       <c r="L7">
-        <v>8363</v>
+        <v>8393</v>
       </c>
       <c r="M7">
-        <v>32.79</v>
+        <v>32.78</v>
       </c>
       <c r="N7">
-        <v>52.77</v>
+        <v>52.75</v>
       </c>
       <c r="O7">
         <v>5.53</v>
@@ -2767,16 +2761,16 @@
         <v>6.62</v>
       </c>
       <c r="AC7">
-        <v>39.2363333333</v>
+        <v>39.236</v>
       </c>
       <c r="AD7">
         <v>-103.697</v>
       </c>
       <c r="AE7">
-        <v>5457</v>
+        <v>5395</v>
       </c>
       <c r="AF7">
-        <v>1663.29</v>
+        <v>1644.4</v>
       </c>
       <c r="AG7">
         <v>39.0383333333</v>
@@ -2785,10 +2779,10 @@
         <v>-103.1405</v>
       </c>
       <c r="AI7">
-        <v>32.79</v>
+        <v>32.78</v>
       </c>
       <c r="AJ7">
-        <v>52.77</v>
+        <v>52.75</v>
       </c>
       <c r="AK7">
         <v>5143</v>
@@ -2826,19 +2820,19 @@
         <v>28844.14</v>
       </c>
       <c r="J8">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K8" t="s">
         <v>449</v>
       </c>
       <c r="L8">
-        <v>8400</v>
+        <v>8420</v>
       </c>
       <c r="M8">
-        <v>34.2</v>
+        <v>34.17</v>
       </c>
       <c r="N8">
-        <v>55.04</v>
+        <v>54.99</v>
       </c>
       <c r="O8">
         <v>5.28</v>
@@ -2883,16 +2877,16 @@
         <v>6.61</v>
       </c>
       <c r="AC8">
-        <v>39.2371666667</v>
+        <v>39.2361666667</v>
       </c>
       <c r="AD8">
         <v>-103.697</v>
       </c>
       <c r="AE8">
-        <v>5758</v>
+        <v>5403</v>
       </c>
       <c r="AF8">
-        <v>1755.04</v>
+        <v>1646.83</v>
       </c>
       <c r="AG8">
         <v>39.0321666667</v>
@@ -2901,10 +2895,10 @@
         <v>-103.1156666667</v>
       </c>
       <c r="AI8">
-        <v>34.2</v>
+        <v>34.17</v>
       </c>
       <c r="AJ8">
-        <v>55.04</v>
+        <v>54.99</v>
       </c>
       <c r="AK8">
         <v>5106</v>
@@ -2942,19 +2936,19 @@
         <v>29907.89</v>
       </c>
       <c r="J9">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="K9" t="s">
         <v>450</v>
       </c>
       <c r="L9">
-        <v>5930</v>
+        <v>5880</v>
       </c>
       <c r="M9">
-        <v>22.03</v>
+        <v>22.05</v>
       </c>
       <c r="N9">
-        <v>35.45</v>
+        <v>35.49</v>
       </c>
       <c r="O9">
         <v>9.59</v>
@@ -3002,31 +2996,31 @@
         <v>39.2785</v>
       </c>
       <c r="AD9">
-        <v>-103.4953333333</v>
+        <v>-103.4951666667</v>
       </c>
       <c r="AE9">
-        <v>5725</v>
+        <v>5717</v>
       </c>
       <c r="AF9">
-        <v>1744.98</v>
+        <v>1742.54</v>
       </c>
       <c r="AG9">
-        <v>39.5965</v>
+        <v>39.5968333333</v>
       </c>
       <c r="AH9">
         <v>-103.462</v>
       </c>
       <c r="AI9">
-        <v>22.03</v>
+        <v>22.05</v>
       </c>
       <c r="AJ9">
-        <v>35.45</v>
+        <v>35.49</v>
       </c>
       <c r="AK9">
-        <v>5267</v>
+        <v>5273</v>
       </c>
       <c r="AL9">
-        <v>1605.38</v>
+        <v>1607.21</v>
       </c>
     </row>
     <row r="10" spans="1:38">
@@ -3058,19 +3052,19 @@
         <v>29527.2</v>
       </c>
       <c r="J10">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="K10" t="s">
         <v>451</v>
       </c>
       <c r="L10">
-        <v>9360</v>
+        <v>9370</v>
       </c>
       <c r="M10">
         <v>35.77</v>
       </c>
       <c r="N10">
-        <v>57.57</v>
+        <v>57.56</v>
       </c>
       <c r="O10">
         <v>3.97</v>
@@ -3121,28 +3115,28 @@
         <v>-105.0078333333</v>
       </c>
       <c r="AE10">
-        <v>5723</v>
+        <v>5532</v>
       </c>
       <c r="AF10">
-        <v>1744.37</v>
+        <v>1686.15</v>
       </c>
       <c r="AG10">
-        <v>40.0388333333</v>
+        <v>40.039</v>
       </c>
       <c r="AH10">
-        <v>-104.3635</v>
+        <v>-104.3636666667</v>
       </c>
       <c r="AI10">
         <v>35.77</v>
       </c>
       <c r="AJ10">
-        <v>57.57</v>
+        <v>57.56</v>
       </c>
       <c r="AK10">
-        <v>4876</v>
+        <v>4889</v>
       </c>
       <c r="AL10">
-        <v>1486.2</v>
+        <v>1490.17</v>
       </c>
     </row>
     <row r="11" spans="1:38">
@@ -3290,13 +3284,13 @@
         <v>19231.97</v>
       </c>
       <c r="J12">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="K12" t="s">
         <v>453</v>
       </c>
       <c r="L12">
-        <v>4523</v>
+        <v>4538</v>
       </c>
       <c r="M12">
         <v>15.88</v>
@@ -3353,10 +3347,10 @@
         <v>-103.6968333333</v>
       </c>
       <c r="AE12">
-        <v>5508</v>
+        <v>5402</v>
       </c>
       <c r="AF12">
-        <v>1678.84</v>
+        <v>1646.53</v>
       </c>
       <c r="AG12">
         <v>39.0065</v>
@@ -3406,19 +3400,19 @@
         <v>28522.27</v>
       </c>
       <c r="J13">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K13" t="s">
         <v>454</v>
       </c>
       <c r="L13">
-        <v>7660</v>
+        <v>7700</v>
       </c>
       <c r="M13">
-        <v>22.46</v>
+        <v>22.47</v>
       </c>
       <c r="N13">
-        <v>36.15</v>
+        <v>36.16</v>
       </c>
       <c r="O13">
         <v>6.28</v>
@@ -3463,34 +3457,34 @@
         <v>7.13</v>
       </c>
       <c r="AC13">
-        <v>39.2365</v>
+        <v>39.2363333333</v>
       </c>
       <c r="AD13">
-        <v>-103.6966666667</v>
+        <v>-103.697</v>
       </c>
       <c r="AE13">
-        <v>5773</v>
+        <v>5401</v>
       </c>
       <c r="AF13">
-        <v>1759.61</v>
+        <v>1646.22</v>
       </c>
       <c r="AG13">
-        <v>38.9131666667</v>
+        <v>38.913</v>
       </c>
       <c r="AH13">
         <v>-103.65</v>
       </c>
       <c r="AI13">
-        <v>22.46</v>
+        <v>22.47</v>
       </c>
       <c r="AJ13">
-        <v>36.15</v>
+        <v>36.16</v>
       </c>
       <c r="AK13">
-        <v>5263</v>
+        <v>5260</v>
       </c>
       <c r="AL13">
-        <v>1604.16</v>
+        <v>1603.25</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -3522,19 +3516,19 @@
         <v>26529.49</v>
       </c>
       <c r="J14">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="K14" t="s">
         <v>455</v>
       </c>
       <c r="L14">
-        <v>7026</v>
+        <v>7056</v>
       </c>
       <c r="M14">
-        <v>24.29</v>
+        <v>24.26</v>
       </c>
       <c r="N14">
-        <v>39.1</v>
+        <v>39.04</v>
       </c>
       <c r="O14">
         <v>7.41</v>
@@ -3579,16 +3573,16 @@
         <v>8.449999999999999</v>
       </c>
       <c r="AC14">
-        <v>39.2366666667</v>
+        <v>39.2361666667</v>
       </c>
       <c r="AD14">
-        <v>-103.6966666667</v>
+        <v>-103.6968333333</v>
       </c>
       <c r="AE14">
-        <v>5842</v>
+        <v>5402</v>
       </c>
       <c r="AF14">
-        <v>1780.64</v>
+        <v>1646.53</v>
       </c>
       <c r="AG14">
         <v>38.8918333333</v>
@@ -3597,10 +3591,10 @@
         <v>-103.6066666667</v>
       </c>
       <c r="AI14">
-        <v>24.29</v>
+        <v>24.26</v>
       </c>
       <c r="AJ14">
-        <v>39.1</v>
+        <v>39.04</v>
       </c>
       <c r="AK14">
         <v>5136</v>
@@ -3638,19 +3632,19 @@
         <v>27397.25</v>
       </c>
       <c r="J15">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="K15" t="s">
         <v>456</v>
       </c>
       <c r="L15">
-        <v>7060</v>
+        <v>7170</v>
       </c>
       <c r="M15">
-        <v>25.06</v>
+        <v>25.04</v>
       </c>
       <c r="N15">
-        <v>40.33</v>
+        <v>40.3</v>
       </c>
       <c r="O15">
         <v>8.32</v>
@@ -3695,34 +3689,34 @@
         <v>8.41</v>
       </c>
       <c r="AC15">
-        <v>39.2365</v>
+        <v>39.2361666667</v>
       </c>
       <c r="AD15">
-        <v>-103.697</v>
+        <v>-103.6968333333</v>
       </c>
       <c r="AE15">
-        <v>5795</v>
+        <v>5408</v>
       </c>
       <c r="AF15">
-        <v>1766.32</v>
+        <v>1648.36</v>
       </c>
       <c r="AG15">
         <v>38.8808333333</v>
       </c>
       <c r="AH15">
-        <v>-103.6038333333</v>
+        <v>-103.6035</v>
       </c>
       <c r="AI15">
-        <v>25.06</v>
+        <v>25.04</v>
       </c>
       <c r="AJ15">
-        <v>40.33</v>
+        <v>40.3</v>
       </c>
       <c r="AK15">
-        <v>5319</v>
+        <v>5110</v>
       </c>
       <c r="AL15">
-        <v>1621.23</v>
+        <v>1557.53</v>
       </c>
     </row>
     <row r="16" spans="1:38">
@@ -3754,13 +3748,13 @@
         <v>30407.76</v>
       </c>
       <c r="J16">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="K16" t="s">
         <v>457</v>
       </c>
       <c r="L16">
-        <v>7090</v>
+        <v>6920</v>
       </c>
       <c r="M16">
         <v>40.62</v>
@@ -3811,19 +3805,19 @@
         <v>13.05</v>
       </c>
       <c r="AC16">
-        <v>39.6081666667</v>
+        <v>39.608</v>
       </c>
       <c r="AD16">
         <v>-104.0423333333</v>
       </c>
       <c r="AE16">
-        <v>5284</v>
+        <v>5219</v>
       </c>
       <c r="AF16">
-        <v>1610.56</v>
+        <v>1590.75</v>
       </c>
       <c r="AG16">
-        <v>39.5006666667</v>
+        <v>39.5005</v>
       </c>
       <c r="AH16">
         <v>-103.2921666667</v>
@@ -3835,10 +3829,10 @@
         <v>65.37</v>
       </c>
       <c r="AK16">
-        <v>5099</v>
+        <v>5084</v>
       </c>
       <c r="AL16">
-        <v>1554.18</v>
+        <v>1549.6</v>
       </c>
     </row>
     <row r="17" spans="1:38">
@@ -3870,19 +3864,19 @@
         <v>27814.22</v>
       </c>
       <c r="J17">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="K17" t="s">
         <v>458</v>
       </c>
       <c r="L17">
-        <v>7500</v>
+        <v>7487</v>
       </c>
       <c r="M17">
         <v>54.27</v>
       </c>
       <c r="N17">
-        <v>87.33</v>
+        <v>87.34</v>
       </c>
       <c r="O17">
         <v>6.85</v>
@@ -3927,34 +3921,34 @@
         <v>8.17</v>
       </c>
       <c r="AC17">
-        <v>39.6085166667</v>
+        <v>39.608</v>
       </c>
       <c r="AD17">
-        <v>-104.0418833333</v>
+        <v>-104.0421666667</v>
       </c>
       <c r="AE17">
-        <v>5414</v>
+        <v>5223</v>
       </c>
       <c r="AF17">
-        <v>1650.19</v>
+        <v>1591.97</v>
       </c>
       <c r="AG17">
         <v>39.4465666667</v>
       </c>
       <c r="AH17">
-        <v>-103.0447833333</v>
+        <v>-103.0448166667</v>
       </c>
       <c r="AI17">
         <v>54.27</v>
       </c>
       <c r="AJ17">
-        <v>87.33</v>
+        <v>87.34</v>
       </c>
       <c r="AK17">
-        <v>4768</v>
+        <v>4778</v>
       </c>
       <c r="AL17">
-        <v>1453.29</v>
+        <v>1456.33</v>
       </c>
     </row>
     <row r="18" spans="1:38">
@@ -3986,19 +3980,19 @@
         <v>28673.76</v>
       </c>
       <c r="J18">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="K18" t="s">
         <v>459</v>
       </c>
       <c r="L18">
-        <v>6490</v>
+        <v>6480</v>
       </c>
       <c r="M18">
-        <v>25.82</v>
+        <v>25.8</v>
       </c>
       <c r="N18">
-        <v>41.56</v>
+        <v>41.52</v>
       </c>
       <c r="O18">
         <v>11.03</v>
@@ -4043,16 +4037,16 @@
         <v>10.05</v>
       </c>
       <c r="AC18">
-        <v>39.6083333333</v>
+        <v>39.608</v>
       </c>
       <c r="AD18">
-        <v>-104.042</v>
+        <v>-104.0423333333</v>
       </c>
       <c r="AE18">
-        <v>5418</v>
+        <v>5211</v>
       </c>
       <c r="AF18">
-        <v>1651.41</v>
+        <v>1588.31</v>
       </c>
       <c r="AG18">
         <v>39.2358333333</v>
@@ -4061,16 +4055,16 @@
         <v>-103.9986666667</v>
       </c>
       <c r="AI18">
-        <v>25.82</v>
+        <v>25.8</v>
       </c>
       <c r="AJ18">
-        <v>41.56</v>
+        <v>41.52</v>
       </c>
       <c r="AK18">
-        <v>6011</v>
+        <v>6014</v>
       </c>
       <c r="AL18">
-        <v>1832.15</v>
+        <v>1833.07</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -4102,19 +4096,19 @@
         <v>28635.66</v>
       </c>
       <c r="J19">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="K19" t="s">
         <v>460</v>
       </c>
       <c r="L19">
-        <v>7037</v>
+        <v>7050</v>
       </c>
       <c r="M19">
-        <v>29.96</v>
+        <v>29.94</v>
       </c>
       <c r="N19">
-        <v>48.21</v>
+        <v>48.18</v>
       </c>
       <c r="O19">
         <v>8.77</v>
@@ -4159,16 +4153,16 @@
         <v>9.33</v>
       </c>
       <c r="AC19">
-        <v>39.6083</v>
+        <v>39.608</v>
       </c>
       <c r="AD19">
-        <v>-104.0423</v>
+        <v>-104.0421666667</v>
       </c>
       <c r="AE19">
-        <v>5289</v>
+        <v>5229</v>
       </c>
       <c r="AF19">
-        <v>1612.09</v>
+        <v>1593.8</v>
       </c>
       <c r="AG19">
         <v>39.1748333333</v>
@@ -4177,10 +4171,10 @@
         <v>-104.0171666667</v>
       </c>
       <c r="AI19">
-        <v>29.96</v>
+        <v>29.94</v>
       </c>
       <c r="AJ19">
-        <v>48.21</v>
+        <v>48.18</v>
       </c>
       <c r="AK19">
         <v>5847</v>
@@ -4224,13 +4218,13 @@
         <v>461</v>
       </c>
       <c r="L20">
-        <v>6566</v>
+        <v>6544</v>
       </c>
       <c r="M20">
-        <v>60.91</v>
+        <v>60.89</v>
       </c>
       <c r="N20">
-        <v>98.03</v>
+        <v>97.98999999999999</v>
       </c>
       <c r="O20">
         <v>8.99</v>
@@ -4275,34 +4269,34 @@
         <v>9.17</v>
       </c>
       <c r="AC20">
-        <v>39.6081666667</v>
+        <v>39.608</v>
       </c>
       <c r="AD20">
         <v>-104.0421666667</v>
       </c>
       <c r="AE20">
-        <v>5235</v>
+        <v>5215</v>
       </c>
       <c r="AF20">
-        <v>1595.63</v>
+        <v>1589.53</v>
       </c>
       <c r="AG20">
-        <v>39.0996666667</v>
+        <v>39.1001666667</v>
       </c>
       <c r="AH20">
         <v>-103.1098333333</v>
       </c>
       <c r="AI20">
-        <v>60.91</v>
+        <v>60.89</v>
       </c>
       <c r="AJ20">
-        <v>98.03</v>
+        <v>97.98999999999999</v>
       </c>
       <c r="AK20">
-        <v>5131</v>
+        <v>5125</v>
       </c>
       <c r="AL20">
-        <v>1563.93</v>
+        <v>1562.1</v>
       </c>
     </row>
     <row r="21" spans="1:38">
@@ -4334,19 +4328,19 @@
         <v>27902.61</v>
       </c>
       <c r="J21">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K21" t="s">
         <v>462</v>
       </c>
       <c r="L21">
-        <v>7740</v>
+        <v>7770</v>
       </c>
       <c r="M21">
-        <v>87.26000000000001</v>
+        <v>87.27</v>
       </c>
       <c r="N21">
-        <v>140.43</v>
+        <v>140.44</v>
       </c>
       <c r="O21">
         <v>6.7</v>
@@ -4391,34 +4385,34 @@
         <v>7.45</v>
       </c>
       <c r="AC21">
-        <v>39.6083333333</v>
+        <v>39.608</v>
       </c>
       <c r="AD21">
         <v>-104.0421666667</v>
       </c>
       <c r="AE21">
-        <v>5423</v>
+        <v>5212</v>
       </c>
       <c r="AF21">
-        <v>1652.93</v>
+        <v>1588.62</v>
       </c>
       <c r="AG21">
         <v>39.3553333333</v>
       </c>
       <c r="AH21">
-        <v>-102.4378333333</v>
+        <v>-102.4376666667</v>
       </c>
       <c r="AI21">
-        <v>87.26000000000001</v>
+        <v>87.27</v>
       </c>
       <c r="AJ21">
-        <v>140.43</v>
+        <v>140.44</v>
       </c>
       <c r="AK21">
-        <v>4181</v>
+        <v>4168</v>
       </c>
       <c r="AL21">
-        <v>1274.37</v>
+        <v>1270.41</v>
       </c>
     </row>
     <row r="22" spans="1:38">
@@ -4450,19 +4444,19 @@
         <v>27201.88</v>
       </c>
       <c r="J22">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K22" t="s">
         <v>463</v>
       </c>
       <c r="L22">
-        <v>7294</v>
+        <v>7290</v>
       </c>
       <c r="M22">
-        <v>81.78</v>
+        <v>81.79000000000001</v>
       </c>
       <c r="N22">
-        <v>131.61</v>
+        <v>131.62</v>
       </c>
       <c r="O22">
         <v>7.31</v>
@@ -4510,13 +4504,13 @@
         <v>39.608</v>
       </c>
       <c r="AD22">
-        <v>-104.042</v>
+        <v>-104.0421666667</v>
       </c>
       <c r="AE22">
-        <v>5664</v>
+        <v>5208</v>
       </c>
       <c r="AF22">
-        <v>1726.39</v>
+        <v>1587.4</v>
       </c>
       <c r="AG22">
         <v>39.3813333333</v>
@@ -4525,16 +4519,16 @@
         <v>-102.5355</v>
       </c>
       <c r="AI22">
-        <v>81.78</v>
+        <v>81.79000000000001</v>
       </c>
       <c r="AJ22">
-        <v>131.61</v>
+        <v>131.62</v>
       </c>
       <c r="AK22">
-        <v>4273</v>
+        <v>4276</v>
       </c>
       <c r="AL22">
-        <v>1302.41</v>
+        <v>1303.32</v>
       </c>
     </row>
     <row r="23" spans="1:38">
@@ -4566,19 +4560,19 @@
         <v>26864.16</v>
       </c>
       <c r="J23">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K23" t="s">
         <v>464</v>
       </c>
       <c r="L23">
-        <v>6930</v>
+        <v>6900</v>
       </c>
       <c r="M23">
-        <v>32.86</v>
+        <v>32.84</v>
       </c>
       <c r="N23">
-        <v>52.88</v>
+        <v>52.85</v>
       </c>
       <c r="O23">
         <v>12.33</v>
@@ -4623,16 +4617,16 @@
         <v>10.12</v>
       </c>
       <c r="AC23">
-        <v>39.6085</v>
+        <v>39.6081666667</v>
       </c>
       <c r="AD23">
         <v>-104.0421666667</v>
       </c>
       <c r="AE23">
-        <v>5444</v>
+        <v>5218</v>
       </c>
       <c r="AF23">
-        <v>1659.33</v>
+        <v>1590.45</v>
       </c>
       <c r="AG23">
         <v>39.1426666667</v>
@@ -4641,16 +4635,16 @@
         <v>-103.9161666667</v>
       </c>
       <c r="AI23">
-        <v>32.86</v>
+        <v>32.84</v>
       </c>
       <c r="AJ23">
-        <v>52.88</v>
+        <v>52.85</v>
       </c>
       <c r="AK23">
-        <v>6013</v>
+        <v>6018</v>
       </c>
       <c r="AL23">
-        <v>1832.76</v>
+        <v>1834.29</v>
       </c>
     </row>
     <row r="24" spans="1:38">
@@ -4682,19 +4676,19 @@
         <v>27619.45</v>
       </c>
       <c r="J24">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="K24" t="s">
         <v>465</v>
       </c>
       <c r="L24">
-        <v>6990</v>
+        <v>7054</v>
       </c>
       <c r="M24">
-        <v>35.75</v>
+        <v>35.7</v>
       </c>
       <c r="N24">
-        <v>57.53</v>
+        <v>57.46</v>
       </c>
       <c r="O24">
         <v>9.91</v>
@@ -4739,16 +4733,16 @@
         <v>8.779999999999999</v>
       </c>
       <c r="AC24">
-        <v>39.6085</v>
+        <v>39.6078333333</v>
       </c>
       <c r="AD24">
-        <v>-104.0418333333</v>
+        <v>-104.0421666667</v>
       </c>
       <c r="AE24">
-        <v>5514</v>
+        <v>5212</v>
       </c>
       <c r="AF24">
-        <v>1680.67</v>
+        <v>1588.62</v>
       </c>
       <c r="AG24">
         <v>39.0968333333</v>
@@ -4757,10 +4751,10 @@
         <v>-103.9398333333</v>
       </c>
       <c r="AI24">
-        <v>35.75</v>
+        <v>35.7</v>
       </c>
       <c r="AJ24">
-        <v>57.53</v>
+        <v>57.46</v>
       </c>
       <c r="AK24">
         <v>6055</v>
@@ -4798,19 +4792,19 @@
         <v>25754.99</v>
       </c>
       <c r="J25">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="K25" t="s">
         <v>466</v>
       </c>
       <c r="L25">
-        <v>5160</v>
+        <v>5200</v>
       </c>
       <c r="M25">
-        <v>83.91</v>
+        <v>83.93000000000001</v>
       </c>
       <c r="N25">
-        <v>135.04</v>
+        <v>135.07</v>
       </c>
       <c r="O25">
         <v>11.03</v>
@@ -4855,16 +4849,16 @@
         <v>9.42</v>
       </c>
       <c r="AC25">
-        <v>39.6085</v>
+        <v>39.6083333333</v>
       </c>
       <c r="AD25">
-        <v>-104.042</v>
+        <v>-104.0421666667</v>
       </c>
       <c r="AE25">
-        <v>5322</v>
+        <v>5226</v>
       </c>
       <c r="AF25">
-        <v>1622.15</v>
+        <v>1592.88</v>
       </c>
       <c r="AG25">
         <v>40.3986666667</v>
@@ -4873,10 +4867,10 @@
         <v>-102.8365</v>
       </c>
       <c r="AI25">
-        <v>83.91</v>
+        <v>83.93000000000001</v>
       </c>
       <c r="AJ25">
-        <v>135.04</v>
+        <v>135.07</v>
       </c>
       <c r="AK25">
         <v>4698</v>
@@ -4914,19 +4908,19 @@
         <v>32334.71</v>
       </c>
       <c r="J26">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K26" t="s">
         <v>467</v>
       </c>
       <c r="L26">
-        <v>7924</v>
+        <v>7886</v>
       </c>
       <c r="M26">
-        <v>97.72</v>
+        <v>97.75</v>
       </c>
       <c r="N26">
-        <v>157.26</v>
+        <v>157.32</v>
       </c>
       <c r="O26">
         <v>15.62</v>
@@ -4971,34 +4965,34 @@
         <v>11.89</v>
       </c>
       <c r="AC26">
-        <v>39.6091666667</v>
+        <v>39.6083333333</v>
       </c>
       <c r="AD26">
-        <v>-104.042</v>
+        <v>-104.0421666667</v>
       </c>
       <c r="AE26">
-        <v>5431</v>
+        <v>5219</v>
       </c>
       <c r="AF26">
-        <v>1655.37</v>
+        <v>1590.75</v>
       </c>
       <c r="AG26">
-        <v>40.4661666667</v>
+        <v>40.466</v>
       </c>
       <c r="AH26">
         <v>-102.5708333333</v>
       </c>
       <c r="AI26">
-        <v>97.72</v>
+        <v>97.75</v>
       </c>
       <c r="AJ26">
-        <v>157.26</v>
+        <v>157.32</v>
       </c>
       <c r="AK26">
-        <v>3969</v>
+        <v>3989</v>
       </c>
       <c r="AL26">
-        <v>1209.75</v>
+        <v>1215.85</v>
       </c>
     </row>
     <row r="27" spans="1:38">
@@ -5030,19 +5024,19 @@
         <v>30171.24</v>
       </c>
       <c r="J27">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K27" t="s">
         <v>468</v>
       </c>
       <c r="L27">
-        <v>6035</v>
+        <v>6045</v>
       </c>
       <c r="M27">
-        <v>38.68</v>
+        <v>38.71</v>
       </c>
       <c r="N27">
-        <v>62.25</v>
+        <v>62.3</v>
       </c>
       <c r="O27">
         <v>5.81</v>
@@ -5087,16 +5081,16 @@
         <v>7.72</v>
       </c>
       <c r="AC27">
-        <v>39.6083333333</v>
+        <v>39.608</v>
       </c>
       <c r="AD27">
-        <v>-104.0418333333</v>
+        <v>-104.0421666667</v>
       </c>
       <c r="AE27">
-        <v>5351</v>
+        <v>5222</v>
       </c>
       <c r="AF27">
-        <v>1630.98</v>
+        <v>1591.67</v>
       </c>
       <c r="AG27">
         <v>40.077</v>
@@ -5105,10 +5099,10 @@
         <v>-103.642</v>
       </c>
       <c r="AI27">
-        <v>38.68</v>
+        <v>38.71</v>
       </c>
       <c r="AJ27">
-        <v>62.25</v>
+        <v>62.3</v>
       </c>
       <c r="AK27">
         <v>11560</v>
@@ -5146,19 +5140,19 @@
         <v>30216.65</v>
       </c>
       <c r="J28">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="K28" t="s">
         <v>469</v>
       </c>
       <c r="L28">
-        <v>5730</v>
+        <v>5693</v>
       </c>
       <c r="M28">
-        <v>27.05</v>
+        <v>27.04</v>
       </c>
       <c r="N28">
-        <v>43.53</v>
+        <v>43.51</v>
       </c>
       <c r="O28">
         <v>12.29</v>
@@ -5215,22 +5209,22 @@
         <v>8707.219999999999</v>
       </c>
       <c r="AG28">
-        <v>38.8186666667</v>
+        <v>38.8188333333</v>
       </c>
       <c r="AH28">
         <v>-103.9661666667</v>
       </c>
       <c r="AI28">
-        <v>27.05</v>
+        <v>27.04</v>
       </c>
       <c r="AJ28">
-        <v>43.53</v>
+        <v>43.51</v>
       </c>
       <c r="AK28">
-        <v>5621</v>
+        <v>5610</v>
       </c>
       <c r="AL28">
-        <v>1713.28</v>
+        <v>1709.93</v>
       </c>
     </row>
     <row r="29" spans="1:38">
@@ -5262,19 +5256,19 @@
         <v>30473.9</v>
       </c>
       <c r="J29">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="K29" t="s">
         <v>470</v>
       </c>
       <c r="L29">
-        <v>6431</v>
+        <v>6450</v>
       </c>
       <c r="M29">
-        <v>32.74</v>
+        <v>32.71</v>
       </c>
       <c r="N29">
-        <v>52.68</v>
+        <v>52.65</v>
       </c>
       <c r="O29">
         <v>14.79</v>
@@ -5319,16 +5313,16 @@
         <v>13.2</v>
       </c>
       <c r="AC29">
-        <v>39.6076666667</v>
+        <v>39.608</v>
       </c>
       <c r="AD29">
-        <v>-104.0425</v>
+        <v>-104.0421666667</v>
       </c>
       <c r="AE29">
-        <v>5394</v>
+        <v>5222</v>
       </c>
       <c r="AF29">
-        <v>1644.09</v>
+        <v>1591.67</v>
       </c>
       <c r="AG29">
         <v>39.7298333333</v>
@@ -5337,10 +5331,10 @@
         <v>-103.4473333333</v>
       </c>
       <c r="AI29">
-        <v>32.74</v>
+        <v>32.71</v>
       </c>
       <c r="AJ29">
-        <v>52.68</v>
+        <v>52.65</v>
       </c>
       <c r="AK29">
         <v>5285</v>
@@ -5378,19 +5372,19 @@
         <v>31062.47</v>
       </c>
       <c r="J30">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="K30" t="s">
         <v>471</v>
       </c>
       <c r="L30">
-        <v>6510</v>
+        <v>6539</v>
       </c>
       <c r="M30">
         <v>37.42</v>
       </c>
       <c r="N30">
-        <v>60.22</v>
+        <v>60.23</v>
       </c>
       <c r="O30">
         <v>8.5</v>
@@ -5435,16 +5429,16 @@
         <v>8.859999999999999</v>
       </c>
       <c r="AC30">
-        <v>39.6083333333</v>
+        <v>39.6081666667</v>
       </c>
       <c r="AD30">
         <v>-104.0421666667</v>
       </c>
       <c r="AE30">
-        <v>5519</v>
+        <v>5242</v>
       </c>
       <c r="AF30">
-        <v>1682.19</v>
+        <v>1597.76</v>
       </c>
       <c r="AG30">
         <v>39.7598333333</v>
@@ -5456,7 +5450,7 @@
         <v>37.42</v>
       </c>
       <c r="AJ30">
-        <v>60.22</v>
+        <v>60.23</v>
       </c>
       <c r="AK30">
         <v>34398</v>
@@ -5494,19 +5488,19 @@
         <v>27275.03</v>
       </c>
       <c r="J31">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K31" t="s">
         <v>472</v>
       </c>
       <c r="L31">
-        <v>5269</v>
+        <v>5299</v>
       </c>
       <c r="M31">
-        <v>37.35</v>
+        <v>37.36</v>
       </c>
       <c r="N31">
-        <v>60.11</v>
+        <v>60.13</v>
       </c>
       <c r="O31">
         <v>6.64</v>
@@ -5551,16 +5545,16 @@
         <v>7.46</v>
       </c>
       <c r="AC31">
-        <v>39.6083333333</v>
+        <v>39.6081666667</v>
       </c>
       <c r="AD31">
-        <v>-104.042</v>
+        <v>-104.0421666667</v>
       </c>
       <c r="AE31">
-        <v>5367</v>
+        <v>5213</v>
       </c>
       <c r="AF31">
-        <v>1635.86</v>
+        <v>1588.92</v>
       </c>
       <c r="AG31">
         <v>39.7646666667</v>
@@ -5569,10 +5563,10 @@
         <v>-103.369</v>
       </c>
       <c r="AI31">
-        <v>37.35</v>
+        <v>37.36</v>
       </c>
       <c r="AJ31">
-        <v>60.11</v>
+        <v>60.13</v>
       </c>
       <c r="AK31">
         <v>45636</v>
@@ -5610,19 +5604,19 @@
         <v>27295.45</v>
       </c>
       <c r="J32">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="K32" t="s">
         <v>473</v>
       </c>
       <c r="L32">
-        <v>6707</v>
+        <v>6737</v>
       </c>
       <c r="M32">
-        <v>71.97</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="N32">
-        <v>115.82</v>
+        <v>115.81</v>
       </c>
       <c r="O32">
         <v>6.21</v>
@@ -5670,13 +5664,13 @@
         <v>39.608</v>
       </c>
       <c r="AD32">
-        <v>-104.0423333333</v>
+        <v>-104.0421666667</v>
       </c>
       <c r="AE32">
-        <v>5421</v>
+        <v>5223</v>
       </c>
       <c r="AF32">
-        <v>1652.32</v>
+        <v>1591.97</v>
       </c>
       <c r="AG32">
         <v>38.9500166667</v>
@@ -5685,10 +5679,10 @@
         <v>-102.998</v>
       </c>
       <c r="AI32">
-        <v>71.97</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="AJ32">
-        <v>115.82</v>
+        <v>115.81</v>
       </c>
       <c r="AK32">
         <v>6746</v>
@@ -5726,19 +5720,19 @@
         <v>27576.17</v>
       </c>
       <c r="J33">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K33" t="s">
         <v>474</v>
       </c>
       <c r="L33">
-        <v>6840</v>
+        <v>6866</v>
       </c>
       <c r="M33">
-        <v>74.36</v>
+        <v>74.33</v>
       </c>
       <c r="N33">
-        <v>119.67</v>
+        <v>119.62</v>
       </c>
       <c r="O33">
         <v>8.82</v>
@@ -5783,16 +5777,16 @@
         <v>8.529999999999999</v>
       </c>
       <c r="AC33">
-        <v>39.6081666667</v>
+        <v>39.608</v>
       </c>
       <c r="AD33">
-        <v>-104.0426666667</v>
+        <v>-104.0421666667</v>
       </c>
       <c r="AE33">
-        <v>5594</v>
+        <v>5212</v>
       </c>
       <c r="AF33">
-        <v>1705.05</v>
+        <v>1588.62</v>
       </c>
       <c r="AG33">
         <v>38.9375</v>
@@ -5801,10 +5795,10 @@
         <v>-102.9541666667</v>
       </c>
       <c r="AI33">
-        <v>74.36</v>
+        <v>74.33</v>
       </c>
       <c r="AJ33">
-        <v>119.67</v>
+        <v>119.62</v>
       </c>
       <c r="AK33">
         <v>5134</v>
@@ -5842,19 +5836,19 @@
         <v>33452.41</v>
       </c>
       <c r="J34">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="K34" t="s">
         <v>475</v>
       </c>
       <c r="L34">
-        <v>8221</v>
+        <v>8280</v>
       </c>
       <c r="M34">
-        <v>81.86</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="N34">
-        <v>131.74</v>
+        <v>131.72</v>
       </c>
       <c r="O34">
         <v>9.01</v>
@@ -5902,13 +5896,13 @@
         <v>39.608</v>
       </c>
       <c r="AD34">
-        <v>-104.0423333333</v>
+        <v>-104.0421666667</v>
       </c>
       <c r="AE34">
-        <v>5281</v>
+        <v>5227</v>
       </c>
       <c r="AF34">
-        <v>1609.65</v>
+        <v>1593.19</v>
       </c>
       <c r="AG34">
         <v>38.9566666667</v>
@@ -5917,16 +5911,16 @@
         <v>-102.7625</v>
       </c>
       <c r="AI34">
-        <v>81.86</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="AJ34">
-        <v>131.74</v>
+        <v>131.72</v>
       </c>
       <c r="AK34">
-        <v>4489</v>
+        <v>4499</v>
       </c>
       <c r="AL34">
-        <v>1368.25</v>
+        <v>1371.3</v>
       </c>
     </row>
     <row r="35" spans="1:38">
@@ -5958,19 +5952,19 @@
         <v>30120.64</v>
       </c>
       <c r="J35">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="K35" t="s">
         <v>476</v>
       </c>
       <c r="L35">
-        <v>6557</v>
+        <v>6587</v>
       </c>
       <c r="M35">
-        <v>21.94</v>
+        <v>21.96</v>
       </c>
       <c r="N35">
-        <v>35.3</v>
+        <v>35.34</v>
       </c>
       <c r="O35">
         <v>8.06</v>
@@ -6015,16 +6009,16 @@
         <v>7.9</v>
       </c>
       <c r="AC35">
-        <v>39.608</v>
+        <v>39.6083333333</v>
       </c>
       <c r="AD35">
-        <v>-104.0418333333</v>
+        <v>-104.042</v>
       </c>
       <c r="AE35">
-        <v>5391</v>
+        <v>5225</v>
       </c>
       <c r="AF35">
-        <v>1643.18</v>
+        <v>1592.58</v>
       </c>
       <c r="AG35">
         <v>39.3363</v>
@@ -6033,10 +6027,10 @@
         <v>-103.8284666667</v>
       </c>
       <c r="AI35">
-        <v>21.94</v>
+        <v>21.96</v>
       </c>
       <c r="AJ35">
-        <v>35.3</v>
+        <v>35.34</v>
       </c>
       <c r="AK35">
         <v>6175</v>
@@ -6074,19 +6068,19 @@
         <v>22073.92</v>
       </c>
       <c r="J36">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K36" t="s">
         <v>477</v>
       </c>
       <c r="L36">
-        <v>5921</v>
+        <v>5808</v>
       </c>
       <c r="M36">
-        <v>48.27</v>
+        <v>48.26</v>
       </c>
       <c r="N36">
-        <v>77.69</v>
+        <v>77.67</v>
       </c>
       <c r="O36">
         <v>8.859999999999999</v>
@@ -6131,34 +6125,34 @@
         <v>8.31</v>
       </c>
       <c r="AC36">
-        <v>39.6083166667</v>
+        <v>39.6084166667</v>
       </c>
       <c r="AD36">
-        <v>-104.0419333333</v>
+        <v>-104.04205</v>
       </c>
       <c r="AE36">
-        <v>5230</v>
+        <v>5201</v>
       </c>
       <c r="AF36">
-        <v>1594.1</v>
+        <v>1585.26</v>
       </c>
       <c r="AG36">
-        <v>39.7446666667</v>
+        <v>39.7446</v>
       </c>
       <c r="AH36">
-        <v>-103.151</v>
+        <v>-103.1512833333</v>
       </c>
       <c r="AI36">
-        <v>48.27</v>
+        <v>48.26</v>
       </c>
       <c r="AJ36">
-        <v>77.69</v>
+        <v>77.67</v>
       </c>
       <c r="AK36">
-        <v>4812</v>
+        <v>4814</v>
       </c>
       <c r="AL36">
-        <v>1466.7</v>
+        <v>1467.31</v>
       </c>
     </row>
     <row r="37" spans="1:38">
@@ -6196,13 +6190,13 @@
         <v>478</v>
       </c>
       <c r="L37">
-        <v>5470</v>
+        <v>5480</v>
       </c>
       <c r="M37">
-        <v>44.44</v>
+        <v>44.46</v>
       </c>
       <c r="N37">
-        <v>71.51000000000001</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="O37">
         <v>9.140000000000001</v>
@@ -6250,31 +6244,31 @@
         <v>39.6083333333</v>
       </c>
       <c r="AD37">
-        <v>-104.0418333333</v>
+        <v>-104.042</v>
       </c>
       <c r="AE37">
-        <v>5320</v>
+        <v>5213</v>
       </c>
       <c r="AF37">
-        <v>1621.54</v>
+        <v>1588.92</v>
       </c>
       <c r="AG37">
-        <v>39.7373333333</v>
+        <v>39.7375</v>
       </c>
       <c r="AH37">
-        <v>-103.2226666667</v>
+        <v>-103.2225</v>
       </c>
       <c r="AI37">
-        <v>44.44</v>
+        <v>44.46</v>
       </c>
       <c r="AJ37">
-        <v>71.51000000000001</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="AK37">
-        <v>4897</v>
+        <v>4894</v>
       </c>
       <c r="AL37">
-        <v>1492.61</v>
+        <v>1491.69</v>
       </c>
     </row>
     <row r="38" spans="1:38">
@@ -6306,19 +6300,19 @@
         <v>20454.52</v>
       </c>
       <c r="J38">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="K38" t="s">
         <v>479</v>
       </c>
       <c r="L38">
-        <v>4950</v>
+        <v>4998</v>
       </c>
       <c r="M38">
-        <v>40.84</v>
+        <v>40.85</v>
       </c>
       <c r="N38">
-        <v>65.73</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="O38">
         <v>8</v>
@@ -6363,16 +6357,16 @@
         <v>8.24</v>
       </c>
       <c r="AC38">
-        <v>39.6083333333</v>
+        <v>39.6084333333</v>
       </c>
       <c r="AD38">
-        <v>-104.0418333333</v>
+        <v>-104.042</v>
       </c>
       <c r="AE38">
-        <v>5368</v>
+        <v>5175</v>
       </c>
       <c r="AF38">
-        <v>1636.17</v>
+        <v>1577.34</v>
       </c>
       <c r="AG38">
         <v>39.735</v>
@@ -6381,16 +6375,16 @@
         <v>-103.2911666667</v>
       </c>
       <c r="AI38">
-        <v>40.84</v>
+        <v>40.85</v>
       </c>
       <c r="AJ38">
-        <v>65.73</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="AK38">
-        <v>4971</v>
+        <v>4969</v>
       </c>
       <c r="AL38">
-        <v>1515.16</v>
+        <v>1514.55</v>
       </c>
     </row>
     <row r="39" spans="1:38">
@@ -6422,7 +6416,7 @@
         <v>24134.98</v>
       </c>
       <c r="J39">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K39" t="s">
         <v>480</v>
@@ -6434,7 +6428,7 @@
         <v>56.25</v>
       </c>
       <c r="N39">
-        <v>90.52</v>
+        <v>90.53</v>
       </c>
       <c r="O39">
         <v>13.95</v>
@@ -6479,16 +6473,16 @@
         <v>12.49</v>
       </c>
       <c r="AC39">
-        <v>39.6085166667</v>
+        <v>39.6081833333</v>
       </c>
       <c r="AD39">
-        <v>-104.0422166667</v>
+        <v>-104.0423166667</v>
       </c>
       <c r="AE39">
-        <v>5434</v>
+        <v>5237</v>
       </c>
       <c r="AF39">
-        <v>1656.28</v>
+        <v>1596.24</v>
       </c>
       <c r="AG39">
         <v>39.5215</v>
@@ -6500,13 +6494,13 @@
         <v>56.25</v>
       </c>
       <c r="AJ39">
-        <v>90.52</v>
+        <v>90.53</v>
       </c>
       <c r="AK39">
-        <v>4713</v>
+        <v>4717</v>
       </c>
       <c r="AL39">
-        <v>1436.52</v>
+        <v>1437.74</v>
       </c>
     </row>
     <row r="40" spans="1:38">
@@ -6538,19 +6532,19 @@
         <v>30659.53</v>
       </c>
       <c r="J40">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K40" t="s">
-        <v>465</v>
+        <v>481</v>
       </c>
       <c r="L40">
-        <v>6990</v>
+        <v>7009</v>
       </c>
       <c r="M40">
-        <v>80.22</v>
+        <v>80.23</v>
       </c>
       <c r="N40">
-        <v>129.1</v>
+        <v>129.12</v>
       </c>
       <c r="O40">
         <v>12.12</v>
@@ -6595,16 +6589,16 @@
         <v>10.47</v>
       </c>
       <c r="AC40">
-        <v>39.6078333333</v>
+        <v>39.6077666667</v>
       </c>
       <c r="AD40">
-        <v>-104.0415</v>
+        <v>-104.04185</v>
       </c>
       <c r="AE40">
-        <v>5366</v>
+        <v>5217</v>
       </c>
       <c r="AF40">
-        <v>1635.56</v>
+        <v>1590.14</v>
       </c>
       <c r="AG40">
         <v>38.8346666667</v>
@@ -6613,10 +6607,10 @@
         <v>-102.922</v>
       </c>
       <c r="AI40">
-        <v>80.22</v>
+        <v>80.23</v>
       </c>
       <c r="AJ40">
-        <v>129.1</v>
+        <v>129.12</v>
       </c>
       <c r="AK40">
         <v>5042</v>
@@ -6657,16 +6651,16 @@
         <v>486</v>
       </c>
       <c r="K41" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L41">
-        <v>5052</v>
+        <v>5055</v>
       </c>
       <c r="M41">
-        <v>64.63</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="N41">
-        <v>104.01</v>
+        <v>104.04</v>
       </c>
       <c r="O41">
         <v>14.39</v>
@@ -6711,34 +6705,34 @@
         <v>12.73</v>
       </c>
       <c r="AC41">
-        <v>39.6078333333</v>
+        <v>39.6076666667</v>
       </c>
       <c r="AD41">
-        <v>-104.0415</v>
+        <v>-104.0418333333</v>
       </c>
       <c r="AE41">
-        <v>5285</v>
+        <v>5225</v>
       </c>
       <c r="AF41">
-        <v>1610.87</v>
+        <v>1592.58</v>
       </c>
       <c r="AG41">
-        <v>38.9044166667</v>
+        <v>38.9043333333</v>
       </c>
       <c r="AH41">
-        <v>-103.2439</v>
+        <v>-103.2436666667</v>
       </c>
       <c r="AI41">
-        <v>64.63</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="AJ41">
-        <v>104.01</v>
+        <v>104.04</v>
       </c>
       <c r="AK41">
-        <v>4689</v>
+        <v>4686</v>
       </c>
       <c r="AL41">
-        <v>1429.21</v>
+        <v>1428.29</v>
       </c>
     </row>
     <row r="42" spans="1:38">
@@ -6770,19 +6764,19 @@
         <v>26498.4</v>
       </c>
       <c r="J42">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="K42" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L42">
-        <v>6671</v>
+        <v>6720</v>
       </c>
       <c r="M42">
-        <v>47.85</v>
+        <v>47.82</v>
       </c>
       <c r="N42">
-        <v>77</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="O42">
         <v>4.93</v>
@@ -6827,34 +6821,34 @@
         <v>7.98</v>
       </c>
       <c r="AC42">
-        <v>39.6085</v>
+        <v>39.6083666667</v>
       </c>
       <c r="AD42">
-        <v>-104.042</v>
+        <v>-104.04205</v>
       </c>
       <c r="AE42">
-        <v>5396</v>
+        <v>5240</v>
       </c>
       <c r="AF42">
-        <v>1644.7</v>
+        <v>1597.15</v>
       </c>
       <c r="AG42">
-        <v>39.6008166667</v>
+        <v>39.6019666667</v>
       </c>
       <c r="AH42">
-        <v>-103.1426166667</v>
+        <v>-103.14315</v>
       </c>
       <c r="AI42">
-        <v>47.85</v>
+        <v>47.82</v>
       </c>
       <c r="AJ42">
-        <v>77</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="AK42">
-        <v>5460</v>
+        <v>5027</v>
       </c>
       <c r="AL42">
-        <v>1664.21</v>
+        <v>1532.23</v>
       </c>
     </row>
     <row r="43" spans="1:38">
@@ -6886,19 +6880,19 @@
         <v>29330.6</v>
       </c>
       <c r="J43">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K43" t="s">
-        <v>483</v>
+        <v>462</v>
       </c>
       <c r="L43">
-        <v>7721</v>
+        <v>7770</v>
       </c>
       <c r="M43">
-        <v>38.55</v>
+        <v>38.64</v>
       </c>
       <c r="N43">
-        <v>62.03</v>
+        <v>62.19</v>
       </c>
       <c r="O43">
         <v>1.02</v>
@@ -6943,34 +6937,34 @@
         <v>6.79</v>
       </c>
       <c r="AC43">
-        <v>39.6073333333</v>
+        <v>39.6074</v>
       </c>
       <c r="AD43">
-        <v>-104.0398333333</v>
+        <v>-104.04015</v>
       </c>
       <c r="AE43">
-        <v>5417</v>
+        <v>5224</v>
       </c>
       <c r="AF43">
-        <v>1651.1</v>
+        <v>1592.28</v>
       </c>
       <c r="AG43">
-        <v>39.3150333333</v>
+        <v>39.3128333333</v>
       </c>
       <c r="AH43">
-        <v>-103.4237666667</v>
+        <v>-103.4238333333</v>
       </c>
       <c r="AI43">
-        <v>38.55</v>
+        <v>38.64</v>
       </c>
       <c r="AJ43">
-        <v>62.03</v>
+        <v>62.19</v>
       </c>
       <c r="AK43">
-        <v>6287</v>
+        <v>5821</v>
       </c>
       <c r="AL43">
-        <v>1916.28</v>
+        <v>1774.24</v>
       </c>
     </row>
     <row r="44" spans="1:38">
@@ -7002,19 +6996,19 @@
         <v>31116.12</v>
       </c>
       <c r="J44">
-        <v>390</v>
+        <v>492</v>
       </c>
       <c r="K44" t="s">
         <v>484</v>
       </c>
       <c r="L44">
-        <v>5936</v>
+        <v>7594</v>
       </c>
       <c r="M44">
-        <v>7.52</v>
+        <v>7.51</v>
       </c>
       <c r="N44">
-        <v>12.1</v>
+        <v>12.09</v>
       </c>
       <c r="O44">
         <v>7.52</v>
@@ -7059,34 +7053,34 @@
         <v>8.25</v>
       </c>
       <c r="AC44">
-        <v>39.236</v>
+        <v>39.2362166667</v>
       </c>
       <c r="AD44">
-        <v>-103.697</v>
+        <v>-103.6967666667</v>
       </c>
       <c r="AE44">
-        <v>5391</v>
+        <v>5362</v>
       </c>
       <c r="AF44">
-        <v>1643.18</v>
+        <v>1634.34</v>
       </c>
       <c r="AG44">
-        <v>39.1517833333</v>
+        <v>39.1518333333</v>
       </c>
       <c r="AH44">
-        <v>-103.6078666667</v>
+        <v>-103.6081666667</v>
       </c>
       <c r="AI44">
-        <v>7.52</v>
+        <v>7.51</v>
       </c>
       <c r="AJ44">
-        <v>12.1</v>
+        <v>12.09</v>
       </c>
       <c r="AK44">
-        <v>5496</v>
+        <v>5509</v>
       </c>
       <c r="AL44">
-        <v>1675.18</v>
+        <v>1679.14</v>
       </c>
     </row>
     <row r="45" spans="1:38">
@@ -7118,19 +7112,19 @@
         <v>31472.73</v>
       </c>
       <c r="J45">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K45" t="s">
         <v>485</v>
       </c>
       <c r="L45">
-        <v>6600</v>
+        <v>6626</v>
       </c>
       <c r="M45">
-        <v>32.05</v>
+        <v>32.03</v>
       </c>
       <c r="N45">
-        <v>51.57</v>
+        <v>51.55</v>
       </c>
       <c r="O45">
         <v>8.07</v>
@@ -7175,16 +7169,16 @@
         <v>9.19</v>
       </c>
       <c r="AC45">
-        <v>39.2783666667</v>
+        <v>39.278</v>
       </c>
       <c r="AD45">
-        <v>-103.4952333333</v>
+        <v>-103.4956666667</v>
       </c>
       <c r="AE45">
-        <v>5713</v>
+        <v>5652</v>
       </c>
       <c r="AF45">
-        <v>1741.32</v>
+        <v>1722.73</v>
       </c>
       <c r="AG45">
         <v>38.8373</v>
@@ -7193,10 +7187,10 @@
         <v>-103.30915</v>
       </c>
       <c r="AI45">
-        <v>32.05</v>
+        <v>32.03</v>
       </c>
       <c r="AJ45">
-        <v>51.57</v>
+        <v>51.55</v>
       </c>
       <c r="AK45">
         <v>9506</v>
@@ -7234,19 +7228,19 @@
         <v>24002.7</v>
       </c>
       <c r="J46">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K46" t="s">
         <v>486</v>
       </c>
       <c r="L46">
-        <v>6319</v>
+        <v>6915</v>
       </c>
       <c r="M46">
-        <v>37.98</v>
+        <v>39.94</v>
       </c>
       <c r="N46">
-        <v>61.12</v>
+        <v>64.27</v>
       </c>
       <c r="O46">
         <v>3.13</v>
@@ -7297,28 +7291,28 @@
         <v>-86.64700000000001</v>
       </c>
       <c r="AE46">
-        <v>741</v>
+        <v>705</v>
       </c>
       <c r="AF46">
-        <v>225.86</v>
+        <v>214.88</v>
       </c>
       <c r="AG46">
-        <v>34.4031166667</v>
+        <v>34.3866833333</v>
       </c>
       <c r="AH46">
-        <v>-86.1054833333</v>
+        <v>-86.07745</v>
       </c>
       <c r="AI46">
-        <v>37.98</v>
+        <v>39.94</v>
       </c>
       <c r="AJ46">
-        <v>61.12</v>
+        <v>64.27</v>
       </c>
       <c r="AK46">
-        <v>14794</v>
+        <v>9711</v>
       </c>
       <c r="AL46">
-        <v>4509.21</v>
+        <v>2959.91</v>
       </c>
     </row>
     <row r="47" spans="1:38">
@@ -7350,7 +7344,7 @@
         <v>30852.77</v>
       </c>
       <c r="J47">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K47" t="s">
         <v>487</v>
@@ -7359,10 +7353,10 @@
         <v>6390</v>
       </c>
       <c r="M47">
-        <v>41.2</v>
+        <v>41.19</v>
       </c>
       <c r="N47">
-        <v>66.31</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="O47">
         <v>5.58</v>
@@ -7407,28 +7401,28 @@
         <v>7.05</v>
       </c>
       <c r="AC47">
-        <v>40.2265</v>
+        <v>40.2264833333</v>
       </c>
       <c r="AD47">
-        <v>-104.0778333333</v>
+        <v>-104.0778833333</v>
       </c>
       <c r="AE47">
-        <v>4721</v>
+        <v>4561</v>
       </c>
       <c r="AF47">
-        <v>1438.96</v>
+        <v>1390.19</v>
       </c>
       <c r="AG47">
-        <v>40.5656666667</v>
+        <v>40.56565</v>
       </c>
       <c r="AH47">
-        <v>-104.7225</v>
+        <v>-104.7223833333</v>
       </c>
       <c r="AI47">
-        <v>41.2</v>
+        <v>41.19</v>
       </c>
       <c r="AJ47">
-        <v>66.31</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="AK47">
         <v>4915</v>
@@ -7466,19 +7460,19 @@
         <v>25859.54</v>
       </c>
       <c r="J48">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K48" t="s">
         <v>488</v>
       </c>
       <c r="L48">
-        <v>7710</v>
+        <v>7497</v>
       </c>
       <c r="M48">
-        <v>37.69</v>
+        <v>37.99</v>
       </c>
       <c r="N48">
-        <v>60.65</v>
+        <v>61.14</v>
       </c>
       <c r="O48">
         <v>2.8</v>
@@ -7523,34 +7517,34 @@
         <v>5.83</v>
       </c>
       <c r="AC48">
-        <v>39.7588166667</v>
+        <v>39.7555</v>
       </c>
       <c r="AD48">
-        <v>-104.9900666667</v>
+        <v>-104.994</v>
       </c>
       <c r="AE48">
-        <v>6661</v>
+        <v>5729</v>
       </c>
       <c r="AF48">
-        <v>2030.27</v>
+        <v>1746.2</v>
       </c>
       <c r="AG48">
         <v>40.07435</v>
       </c>
       <c r="AH48">
-        <v>-104.4093666667</v>
+        <v>-104.40935</v>
       </c>
       <c r="AI48">
-        <v>37.69</v>
+        <v>37.99</v>
       </c>
       <c r="AJ48">
-        <v>60.65</v>
+        <v>61.14</v>
       </c>
       <c r="AK48">
-        <v>4837</v>
+        <v>4823</v>
       </c>
       <c r="AL48">
-        <v>1474.32</v>
+        <v>1470.05</v>
       </c>
     </row>
     <row r="49" spans="1:38">
@@ -7582,19 +7576,19 @@
         <v>28050.44</v>
       </c>
       <c r="J49">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="K49" t="s">
         <v>489</v>
       </c>
       <c r="L49">
-        <v>7440</v>
+        <v>7470</v>
       </c>
       <c r="M49">
-        <v>71.73</v>
+        <v>71.75</v>
       </c>
       <c r="N49">
-        <v>115.44</v>
+        <v>115.48</v>
       </c>
       <c r="O49">
         <v>6.01</v>
@@ -7639,34 +7633,34 @@
         <v>7.53</v>
       </c>
       <c r="AC49">
-        <v>39.6075</v>
+        <v>39.60775</v>
       </c>
       <c r="AD49">
-        <v>-104.0411666667</v>
+        <v>-104.0412833333</v>
       </c>
       <c r="AE49">
-        <v>5443</v>
+        <v>5234</v>
       </c>
       <c r="AF49">
-        <v>1659.03</v>
+        <v>1595.32</v>
       </c>
       <c r="AG49">
-        <v>39.1121666667</v>
+        <v>39.11175</v>
       </c>
       <c r="AH49">
-        <v>-102.86</v>
+        <v>-102.86015</v>
       </c>
       <c r="AI49">
-        <v>71.73</v>
+        <v>71.75</v>
       </c>
       <c r="AJ49">
-        <v>115.44</v>
+        <v>115.48</v>
       </c>
       <c r="AK49">
-        <v>5143</v>
+        <v>4945</v>
       </c>
       <c r="AL49">
-        <v>1567.59</v>
+        <v>1507.24</v>
       </c>
     </row>
     <row r="50" spans="1:38">
@@ -7698,19 +7692,19 @@
         <v>29633.57</v>
       </c>
       <c r="J50">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="K50" t="s">
         <v>490</v>
       </c>
       <c r="L50">
-        <v>7980</v>
+        <v>7947</v>
       </c>
       <c r="M50">
-        <v>76.06</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="N50">
-        <v>122.4</v>
+        <v>122.42</v>
       </c>
       <c r="O50">
         <v>7.16</v>
@@ -7755,34 +7749,34 @@
         <v>8.210000000000001</v>
       </c>
       <c r="AC50">
-        <v>39.6075833333</v>
+        <v>39.6078333333</v>
       </c>
       <c r="AD50">
-        <v>-104.0413166667</v>
+        <v>-104.0413333333</v>
       </c>
       <c r="AE50">
-        <v>5335</v>
+        <v>5237</v>
       </c>
       <c r="AF50">
-        <v>1626.11</v>
+        <v>1596.24</v>
       </c>
       <c r="AG50">
         <v>39.0711</v>
       </c>
       <c r="AH50">
-        <v>-102.7973166667</v>
+        <v>-102.7973333333</v>
       </c>
       <c r="AI50">
-        <v>76.06</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="AJ50">
-        <v>122.4</v>
+        <v>122.42</v>
       </c>
       <c r="AK50">
-        <v>4761</v>
+        <v>4764</v>
       </c>
       <c r="AL50">
-        <v>1451.15</v>
+        <v>1452.07</v>
       </c>
     </row>
     <row r="51" spans="1:38">
@@ -7814,19 +7808,19 @@
         <v>32055.82</v>
       </c>
       <c r="J51">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="K51" t="s">
         <v>491</v>
       </c>
       <c r="L51">
-        <v>7050</v>
+        <v>7080</v>
       </c>
       <c r="M51">
-        <v>54.25</v>
+        <v>54.23</v>
       </c>
       <c r="N51">
-        <v>87.3</v>
+        <v>87.28</v>
       </c>
       <c r="O51">
         <v>15</v>
@@ -7871,16 +7865,16 @@
         <v>11.95</v>
       </c>
       <c r="AC51">
-        <v>39.6085</v>
+        <v>39.6081666667</v>
       </c>
       <c r="AD51">
         <v>-104.0425</v>
       </c>
       <c r="AE51">
-        <v>5334</v>
+        <v>5212</v>
       </c>
       <c r="AF51">
-        <v>1625.8</v>
+        <v>1588.62</v>
       </c>
       <c r="AG51">
         <v>39.2156666667</v>
@@ -7889,10 +7883,10 @@
         <v>-103.1618333333</v>
       </c>
       <c r="AI51">
-        <v>54.25</v>
+        <v>54.23</v>
       </c>
       <c r="AJ51">
-        <v>87.3</v>
+        <v>87.28</v>
       </c>
       <c r="AK51">
         <v>5740</v>
@@ -7936,13 +7930,13 @@
         <v>492</v>
       </c>
       <c r="L52">
-        <v>5231</v>
+        <v>5239</v>
       </c>
       <c r="M52">
         <v>81.72</v>
       </c>
       <c r="N52">
-        <v>131.51</v>
+        <v>131.52</v>
       </c>
       <c r="O52">
         <v>5.38</v>
@@ -7987,34 +7981,34 @@
         <v>7.42</v>
       </c>
       <c r="AC52">
-        <v>39.6083333333</v>
+        <v>39.6083</v>
       </c>
       <c r="AD52">
-        <v>-104.0425</v>
+        <v>-104.0425833333</v>
       </c>
       <c r="AE52">
-        <v>5367</v>
+        <v>5224</v>
       </c>
       <c r="AF52">
-        <v>1635.86</v>
+        <v>1592.28</v>
       </c>
       <c r="AG52">
-        <v>39.48805</v>
+        <v>39.4881666667</v>
       </c>
       <c r="AH52">
-        <v>-102.51555</v>
+        <v>-102.5155</v>
       </c>
       <c r="AI52">
         <v>81.72</v>
       </c>
       <c r="AJ52">
-        <v>131.51</v>
+        <v>131.52</v>
       </c>
       <c r="AK52">
-        <v>4075</v>
+        <v>4042</v>
       </c>
       <c r="AL52">
-        <v>1242.06</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="53" spans="1:38">
@@ -8052,13 +8046,13 @@
         <v>493</v>
       </c>
       <c r="L53">
-        <v>7323</v>
+        <v>7320</v>
       </c>
       <c r="M53">
-        <v>80.5</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="N53">
-        <v>129.55</v>
+        <v>129.53</v>
       </c>
       <c r="O53">
         <v>12.61</v>
@@ -8103,16 +8097,16 @@
         <v>10.65</v>
       </c>
       <c r="AC53">
-        <v>39.6083</v>
+        <v>39.6081666667</v>
       </c>
       <c r="AD53">
-        <v>-104.0426666667</v>
+        <v>-104.0425</v>
       </c>
       <c r="AE53">
-        <v>5234</v>
+        <v>5203</v>
       </c>
       <c r="AF53">
-        <v>1595.32</v>
+        <v>1585.87</v>
       </c>
       <c r="AG53">
         <v>39.4588333333</v>
@@ -8121,10 +8115,10 @@
         <v>-102.5435</v>
       </c>
       <c r="AI53">
-        <v>80.5</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="AJ53">
-        <v>129.55</v>
+        <v>129.53</v>
       </c>
       <c r="AK53">
         <v>4646</v>
@@ -8162,19 +8156,19 @@
         <v>31589.17</v>
       </c>
       <c r="J54">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="K54" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="L54">
-        <v>6371</v>
+        <v>6390</v>
       </c>
       <c r="M54">
         <v>56.46</v>
       </c>
       <c r="N54">
-        <v>90.86</v>
+        <v>90.87</v>
       </c>
       <c r="O54">
         <v>8.23</v>
@@ -8225,28 +8219,28 @@
         <v>-104.0421666667</v>
       </c>
       <c r="AE54">
-        <v>5388</v>
+        <v>5197</v>
       </c>
       <c r="AF54">
-        <v>1642.26</v>
+        <v>1584.05</v>
       </c>
       <c r="AG54">
-        <v>39.8818166667</v>
+        <v>39.8815</v>
       </c>
       <c r="AH54">
-        <v>-103.0400833333</v>
+        <v>-103.0398333333</v>
       </c>
       <c r="AI54">
         <v>56.46</v>
       </c>
       <c r="AJ54">
-        <v>90.86</v>
+        <v>90.87</v>
       </c>
       <c r="AK54">
-        <v>6891</v>
+        <v>6833</v>
       </c>
       <c r="AL54">
-        <v>2100.38</v>
+        <v>2082.7</v>
       </c>
     </row>
     <row r="55" spans="1:38">
@@ -8278,19 +8272,19 @@
         <v>26277.11</v>
       </c>
       <c r="J55">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K55" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="L55">
-        <v>7168</v>
+        <v>7192</v>
       </c>
       <c r="M55">
-        <v>75.56999999999999</v>
+        <v>75.56</v>
       </c>
       <c r="N55">
-        <v>121.63</v>
+        <v>121.6</v>
       </c>
       <c r="O55">
         <v>7.46</v>
@@ -8335,16 +8329,16 @@
         <v>8.08</v>
       </c>
       <c r="AC55">
-        <v>39.6083333333</v>
+        <v>39.6081666667</v>
       </c>
       <c r="AD55">
-        <v>-104.0423333333</v>
+        <v>-104.042</v>
       </c>
       <c r="AE55">
-        <v>5251</v>
+        <v>5215</v>
       </c>
       <c r="AF55">
-        <v>1600.5</v>
+        <v>1589.53</v>
       </c>
       <c r="AG55">
         <v>39.7735</v>
@@ -8353,10 +8347,10 @@
         <v>-102.6361666667</v>
       </c>
       <c r="AI55">
-        <v>75.56999999999999</v>
+        <v>75.56</v>
       </c>
       <c r="AJ55">
-        <v>121.63</v>
+        <v>121.6</v>
       </c>
       <c r="AK55">
         <v>5519</v>
@@ -8394,19 +8388,19 @@
         <v>28106.52</v>
       </c>
       <c r="J56">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K56" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="L56">
-        <v>6521</v>
+        <v>6559</v>
       </c>
       <c r="M56">
         <v>62.99</v>
       </c>
       <c r="N56">
-        <v>101.37</v>
+        <v>101.38</v>
       </c>
       <c r="O56">
         <v>8.529999999999999</v>
@@ -8451,34 +8445,34 @@
         <v>8.210000000000001</v>
       </c>
       <c r="AC56">
-        <v>39.6086666667</v>
+        <v>39.60845</v>
       </c>
       <c r="AD56">
-        <v>-104.0423333333</v>
+        <v>-104.0420833333</v>
       </c>
       <c r="AE56">
-        <v>5389</v>
+        <v>5240</v>
       </c>
       <c r="AF56">
-        <v>1642.57</v>
+        <v>1597.15</v>
       </c>
       <c r="AG56">
-        <v>39.6407833333</v>
+        <v>39.6406666667</v>
       </c>
       <c r="AH56">
-        <v>-102.8586666667</v>
+        <v>-102.8583333333</v>
       </c>
       <c r="AI56">
         <v>62.99</v>
       </c>
       <c r="AJ56">
-        <v>101.37</v>
+        <v>101.38</v>
       </c>
       <c r="AK56">
-        <v>5713</v>
+        <v>5368</v>
       </c>
       <c r="AL56">
-        <v>1741.32</v>
+        <v>1636.17</v>
       </c>
     </row>
     <row r="57" spans="1:38">
@@ -8510,19 +8504,19 @@
         <v>29048.35</v>
       </c>
       <c r="J57">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="K57" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="L57">
-        <v>7413</v>
+        <v>7470</v>
       </c>
       <c r="M57">
-        <v>70.08</v>
+        <v>70.06</v>
       </c>
       <c r="N57">
-        <v>112.79</v>
+        <v>112.75</v>
       </c>
       <c r="O57">
         <v>5.02</v>
@@ -8567,34 +8561,34 @@
         <v>6.72</v>
       </c>
       <c r="AC57">
-        <v>39.6087666667</v>
+        <v>39.6084666667</v>
       </c>
       <c r="AD57">
-        <v>-104.0423166667</v>
+        <v>-104.0421166667</v>
       </c>
       <c r="AE57">
-        <v>5312</v>
+        <v>5204</v>
       </c>
       <c r="AF57">
-        <v>1619.1</v>
+        <v>1586.18</v>
       </c>
       <c r="AG57">
         <v>39.6068333333</v>
       </c>
       <c r="AH57">
-        <v>-102.7248333333</v>
+        <v>-102.7250333333</v>
       </c>
       <c r="AI57">
-        <v>70.08</v>
+        <v>70.06</v>
       </c>
       <c r="AJ57">
-        <v>112.79</v>
+        <v>112.75</v>
       </c>
       <c r="AK57">
-        <v>4310</v>
+        <v>4354</v>
       </c>
       <c r="AL57">
-        <v>1313.69</v>
+        <v>1327.1</v>
       </c>
     </row>
     <row r="58" spans="1:38">
@@ -8626,19 +8620,19 @@
         <v>33886.75</v>
       </c>
       <c r="J58">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="K58" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="L58">
-        <v>7512</v>
+        <v>7545</v>
       </c>
       <c r="M58">
-        <v>76.73</v>
+        <v>76.70999999999999</v>
       </c>
       <c r="N58">
-        <v>123.49</v>
+        <v>123.45</v>
       </c>
       <c r="O58">
         <v>11.26</v>
@@ -8683,34 +8677,34 @@
         <v>10.8</v>
       </c>
       <c r="AC58">
-        <v>39.6078333333</v>
+        <v>39.6073333333</v>
       </c>
       <c r="AD58">
-        <v>-104.0413333333</v>
+        <v>-104.041</v>
       </c>
       <c r="AE58">
-        <v>5340</v>
+        <v>5223</v>
       </c>
       <c r="AF58">
-        <v>1627.63</v>
+        <v>1591.97</v>
       </c>
       <c r="AG58">
-        <v>39.1830333333</v>
+        <v>39.1841666667</v>
       </c>
       <c r="AH58">
-        <v>-102.7124166667</v>
+        <v>-102.7116666667</v>
       </c>
       <c r="AI58">
-        <v>76.73</v>
+        <v>76.70999999999999</v>
       </c>
       <c r="AJ58">
-        <v>123.49</v>
+        <v>123.45</v>
       </c>
       <c r="AK58">
-        <v>5060</v>
+        <v>4727</v>
       </c>
       <c r="AL58">
-        <v>1542.29</v>
+        <v>1440.79</v>
       </c>
     </row>
     <row r="59" spans="1:38">
@@ -8742,19 +8736,19 @@
         <v>31058.82</v>
       </c>
       <c r="J59">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="K59" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L59">
-        <v>6507</v>
+        <v>6540</v>
       </c>
       <c r="M59">
-        <v>34.24</v>
+        <v>34.25</v>
       </c>
       <c r="N59">
-        <v>55.11</v>
+        <v>55.13</v>
       </c>
       <c r="O59">
         <v>15.87</v>
@@ -8799,16 +8793,16 @@
         <v>12.44</v>
       </c>
       <c r="AC59">
-        <v>39.6083333333</v>
+        <v>39.6083833333</v>
       </c>
       <c r="AD59">
-        <v>-104.042</v>
+        <v>-104.0422333333</v>
       </c>
       <c r="AE59">
-        <v>5284</v>
+        <v>5214</v>
       </c>
       <c r="AF59">
-        <v>1610.56</v>
+        <v>1589.23</v>
       </c>
       <c r="AG59">
         <v>39.8047333333</v>
@@ -8817,10 +8811,10 @@
         <v>-103.4500166667</v>
       </c>
       <c r="AI59">
-        <v>34.24</v>
+        <v>34.25</v>
       </c>
       <c r="AJ59">
-        <v>55.11</v>
+        <v>55.13</v>
       </c>
       <c r="AK59">
         <v>4718</v>
@@ -8861,10 +8855,10 @@
         <v>677</v>
       </c>
       <c r="K60" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="L60">
-        <v>6885</v>
+        <v>6870</v>
       </c>
       <c r="M60">
         <v>51.37</v>
@@ -8915,22 +8909,22 @@
         <v>8.5</v>
       </c>
       <c r="AC60">
-        <v>39.6081666667</v>
+        <v>39.6080333333</v>
       </c>
       <c r="AD60">
         <v>-104.0421666667</v>
       </c>
       <c r="AE60">
-        <v>5246</v>
+        <v>5211</v>
       </c>
       <c r="AF60">
-        <v>1598.98</v>
+        <v>1588.31</v>
       </c>
       <c r="AG60">
-        <v>39.412</v>
+        <v>39.4121666667</v>
       </c>
       <c r="AH60">
-        <v>-103.112</v>
+        <v>-103.1118666667</v>
       </c>
       <c r="AI60">
         <v>51.37</v>
@@ -8939,10 +8933,10 @@
         <v>82.67</v>
       </c>
       <c r="AK60">
-        <v>4911</v>
+        <v>4902</v>
       </c>
       <c r="AL60">
-        <v>1496.87</v>
+        <v>1494.13</v>
       </c>
     </row>
     <row r="61" spans="1:38">
@@ -8974,19 +8968,19 @@
         <v>26934.87</v>
       </c>
       <c r="J61">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="K61" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="L61">
-        <v>9683</v>
+        <v>9365</v>
       </c>
       <c r="M61">
-        <v>19</v>
+        <v>19.24</v>
       </c>
       <c r="N61">
-        <v>30.58</v>
+        <v>30.97</v>
       </c>
       <c r="O61">
         <v>6.89</v>
@@ -9031,34 +9025,34 @@
         <v>7.86</v>
       </c>
       <c r="AC61">
-        <v>39.2788333333</v>
+        <v>39.2781666667</v>
       </c>
       <c r="AD61">
-        <v>-103.4953333333</v>
+        <v>-103.4955</v>
       </c>
       <c r="AE61">
-        <v>5830</v>
+        <v>5640</v>
       </c>
       <c r="AF61">
-        <v>1776.98</v>
+        <v>1719.07</v>
       </c>
       <c r="AG61">
-        <v>39.0613333333</v>
+        <v>39.0551666667</v>
       </c>
       <c r="AH61">
-        <v>-103.2778333333</v>
+        <v>-103.2798333333</v>
       </c>
       <c r="AI61">
-        <v>19</v>
+        <v>19.24</v>
       </c>
       <c r="AJ61">
-        <v>30.58</v>
+        <v>30.97</v>
       </c>
       <c r="AK61">
-        <v>5119</v>
+        <v>5620</v>
       </c>
       <c r="AL61">
-        <v>1560.27</v>
+        <v>1712.98</v>
       </c>
     </row>
     <row r="62" spans="1:38">
@@ -9093,16 +9087,16 @@
         <v>480</v>
       </c>
       <c r="K62" t="s">
-        <v>502</v>
+        <v>475</v>
       </c>
       <c r="L62">
-        <v>8340</v>
+        <v>8280</v>
       </c>
       <c r="M62">
-        <v>13.41</v>
+        <v>13.4</v>
       </c>
       <c r="N62">
-        <v>21.58</v>
+        <v>21.57</v>
       </c>
       <c r="O62">
         <v>8.32</v>
@@ -9147,34 +9141,34 @@
         <v>7.83</v>
       </c>
       <c r="AC62">
-        <v>39.2779</v>
+        <v>39.2779833333</v>
       </c>
       <c r="AD62">
         <v>-103.4955333333</v>
       </c>
       <c r="AE62">
-        <v>5677</v>
+        <v>5582</v>
       </c>
       <c r="AF62">
-        <v>1730.35</v>
+        <v>1701.39</v>
       </c>
       <c r="AG62">
-        <v>39.0890666667</v>
+        <v>39.0892833333</v>
       </c>
       <c r="AH62">
-        <v>-103.43705</v>
+        <v>-103.4370166667</v>
       </c>
       <c r="AI62">
-        <v>13.41</v>
+        <v>13.4</v>
       </c>
       <c r="AJ62">
-        <v>21.58</v>
+        <v>21.57</v>
       </c>
       <c r="AK62">
-        <v>4968</v>
+        <v>4977</v>
       </c>
       <c r="AL62">
-        <v>1514.25</v>
+        <v>1516.99</v>
       </c>
     </row>
     <row r="63" spans="1:38">
@@ -9209,16 +9203,16 @@
         <v>432</v>
       </c>
       <c r="K63" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="L63">
-        <v>7661</v>
+        <v>7669</v>
       </c>
       <c r="M63">
-        <v>11.38</v>
+        <v>11.34</v>
       </c>
       <c r="N63">
-        <v>18.31</v>
+        <v>18.25</v>
       </c>
       <c r="O63">
         <v>6.61</v>
@@ -9263,34 +9257,34 @@
         <v>6.9</v>
       </c>
       <c r="AC63">
-        <v>39.2786666667</v>
+        <v>39.27815</v>
       </c>
       <c r="AD63">
-        <v>-103.4953333333</v>
+        <v>-103.4954666667</v>
       </c>
       <c r="AE63">
-        <v>5774</v>
+        <v>5611</v>
       </c>
       <c r="AF63">
-        <v>1759.92</v>
+        <v>1710.23</v>
       </c>
       <c r="AG63">
-        <v>39.1167166667</v>
+        <v>39.1168333333</v>
       </c>
       <c r="AH63">
-        <v>-103.4558666667</v>
+        <v>-103.4558333333</v>
       </c>
       <c r="AI63">
-        <v>11.38</v>
+        <v>11.34</v>
       </c>
       <c r="AJ63">
-        <v>18.31</v>
+        <v>18.25</v>
       </c>
       <c r="AK63">
-        <v>5020</v>
+        <v>5041</v>
       </c>
       <c r="AL63">
-        <v>1530.1</v>
+        <v>1536.5</v>
       </c>
     </row>
     <row r="64" spans="1:38">
@@ -9322,19 +9316,19 @@
         <v>28398.22</v>
       </c>
       <c r="J64">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="K64" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="L64">
-        <v>7590</v>
+        <v>7680</v>
       </c>
       <c r="M64">
-        <v>35.52</v>
+        <v>35.54</v>
       </c>
       <c r="N64">
-        <v>57.17</v>
+        <v>57.19</v>
       </c>
       <c r="O64">
         <v>7.52</v>
@@ -9379,34 +9373,34 @@
         <v>7.02</v>
       </c>
       <c r="AC64">
-        <v>39.6083166667</v>
+        <v>39.6083833333</v>
       </c>
       <c r="AD64">
-        <v>-104.0420166667</v>
+        <v>-104.0419666667</v>
       </c>
       <c r="AE64">
-        <v>5289</v>
+        <v>5226</v>
       </c>
       <c r="AF64">
-        <v>1612.09</v>
+        <v>1592.88</v>
       </c>
       <c r="AG64">
-        <v>39.7067</v>
+        <v>39.7059</v>
       </c>
       <c r="AH64">
-        <v>-103.3860333333</v>
+        <v>-103.3855666667</v>
       </c>
       <c r="AI64">
-        <v>35.52</v>
+        <v>35.54</v>
       </c>
       <c r="AJ64">
-        <v>57.17</v>
+        <v>57.19</v>
       </c>
       <c r="AK64">
-        <v>4701</v>
+        <v>4981</v>
       </c>
       <c r="AL64">
-        <v>1432.86</v>
+        <v>1518.21</v>
       </c>
     </row>
     <row r="65" spans="1:38">
@@ -9438,19 +9432,19 @@
         <v>28182.42</v>
       </c>
       <c r="J65">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="K65" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="L65">
-        <v>7792</v>
+        <v>7824</v>
       </c>
       <c r="M65">
-        <v>51.96</v>
+        <v>52.01</v>
       </c>
       <c r="N65">
-        <v>83.63</v>
+        <v>83.69</v>
       </c>
       <c r="O65">
         <v>8.619999999999999</v>
@@ -9495,16 +9489,16 @@
         <v>8.01</v>
       </c>
       <c r="AC65">
-        <v>39.6088333333</v>
+        <v>39.6076666667</v>
       </c>
       <c r="AD65">
-        <v>-104.04</v>
+        <v>-104.0413333333</v>
       </c>
       <c r="AE65">
-        <v>5691</v>
+        <v>5218</v>
       </c>
       <c r="AF65">
-        <v>1734.62</v>
+        <v>1590.45</v>
       </c>
       <c r="AG65">
         <v>39.3678333333</v>
@@ -9513,10 +9507,10 @@
         <v>-103.1161666667</v>
       </c>
       <c r="AI65">
-        <v>51.96</v>
+        <v>52.01</v>
       </c>
       <c r="AJ65">
-        <v>83.63</v>
+        <v>83.69</v>
       </c>
       <c r="AK65">
         <v>5425</v>
@@ -9554,19 +9548,19 @@
         <v>20625.82</v>
       </c>
       <c r="J66">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K66" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="L66">
-        <v>5580</v>
+        <v>5599</v>
       </c>
       <c r="M66">
-        <v>51.6</v>
+        <v>51.59</v>
       </c>
       <c r="N66">
-        <v>83.05</v>
+        <v>83.03</v>
       </c>
       <c r="O66">
         <v>4.78</v>
@@ -9611,16 +9605,16 @@
         <v>6.5</v>
       </c>
       <c r="AC66">
-        <v>39.608</v>
+        <v>39.6076666667</v>
       </c>
       <c r="AD66">
-        <v>-104.0413333333</v>
+        <v>-104.04115</v>
       </c>
       <c r="AE66">
-        <v>5270</v>
+        <v>5227</v>
       </c>
       <c r="AF66">
-        <v>1606.3</v>
+        <v>1593.19</v>
       </c>
       <c r="AG66">
         <v>39.4133333333</v>
@@ -9629,10 +9623,10 @@
         <v>-103.106</v>
       </c>
       <c r="AI66">
-        <v>51.6</v>
+        <v>51.59</v>
       </c>
       <c r="AJ66">
-        <v>83.05</v>
+        <v>83.03</v>
       </c>
       <c r="AK66">
         <v>4921</v>
@@ -9670,19 +9664,19 @@
         <v>28004.41</v>
       </c>
       <c r="J67">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="K67" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="L67">
-        <v>7230</v>
+        <v>7272</v>
       </c>
       <c r="M67">
-        <v>48.14</v>
+        <v>48.25</v>
       </c>
       <c r="N67">
-        <v>77.48</v>
+        <v>77.66</v>
       </c>
       <c r="O67">
         <v>7.5</v>
@@ -9727,34 +9721,34 @@
         <v>7.93</v>
       </c>
       <c r="AC67">
-        <v>39.6086333333</v>
+        <v>39.6077</v>
       </c>
       <c r="AD67">
-        <v>-104.0395833333</v>
+        <v>-104.0411333333</v>
       </c>
       <c r="AE67">
-        <v>5673</v>
+        <v>5214</v>
       </c>
       <c r="AF67">
-        <v>1729.13</v>
+        <v>1589.23</v>
       </c>
       <c r="AG67">
-        <v>39.3669166667</v>
+        <v>39.3671333333</v>
       </c>
       <c r="AH67">
-        <v>-103.1921333333</v>
+        <v>-103.1909333333</v>
       </c>
       <c r="AI67">
-        <v>48.14</v>
+        <v>48.25</v>
       </c>
       <c r="AJ67">
-        <v>77.48</v>
+        <v>77.66</v>
       </c>
       <c r="AK67">
-        <v>5436</v>
+        <v>5191</v>
       </c>
       <c r="AL67">
-        <v>1656.89</v>
+        <v>1582.22</v>
       </c>
     </row>
     <row r="68" spans="1:38">
@@ -9786,19 +9780,19 @@
         <v>28943.5</v>
       </c>
       <c r="J68">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="K68" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="L68">
-        <v>5850</v>
+        <v>5898</v>
       </c>
       <c r="M68">
-        <v>39.35</v>
+        <v>39.34</v>
       </c>
       <c r="N68">
-        <v>63.33</v>
+        <v>63.3</v>
       </c>
       <c r="O68">
         <v>14.77</v>
@@ -9843,16 +9837,16 @@
         <v>11.81</v>
       </c>
       <c r="AC68">
-        <v>39.6091666667</v>
+        <v>39.6085</v>
       </c>
       <c r="AD68">
-        <v>-104.042</v>
+        <v>-104.04235</v>
       </c>
       <c r="AE68">
-        <v>5646</v>
+        <v>5217</v>
       </c>
       <c r="AF68">
-        <v>1720.9</v>
+        <v>1590.14</v>
       </c>
       <c r="AG68">
         <v>39.2631666667</v>
@@ -9861,10 +9855,10 @@
         <v>-103.4556666667</v>
       </c>
       <c r="AI68">
-        <v>39.35</v>
+        <v>39.34</v>
       </c>
       <c r="AJ68">
-        <v>63.33</v>
+        <v>63.3</v>
       </c>
       <c r="AK68">
         <v>8248</v>
@@ -9902,19 +9896,19 @@
         <v>28393.64</v>
       </c>
       <c r="J69">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K69" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="L69">
-        <v>6960</v>
+        <v>6964</v>
       </c>
       <c r="M69">
-        <v>77.23</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="N69">
-        <v>124.28</v>
+        <v>124.31</v>
       </c>
       <c r="O69">
         <v>7.75</v>
@@ -9959,16 +9953,16 @@
         <v>8.84</v>
       </c>
       <c r="AC69">
-        <v>39.6080166667</v>
+        <v>39.6082333333</v>
       </c>
       <c r="AD69">
         <v>-104.0423</v>
       </c>
       <c r="AE69">
-        <v>5306</v>
+        <v>5234</v>
       </c>
       <c r="AF69">
-        <v>1617.27</v>
+        <v>1595.32</v>
       </c>
       <c r="AG69">
         <v>38.6113</v>
@@ -9977,10 +9971,10 @@
         <v>-103.3882</v>
       </c>
       <c r="AI69">
-        <v>77.23</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="AJ69">
-        <v>124.28</v>
+        <v>124.31</v>
       </c>
       <c r="AK69">
         <v>5141</v>
@@ -10018,19 +10012,19 @@
         <v>29202.89</v>
       </c>
       <c r="J70">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K70" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="L70">
-        <v>6963</v>
+        <v>6990</v>
       </c>
       <c r="M70">
-        <v>78.61</v>
+        <v>78.59</v>
       </c>
       <c r="N70">
-        <v>126.5</v>
+        <v>126.48</v>
       </c>
       <c r="O70">
         <v>13.12</v>
@@ -10075,16 +10069,16 @@
         <v>11.24</v>
       </c>
       <c r="AC70">
-        <v>39.6082</v>
+        <v>39.608</v>
       </c>
       <c r="AD70">
-        <v>-104.04225</v>
+        <v>-104.0421666667</v>
       </c>
       <c r="AE70">
-        <v>5296</v>
+        <v>5203</v>
       </c>
       <c r="AF70">
-        <v>1614.22</v>
+        <v>1585.87</v>
       </c>
       <c r="AG70">
         <v>38.5923333333</v>
@@ -10093,10 +10087,10 @@
         <v>-103.38</v>
       </c>
       <c r="AI70">
-        <v>78.61</v>
+        <v>78.59</v>
       </c>
       <c r="AJ70">
-        <v>126.5</v>
+        <v>126.48</v>
       </c>
       <c r="AK70">
         <v>5405</v>
@@ -10137,13 +10131,13 @@
         <v>507</v>
       </c>
       <c r="K71" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="L71">
-        <v>8130</v>
+        <v>8097</v>
       </c>
       <c r="M71">
-        <v>83.86</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="N71">
         <v>134.95</v>
@@ -10197,28 +10191,28 @@
         <v>-104.0418333333</v>
       </c>
       <c r="AE71">
-        <v>5205</v>
+        <v>5240</v>
       </c>
       <c r="AF71">
-        <v>1586.48</v>
+        <v>1597.15</v>
       </c>
       <c r="AG71">
-        <v>39.6491666667</v>
+        <v>39.6490166667</v>
       </c>
       <c r="AH71">
-        <v>-102.4658333333</v>
+        <v>-102.46585</v>
       </c>
       <c r="AI71">
-        <v>83.86</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="AJ71">
         <v>134.95</v>
       </c>
       <c r="AK71">
-        <v>4139</v>
+        <v>4164</v>
       </c>
       <c r="AL71">
-        <v>1261.57</v>
+        <v>1269.19</v>
       </c>
     </row>
     <row r="72" spans="1:38">
@@ -10250,19 +10244,19 @@
         <v>29960.62</v>
       </c>
       <c r="J72">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="K72" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="L72">
-        <v>7635</v>
+        <v>7668</v>
       </c>
       <c r="M72">
-        <v>41.86</v>
+        <v>41.87</v>
       </c>
       <c r="N72">
-        <v>67.37</v>
+        <v>67.38</v>
       </c>
       <c r="O72">
         <v>16.95</v>
@@ -10307,16 +10301,16 @@
         <v>13.21</v>
       </c>
       <c r="AC72">
-        <v>40.4735</v>
+        <v>40.4733333333</v>
       </c>
       <c r="AD72">
-        <v>-104.9626666667</v>
+        <v>-104.9627666667</v>
       </c>
       <c r="AE72">
-        <v>5042</v>
+        <v>4951</v>
       </c>
       <c r="AF72">
-        <v>1536.8</v>
+        <v>1509.06</v>
       </c>
       <c r="AG72">
         <v>40.4116666667</v>
@@ -10325,16 +10319,16 @@
         <v>-104.1701666667</v>
       </c>
       <c r="AI72">
-        <v>41.86</v>
+        <v>41.87</v>
       </c>
       <c r="AJ72">
-        <v>67.37</v>
+        <v>67.38</v>
       </c>
       <c r="AK72">
-        <v>4695</v>
+        <v>4697</v>
       </c>
       <c r="AL72">
-        <v>1431.04</v>
+        <v>1431.65</v>
       </c>
     </row>
     <row r="73" spans="1:38">
@@ -10366,16 +10360,16 @@
         <v>33012.89</v>
       </c>
       <c r="J73">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K73" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="L73">
-        <v>6229</v>
+        <v>6240</v>
       </c>
       <c r="M73">
-        <v>22.8</v>
+        <v>22.81</v>
       </c>
       <c r="N73">
         <v>36.7</v>
@@ -10423,16 +10417,16 @@
         <v>10.18</v>
       </c>
       <c r="AC73">
-        <v>39.6082333333</v>
+        <v>39.6083333333</v>
       </c>
       <c r="AD73">
-        <v>-104.0421</v>
+        <v>-104.0421666667</v>
       </c>
       <c r="AE73">
-        <v>5312</v>
+        <v>5213</v>
       </c>
       <c r="AF73">
-        <v>1619.1</v>
+        <v>1588.92</v>
       </c>
       <c r="AG73">
         <v>39.5823333333</v>
@@ -10441,7 +10435,7 @@
         <v>-103.6148333333</v>
       </c>
       <c r="AI73">
-        <v>22.8</v>
+        <v>22.81</v>
       </c>
       <c r="AJ73">
         <v>36.7</v>
@@ -10482,19 +10476,19 @@
         <v>28324.45</v>
       </c>
       <c r="J74">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="K74" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="L74">
-        <v>6870</v>
+        <v>6882</v>
       </c>
       <c r="M74">
         <v>31.8</v>
       </c>
       <c r="N74">
-        <v>51.18</v>
+        <v>51.17</v>
       </c>
       <c r="O74">
         <v>6.87</v>
@@ -10539,16 +10533,16 @@
         <v>7.24</v>
       </c>
       <c r="AC74">
-        <v>39.6084333333</v>
+        <v>39.6081666667</v>
       </c>
       <c r="AD74">
-        <v>-104.0421333333</v>
+        <v>-104.042</v>
       </c>
       <c r="AE74">
-        <v>5280</v>
+        <v>5206</v>
       </c>
       <c r="AF74">
-        <v>1609.34</v>
+        <v>1586.79</v>
       </c>
       <c r="AG74">
         <v>39.6995666667</v>
@@ -10560,7 +10554,7 @@
         <v>31.8</v>
       </c>
       <c r="AJ74">
-        <v>51.18</v>
+        <v>51.17</v>
       </c>
       <c r="AK74">
         <v>5526</v>
@@ -10598,19 +10592,19 @@
         <v>29625.95</v>
       </c>
       <c r="J75">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="K75" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="L75">
-        <v>8010</v>
+        <v>8040</v>
       </c>
       <c r="M75">
-        <v>22.69</v>
+        <v>22.71</v>
       </c>
       <c r="N75">
-        <v>36.52</v>
+        <v>36.55</v>
       </c>
       <c r="O75">
         <v>4.8</v>
@@ -10655,16 +10649,16 @@
         <v>6.05</v>
       </c>
       <c r="AC75">
-        <v>39.278</v>
+        <v>39.2783333333</v>
       </c>
       <c r="AD75">
-        <v>-103.4955</v>
+        <v>-103.4953333333</v>
       </c>
       <c r="AE75">
-        <v>5806</v>
+        <v>5606</v>
       </c>
       <c r="AF75">
-        <v>1769.67</v>
+        <v>1708.71</v>
       </c>
       <c r="AG75">
         <v>38.9785</v>
@@ -10673,10 +10667,10 @@
         <v>-103.6698333333</v>
       </c>
       <c r="AI75">
-        <v>22.69</v>
+        <v>22.71</v>
       </c>
       <c r="AJ75">
-        <v>36.52</v>
+        <v>36.55</v>
       </c>
       <c r="AK75">
         <v>5501</v>
@@ -10714,19 +10708,19 @@
         <v>30095.34</v>
       </c>
       <c r="J76">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K76" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="L76">
-        <v>7890</v>
+        <v>7920</v>
       </c>
       <c r="M76">
-        <v>21.96</v>
+        <v>21.98</v>
       </c>
       <c r="N76">
-        <v>35.34</v>
+        <v>35.37</v>
       </c>
       <c r="O76">
         <v>6.97</v>
@@ -10771,16 +10765,16 @@
         <v>7.14</v>
       </c>
       <c r="AC76">
-        <v>39.2780833333</v>
+        <v>39.2783</v>
       </c>
       <c r="AD76">
-        <v>-103.4953</v>
+        <v>-103.4952166667</v>
       </c>
       <c r="AE76">
-        <v>5724</v>
+        <v>5622</v>
       </c>
       <c r="AF76">
-        <v>1744.68</v>
+        <v>1713.59</v>
       </c>
       <c r="AG76">
         <v>38.9941666667</v>
@@ -10789,10 +10783,10 @@
         <v>-103.6801166667</v>
       </c>
       <c r="AI76">
-        <v>21.96</v>
+        <v>21.98</v>
       </c>
       <c r="AJ76">
-        <v>35.34</v>
+        <v>35.37</v>
       </c>
       <c r="AK76">
         <v>5424</v>
@@ -10830,19 +10824,19 @@
         <v>30091.68</v>
       </c>
       <c r="J77">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="K77" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="L77">
-        <v>8070</v>
+        <v>8088</v>
       </c>
       <c r="M77">
-        <v>22.81</v>
+        <v>22.83</v>
       </c>
       <c r="N77">
-        <v>36.71</v>
+        <v>36.75</v>
       </c>
       <c r="O77">
         <v>6.97</v>
@@ -10887,16 +10881,16 @@
         <v>7.14</v>
       </c>
       <c r="AC77">
-        <v>39.278</v>
+        <v>39.2782333333</v>
       </c>
       <c r="AD77">
-        <v>-103.4953333333</v>
+        <v>-103.4950833333</v>
       </c>
       <c r="AE77">
-        <v>5842</v>
+        <v>5588</v>
       </c>
       <c r="AF77">
-        <v>1780.64</v>
+        <v>1703.22</v>
       </c>
       <c r="AG77">
         <v>38.9778333333</v>
@@ -10905,10 +10899,10 @@
         <v>-103.6733333333</v>
       </c>
       <c r="AI77">
-        <v>22.81</v>
+        <v>22.83</v>
       </c>
       <c r="AJ77">
-        <v>36.71</v>
+        <v>36.75</v>
       </c>
       <c r="AK77">
         <v>5392</v>
@@ -10946,19 +10940,19 @@
         <v>28709.72</v>
       </c>
       <c r="J78">
-        <v>378</v>
+        <v>414</v>
       </c>
       <c r="K78" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="L78">
-        <v>5952</v>
+        <v>6492</v>
       </c>
       <c r="M78">
-        <v>14.87</v>
+        <v>16.06</v>
       </c>
       <c r="N78">
-        <v>23.93</v>
+        <v>25.84</v>
       </c>
       <c r="O78">
         <v>5.5</v>
@@ -11003,16 +10997,16 @@
         <v>7.9</v>
       </c>
       <c r="AC78">
-        <v>39.2153333333</v>
+        <v>39.2363333333</v>
       </c>
       <c r="AD78">
-        <v>-103.7201666667</v>
+        <v>-103.6968333333</v>
       </c>
       <c r="AE78">
-        <v>18606</v>
+        <v>5391</v>
       </c>
       <c r="AF78">
-        <v>5671.11</v>
+        <v>1643.18</v>
       </c>
       <c r="AG78">
         <v>39.23415</v>
@@ -11021,10 +11015,10 @@
         <v>-103.99705</v>
       </c>
       <c r="AI78">
-        <v>14.87</v>
+        <v>16.06</v>
       </c>
       <c r="AJ78">
-        <v>23.93</v>
+        <v>25.84</v>
       </c>
       <c r="AK78">
         <v>6421</v>
@@ -11062,19 +11056,19 @@
         <v>32196.94</v>
       </c>
       <c r="J79">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="K79" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="L79">
-        <v>7578</v>
+        <v>7638</v>
       </c>
       <c r="M79">
-        <v>52.07</v>
+        <v>52.2</v>
       </c>
       <c r="N79">
-        <v>83.79000000000001</v>
+        <v>84</v>
       </c>
       <c r="O79">
         <v>10.24</v>
@@ -11119,16 +11113,16 @@
         <v>9.42</v>
       </c>
       <c r="AC79">
-        <v>39.6066833333</v>
+        <v>39.6075</v>
       </c>
       <c r="AD79">
-        <v>-104.0389666667</v>
+        <v>-104.0411833333</v>
       </c>
       <c r="AE79">
-        <v>5795</v>
+        <v>5201</v>
       </c>
       <c r="AF79">
-        <v>1766.32</v>
+        <v>1585.26</v>
       </c>
       <c r="AG79">
         <v>39.242</v>
@@ -11137,10 +11131,10 @@
         <v>-103.1845</v>
       </c>
       <c r="AI79">
-        <v>52.07</v>
+        <v>52.2</v>
       </c>
       <c r="AJ79">
-        <v>83.79000000000001</v>
+        <v>84</v>
       </c>
       <c r="AK79">
         <v>6623</v>
@@ -11178,19 +11172,19 @@
         <v>30373.62</v>
       </c>
       <c r="J80">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K80" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="L80">
-        <v>6694</v>
+        <v>6750</v>
       </c>
       <c r="M80">
-        <v>46.57</v>
+        <v>46.65</v>
       </c>
       <c r="N80">
-        <v>74.94</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="O80">
         <v>15.91</v>
@@ -11235,34 +11229,34 @@
         <v>11.78</v>
       </c>
       <c r="AC80">
-        <v>40.2258833333</v>
+        <v>40.2256666667</v>
       </c>
       <c r="AD80">
-        <v>-104.0762666667</v>
+        <v>-104.077</v>
       </c>
       <c r="AE80">
-        <v>5001</v>
+        <v>4567</v>
       </c>
       <c r="AF80">
-        <v>1524.3</v>
+        <v>1392.02</v>
       </c>
       <c r="AG80">
-        <v>39.8741666667</v>
+        <v>39.8751666667</v>
       </c>
       <c r="AH80">
-        <v>-103.3245</v>
+        <v>-103.3225</v>
       </c>
       <c r="AI80">
-        <v>46.57</v>
+        <v>46.65</v>
       </c>
       <c r="AJ80">
-        <v>74.94</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="AK80">
-        <v>5807</v>
+        <v>5209</v>
       </c>
       <c r="AL80">
-        <v>1769.97</v>
+        <v>1587.7</v>
       </c>
     </row>
     <row r="81" spans="1:38">
@@ -11297,10 +11291,10 @@
         <v>209</v>
       </c>
       <c r="K81" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="L81">
-        <v>5790</v>
+        <v>5718</v>
       </c>
       <c r="M81">
         <v>41.89</v>
@@ -11354,7 +11348,7 @@
         <v>39.6076333333</v>
       </c>
       <c r="AD81">
-        <v>-104.0412666667</v>
+        <v>-104.04125</v>
       </c>
       <c r="AE81">
         <v>5204</v>
@@ -11363,10 +11357,10 @@
         <v>1586.18</v>
       </c>
       <c r="AG81">
-        <v>39.4219166667</v>
+        <v>39.422</v>
       </c>
       <c r="AH81">
-        <v>-103.2925833333</v>
+        <v>-103.2925</v>
       </c>
       <c r="AI81">
         <v>41.89</v>
@@ -11375,10 +11369,10 @@
         <v>67.42</v>
       </c>
       <c r="AK81">
-        <v>5115</v>
+        <v>5151</v>
       </c>
       <c r="AL81">
-        <v>1559.05</v>
+        <v>1570.02</v>
       </c>
     </row>
     <row r="82" spans="1:38">
@@ -11410,19 +11404,19 @@
         <v>31915</v>
       </c>
       <c r="J82">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="K82" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="L82">
-        <v>6000</v>
+        <v>5984</v>
       </c>
       <c r="M82">
-        <v>56</v>
+        <v>55.99</v>
       </c>
       <c r="N82">
-        <v>90.12</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="O82">
         <v>8.44</v>
@@ -11479,22 +11473,22 @@
         <v>1602.33</v>
       </c>
       <c r="AG82">
-        <v>39.78105</v>
+        <v>39.781</v>
       </c>
       <c r="AH82">
-        <v>-103.01055</v>
+        <v>-103.0107166667</v>
       </c>
       <c r="AI82">
-        <v>56</v>
+        <v>55.99</v>
       </c>
       <c r="AJ82">
-        <v>90.12</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="AK82">
-        <v>4571</v>
+        <v>4554</v>
       </c>
       <c r="AL82">
-        <v>1393.24</v>
+        <v>1388.06</v>
       </c>
     </row>
     <row r="83" spans="1:38">
@@ -11526,19 +11520,19 @@
         <v>27361.9</v>
       </c>
       <c r="J83">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="K83" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="L83">
-        <v>6750</v>
+        <v>6810</v>
       </c>
       <c r="M83">
-        <v>57.99</v>
+        <v>58.13</v>
       </c>
       <c r="N83">
-        <v>93.33</v>
+        <v>93.55</v>
       </c>
       <c r="O83">
         <v>6.7</v>
@@ -11583,34 +11577,34 @@
         <v>8.01</v>
       </c>
       <c r="AC83">
-        <v>39.6073333333</v>
+        <v>39.6075</v>
       </c>
       <c r="AD83">
-        <v>-104.0408333333</v>
+        <v>-104.0411166667</v>
       </c>
       <c r="AE83">
-        <v>5673</v>
+        <v>5220</v>
       </c>
       <c r="AF83">
-        <v>1729.13</v>
+        <v>1591.06</v>
       </c>
       <c r="AG83">
-        <v>38.8768333333</v>
+        <v>38.87505</v>
       </c>
       <c r="AH83">
-        <v>-103.5055</v>
+        <v>-103.50505</v>
       </c>
       <c r="AI83">
-        <v>57.99</v>
+        <v>58.13</v>
       </c>
       <c r="AJ83">
-        <v>93.33</v>
+        <v>93.55</v>
       </c>
       <c r="AK83">
-        <v>5811</v>
+        <v>5473</v>
       </c>
       <c r="AL83">
-        <v>1771.19</v>
+        <v>1668.17</v>
       </c>
     </row>
     <row r="84" spans="1:38">
@@ -11642,19 +11636,19 @@
         <v>27325.62</v>
       </c>
       <c r="J84">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K84" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="L84">
-        <v>7519</v>
+        <v>7533</v>
       </c>
       <c r="M84">
-        <v>75.94</v>
+        <v>76.02</v>
       </c>
       <c r="N84">
-        <v>122.22</v>
+        <v>122.35</v>
       </c>
       <c r="O84">
         <v>7.86</v>
@@ -11699,34 +11693,34 @@
         <v>7.52</v>
       </c>
       <c r="AC84">
-        <v>40.22645</v>
+        <v>40.2257166667</v>
       </c>
       <c r="AD84">
-        <v>-104.0757</v>
+        <v>-104.0769166667</v>
       </c>
       <c r="AE84">
-        <v>5115</v>
+        <v>4581</v>
       </c>
       <c r="AF84">
-        <v>1559.05</v>
+        <v>1396.29</v>
       </c>
       <c r="AG84">
-        <v>41.0114</v>
+        <v>41.0115166667</v>
       </c>
       <c r="AH84">
-        <v>-103.0606333333</v>
+        <v>-103.0607833333</v>
       </c>
       <c r="AI84">
-        <v>75.94</v>
+        <v>76.02</v>
       </c>
       <c r="AJ84">
-        <v>122.22</v>
+        <v>122.35</v>
       </c>
       <c r="AK84">
-        <v>4394</v>
+        <v>4402</v>
       </c>
       <c r="AL84">
-        <v>1339.29</v>
+        <v>1341.73</v>
       </c>
     </row>
     <row r="85" spans="1:38">
@@ -11761,16 +11755,16 @@
         <v>512</v>
       </c>
       <c r="K85" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="L85">
-        <v>8404</v>
+        <v>8396</v>
       </c>
       <c r="M85">
-        <v>86</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="N85">
-        <v>138.41</v>
+        <v>138.39</v>
       </c>
       <c r="O85">
         <v>8.630000000000001</v>
@@ -11815,34 +11809,34 @@
         <v>7.77</v>
       </c>
       <c r="AC85">
-        <v>40.22565</v>
+        <v>40.2258333333</v>
       </c>
       <c r="AD85">
-        <v>-104.0767333333</v>
+        <v>-104.077</v>
       </c>
       <c r="AE85">
-        <v>4633</v>
+        <v>4556</v>
       </c>
       <c r="AF85">
-        <v>1412.14</v>
+        <v>1388.67</v>
       </c>
       <c r="AG85">
-        <v>41.1266666667</v>
+        <v>41.1265</v>
       </c>
       <c r="AH85">
-        <v>-102.9426666667</v>
+        <v>-102.9427666667</v>
       </c>
       <c r="AI85">
-        <v>86</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="AJ85">
-        <v>138.41</v>
+        <v>138.39</v>
       </c>
       <c r="AK85">
-        <v>4150</v>
+        <v>4144</v>
       </c>
       <c r="AL85">
-        <v>1264.92</v>
+        <v>1263.09</v>
       </c>
     </row>
     <row r="86" spans="1:38">
@@ -11874,19 +11868,19 @@
         <v>30593.39</v>
       </c>
       <c r="J86">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="K86" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="L86">
-        <v>7076</v>
+        <v>7043</v>
       </c>
       <c r="M86">
-        <v>63.56</v>
+        <v>63.59</v>
       </c>
       <c r="N86">
-        <v>102.29</v>
+        <v>102.33</v>
       </c>
       <c r="O86">
         <v>16.09</v>
@@ -11931,34 +11925,34 @@
         <v>13.03</v>
       </c>
       <c r="AC86">
-        <v>40.2258333333</v>
+        <v>40.2257666667</v>
       </c>
       <c r="AD86">
-        <v>-104.0761666667</v>
+        <v>-104.07695</v>
       </c>
       <c r="AE86">
-        <v>4712</v>
+        <v>4561</v>
       </c>
       <c r="AF86">
-        <v>1436.22</v>
+        <v>1390.19</v>
       </c>
       <c r="AG86">
-        <v>39.7649</v>
+        <v>39.76525</v>
       </c>
       <c r="AH86">
-        <v>-103.036</v>
+        <v>-103.0359333333</v>
       </c>
       <c r="AI86">
-        <v>63.56</v>
+        <v>63.59</v>
       </c>
       <c r="AJ86">
-        <v>102.29</v>
+        <v>102.33</v>
       </c>
       <c r="AK86">
-        <v>4597</v>
+        <v>4601</v>
       </c>
       <c r="AL86">
-        <v>1401.17</v>
+        <v>1402.38</v>
       </c>
     </row>
     <row r="87" spans="1:38">
@@ -11990,16 +11984,16 @@
         <v>33555.43</v>
       </c>
       <c r="J87">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K87" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="L87">
-        <v>6618</v>
+        <v>6630</v>
       </c>
       <c r="M87">
-        <v>66.95</v>
+        <v>66.95999999999999</v>
       </c>
       <c r="N87">
         <v>107.75</v>
@@ -12047,34 +12041,34 @@
         <v>7.88</v>
       </c>
       <c r="AC87">
-        <v>39.6082</v>
+        <v>39.6083166667</v>
       </c>
       <c r="AD87">
-        <v>-104.0416833333</v>
+        <v>-104.0421166667</v>
       </c>
       <c r="AE87">
-        <v>5398</v>
+        <v>5211</v>
       </c>
       <c r="AF87">
-        <v>1645.31</v>
+        <v>1588.31</v>
       </c>
       <c r="AG87">
-        <v>38.7788333333</v>
+        <v>38.7790833333</v>
       </c>
       <c r="AH87">
-        <v>-103.3933333333</v>
+        <v>-103.3934</v>
       </c>
       <c r="AI87">
-        <v>66.95</v>
+        <v>66.95999999999999</v>
       </c>
       <c r="AJ87">
         <v>107.75</v>
       </c>
       <c r="AK87">
-        <v>4798</v>
+        <v>4797</v>
       </c>
       <c r="AL87">
-        <v>1462.43</v>
+        <v>1462.13</v>
       </c>
     </row>
     <row r="88" spans="1:38">
@@ -12106,19 +12100,19 @@
         <v>30007.86</v>
       </c>
       <c r="J88">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="K88" t="s">
-        <v>451</v>
+        <v>525</v>
       </c>
       <c r="L88">
-        <v>9360</v>
+        <v>9390</v>
       </c>
       <c r="M88">
-        <v>55.13</v>
+        <v>55.17</v>
       </c>
       <c r="N88">
-        <v>88.73</v>
+        <v>88.78</v>
       </c>
       <c r="O88">
         <v>17.64</v>
@@ -12163,16 +12157,16 @@
         <v>13.12</v>
       </c>
       <c r="AC88">
-        <v>39.6086666667</v>
+        <v>39.6091666667</v>
       </c>
       <c r="AD88">
-        <v>-104.0421666667</v>
+        <v>-104.0423333333</v>
       </c>
       <c r="AE88">
-        <v>5250</v>
+        <v>5147</v>
       </c>
       <c r="AF88">
-        <v>1600.2</v>
+        <v>1568.81</v>
       </c>
       <c r="AG88">
         <v>38.8388333333</v>
@@ -12181,16 +12175,16 @@
         <v>-104.316</v>
       </c>
       <c r="AI88">
-        <v>55.13</v>
+        <v>55.17</v>
       </c>
       <c r="AJ88">
-        <v>88.73</v>
+        <v>88.78</v>
       </c>
       <c r="AK88">
-        <v>6134</v>
+        <v>6135</v>
       </c>
       <c r="AL88">
-        <v>1869.64</v>
+        <v>1869.95</v>
       </c>
     </row>
     <row r="89" spans="1:38">
@@ -12222,13 +12216,13 @@
         <v>3420.77</v>
       </c>
       <c r="J89">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K89" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="L89">
-        <v>1496</v>
+        <v>1526</v>
       </c>
       <c r="M89">
         <v>4.32</v>
@@ -12279,16 +12273,16 @@
         <v>5.14</v>
       </c>
       <c r="AC89">
-        <v>40.6483166667</v>
+        <v>40.6488333333</v>
       </c>
       <c r="AD89">
-        <v>-104.3849333333</v>
+        <v>-104.3843333333</v>
       </c>
       <c r="AE89">
-        <v>5109</v>
+        <v>4995</v>
       </c>
       <c r="AF89">
-        <v>1557.22</v>
+        <v>1522.48</v>
       </c>
       <c r="AG89">
         <v>40.6065166667</v>
@@ -12338,13 +12332,13 @@
         <v>28377.49</v>
       </c>
       <c r="J90">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K90" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="L90">
-        <v>6297</v>
+        <v>6300</v>
       </c>
       <c r="M90">
         <v>11.64</v>
@@ -12395,16 +12389,16 @@
         <v>11.51</v>
       </c>
       <c r="AC90">
-        <v>39.6083833333</v>
+        <v>39.60835</v>
       </c>
       <c r="AD90">
-        <v>-104.04185</v>
+        <v>-104.0419166667</v>
       </c>
       <c r="AE90">
-        <v>5316</v>
+        <v>5243</v>
       </c>
       <c r="AF90">
-        <v>1620.32</v>
+        <v>1598.07</v>
       </c>
       <c r="AG90">
         <v>39.4658666667</v>
@@ -12454,19 +12448,19 @@
         <v>25712.32</v>
       </c>
       <c r="J91">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K91" t="s">
-        <v>511</v>
+        <v>528</v>
       </c>
       <c r="L91">
-        <v>8130</v>
+        <v>8190</v>
       </c>
       <c r="M91">
         <v>129.41</v>
       </c>
       <c r="N91">
-        <v>208.26</v>
+        <v>208.27</v>
       </c>
       <c r="O91">
         <v>4.13</v>
@@ -12517,28 +12511,28 @@
         <v>-104.9626666667</v>
       </c>
       <c r="AE91">
-        <v>5198</v>
+        <v>4940</v>
       </c>
       <c r="AF91">
-        <v>1584.35</v>
+        <v>1505.71</v>
       </c>
       <c r="AG91">
-        <v>40.8561666667</v>
+        <v>40.8579333333</v>
       </c>
       <c r="AH91">
-        <v>-102.5436666667</v>
+        <v>-102.5440833333</v>
       </c>
       <c r="AI91">
         <v>129.41</v>
       </c>
       <c r="AJ91">
-        <v>208.26</v>
+        <v>208.27</v>
       </c>
       <c r="AK91">
-        <v>4815</v>
+        <v>4361</v>
       </c>
       <c r="AL91">
-        <v>1467.61</v>
+        <v>1329.23</v>
       </c>
     </row>
     <row r="92" spans="1:38">
@@ -12570,19 +12564,19 @@
         <v>26009.19</v>
       </c>
       <c r="J92">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="K92" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="L92">
-        <v>7055</v>
+        <v>7113</v>
       </c>
       <c r="M92">
-        <v>109.12</v>
+        <v>109.11</v>
       </c>
       <c r="N92">
-        <v>175.61</v>
+        <v>175.6</v>
       </c>
       <c r="O92">
         <v>6.78</v>
@@ -12627,16 +12621,16 @@
         <v>6.5</v>
       </c>
       <c r="AC92">
-        <v>40.4736</v>
+        <v>40.47355</v>
       </c>
       <c r="AD92">
-        <v>-104.9627166667</v>
+        <v>-104.9626166667</v>
       </c>
       <c r="AE92">
-        <v>5181</v>
+        <v>4955</v>
       </c>
       <c r="AF92">
-        <v>1579.17</v>
+        <v>1510.28</v>
       </c>
       <c r="AG92">
         <v>40.8481</v>
@@ -12645,10 +12639,10 @@
         <v>-102.9386833333</v>
       </c>
       <c r="AI92">
-        <v>109.12</v>
+        <v>109.11</v>
       </c>
       <c r="AJ92">
-        <v>175.61</v>
+        <v>175.6</v>
       </c>
       <c r="AK92">
         <v>3780</v>
@@ -12686,13 +12680,13 @@
         <v>31706.21</v>
       </c>
       <c r="J93">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="K93" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="L93">
-        <v>7395</v>
+        <v>7380</v>
       </c>
       <c r="M93">
         <v>80.27</v>
@@ -12743,19 +12737,19 @@
         <v>8.699999999999999</v>
       </c>
       <c r="AC93">
-        <v>40.5265</v>
+        <v>40.52645</v>
       </c>
       <c r="AD93">
-        <v>-104.7233333333</v>
+        <v>-104.7234</v>
       </c>
       <c r="AE93">
-        <v>4894</v>
+        <v>4846</v>
       </c>
       <c r="AF93">
-        <v>1491.69</v>
+        <v>1477.06</v>
       </c>
       <c r="AG93">
-        <v>40.0466333333</v>
+        <v>40.04665</v>
       </c>
       <c r="AH93">
         <v>-103.3351666667</v>
@@ -12767,10 +12761,10 @@
         <v>129.18</v>
       </c>
       <c r="AK93">
-        <v>4774</v>
+        <v>4778</v>
       </c>
       <c r="AL93">
-        <v>1455.12</v>
+        <v>1456.33</v>
       </c>
     </row>
     <row r="94" spans="1:38">
@@ -12802,19 +12796,19 @@
         <v>33558.78</v>
       </c>
       <c r="J94">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="K94" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="L94">
-        <v>7800</v>
+        <v>7830</v>
       </c>
       <c r="M94">
-        <v>88.25</v>
+        <v>88.28</v>
       </c>
       <c r="N94">
-        <v>142.03</v>
+        <v>142.07</v>
       </c>
       <c r="O94">
         <v>17.39</v>
@@ -12859,34 +12853,34 @@
         <v>11.75</v>
       </c>
       <c r="AC94">
-        <v>40.5265166667</v>
+        <v>40.5265333333</v>
       </c>
       <c r="AD94">
-        <v>-104.7232333333</v>
+        <v>-104.72345</v>
       </c>
       <c r="AE94">
-        <v>4968</v>
+        <v>4846</v>
       </c>
       <c r="AF94">
-        <v>1514.25</v>
+        <v>1477.06</v>
       </c>
       <c r="AG94">
-        <v>40.0466833333</v>
+        <v>40.0469333333</v>
       </c>
       <c r="AH94">
-        <v>-103.1701333333</v>
+        <v>-103.1697</v>
       </c>
       <c r="AI94">
-        <v>88.25</v>
+        <v>88.28</v>
       </c>
       <c r="AJ94">
-        <v>142.03</v>
+        <v>142.07</v>
       </c>
       <c r="AK94">
-        <v>4971</v>
+        <v>4942</v>
       </c>
       <c r="AL94">
-        <v>1515.16</v>
+        <v>1506.32</v>
       </c>
     </row>
     <row r="95" spans="1:38">
@@ -12921,16 +12915,16 @@
         <v>365</v>
       </c>
       <c r="K95" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L95">
         <v>6495</v>
       </c>
       <c r="M95">
-        <v>94.23999999999999</v>
+        <v>94.25</v>
       </c>
       <c r="N95">
-        <v>151.66</v>
+        <v>151.68</v>
       </c>
       <c r="O95">
         <v>15.42</v>
@@ -12975,34 +12969,34 @@
         <v>11.46</v>
       </c>
       <c r="AC95">
-        <v>40.2255</v>
+        <v>40.22485</v>
       </c>
       <c r="AD95">
-        <v>-104.0765</v>
+        <v>-104.0772</v>
       </c>
       <c r="AE95">
-        <v>4752</v>
+        <v>4561</v>
       </c>
       <c r="AF95">
-        <v>1448.41</v>
+        <v>1390.19</v>
       </c>
       <c r="AG95">
-        <v>39.6237333333</v>
+        <v>39.624</v>
       </c>
       <c r="AH95">
-        <v>-102.479</v>
+        <v>-102.4788333333</v>
       </c>
       <c r="AI95">
-        <v>94.23999999999999</v>
+        <v>94.25</v>
       </c>
       <c r="AJ95">
-        <v>151.66</v>
+        <v>151.68</v>
       </c>
       <c r="AK95">
-        <v>4111</v>
+        <v>4109</v>
       </c>
       <c r="AL95">
-        <v>1253.03</v>
+        <v>1252.42</v>
       </c>
     </row>
     <row r="96" spans="1:38">
@@ -13037,16 +13031,16 @@
         <v>487</v>
       </c>
       <c r="K96" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="L96">
-        <v>7855</v>
+        <v>7830</v>
       </c>
       <c r="M96">
         <v>87.38</v>
       </c>
       <c r="N96">
-        <v>140.63</v>
+        <v>140.62</v>
       </c>
       <c r="O96">
         <v>7.02</v>
@@ -13091,34 +13085,34 @@
         <v>7.65</v>
       </c>
       <c r="AC96">
-        <v>39.61065</v>
+        <v>39.6104666667</v>
       </c>
       <c r="AD96">
-        <v>-104.0421666667</v>
+        <v>-104.04215</v>
       </c>
       <c r="AE96">
-        <v>5326</v>
+        <v>5217</v>
       </c>
       <c r="AF96">
-        <v>1623.36</v>
+        <v>1590.14</v>
       </c>
       <c r="AG96">
-        <v>39.43295</v>
+        <v>39.4329666667</v>
       </c>
       <c r="AH96">
-        <v>-102.4176833333</v>
+        <v>-102.4177166667</v>
       </c>
       <c r="AI96">
         <v>87.38</v>
       </c>
       <c r="AJ96">
-        <v>140.63</v>
+        <v>140.62</v>
       </c>
       <c r="AK96">
-        <v>4164</v>
+        <v>4184</v>
       </c>
       <c r="AL96">
-        <v>1269.19</v>
+        <v>1275.28</v>
       </c>
     </row>
     <row r="97" spans="1:38">
@@ -13150,19 +13144,19 @@
         <v>32628.84</v>
       </c>
       <c r="J97">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="K97" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="L97">
-        <v>8875</v>
+        <v>8910</v>
       </c>
       <c r="M97">
-        <v>19.02</v>
+        <v>19.08</v>
       </c>
       <c r="N97">
-        <v>30.6</v>
+        <v>30.71</v>
       </c>
       <c r="O97">
         <v>8.27</v>
@@ -13207,34 +13201,34 @@
         <v>7.82</v>
       </c>
       <c r="AC97">
-        <v>39.2356666667</v>
+        <v>39.2361666667</v>
       </c>
       <c r="AD97">
-        <v>-103.6976666667</v>
+        <v>-103.697</v>
       </c>
       <c r="AE97">
-        <v>5746</v>
+        <v>5401</v>
       </c>
       <c r="AF97">
-        <v>1751.38</v>
+        <v>1646.22</v>
       </c>
       <c r="AG97">
-        <v>39.07765</v>
+        <v>39.0775</v>
       </c>
       <c r="AH97">
-        <v>-103.9885833333</v>
+        <v>-103.9888333333</v>
       </c>
       <c r="AI97">
-        <v>19.02</v>
+        <v>19.08</v>
       </c>
       <c r="AJ97">
-        <v>30.6</v>
+        <v>30.71</v>
       </c>
       <c r="AK97">
-        <v>6441</v>
+        <v>6412</v>
       </c>
       <c r="AL97">
-        <v>1963.22</v>
+        <v>1954.38</v>
       </c>
     </row>
     <row r="98" spans="1:38">
@@ -13266,19 +13260,19 @@
         <v>31353.86</v>
       </c>
       <c r="J98">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="K98" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="L98">
-        <v>7665</v>
+        <v>7695</v>
       </c>
       <c r="M98">
-        <v>8.380000000000001</v>
+        <v>8.32</v>
       </c>
       <c r="N98">
-        <v>13.49</v>
+        <v>13.39</v>
       </c>
       <c r="O98">
         <v>11.9</v>
@@ -13323,16 +13317,16 @@
         <v>9.41</v>
       </c>
       <c r="AC98">
-        <v>39.2794333333</v>
+        <v>39.2781833333</v>
       </c>
       <c r="AD98">
-        <v>-103.4946166667</v>
+        <v>-103.49525</v>
       </c>
       <c r="AE98">
-        <v>5905</v>
+        <v>5593</v>
       </c>
       <c r="AF98">
-        <v>1799.84</v>
+        <v>1704.75</v>
       </c>
       <c r="AG98">
         <v>39.2383333333</v>
@@ -13341,10 +13335,10 @@
         <v>-103.64215</v>
       </c>
       <c r="AI98">
-        <v>8.380000000000001</v>
+        <v>8.32</v>
       </c>
       <c r="AJ98">
-        <v>13.49</v>
+        <v>13.39</v>
       </c>
       <c r="AK98">
         <v>5303</v>

--- a/www/flightdata/xlsx/flights_metadata.xlsx
+++ b/www/flightdata/xlsx/flights_metadata.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="534">
   <si>
     <t>flight</t>
   </si>
@@ -1087,7 +1087,7 @@
     <t>[{'transition': 'high_to_low', 'altitude_ft': 54081.0, 'altitude_m': 16483.89}]</t>
   </si>
   <si>
-    <t>[{'transition': 'low_to_high', 'altitude_ft': 5773.0, 'altitude_m': 1759.61}, {'transition': 'high_to_low', 'altitude_ft': 43536.0, 'altitude_m': 13269.77}]</t>
+    <t>[{'transition': 'high_to_low', 'altitude_ft': 43536.0, 'altitude_m': 13269.77}]</t>
   </si>
   <si>
     <t>[{'transition': 'high_to_low', 'altitude_ft': 45552.0, 'altitude_m': 13884.25}]</t>
@@ -1153,7 +1153,7 @@
     <t>[{'transition': 'high_to_low', 'altitude_ft': 68226.0, 'altitude_m': 20795.28}]</t>
   </si>
   <si>
-    <t>[{'transition': 'low_to_high', 'altitude_ft': 9581.0, 'altitude_m': 2920.29}, {'transition': 'high_to_low', 'altitude_ft': 55168.0, 'altitude_m': 16815.21}]</t>
+    <t>[{'transition': 'low_to_high', 'altitude_ft': 10274.0, 'altitude_m': 3131.52}, {'transition': 'high_to_low', 'altitude_ft': 55168.0, 'altitude_m': 16815.21}]</t>
   </si>
   <si>
     <t>[{'transition': 'low_to_high', 'altitude_ft': 16931.0, 'altitude_m': 5160.57}, {'transition': 'high_to_low', 'altitude_ft': 46196.0, 'altitude_m': 14080.54}]</t>
@@ -1180,7 +1180,7 @@
     <t>[{'transition': 'high_to_low', 'altitude_ft': 40575.0, 'altitude_m': 12367.26}]</t>
   </si>
   <si>
-    <t>[{'transition': 'low_to_high', 'altitude_ft': 5795.0, 'altitude_m': 1766.32}]</t>
+    <t>[{'transition': 'low_to_high', 'altitude_ft': 41108.0, 'altitude_m': 12529.72}]</t>
   </si>
   <si>
     <t>[{'transition': 'high_to_low', 'altitude_ft': 52066.0, 'altitude_m': 15869.72}]</t>
@@ -1213,7 +1213,7 @@
     <t>[{'transition': 'high_to_low', 'altitude_ft': 48301.0, 'altitude_m': 14722.14}]</t>
   </si>
   <si>
-    <t>[{'transition': 'low_to_high', 'altitude_ft': 9997.0, 'altitude_m': 3047.09}, {'transition': 'high_to_low', 'altitude_ft': 55507.0, 'altitude_m': 16918.53}]</t>
+    <t>[{'transition': 'high_to_low', 'altitude_ft': 55507.0, 'altitude_m': 16918.53}]</t>
   </si>
   <si>
     <t>[{'transition': 'high_to_low', 'altitude_ft': 54974.0, 'altitude_m': 16756.08}]</t>
@@ -1240,7 +1240,7 @@
     <t>[{'transition': 'high_to_low', 'altitude_ft': 52446.0, 'altitude_m': 15985.54}]</t>
   </si>
   <si>
-    <t>[{'transition': 'low_to_high', 'altitude_ft': 5949.0, 'altitude_m': 1813.26}, {'transition': 'high_to_low', 'altitude_ft': 62431.0, 'altitude_m': 19028.97}]</t>
+    <t>[{'transition': 'high_to_low', 'altitude_ft': 62431.0, 'altitude_m': 19028.97}]</t>
   </si>
   <si>
     <t>[{'transition': 'high_to_low', 'altitude_ft': 51806.0, 'altitude_m': 15790.47}]</t>
@@ -1252,7 +1252,7 @@
     <t>[{'transition': 'high_to_low', 'altitude_ft': 50361.0, 'altitude_m': 15350.03}]</t>
   </si>
   <si>
-    <t>[{'transition': 'low_to_high', 'altitude_ft': 7718.0, 'altitude_m': 2352.45}, {'transition': 'high_to_low', 'altitude_ft': 56579.0, 'altitude_m': 17245.28}]</t>
+    <t>[{'transition': 'high_to_low', 'altitude_ft': 56579.0, 'altitude_m': 17245.28}]</t>
   </si>
   <si>
     <t>[{'transition': 'high_to_low', 'altitude_ft': 48010.0, 'altitude_m': 14633.45}]</t>
@@ -1285,7 +1285,7 @@
     <t>[{'transition': 'high_to_low', 'altitude_ft': 53199.0, 'altitude_m': 16215.06}]</t>
   </si>
   <si>
-    <t>[{'transition': 'low_to_high', 'altitude_ft': 8118.0, 'altitude_m': 2474.37}, {'transition': 'high_to_low', 'altitude_ft': 55820.0, 'altitude_m': 17013.94}]</t>
+    <t>[{'transition': 'high_to_low', 'altitude_ft': 55820.0, 'altitude_m': 17013.94}]</t>
   </si>
   <si>
     <t>[{'transition': 'high_to_low', 'altitude_ft': 66320.0, 'altitude_m': 20214.34}]</t>
@@ -1297,7 +1297,7 @@
     <t>[{'transition': 'low_to_high', 'altitude_ft': 21272.0, 'altitude_m': 6483.71}, {'transition': 'high_to_low', 'altitude_ft': 74152.0, 'altitude_m': 22601.53}]</t>
   </si>
   <si>
-    <t>[{'transition': 'low_to_high', 'altitude_ft': 5667.0, 'altitude_m': 1727.3}, {'transition': 'high_to_low', 'altitude_ft': 40581.0, 'altitude_m': 12369.09}]</t>
+    <t>[{'transition': 'high_to_low', 'altitude_ft': 40581.0, 'altitude_m': 12369.09}]</t>
   </si>
   <si>
     <t>[{'transition': 'high_to_low', 'altitude_ft': 40592.0, 'altitude_m': 12372.44}]</t>
@@ -1309,7 +1309,7 @@
     <t>[{'transition': 'high_to_low', 'altitude_ft': 52415.0, 'altitude_m': 15976.09}]</t>
   </si>
   <si>
-    <t>[{'transition': 'low_to_high', 'altitude_ft': 8489.0, 'altitude_m': 2587.45}, {'transition': 'high_to_low', 'altitude_ft': 62268.0, 'altitude_m': 18979.29}]</t>
+    <t>[{'transition': 'high_to_low', 'altitude_ft': 62268.0, 'altitude_m': 18979.29}]</t>
   </si>
   <si>
     <t>[{'transition': 'low_to_high', 'altitude_ft': 12462.0, 'altitude_m': 3798.42}, {'transition': 'high_to_low', 'altitude_ft': 52124.0, 'altitude_m': 15887.4}]</t>
@@ -1327,7 +1327,7 @@
     <t>[{'transition': 'high_to_low', 'altitude_ft': 32694.0, 'altitude_m': 9965.13}]</t>
   </si>
   <si>
-    <t>[{'transition': 'low_to_high', 'altitude_ft': 9847.0, 'altitude_m': 3001.37}, {'transition': 'high_to_low', 'altitude_ft': 48953.0, 'altitude_m': 14920.87}]</t>
+    <t>[{'transition': 'low_to_high', 'altitude_ft': 10474.0, 'altitude_m': 3192.48}, {'transition': 'high_to_low', 'altitude_ft': 48953.0, 'altitude_m': 14920.87}]</t>
   </si>
   <si>
     <t>[{'transition': 'high_to_low', 'altitude_ft': 74746.0, 'altitude_m': 22782.58}]</t>
@@ -1363,7 +1363,7 @@
     <t>2hrs 19mins 53secs</t>
   </si>
   <si>
-    <t>2hrs 20mins 20secs</t>
+    <t>2hrs 28mins 20secs</t>
   </si>
   <si>
     <t>1hrs 38mins 0secs</t>
@@ -1375,7 +1375,7 @@
     <t>2hrs 27mins 30secs</t>
   </si>
   <si>
-    <t>1hrs 15mins 38secs</t>
+    <t>1hrs 24mins 38secs</t>
   </si>
   <si>
     <t>2hrs 8mins 20secs</t>
@@ -1393,7 +1393,7 @@
     <t>2hrs 4mins 47secs</t>
   </si>
   <si>
-    <t>1hrs 48mins 0secs</t>
+    <t>1hrs 51mins 0secs</t>
   </si>
   <si>
     <t>1hrs 57mins 30secs</t>
@@ -1411,7 +1411,7 @@
     <t>1hrs 55mins 0secs</t>
   </si>
   <si>
-    <t>1hrs 57mins 34secs</t>
+    <t>2hrs 6mins 4secs</t>
   </si>
   <si>
     <t>1hrs 26mins 40secs</t>
@@ -1453,7 +1453,7 @@
     <t>1hrs 31mins 20secs</t>
   </si>
   <si>
-    <t>1hrs 23mins 18secs</t>
+    <t>1hrs 33mins 18secs</t>
   </si>
   <si>
     <t>1hrs 42mins 48secs</t>
@@ -1468,7 +1468,7 @@
     <t>1hrs 52mins 0secs</t>
   </si>
   <si>
-    <t>2hrs 6mins 34secs</t>
+    <t>1hrs 39mins 4secs</t>
   </si>
   <si>
     <t>1hrs 50mins 26secs</t>
@@ -1531,9 +1531,6 @@
     <t>2hrs 1mins 12secs</t>
   </si>
   <si>
-    <t>1hrs 38mins 18secs</t>
-  </si>
-  <si>
     <t>1hrs 56mins 4secs</t>
   </si>
   <si>
@@ -1543,7 +1540,7 @@
     <t>2hrs 14mins 57secs</t>
   </si>
   <si>
-    <t>2hrs 7mins 48secs</t>
+    <t>2hrs 9mins 48secs</t>
   </si>
   <si>
     <t>1hrs 44mins 0secs</t>
@@ -1555,10 +1552,10 @@
     <t>2hrs 14mins 0secs</t>
   </si>
   <si>
-    <t>2hrs 12mins 0secs</t>
-  </si>
-  <si>
-    <t>2hrs 14mins 48secs</t>
+    <t>2hrs 13mins 30secs</t>
+  </si>
+  <si>
+    <t>2hrs 15mins 48secs</t>
   </si>
   <si>
     <t>1hrs 48mins 12secs</t>
@@ -1576,7 +1573,7 @@
     <t>1hrs 39mins 44secs</t>
   </si>
   <si>
-    <t>1hrs 53mins 30secs</t>
+    <t>1hrs 53mins 12secs</t>
   </si>
   <si>
     <t>2hrs 5mins 33secs</t>
@@ -1591,7 +1588,7 @@
     <t>1hrs 50mins 30secs</t>
   </si>
   <si>
-    <t>2hrs 36mins 30secs</t>
+    <t>2hrs 37mins 30secs</t>
   </si>
   <si>
     <t>0hrs 25mins 26secs</t>
@@ -1603,7 +1600,7 @@
     <t>2hrs 16mins 30secs</t>
   </si>
   <si>
-    <t>1hrs 58mins 33secs</t>
+    <t>1hrs 59mins 31secs</t>
   </si>
   <si>
     <t>2hrs 3mins 0secs</t>
@@ -2124,7 +2121,7 @@
         <v>27272.59</v>
       </c>
       <c r="J2">
-        <v>221</v>
+        <v>355</v>
       </c>
       <c r="K2" t="s">
         <v>443</v>
@@ -2240,7 +2237,7 @@
         <v>30445.86</v>
       </c>
       <c r="J3">
-        <v>350</v>
+        <v>543</v>
       </c>
       <c r="K3" t="s">
         <v>444</v>
@@ -2249,10 +2246,10 @@
         <v>5870</v>
       </c>
       <c r="M3">
-        <v>93.79000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="N3">
-        <v>150.94</v>
+        <v>150.95</v>
       </c>
       <c r="O3">
         <v>7.8</v>
@@ -2297,16 +2294,16 @@
         <v>8.550000000000001</v>
       </c>
       <c r="AC3">
-        <v>40.2246666667</v>
+        <v>40.2248333333</v>
       </c>
       <c r="AD3">
         <v>-104.0771666667</v>
       </c>
       <c r="AE3">
-        <v>4567</v>
+        <v>4555</v>
       </c>
       <c r="AF3">
-        <v>1392.02</v>
+        <v>1388.36</v>
       </c>
       <c r="AG3">
         <v>39.4631666667</v>
@@ -2315,10 +2312,10 @@
         <v>-102.612</v>
       </c>
       <c r="AI3">
-        <v>93.79000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="AJ3">
-        <v>150.94</v>
+        <v>150.95</v>
       </c>
       <c r="AK3">
         <v>5140</v>
@@ -2356,7 +2353,7 @@
         <v>29202.58</v>
       </c>
       <c r="J4">
-        <v>331</v>
+        <v>521</v>
       </c>
       <c r="K4" t="s">
         <v>445</v>
@@ -2472,7 +2469,7 @@
         <v>31019.5</v>
       </c>
       <c r="J5">
-        <v>333</v>
+        <v>599</v>
       </c>
       <c r="K5" t="s">
         <v>446</v>
@@ -2588,7 +2585,7 @@
         <v>29367.48</v>
       </c>
       <c r="J6">
-        <v>449</v>
+        <v>724</v>
       </c>
       <c r="K6" t="s">
         <v>447</v>
@@ -2704,7 +2701,7 @@
         <v>29403.45</v>
       </c>
       <c r="J7">
-        <v>542</v>
+        <v>822</v>
       </c>
       <c r="K7" t="s">
         <v>448</v>
@@ -2820,13 +2817,13 @@
         <v>28844.14</v>
       </c>
       <c r="J8">
-        <v>487</v>
+        <v>778</v>
       </c>
       <c r="K8" t="s">
         <v>449</v>
       </c>
       <c r="L8">
-        <v>8420</v>
+        <v>8900</v>
       </c>
       <c r="M8">
         <v>34.17</v>
@@ -2901,10 +2898,10 @@
         <v>54.99</v>
       </c>
       <c r="AK8">
-        <v>5106</v>
+        <v>5109</v>
       </c>
       <c r="AL8">
-        <v>1556.31</v>
+        <v>1557.22</v>
       </c>
     </row>
     <row r="9" spans="1:38">
@@ -2936,7 +2933,7 @@
         <v>29907.89</v>
       </c>
       <c r="J9">
-        <v>710</v>
+        <v>1088</v>
       </c>
       <c r="K9" t="s">
         <v>450</v>
@@ -2945,10 +2942,10 @@
         <v>5880</v>
       </c>
       <c r="M9">
-        <v>22.05</v>
+        <v>22.03</v>
       </c>
       <c r="N9">
-        <v>35.49</v>
+        <v>35.45</v>
       </c>
       <c r="O9">
         <v>9.59</v>
@@ -3005,22 +3002,22 @@
         <v>1742.54</v>
       </c>
       <c r="AG9">
-        <v>39.5968333333</v>
+        <v>39.5965</v>
       </c>
       <c r="AH9">
         <v>-103.462</v>
       </c>
       <c r="AI9">
-        <v>22.05</v>
+        <v>22.03</v>
       </c>
       <c r="AJ9">
-        <v>35.49</v>
+        <v>35.45</v>
       </c>
       <c r="AK9">
-        <v>5273</v>
+        <v>5271</v>
       </c>
       <c r="AL9">
-        <v>1607.21</v>
+        <v>1606.6</v>
       </c>
     </row>
     <row r="10" spans="1:38">
@@ -3052,7 +3049,7 @@
         <v>29527.2</v>
       </c>
       <c r="J10">
-        <v>571</v>
+        <v>896</v>
       </c>
       <c r="K10" t="s">
         <v>451</v>
@@ -3168,7 +3165,7 @@
         <v>27177.49</v>
       </c>
       <c r="J11">
-        <v>214</v>
+        <v>331</v>
       </c>
       <c r="K11" t="s">
         <v>452</v>
@@ -3284,13 +3281,13 @@
         <v>19231.97</v>
       </c>
       <c r="J12">
-        <v>434</v>
+        <v>671</v>
       </c>
       <c r="K12" t="s">
         <v>453</v>
       </c>
       <c r="L12">
-        <v>4538</v>
+        <v>5078</v>
       </c>
       <c r="M12">
         <v>15.88</v>
@@ -3365,10 +3362,10 @@
         <v>25.56</v>
       </c>
       <c r="AK12">
-        <v>5359</v>
+        <v>5360</v>
       </c>
       <c r="AL12">
-        <v>1633.42</v>
+        <v>1633.73</v>
       </c>
     </row>
     <row r="13" spans="1:38">
@@ -3400,7 +3397,7 @@
         <v>28522.27</v>
       </c>
       <c r="J13">
-        <v>456</v>
+        <v>720</v>
       </c>
       <c r="K13" t="s">
         <v>454</v>
@@ -3516,7 +3513,7 @@
         <v>26529.49</v>
       </c>
       <c r="J14">
-        <v>673</v>
+        <v>1023</v>
       </c>
       <c r="K14" t="s">
         <v>455</v>
@@ -3632,7 +3629,7 @@
         <v>27397.25</v>
       </c>
       <c r="J15">
-        <v>424</v>
+        <v>670</v>
       </c>
       <c r="K15" t="s">
         <v>456</v>
@@ -3748,7 +3745,7 @@
         <v>30407.76</v>
       </c>
       <c r="J16">
-        <v>444</v>
+        <v>679</v>
       </c>
       <c r="K16" t="s">
         <v>457</v>
@@ -3864,7 +3861,7 @@
         <v>27814.22</v>
       </c>
       <c r="J17">
-        <v>487</v>
+        <v>652</v>
       </c>
       <c r="K17" t="s">
         <v>458</v>
@@ -3980,13 +3977,13 @@
         <v>28673.76</v>
       </c>
       <c r="J18">
-        <v>620</v>
+        <v>954</v>
       </c>
       <c r="K18" t="s">
         <v>459</v>
       </c>
       <c r="L18">
-        <v>6480</v>
+        <v>6660</v>
       </c>
       <c r="M18">
         <v>25.8</v>
@@ -4061,10 +4058,10 @@
         <v>41.52</v>
       </c>
       <c r="AK18">
-        <v>6014</v>
+        <v>6017</v>
       </c>
       <c r="AL18">
-        <v>1833.07</v>
+        <v>1833.98</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -4096,7 +4093,7 @@
         <v>28635.66</v>
       </c>
       <c r="J19">
-        <v>695</v>
+        <v>969</v>
       </c>
       <c r="K19" t="s">
         <v>460</v>
@@ -4212,7 +4209,7 @@
         <v>29112.97</v>
       </c>
       <c r="J20">
-        <v>258</v>
+        <v>395</v>
       </c>
       <c r="K20" t="s">
         <v>461</v>
@@ -4328,7 +4325,7 @@
         <v>27902.61</v>
       </c>
       <c r="J21">
-        <v>503</v>
+        <v>765</v>
       </c>
       <c r="K21" t="s">
         <v>462</v>
@@ -4444,7 +4441,7 @@
         <v>27201.88</v>
       </c>
       <c r="J22">
-        <v>309</v>
+        <v>471</v>
       </c>
       <c r="K22" t="s">
         <v>463</v>
@@ -4560,7 +4557,7 @@
         <v>26864.16</v>
       </c>
       <c r="J23">
-        <v>375</v>
+        <v>586</v>
       </c>
       <c r="K23" t="s">
         <v>464</v>
@@ -4676,13 +4673,13 @@
         <v>27619.45</v>
       </c>
       <c r="J24">
-        <v>427</v>
+        <v>671</v>
       </c>
       <c r="K24" t="s">
         <v>465</v>
       </c>
       <c r="L24">
-        <v>7054</v>
+        <v>7564</v>
       </c>
       <c r="M24">
         <v>35.7</v>
@@ -4757,10 +4754,10 @@
         <v>57.46</v>
       </c>
       <c r="AK24">
-        <v>6055</v>
+        <v>6063</v>
       </c>
       <c r="AL24">
-        <v>1845.56</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="25" spans="1:38">
@@ -4792,7 +4789,7 @@
         <v>25754.99</v>
       </c>
       <c r="J25">
-        <v>285</v>
+        <v>445</v>
       </c>
       <c r="K25" t="s">
         <v>466</v>
@@ -4908,7 +4905,7 @@
         <v>32334.71</v>
       </c>
       <c r="J26">
-        <v>488</v>
+        <v>745</v>
       </c>
       <c r="K26" t="s">
         <v>467</v>
@@ -5024,7 +5021,7 @@
         <v>30171.24</v>
       </c>
       <c r="J27">
-        <v>428</v>
+        <v>649</v>
       </c>
       <c r="K27" t="s">
         <v>468</v>
@@ -5140,7 +5137,7 @@
         <v>30216.65</v>
       </c>
       <c r="J28">
-        <v>494</v>
+        <v>750</v>
       </c>
       <c r="K28" t="s">
         <v>469</v>
@@ -5256,7 +5253,7 @@
         <v>30473.9</v>
       </c>
       <c r="J29">
-        <v>627</v>
+        <v>947</v>
       </c>
       <c r="K29" t="s">
         <v>470</v>
@@ -5372,7 +5369,7 @@
         <v>31062.47</v>
       </c>
       <c r="J30">
-        <v>527</v>
+        <v>807</v>
       </c>
       <c r="K30" t="s">
         <v>471</v>
@@ -5488,7 +5485,7 @@
         <v>27275.03</v>
       </c>
       <c r="J31">
-        <v>152</v>
+        <v>250</v>
       </c>
       <c r="K31" t="s">
         <v>472</v>
@@ -5604,7 +5601,7 @@
         <v>27295.45</v>
       </c>
       <c r="J32">
-        <v>226</v>
+        <v>282</v>
       </c>
       <c r="K32" t="s">
         <v>473</v>
@@ -5720,7 +5717,7 @@
         <v>27576.17</v>
       </c>
       <c r="J33">
-        <v>381</v>
+        <v>599</v>
       </c>
       <c r="K33" t="s">
         <v>474</v>
@@ -5836,7 +5833,7 @@
         <v>33452.41</v>
       </c>
       <c r="J34">
-        <v>479</v>
+        <v>731</v>
       </c>
       <c r="K34" t="s">
         <v>475</v>
@@ -5952,7 +5949,7 @@
         <v>30120.64</v>
       </c>
       <c r="J35">
-        <v>420</v>
+        <v>563</v>
       </c>
       <c r="K35" t="s">
         <v>476</v>
@@ -6068,7 +6065,7 @@
         <v>22073.92</v>
       </c>
       <c r="J36">
-        <v>282</v>
+        <v>435</v>
       </c>
       <c r="K36" t="s">
         <v>477</v>
@@ -6184,7 +6181,7 @@
         <v>22054.11</v>
       </c>
       <c r="J37">
-        <v>362</v>
+        <v>548</v>
       </c>
       <c r="K37" t="s">
         <v>478</v>
@@ -6300,13 +6297,13 @@
         <v>20454.52</v>
       </c>
       <c r="J38">
-        <v>295</v>
+        <v>416</v>
       </c>
       <c r="K38" t="s">
         <v>479</v>
       </c>
       <c r="L38">
-        <v>4998</v>
+        <v>5598</v>
       </c>
       <c r="M38">
         <v>40.85</v>
@@ -6381,10 +6378,10 @@
         <v>65.73999999999999</v>
       </c>
       <c r="AK38">
-        <v>4969</v>
+        <v>4965</v>
       </c>
       <c r="AL38">
-        <v>1514.55</v>
+        <v>1513.33</v>
       </c>
     </row>
     <row r="39" spans="1:38">
@@ -6416,7 +6413,7 @@
         <v>24134.98</v>
       </c>
       <c r="J39">
-        <v>388</v>
+        <v>524</v>
       </c>
       <c r="K39" t="s">
         <v>480</v>
@@ -6532,7 +6529,7 @@
         <v>30659.53</v>
       </c>
       <c r="J40">
-        <v>395</v>
+        <v>552</v>
       </c>
       <c r="K40" t="s">
         <v>481</v>
@@ -6648,7 +6645,7 @@
         <v>22799.95</v>
       </c>
       <c r="J41">
-        <v>486</v>
+        <v>686</v>
       </c>
       <c r="K41" t="s">
         <v>482</v>
@@ -6764,7 +6761,7 @@
         <v>26498.4</v>
       </c>
       <c r="J42">
-        <v>378</v>
+        <v>528</v>
       </c>
       <c r="K42" t="s">
         <v>483</v>
@@ -6880,7 +6877,7 @@
         <v>29330.6</v>
       </c>
       <c r="J43">
-        <v>376</v>
+        <v>564</v>
       </c>
       <c r="K43" t="s">
         <v>462</v>
@@ -6996,13 +6993,13 @@
         <v>31116.12</v>
       </c>
       <c r="J44">
-        <v>492</v>
+        <v>531</v>
       </c>
       <c r="K44" t="s">
         <v>484</v>
       </c>
       <c r="L44">
-        <v>7594</v>
+        <v>5944</v>
       </c>
       <c r="M44">
         <v>7.51</v>
@@ -7053,16 +7050,16 @@
         <v>8.25</v>
       </c>
       <c r="AC44">
-        <v>39.2362166667</v>
+        <v>39.2361333333</v>
       </c>
       <c r="AD44">
-        <v>-103.6967666667</v>
+        <v>-103.6969333333</v>
       </c>
       <c r="AE44">
-        <v>5362</v>
+        <v>5408</v>
       </c>
       <c r="AF44">
-        <v>1634.34</v>
+        <v>1648.36</v>
       </c>
       <c r="AG44">
         <v>39.1518333333</v>
@@ -7112,7 +7109,7 @@
         <v>31472.73</v>
       </c>
       <c r="J45">
-        <v>434</v>
+        <v>580</v>
       </c>
       <c r="K45" t="s">
         <v>485</v>
@@ -7228,7 +7225,7 @@
         <v>24002.7</v>
       </c>
       <c r="J46">
-        <v>195</v>
+        <v>322</v>
       </c>
       <c r="K46" t="s">
         <v>486</v>
@@ -7344,7 +7341,7 @@
         <v>30852.77</v>
       </c>
       <c r="J47">
-        <v>413</v>
+        <v>563</v>
       </c>
       <c r="K47" t="s">
         <v>487</v>
@@ -7460,7 +7457,7 @@
         <v>25859.54</v>
       </c>
       <c r="J48">
-        <v>427</v>
+        <v>601</v>
       </c>
       <c r="K48" t="s">
         <v>488</v>
@@ -7576,7 +7573,7 @@
         <v>28050.44</v>
       </c>
       <c r="J49">
-        <v>460</v>
+        <v>628</v>
       </c>
       <c r="K49" t="s">
         <v>489</v>
@@ -7692,7 +7689,7 @@
         <v>29633.57</v>
       </c>
       <c r="J50">
-        <v>506</v>
+        <v>687</v>
       </c>
       <c r="K50" t="s">
         <v>490</v>
@@ -7808,7 +7805,7 @@
         <v>32055.82</v>
       </c>
       <c r="J51">
-        <v>461</v>
+        <v>613</v>
       </c>
       <c r="K51" t="s">
         <v>491</v>
@@ -7924,7 +7921,7 @@
         <v>19250.56</v>
       </c>
       <c r="J52">
-        <v>329</v>
+        <v>454</v>
       </c>
       <c r="K52" t="s">
         <v>492</v>
@@ -8040,7 +8037,7 @@
         <v>32826.96</v>
       </c>
       <c r="J53">
-        <v>472</v>
+        <v>640</v>
       </c>
       <c r="K53" t="s">
         <v>493</v>
@@ -8156,7 +8153,7 @@
         <v>31589.17</v>
       </c>
       <c r="J54">
-        <v>384</v>
+        <v>525</v>
       </c>
       <c r="K54" t="s">
         <v>487</v>
@@ -8272,7 +8269,7 @@
         <v>26277.11</v>
       </c>
       <c r="J55">
-        <v>212</v>
+        <v>241</v>
       </c>
       <c r="K55" t="s">
         <v>494</v>
@@ -8388,7 +8385,7 @@
         <v>28106.52</v>
       </c>
       <c r="J56">
-        <v>367</v>
+        <v>512</v>
       </c>
       <c r="K56" t="s">
         <v>495</v>
@@ -8504,7 +8501,7 @@
         <v>29048.35</v>
       </c>
       <c r="J57">
-        <v>471</v>
+        <v>637</v>
       </c>
       <c r="K57" t="s">
         <v>489</v>
@@ -8620,7 +8617,7 @@
         <v>33886.75</v>
       </c>
       <c r="J58">
-        <v>573</v>
+        <v>813</v>
       </c>
       <c r="K58" t="s">
         <v>496</v>
@@ -8736,7 +8733,7 @@
         <v>31058.82</v>
       </c>
       <c r="J59">
-        <v>420</v>
+        <v>564</v>
       </c>
       <c r="K59" t="s">
         <v>497</v>
@@ -8852,7 +8849,7 @@
         <v>28350.06</v>
       </c>
       <c r="J60">
-        <v>677</v>
+        <v>950</v>
       </c>
       <c r="K60" t="s">
         <v>498</v>
@@ -8968,7 +8965,7 @@
         <v>26934.87</v>
       </c>
       <c r="J61">
-        <v>352</v>
+        <v>465</v>
       </c>
       <c r="K61" t="s">
         <v>499</v>
@@ -9084,7 +9081,7 @@
         <v>27902.61</v>
       </c>
       <c r="J62">
-        <v>480</v>
+        <v>678</v>
       </c>
       <c r="K62" t="s">
         <v>475</v>
@@ -9200,7 +9197,7 @@
         <v>28033.37</v>
       </c>
       <c r="J63">
-        <v>432</v>
+        <v>601</v>
       </c>
       <c r="K63" t="s">
         <v>500</v>
@@ -9316,7 +9313,7 @@
         <v>28398.22</v>
       </c>
       <c r="J64">
-        <v>493</v>
+        <v>662</v>
       </c>
       <c r="K64" t="s">
         <v>501</v>
@@ -9432,7 +9429,7 @@
         <v>28182.42</v>
       </c>
       <c r="J65">
-        <v>492</v>
+        <v>659</v>
       </c>
       <c r="K65" t="s">
         <v>502</v>
@@ -9548,7 +9545,7 @@
         <v>20625.82</v>
       </c>
       <c r="J66">
-        <v>337</v>
+        <v>457</v>
       </c>
       <c r="K66" t="s">
         <v>503</v>
@@ -9664,7 +9661,7 @@
         <v>28004.41</v>
       </c>
       <c r="J67">
-        <v>429</v>
+        <v>593</v>
       </c>
       <c r="K67" t="s">
         <v>504</v>
@@ -9780,19 +9777,19 @@
         <v>28943.5</v>
       </c>
       <c r="J68">
-        <v>567</v>
+        <v>794</v>
       </c>
       <c r="K68" t="s">
-        <v>505</v>
+        <v>450</v>
       </c>
       <c r="L68">
-        <v>5898</v>
+        <v>5880</v>
       </c>
       <c r="M68">
-        <v>39.34</v>
+        <v>39.31</v>
       </c>
       <c r="N68">
-        <v>63.3</v>
+        <v>63.26</v>
       </c>
       <c r="O68">
         <v>14.77</v>
@@ -9837,34 +9834,34 @@
         <v>11.81</v>
       </c>
       <c r="AC68">
-        <v>39.6085</v>
+        <v>39.6081666667</v>
       </c>
       <c r="AD68">
-        <v>-104.04235</v>
+        <v>-104.0421666667</v>
       </c>
       <c r="AE68">
-        <v>5217</v>
+        <v>5211</v>
       </c>
       <c r="AF68">
-        <v>1590.14</v>
+        <v>1588.31</v>
       </c>
       <c r="AG68">
-        <v>39.2631666667</v>
+        <v>39.2631833333</v>
       </c>
       <c r="AH68">
-        <v>-103.4556666667</v>
+        <v>-103.4557666667</v>
       </c>
       <c r="AI68">
-        <v>39.34</v>
+        <v>39.31</v>
       </c>
       <c r="AJ68">
-        <v>63.3</v>
+        <v>63.26</v>
       </c>
       <c r="AK68">
-        <v>8248</v>
+        <v>8278</v>
       </c>
       <c r="AL68">
-        <v>2513.99</v>
+        <v>2523.13</v>
       </c>
     </row>
     <row r="69" spans="1:38">
@@ -9896,10 +9893,10 @@
         <v>28393.64</v>
       </c>
       <c r="J69">
-        <v>436</v>
+        <v>594</v>
       </c>
       <c r="K69" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="L69">
         <v>6964</v>
@@ -10012,10 +10009,10 @@
         <v>29202.89</v>
       </c>
       <c r="J70">
-        <v>451</v>
+        <v>609</v>
       </c>
       <c r="K70" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="L70">
         <v>6990</v>
@@ -10128,10 +10125,10 @@
         <v>32300.27</v>
       </c>
       <c r="J71">
+        <v>695</v>
+      </c>
+      <c r="K71" t="s">
         <v>507</v>
-      </c>
-      <c r="K71" t="s">
-        <v>508</v>
       </c>
       <c r="L71">
         <v>8097</v>
@@ -10244,13 +10241,13 @@
         <v>29960.62</v>
       </c>
       <c r="J72">
-        <v>733</v>
+        <v>1042</v>
       </c>
       <c r="K72" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="L72">
-        <v>7668</v>
+        <v>7788</v>
       </c>
       <c r="M72">
         <v>41.87</v>
@@ -10325,10 +10322,10 @@
         <v>67.38</v>
       </c>
       <c r="AK72">
-        <v>4697</v>
+        <v>4699</v>
       </c>
       <c r="AL72">
-        <v>1431.65</v>
+        <v>1432.26</v>
       </c>
     </row>
     <row r="73" spans="1:38">
@@ -10360,10 +10357,10 @@
         <v>33012.89</v>
       </c>
       <c r="J73">
-        <v>377</v>
+        <v>515</v>
       </c>
       <c r="K73" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="L73">
         <v>6240</v>
@@ -10476,10 +10473,10 @@
         <v>28324.45</v>
       </c>
       <c r="J74">
-        <v>431</v>
+        <v>580</v>
       </c>
       <c r="K74" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="L74">
         <v>6882</v>
@@ -10592,10 +10589,10 @@
         <v>29625.95</v>
       </c>
       <c r="J75">
-        <v>505</v>
+        <v>679</v>
       </c>
       <c r="K75" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="L75">
         <v>8040</v>
@@ -10708,13 +10705,13 @@
         <v>30095.34</v>
       </c>
       <c r="J76">
-        <v>336</v>
+        <v>622</v>
       </c>
       <c r="K76" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="L76">
-        <v>7920</v>
+        <v>8010</v>
       </c>
       <c r="M76">
         <v>21.98</v>
@@ -10824,13 +10821,13 @@
         <v>30091.68</v>
       </c>
       <c r="J77">
-        <v>464</v>
+        <v>640</v>
       </c>
       <c r="K77" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="L77">
-        <v>8088</v>
+        <v>8148</v>
       </c>
       <c r="M77">
         <v>22.83</v>
@@ -10905,10 +10902,10 @@
         <v>36.75</v>
       </c>
       <c r="AK77">
-        <v>5392</v>
+        <v>5390</v>
       </c>
       <c r="AL77">
-        <v>1643.48</v>
+        <v>1642.87</v>
       </c>
     </row>
     <row r="78" spans="1:38">
@@ -10940,10 +10937,10 @@
         <v>28709.72</v>
       </c>
       <c r="J78">
-        <v>414</v>
+        <v>559</v>
       </c>
       <c r="K78" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="L78">
         <v>6492</v>
@@ -11056,10 +11053,10 @@
         <v>32196.94</v>
       </c>
       <c r="J79">
-        <v>205</v>
+        <v>235</v>
       </c>
       <c r="K79" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="L79">
         <v>7638</v>
@@ -11172,10 +11169,10 @@
         <v>30373.62</v>
       </c>
       <c r="J80">
-        <v>425</v>
+        <v>573</v>
       </c>
       <c r="K80" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="L80">
         <v>6750</v>
@@ -11288,10 +11285,10 @@
         <v>29959.1</v>
       </c>
       <c r="J81">
-        <v>209</v>
+        <v>246</v>
       </c>
       <c r="K81" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="L81">
         <v>5718</v>
@@ -11404,10 +11401,10 @@
         <v>31915</v>
       </c>
       <c r="J82">
-        <v>721</v>
+        <v>979</v>
       </c>
       <c r="K82" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="L82">
         <v>5984</v>
@@ -11520,19 +11517,19 @@
         <v>27361.9</v>
       </c>
       <c r="J83">
-        <v>482</v>
+        <v>665</v>
       </c>
       <c r="K83" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="L83">
-        <v>6810</v>
+        <v>6792</v>
       </c>
       <c r="M83">
-        <v>58.13</v>
+        <v>58.16</v>
       </c>
       <c r="N83">
-        <v>93.55</v>
+        <v>93.59</v>
       </c>
       <c r="O83">
         <v>6.7</v>
@@ -11577,16 +11574,16 @@
         <v>8.01</v>
       </c>
       <c r="AC83">
-        <v>39.6075</v>
+        <v>39.6078333333</v>
       </c>
       <c r="AD83">
-        <v>-104.0411166667</v>
+        <v>-104.0413333333</v>
       </c>
       <c r="AE83">
-        <v>5220</v>
+        <v>5218</v>
       </c>
       <c r="AF83">
-        <v>1591.06</v>
+        <v>1590.45</v>
       </c>
       <c r="AG83">
         <v>38.87505</v>
@@ -11595,10 +11592,10 @@
         <v>-103.50505</v>
       </c>
       <c r="AI83">
-        <v>58.13</v>
+        <v>58.16</v>
       </c>
       <c r="AJ83">
-        <v>93.55</v>
+        <v>93.59</v>
       </c>
       <c r="AK83">
         <v>5473</v>
@@ -11636,10 +11633,10 @@
         <v>27325.62</v>
       </c>
       <c r="J84">
-        <v>435</v>
+        <v>594</v>
       </c>
       <c r="K84" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="L84">
         <v>7533</v>
@@ -11752,10 +11749,10 @@
         <v>27549.65</v>
       </c>
       <c r="J85">
-        <v>512</v>
+        <v>696</v>
       </c>
       <c r="K85" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L85">
         <v>8396</v>
@@ -11868,10 +11865,10 @@
         <v>30593.39</v>
       </c>
       <c r="J86">
-        <v>626</v>
+        <v>894</v>
       </c>
       <c r="K86" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="L86">
         <v>7043</v>
@@ -11984,10 +11981,10 @@
         <v>33555.43</v>
       </c>
       <c r="J87">
-        <v>425</v>
+        <v>569</v>
       </c>
       <c r="K87" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="L87">
         <v>6630</v>
@@ -12100,13 +12097,13 @@
         <v>30007.86</v>
       </c>
       <c r="J88">
-        <v>864</v>
+        <v>1234</v>
       </c>
       <c r="K88" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="L88">
-        <v>9390</v>
+        <v>9450</v>
       </c>
       <c r="M88">
         <v>55.17</v>
@@ -12181,10 +12178,10 @@
         <v>88.78</v>
       </c>
       <c r="AK88">
-        <v>6135</v>
+        <v>6144</v>
       </c>
       <c r="AL88">
-        <v>1869.95</v>
+        <v>1872.69</v>
       </c>
     </row>
     <row r="89" spans="1:38">
@@ -12216,10 +12213,10 @@
         <v>3420.77</v>
       </c>
       <c r="J89">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="K89" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="L89">
         <v>1526</v>
@@ -12332,10 +12329,10 @@
         <v>28377.49</v>
       </c>
       <c r="J90">
-        <v>400</v>
+        <v>538</v>
       </c>
       <c r="K90" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="L90">
         <v>6300</v>
@@ -12448,10 +12445,10 @@
         <v>25712.32</v>
       </c>
       <c r="J91">
-        <v>452</v>
+        <v>651</v>
       </c>
       <c r="K91" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="L91">
         <v>8190</v>
@@ -12564,13 +12561,13 @@
         <v>26009.19</v>
       </c>
       <c r="J92">
-        <v>227</v>
+        <v>386</v>
       </c>
       <c r="K92" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="L92">
-        <v>7113</v>
+        <v>7171</v>
       </c>
       <c r="M92">
         <v>109.11</v>
@@ -12680,10 +12677,10 @@
         <v>31706.21</v>
       </c>
       <c r="J93">
-        <v>474</v>
+        <v>632</v>
       </c>
       <c r="K93" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="L93">
         <v>7380</v>
@@ -12796,10 +12793,10 @@
         <v>33558.78</v>
       </c>
       <c r="J94">
-        <v>357</v>
+        <v>515</v>
       </c>
       <c r="K94" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="L94">
         <v>7830</v>
@@ -12912,10 +12909,10 @@
         <v>27113.79</v>
       </c>
       <c r="J95">
-        <v>365</v>
+        <v>499</v>
       </c>
       <c r="K95" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="L95">
         <v>6495</v>
@@ -13028,10 +13025,10 @@
         <v>28232.1</v>
       </c>
       <c r="J96">
-        <v>487</v>
+        <v>650</v>
       </c>
       <c r="K96" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="L96">
         <v>7830</v>
@@ -13144,10 +13141,10 @@
         <v>32628.84</v>
       </c>
       <c r="J97">
-        <v>784</v>
+        <v>1017</v>
       </c>
       <c r="K97" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L97">
         <v>8910</v>
@@ -13260,10 +13257,10 @@
         <v>31353.86</v>
       </c>
       <c r="J98">
-        <v>500</v>
+        <v>669</v>
       </c>
       <c r="K98" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="L98">
         <v>7695</v>

--- a/www/flightdata/xlsx/flights_metadata.xlsx
+++ b/www/flightdata/xlsx/flights_metadata.xlsx
@@ -2121,7 +2121,7 @@
         <v>27272.59</v>
       </c>
       <c r="J2">
-        <v>355</v>
+        <v>221</v>
       </c>
       <c r="K2" t="s">
         <v>443</v>
@@ -2237,7 +2237,7 @@
         <v>30445.86</v>
       </c>
       <c r="J3">
-        <v>543</v>
+        <v>350</v>
       </c>
       <c r="K3" t="s">
         <v>444</v>
@@ -2353,7 +2353,7 @@
         <v>29202.58</v>
       </c>
       <c r="J4">
-        <v>521</v>
+        <v>331</v>
       </c>
       <c r="K4" t="s">
         <v>445</v>
@@ -2469,7 +2469,7 @@
         <v>31019.5</v>
       </c>
       <c r="J5">
-        <v>599</v>
+        <v>333</v>
       </c>
       <c r="K5" t="s">
         <v>446</v>
@@ -2585,7 +2585,7 @@
         <v>29367.48</v>
       </c>
       <c r="J6">
-        <v>724</v>
+        <v>449</v>
       </c>
       <c r="K6" t="s">
         <v>447</v>
@@ -2701,7 +2701,7 @@
         <v>29403.45</v>
       </c>
       <c r="J7">
-        <v>822</v>
+        <v>542</v>
       </c>
       <c r="K7" t="s">
         <v>448</v>
@@ -2817,7 +2817,7 @@
         <v>28844.14</v>
       </c>
       <c r="J8">
-        <v>778</v>
+        <v>492</v>
       </c>
       <c r="K8" t="s">
         <v>449</v>
@@ -2933,7 +2933,7 @@
         <v>29907.89</v>
       </c>
       <c r="J9">
-        <v>1088</v>
+        <v>709</v>
       </c>
       <c r="K9" t="s">
         <v>450</v>
@@ -3049,7 +3049,7 @@
         <v>29527.2</v>
       </c>
       <c r="J10">
-        <v>896</v>
+        <v>571</v>
       </c>
       <c r="K10" t="s">
         <v>451</v>
@@ -3165,7 +3165,7 @@
         <v>27177.49</v>
       </c>
       <c r="J11">
-        <v>331</v>
+        <v>214</v>
       </c>
       <c r="K11" t="s">
         <v>452</v>
@@ -3281,7 +3281,7 @@
         <v>19231.97</v>
       </c>
       <c r="J12">
-        <v>671</v>
+        <v>439</v>
       </c>
       <c r="K12" t="s">
         <v>453</v>
@@ -3397,7 +3397,7 @@
         <v>28522.27</v>
       </c>
       <c r="J13">
-        <v>720</v>
+        <v>456</v>
       </c>
       <c r="K13" t="s">
         <v>454</v>
@@ -3513,7 +3513,7 @@
         <v>26529.49</v>
       </c>
       <c r="J14">
-        <v>1023</v>
+        <v>673</v>
       </c>
       <c r="K14" t="s">
         <v>455</v>
@@ -3629,7 +3629,7 @@
         <v>27397.25</v>
       </c>
       <c r="J15">
-        <v>670</v>
+        <v>424</v>
       </c>
       <c r="K15" t="s">
         <v>456</v>
@@ -3745,7 +3745,7 @@
         <v>30407.76</v>
       </c>
       <c r="J16">
-        <v>679</v>
+        <v>444</v>
       </c>
       <c r="K16" t="s">
         <v>457</v>
@@ -3861,7 +3861,7 @@
         <v>27814.22</v>
       </c>
       <c r="J17">
-        <v>652</v>
+        <v>487</v>
       </c>
       <c r="K17" t="s">
         <v>458</v>
@@ -3977,7 +3977,7 @@
         <v>28673.76</v>
       </c>
       <c r="J18">
-        <v>954</v>
+        <v>623</v>
       </c>
       <c r="K18" t="s">
         <v>459</v>
@@ -4093,7 +4093,7 @@
         <v>28635.66</v>
       </c>
       <c r="J19">
-        <v>969</v>
+        <v>695</v>
       </c>
       <c r="K19" t="s">
         <v>460</v>
@@ -4209,7 +4209,7 @@
         <v>29112.97</v>
       </c>
       <c r="J20">
-        <v>395</v>
+        <v>258</v>
       </c>
       <c r="K20" t="s">
         <v>461</v>
@@ -4325,7 +4325,7 @@
         <v>27902.61</v>
       </c>
       <c r="J21">
-        <v>765</v>
+        <v>503</v>
       </c>
       <c r="K21" t="s">
         <v>462</v>
@@ -4441,7 +4441,7 @@
         <v>27201.88</v>
       </c>
       <c r="J22">
-        <v>471</v>
+        <v>309</v>
       </c>
       <c r="K22" t="s">
         <v>463</v>
@@ -4557,7 +4557,7 @@
         <v>26864.16</v>
       </c>
       <c r="J23">
-        <v>586</v>
+        <v>375</v>
       </c>
       <c r="K23" t="s">
         <v>464</v>
@@ -4673,7 +4673,7 @@
         <v>27619.45</v>
       </c>
       <c r="J24">
-        <v>671</v>
+        <v>432</v>
       </c>
       <c r="K24" t="s">
         <v>465</v>
@@ -4789,7 +4789,7 @@
         <v>25754.99</v>
       </c>
       <c r="J25">
-        <v>445</v>
+        <v>285</v>
       </c>
       <c r="K25" t="s">
         <v>466</v>
@@ -4905,7 +4905,7 @@
         <v>32334.71</v>
       </c>
       <c r="J26">
-        <v>745</v>
+        <v>488</v>
       </c>
       <c r="K26" t="s">
         <v>467</v>
@@ -5021,7 +5021,7 @@
         <v>30171.24</v>
       </c>
       <c r="J27">
-        <v>649</v>
+        <v>428</v>
       </c>
       <c r="K27" t="s">
         <v>468</v>
@@ -5137,7 +5137,7 @@
         <v>30216.65</v>
       </c>
       <c r="J28">
-        <v>750</v>
+        <v>494</v>
       </c>
       <c r="K28" t="s">
         <v>469</v>
@@ -5253,7 +5253,7 @@
         <v>30473.9</v>
       </c>
       <c r="J29">
-        <v>947</v>
+        <v>627</v>
       </c>
       <c r="K29" t="s">
         <v>470</v>
@@ -5369,7 +5369,7 @@
         <v>31062.47</v>
       </c>
       <c r="J30">
-        <v>807</v>
+        <v>526</v>
       </c>
       <c r="K30" t="s">
         <v>471</v>
@@ -5485,7 +5485,7 @@
         <v>27275.03</v>
       </c>
       <c r="J31">
-        <v>250</v>
+        <v>152</v>
       </c>
       <c r="K31" t="s">
         <v>472</v>
@@ -5601,7 +5601,7 @@
         <v>27295.45</v>
       </c>
       <c r="J32">
-        <v>282</v>
+        <v>226</v>
       </c>
       <c r="K32" t="s">
         <v>473</v>
@@ -5717,7 +5717,7 @@
         <v>27576.17</v>
       </c>
       <c r="J33">
-        <v>599</v>
+        <v>381</v>
       </c>
       <c r="K33" t="s">
         <v>474</v>
@@ -5833,7 +5833,7 @@
         <v>33452.41</v>
       </c>
       <c r="J34">
-        <v>731</v>
+        <v>479</v>
       </c>
       <c r="K34" t="s">
         <v>475</v>
@@ -5949,7 +5949,7 @@
         <v>30120.64</v>
       </c>
       <c r="J35">
-        <v>563</v>
+        <v>420</v>
       </c>
       <c r="K35" t="s">
         <v>476</v>
@@ -6065,7 +6065,7 @@
         <v>22073.92</v>
       </c>
       <c r="J36">
-        <v>435</v>
+        <v>282</v>
       </c>
       <c r="K36" t="s">
         <v>477</v>
@@ -6181,7 +6181,7 @@
         <v>22054.11</v>
       </c>
       <c r="J37">
-        <v>548</v>
+        <v>362</v>
       </c>
       <c r="K37" t="s">
         <v>478</v>
@@ -6297,7 +6297,7 @@
         <v>20454.52</v>
       </c>
       <c r="J38">
-        <v>416</v>
+        <v>302</v>
       </c>
       <c r="K38" t="s">
         <v>479</v>
@@ -6413,7 +6413,7 @@
         <v>24134.98</v>
       </c>
       <c r="J39">
-        <v>524</v>
+        <v>388</v>
       </c>
       <c r="K39" t="s">
         <v>480</v>
@@ -6529,7 +6529,7 @@
         <v>30659.53</v>
       </c>
       <c r="J40">
-        <v>552</v>
+        <v>395</v>
       </c>
       <c r="K40" t="s">
         <v>481</v>
@@ -6645,7 +6645,7 @@
         <v>22799.95</v>
       </c>
       <c r="J41">
-        <v>686</v>
+        <v>486</v>
       </c>
       <c r="K41" t="s">
         <v>482</v>
@@ -6761,7 +6761,7 @@
         <v>26498.4</v>
       </c>
       <c r="J42">
-        <v>528</v>
+        <v>378</v>
       </c>
       <c r="K42" t="s">
         <v>483</v>
@@ -6877,7 +6877,7 @@
         <v>29330.6</v>
       </c>
       <c r="J43">
-        <v>564</v>
+        <v>376</v>
       </c>
       <c r="K43" t="s">
         <v>462</v>
@@ -6993,7 +6993,7 @@
         <v>31116.12</v>
       </c>
       <c r="J44">
-        <v>531</v>
+        <v>392</v>
       </c>
       <c r="K44" t="s">
         <v>484</v>
@@ -7109,7 +7109,7 @@
         <v>31472.73</v>
       </c>
       <c r="J45">
-        <v>580</v>
+        <v>434</v>
       </c>
       <c r="K45" t="s">
         <v>485</v>
@@ -7225,7 +7225,7 @@
         <v>24002.7</v>
       </c>
       <c r="J46">
-        <v>322</v>
+        <v>195</v>
       </c>
       <c r="K46" t="s">
         <v>486</v>
@@ -7341,7 +7341,7 @@
         <v>30852.77</v>
       </c>
       <c r="J47">
-        <v>563</v>
+        <v>413</v>
       </c>
       <c r="K47" t="s">
         <v>487</v>
@@ -7457,7 +7457,7 @@
         <v>25859.54</v>
       </c>
       <c r="J48">
-        <v>601</v>
+        <v>427</v>
       </c>
       <c r="K48" t="s">
         <v>488</v>
@@ -7573,7 +7573,7 @@
         <v>28050.44</v>
       </c>
       <c r="J49">
-        <v>628</v>
+        <v>460</v>
       </c>
       <c r="K49" t="s">
         <v>489</v>
@@ -7689,7 +7689,7 @@
         <v>29633.57</v>
       </c>
       <c r="J50">
-        <v>687</v>
+        <v>506</v>
       </c>
       <c r="K50" t="s">
         <v>490</v>
@@ -7805,7 +7805,7 @@
         <v>32055.82</v>
       </c>
       <c r="J51">
-        <v>613</v>
+        <v>461</v>
       </c>
       <c r="K51" t="s">
         <v>491</v>
@@ -7921,7 +7921,7 @@
         <v>19250.56</v>
       </c>
       <c r="J52">
-        <v>454</v>
+        <v>329</v>
       </c>
       <c r="K52" t="s">
         <v>492</v>
@@ -8037,7 +8037,7 @@
         <v>32826.96</v>
       </c>
       <c r="J53">
-        <v>640</v>
+        <v>472</v>
       </c>
       <c r="K53" t="s">
         <v>493</v>
@@ -8153,7 +8153,7 @@
         <v>31589.17</v>
       </c>
       <c r="J54">
-        <v>525</v>
+        <v>384</v>
       </c>
       <c r="K54" t="s">
         <v>487</v>
@@ -8269,7 +8269,7 @@
         <v>26277.11</v>
       </c>
       <c r="J55">
-        <v>241</v>
+        <v>212</v>
       </c>
       <c r="K55" t="s">
         <v>494</v>
@@ -8385,7 +8385,7 @@
         <v>28106.52</v>
       </c>
       <c r="J56">
-        <v>512</v>
+        <v>367</v>
       </c>
       <c r="K56" t="s">
         <v>495</v>
@@ -8501,7 +8501,7 @@
         <v>29048.35</v>
       </c>
       <c r="J57">
-        <v>637</v>
+        <v>471</v>
       </c>
       <c r="K57" t="s">
         <v>489</v>
@@ -8617,7 +8617,7 @@
         <v>33886.75</v>
       </c>
       <c r="J58">
-        <v>813</v>
+        <v>573</v>
       </c>
       <c r="K58" t="s">
         <v>496</v>
@@ -8733,7 +8733,7 @@
         <v>31058.82</v>
       </c>
       <c r="J59">
-        <v>564</v>
+        <v>420</v>
       </c>
       <c r="K59" t="s">
         <v>497</v>
@@ -8849,7 +8849,7 @@
         <v>28350.06</v>
       </c>
       <c r="J60">
-        <v>950</v>
+        <v>677</v>
       </c>
       <c r="K60" t="s">
         <v>498</v>
@@ -8965,7 +8965,7 @@
         <v>26934.87</v>
       </c>
       <c r="J61">
-        <v>465</v>
+        <v>352</v>
       </c>
       <c r="K61" t="s">
         <v>499</v>
@@ -9081,7 +9081,7 @@
         <v>27902.61</v>
       </c>
       <c r="J62">
-        <v>678</v>
+        <v>480</v>
       </c>
       <c r="K62" t="s">
         <v>475</v>
@@ -9197,7 +9197,7 @@
         <v>28033.37</v>
       </c>
       <c r="J63">
-        <v>601</v>
+        <v>432</v>
       </c>
       <c r="K63" t="s">
         <v>500</v>
@@ -9313,7 +9313,7 @@
         <v>28398.22</v>
       </c>
       <c r="J64">
-        <v>662</v>
+        <v>493</v>
       </c>
       <c r="K64" t="s">
         <v>501</v>
@@ -9429,7 +9429,7 @@
         <v>28182.42</v>
       </c>
       <c r="J65">
-        <v>659</v>
+        <v>492</v>
       </c>
       <c r="K65" t="s">
         <v>502</v>
@@ -9545,7 +9545,7 @@
         <v>20625.82</v>
       </c>
       <c r="J66">
-        <v>457</v>
+        <v>337</v>
       </c>
       <c r="K66" t="s">
         <v>503</v>
@@ -9661,7 +9661,7 @@
         <v>28004.41</v>
       </c>
       <c r="J67">
-        <v>593</v>
+        <v>429</v>
       </c>
       <c r="K67" t="s">
         <v>504</v>
@@ -9777,7 +9777,7 @@
         <v>28943.5</v>
       </c>
       <c r="J68">
-        <v>794</v>
+        <v>566</v>
       </c>
       <c r="K68" t="s">
         <v>450</v>
@@ -9893,7 +9893,7 @@
         <v>28393.64</v>
       </c>
       <c r="J69">
-        <v>594</v>
+        <v>436</v>
       </c>
       <c r="K69" t="s">
         <v>505</v>
@@ -10009,7 +10009,7 @@
         <v>29202.89</v>
       </c>
       <c r="J70">
-        <v>609</v>
+        <v>451</v>
       </c>
       <c r="K70" t="s">
         <v>506</v>
@@ -10125,7 +10125,7 @@
         <v>32300.27</v>
       </c>
       <c r="J71">
-        <v>695</v>
+        <v>507</v>
       </c>
       <c r="K71" t="s">
         <v>507</v>
@@ -10241,7 +10241,7 @@
         <v>29960.62</v>
       </c>
       <c r="J72">
-        <v>1042</v>
+        <v>736</v>
       </c>
       <c r="K72" t="s">
         <v>508</v>
@@ -10357,7 +10357,7 @@
         <v>33012.89</v>
       </c>
       <c r="J73">
-        <v>515</v>
+        <v>377</v>
       </c>
       <c r="K73" t="s">
         <v>509</v>
@@ -10473,7 +10473,7 @@
         <v>28324.45</v>
       </c>
       <c r="J74">
-        <v>580</v>
+        <v>431</v>
       </c>
       <c r="K74" t="s">
         <v>510</v>
@@ -10589,7 +10589,7 @@
         <v>29625.95</v>
       </c>
       <c r="J75">
-        <v>679</v>
+        <v>505</v>
       </c>
       <c r="K75" t="s">
         <v>511</v>
@@ -10705,7 +10705,7 @@
         <v>30095.34</v>
       </c>
       <c r="J76">
-        <v>622</v>
+        <v>337</v>
       </c>
       <c r="K76" t="s">
         <v>512</v>
@@ -10821,7 +10821,7 @@
         <v>30091.68</v>
       </c>
       <c r="J77">
-        <v>640</v>
+        <v>465</v>
       </c>
       <c r="K77" t="s">
         <v>513</v>
@@ -10937,7 +10937,7 @@
         <v>28709.72</v>
       </c>
       <c r="J78">
-        <v>559</v>
+        <v>414</v>
       </c>
       <c r="K78" t="s">
         <v>514</v>
@@ -11053,7 +11053,7 @@
         <v>32196.94</v>
       </c>
       <c r="J79">
-        <v>235</v>
+        <v>205</v>
       </c>
       <c r="K79" t="s">
         <v>515</v>
@@ -11169,7 +11169,7 @@
         <v>30373.62</v>
       </c>
       <c r="J80">
-        <v>573</v>
+        <v>425</v>
       </c>
       <c r="K80" t="s">
         <v>516</v>
@@ -11285,7 +11285,7 @@
         <v>29959.1</v>
       </c>
       <c r="J81">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="K81" t="s">
         <v>517</v>
@@ -11401,7 +11401,7 @@
         <v>31915</v>
       </c>
       <c r="J82">
-        <v>979</v>
+        <v>721</v>
       </c>
       <c r="K82" t="s">
         <v>518</v>
@@ -11517,7 +11517,7 @@
         <v>27361.9</v>
       </c>
       <c r="J83">
-        <v>665</v>
+        <v>481</v>
       </c>
       <c r="K83" t="s">
         <v>519</v>
@@ -11633,7 +11633,7 @@
         <v>27325.62</v>
       </c>
       <c r="J84">
-        <v>594</v>
+        <v>435</v>
       </c>
       <c r="K84" t="s">
         <v>520</v>
@@ -11749,7 +11749,7 @@
         <v>27549.65</v>
       </c>
       <c r="J85">
-        <v>696</v>
+        <v>512</v>
       </c>
       <c r="K85" t="s">
         <v>521</v>
@@ -11865,7 +11865,7 @@
         <v>30593.39</v>
       </c>
       <c r="J86">
-        <v>894</v>
+        <v>626</v>
       </c>
       <c r="K86" t="s">
         <v>522</v>
@@ -11981,7 +11981,7 @@
         <v>33555.43</v>
       </c>
       <c r="J87">
-        <v>569</v>
+        <v>425</v>
       </c>
       <c r="K87" t="s">
         <v>523</v>
@@ -12097,7 +12097,7 @@
         <v>30007.86</v>
       </c>
       <c r="J88">
-        <v>1234</v>
+        <v>866</v>
       </c>
       <c r="K88" t="s">
         <v>524</v>
@@ -12213,7 +12213,7 @@
         <v>3420.77</v>
       </c>
       <c r="J89">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="K89" t="s">
         <v>525</v>
@@ -12329,7 +12329,7 @@
         <v>28377.49</v>
       </c>
       <c r="J90">
-        <v>538</v>
+        <v>400</v>
       </c>
       <c r="K90" t="s">
         <v>526</v>
@@ -12445,7 +12445,7 @@
         <v>25712.32</v>
       </c>
       <c r="J91">
-        <v>651</v>
+        <v>452</v>
       </c>
       <c r="K91" t="s">
         <v>527</v>
@@ -12561,7 +12561,7 @@
         <v>26009.19</v>
       </c>
       <c r="J92">
-        <v>386</v>
+        <v>229</v>
       </c>
       <c r="K92" t="s">
         <v>528</v>
@@ -12677,7 +12677,7 @@
         <v>31706.21</v>
       </c>
       <c r="J93">
-        <v>632</v>
+        <v>474</v>
       </c>
       <c r="K93" t="s">
         <v>529</v>
@@ -12793,7 +12793,7 @@
         <v>33558.78</v>
       </c>
       <c r="J94">
-        <v>515</v>
+        <v>357</v>
       </c>
       <c r="K94" t="s">
         <v>530</v>
@@ -12909,7 +12909,7 @@
         <v>27113.79</v>
       </c>
       <c r="J95">
-        <v>499</v>
+        <v>365</v>
       </c>
       <c r="K95" t="s">
         <v>531</v>
@@ -13025,7 +13025,7 @@
         <v>28232.1</v>
       </c>
       <c r="J96">
-        <v>650</v>
+        <v>487</v>
       </c>
       <c r="K96" t="s">
         <v>530</v>
@@ -13141,7 +13141,7 @@
         <v>32628.84</v>
       </c>
       <c r="J97">
-        <v>1017</v>
+        <v>784</v>
       </c>
       <c r="K97" t="s">
         <v>532</v>
@@ -13257,7 +13257,7 @@
         <v>31353.86</v>
       </c>
       <c r="J98">
-        <v>669</v>
+        <v>500</v>
       </c>
       <c r="K98" t="s">
         <v>533</v>

--- a/www/flightdata/xlsx/flights_metadata.xlsx
+++ b/www/flightdata/xlsx/flights_metadata.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="561">
   <si>
     <t>balloonsize</t>
   </si>
@@ -460,7 +460,7 @@
     <t>EOSS-307</t>
   </si>
   <si>
-    <t>1hrs 39mins 56secs</t>
+    <t>1hrs 39mins 44secs</t>
   </si>
   <si>
     <t>372</t>
@@ -1625,6 +1625,9 @@
   </si>
   <si>
     <t>EOSS-386</t>
+  </si>
+  <si>
+    <t>1hrs 37mins 50secs</t>
   </si>
   <si>
     <t>344</t>
@@ -3466,10 +3469,10 @@
         <v>1483.16</v>
       </c>
       <c r="M11">
-        <v>6.98</v>
+        <v>6.95</v>
       </c>
       <c r="N11">
-        <v>4.34</v>
+        <v>4.32</v>
       </c>
       <c r="O11">
         <v>40.606516666666664</v>
@@ -3478,16 +3481,16 @@
         <v>-104.32368333333334</v>
       </c>
       <c r="Q11">
-        <v>4973</v>
+        <v>4995</v>
       </c>
       <c r="R11">
-        <v>1515.77</v>
+        <v>1522.48</v>
       </c>
       <c r="S11">
-        <v>40.64908333333334</v>
+        <v>40.648833333333336</v>
       </c>
       <c r="T11">
-        <v>-104.3845</v>
+        <v>-104.38433333333332</v>
       </c>
       <c r="U11" t="s">
         <v>68</v>
@@ -3517,10 +3520,10 @@
         <v>1.63</v>
       </c>
       <c r="AD11">
-        <v>6.98</v>
+        <v>6.95</v>
       </c>
       <c r="AE11">
-        <v>4.34</v>
+        <v>4.32</v>
       </c>
       <c r="AF11" t="s">
         <v>107</v>
@@ -3639,7 +3642,7 @@
         <v>30007.86</v>
       </c>
       <c r="X12">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="Y12" t="s">
         <v>53</v>
@@ -4434,7 +4437,7 @@
         <v>148</v>
       </c>
       <c r="I18">
-        <v>5996</v>
+        <v>5984</v>
       </c>
       <c r="J18" t="s">
         <v>149</v>
@@ -4458,16 +4461,16 @@
         <v>-103.01071666666668</v>
       </c>
       <c r="Q18">
-        <v>5235</v>
+        <v>5257</v>
       </c>
       <c r="R18">
-        <v>1595.63</v>
+        <v>1602.33</v>
       </c>
       <c r="S18">
-        <v>39.6085</v>
+        <v>39.60848333333333</v>
       </c>
       <c r="T18">
-        <v>-104.0405</v>
+        <v>-104.04043333333334</v>
       </c>
       <c r="U18" t="s">
         <v>60</v>
@@ -4479,7 +4482,7 @@
         <v>31915</v>
       </c>
       <c r="X18">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="Y18" t="s">
         <v>53</v>
@@ -15491,40 +15494,40 @@
         <v>536</v>
       </c>
       <c r="H97" t="s">
-        <v>218</v>
+        <v>537</v>
       </c>
       <c r="I97">
-        <v>5880</v>
+        <v>5870</v>
       </c>
       <c r="J97" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="K97">
-        <v>5066</v>
+        <v>5140</v>
       </c>
       <c r="L97">
-        <v>1544.12</v>
+        <v>1566.67</v>
       </c>
       <c r="M97">
-        <v>151</v>
+        <v>150.94</v>
       </c>
       <c r="N97">
-        <v>93.83</v>
+        <v>93.79</v>
       </c>
       <c r="O97">
-        <v>39.46233333333333</v>
+        <v>39.463166666666666</v>
       </c>
       <c r="P97">
         <v>-102.612</v>
       </c>
       <c r="Q97">
-        <v>4555</v>
+        <v>4567</v>
       </c>
       <c r="R97">
-        <v>1388.36</v>
+        <v>1392.02</v>
       </c>
       <c r="S97">
-        <v>40.224833333333336</v>
+        <v>40.224666666666664</v>
       </c>
       <c r="T97">
         <v>-104.07716666666668</v>
@@ -15539,7 +15542,7 @@
         <v>30445.86</v>
       </c>
       <c r="X97">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="Y97" t="s">
         <v>53</v>
@@ -15557,13 +15560,13 @@
         <v>1.7</v>
       </c>
       <c r="AD97">
-        <v>151</v>
+        <v>150.94</v>
       </c>
       <c r="AE97">
-        <v>93.83</v>
+        <v>93.79</v>
       </c>
       <c r="AF97" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG97">
         <v>3</v>
@@ -15628,16 +15631,16 @@
         <v>1</v>
       </c>
       <c r="G98" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H98" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="I98">
         <v>5827</v>
       </c>
       <c r="J98" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="K98">
         <v>4606</v>
@@ -15703,7 +15706,7 @@
         <v>101.65</v>
       </c>
       <c r="AF98" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG98">
         <v>3</v>
@@ -15753,10 +15756,10 @@
         <v>62</v>
       </c>
       <c r="B99" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C99" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D99">
         <v>76670</v>
@@ -15768,7 +15771,7 @@
         <v>1</v>
       </c>
       <c r="G99" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H99" t="s">
         <v>160</v>
@@ -15777,7 +15780,7 @@
         <v>6750</v>
       </c>
       <c r="J99" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="K99">
         <v>5967</v>
@@ -15843,7 +15846,7 @@
         <v>112.5</v>
       </c>
       <c r="AF99" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG99">
         <v>1.5</v>
@@ -15893,10 +15896,10 @@
         <v>62</v>
       </c>
       <c r="B100" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C100" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D100">
         <v>91765</v>
@@ -15908,10 +15911,10 @@
         <v>1</v>
       </c>
       <c r="G100" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H100" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="I100">
         <v>7500</v>
@@ -15983,7 +15986,7 @@
         <v>109.03</v>
       </c>
       <c r="AF100" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG100">
         <v>1.5</v>
@@ -16033,10 +16036,10 @@
         <v>62</v>
       </c>
       <c r="B101" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C101" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D101">
         <v>94256</v>
@@ -16048,10 +16051,10 @@
         <v>1</v>
       </c>
       <c r="G101" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H101" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="I101">
         <v>7559</v>
@@ -16123,7 +16126,7 @@
         <v>106.3</v>
       </c>
       <c r="AF101" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG101">
         <v>1.5</v>
@@ -16173,10 +16176,10 @@
         <v>62</v>
       </c>
       <c r="B102" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C102" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D102">
         <v>91900</v>
@@ -16188,10 +16191,10 @@
         <v>1</v>
       </c>
       <c r="G102" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H102" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="I102">
         <v>6922</v>
@@ -16263,7 +16266,7 @@
         <v>41.83</v>
       </c>
       <c r="AF102" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG102">
         <v>1.5</v>

--- a/www/flightdata/xlsx/flights_metadata.xlsx
+++ b/www/flightdata/xlsx/flights_metadata.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="571">
   <si>
     <t>balloonsize</t>
   </si>
@@ -1697,6 +1697,36 @@
   </si>
   <si>
     <t>[{"altitude_ft":61585.0,"altitude_m":18771.11,"transition":"high_to_low"}]</t>
+  </si>
+  <si>
+    <t>2026-04-04</t>
+  </si>
+  <si>
+    <t>EOSS-392</t>
+  </si>
+  <si>
+    <t>1hrs 38mins 1secs</t>
+  </si>
+  <si>
+    <t>371</t>
+  </si>
+  <si>
+    <t>[{"altitude_ft":58392.0,"altitude_m":17797.88,"transition":"high_to_low"}]</t>
+  </si>
+  <si>
+    <t>["AE0SS-1","AE0SS-3"]</t>
+  </si>
+  <si>
+    <t>EOSS-393</t>
+  </si>
+  <si>
+    <t>2hrs 0mins 30secs</t>
+  </si>
+  <si>
+    <t>374</t>
+  </si>
+  <si>
+    <t>[{"altitude_ft":62992.0,"altitude_m":19199.96,"transition":"high_to_low"}]</t>
   </si>
 </sst>
 </file>
@@ -2028,7 +2058,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AT102"/>
+  <dimension ref="A1:AT104"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:46">
@@ -16311,6 +16341,286 @@
         <v>1.7</v>
       </c>
     </row>
+    <row r="103" spans="1:46">
+      <c r="A103" t="s">
+        <v>46</v>
+      </c>
+      <c r="B103" t="s">
+        <v>552</v>
+      </c>
+      <c r="C103" t="s">
+        <v>561</v>
+      </c>
+      <c r="D103">
+        <v>84489</v>
+      </c>
+      <c r="E103">
+        <v>25752.25</v>
+      </c>
+      <c r="F103" t="b">
+        <v>1</v>
+      </c>
+      <c r="G103" t="s">
+        <v>562</v>
+      </c>
+      <c r="H103" t="s">
+        <v>563</v>
+      </c>
+      <c r="I103">
+        <v>5881</v>
+      </c>
+      <c r="J103" t="s">
+        <v>564</v>
+      </c>
+      <c r="K103">
+        <v>5794</v>
+      </c>
+      <c r="L103">
+        <v>1766.01</v>
+      </c>
+      <c r="M103">
+        <v>83.62</v>
+      </c>
+      <c r="N103">
+        <v>51.96</v>
+      </c>
+      <c r="O103">
+        <v>39.25783333333333</v>
+      </c>
+      <c r="P103">
+        <v>-103.17983333333332</v>
+      </c>
+      <c r="Q103">
+        <v>5210</v>
+      </c>
+      <c r="R103">
+        <v>1588.01</v>
+      </c>
+      <c r="S103">
+        <v>39.60816666666667</v>
+      </c>
+      <c r="T103">
+        <v>-104.04216666666666</v>
+      </c>
+      <c r="U103" t="s">
+        <v>156</v>
+      </c>
+      <c r="V103">
+        <v>84283</v>
+      </c>
+      <c r="W103">
+        <v>25689.46</v>
+      </c>
+      <c r="X103">
+        <v>241</v>
+      </c>
+      <c r="Y103" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z103">
+        <v>12</v>
+      </c>
+      <c r="AA103">
+        <v>3.66</v>
+      </c>
+      <c r="AB103">
+        <v>0.77</v>
+      </c>
+      <c r="AC103">
+        <v>1.7</v>
+      </c>
+      <c r="AD103">
+        <v>83.62</v>
+      </c>
+      <c r="AE103">
+        <v>51.96</v>
+      </c>
+      <c r="AF103" t="s">
+        <v>565</v>
+      </c>
+      <c r="AG103">
+        <v>3</v>
+      </c>
+      <c r="AH103">
+        <v>6.61</v>
+      </c>
+      <c r="AI103">
+        <v>5.07</v>
+      </c>
+      <c r="AJ103">
+        <v>11.18</v>
+      </c>
+      <c r="AK103">
+        <v>1.53</v>
+      </c>
+      <c r="AL103">
+        <v>3.38</v>
+      </c>
+      <c r="AM103">
+        <v>10.37</v>
+      </c>
+      <c r="AN103">
+        <v>22.86</v>
+      </c>
+      <c r="AO103">
+        <v>9.44</v>
+      </c>
+      <c r="AP103">
+        <v>20.82</v>
+      </c>
+      <c r="AQ103">
+        <v>7.37</v>
+      </c>
+      <c r="AR103">
+        <v>16.25</v>
+      </c>
+      <c r="AS103">
+        <v>0.77</v>
+      </c>
+      <c r="AT103">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="104" spans="1:46">
+      <c r="A104" t="s">
+        <v>46</v>
+      </c>
+      <c r="B104" t="s">
+        <v>566</v>
+      </c>
+      <c r="C104" t="s">
+        <v>561</v>
+      </c>
+      <c r="D104">
+        <v>97827</v>
+      </c>
+      <c r="E104">
+        <v>29817.67</v>
+      </c>
+      <c r="F104" t="b">
+        <v>1</v>
+      </c>
+      <c r="G104" t="s">
+        <v>567</v>
+      </c>
+      <c r="H104" t="s">
+        <v>568</v>
+      </c>
+      <c r="I104">
+        <v>7230</v>
+      </c>
+      <c r="J104" t="s">
+        <v>569</v>
+      </c>
+      <c r="K104">
+        <v>4885</v>
+      </c>
+      <c r="L104">
+        <v>1488.95</v>
+      </c>
+      <c r="M104">
+        <v>96.51</v>
+      </c>
+      <c r="N104">
+        <v>59.97</v>
+      </c>
+      <c r="O104">
+        <v>39.25083333333333</v>
+      </c>
+      <c r="P104">
+        <v>-103.01733333333334</v>
+      </c>
+      <c r="Q104">
+        <v>5214</v>
+      </c>
+      <c r="R104">
+        <v>1589.23</v>
+      </c>
+      <c r="S104">
+        <v>39.60816666666667</v>
+      </c>
+      <c r="T104">
+        <v>-104.04233333333332</v>
+      </c>
+      <c r="U104" t="s">
+        <v>156</v>
+      </c>
+      <c r="V104">
+        <v>97827</v>
+      </c>
+      <c r="W104">
+        <v>29817.67</v>
+      </c>
+      <c r="X104">
+        <v>456</v>
+      </c>
+      <c r="Y104" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z104">
+        <v>12</v>
+      </c>
+      <c r="AA104">
+        <v>3.66</v>
+      </c>
+      <c r="AB104">
+        <v>0.79</v>
+      </c>
+      <c r="AC104">
+        <v>1.75</v>
+      </c>
+      <c r="AD104">
+        <v>96.51</v>
+      </c>
+      <c r="AE104">
+        <v>59.97</v>
+      </c>
+      <c r="AF104" t="s">
+        <v>570</v>
+      </c>
+      <c r="AG104">
+        <v>3</v>
+      </c>
+      <c r="AH104">
+        <v>6.61</v>
+      </c>
+      <c r="AI104">
+        <v>5.2</v>
+      </c>
+      <c r="AJ104">
+        <v>11.47</v>
+      </c>
+      <c r="AK104">
+        <v>1.46</v>
+      </c>
+      <c r="AL104">
+        <v>3.21</v>
+      </c>
+      <c r="AM104">
+        <v>10.45</v>
+      </c>
+      <c r="AN104">
+        <v>23.04</v>
+      </c>
+      <c r="AO104">
+        <v>9.54</v>
+      </c>
+      <c r="AP104">
+        <v>21.04</v>
+      </c>
+      <c r="AQ104">
+        <v>7.45</v>
+      </c>
+      <c r="AR104">
+        <v>16.43</v>
+      </c>
+      <c r="AS104">
+        <v>0.79</v>
+      </c>
+      <c r="AT104">
+        <v>1.75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/www/flightdata/xlsx/flights_metadata.xlsx
+++ b/www/flightdata/xlsx/flights_metadata.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="991" uniqueCount="579">
   <si>
     <t>balloonsize</t>
   </si>
@@ -1727,6 +1727,30 @@
   </si>
   <si>
     <t>[{"altitude_ft":62992.0,"altitude_m":19199.96,"transition":"high_to_low"}]</t>
+  </si>
+  <si>
+    <t>2026-04-12</t>
+  </si>
+  <si>
+    <t>EOSS-394</t>
+  </si>
+  <si>
+    <t>2hrs 7mins 30secs</t>
+  </si>
+  <si>
+    <t>[{"altitude_ft":41952.0,"altitude_m":12786.97,"transition":"high_to_low"},{"altitude_ft":54733.0,"altitude_m":16682.62,"transition":"low_to_high"}]</t>
+  </si>
+  <si>
+    <t>["KC0D-2","K0SCC-13","AE0SS-4"]</t>
+  </si>
+  <si>
+    <t>EOSS-395</t>
+  </si>
+  <si>
+    <t>1hrs 55mins 29secs</t>
+  </si>
+  <si>
+    <t>[{"altitude_ft":12263.0,"altitude_m":3737.76,"transition":"low_to_high"},{"altitude_ft":64144.0,"altitude_m":19551.09,"transition":"high_to_low"}]</t>
   </si>
 </sst>
 </file>
@@ -2058,7 +2082,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AT104"/>
+  <dimension ref="A1:AT106"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:46">
@@ -16621,6 +16645,286 @@
         <v>1.75</v>
       </c>
     </row>
+    <row r="105" spans="1:46">
+      <c r="A105" t="s">
+        <v>62</v>
+      </c>
+      <c r="B105" t="s">
+        <v>566</v>
+      </c>
+      <c r="C105" t="s">
+        <v>571</v>
+      </c>
+      <c r="D105">
+        <v>91837</v>
+      </c>
+      <c r="E105">
+        <v>27991.92</v>
+      </c>
+      <c r="F105" t="b">
+        <v>1</v>
+      </c>
+      <c r="G105" t="s">
+        <v>572</v>
+      </c>
+      <c r="H105" t="s">
+        <v>573</v>
+      </c>
+      <c r="I105">
+        <v>7650</v>
+      </c>
+      <c r="J105" t="s">
+        <v>372</v>
+      </c>
+      <c r="K105">
+        <v>4595</v>
+      </c>
+      <c r="L105">
+        <v>1400.56</v>
+      </c>
+      <c r="M105">
+        <v>90.57</v>
+      </c>
+      <c r="N105">
+        <v>56.28</v>
+      </c>
+      <c r="O105">
+        <v>40.01166666666666</v>
+      </c>
+      <c r="P105">
+        <v>-103.12033333333332</v>
+      </c>
+      <c r="Q105">
+        <v>5216</v>
+      </c>
+      <c r="R105">
+        <v>1589.84</v>
+      </c>
+      <c r="S105">
+        <v>39.608</v>
+      </c>
+      <c r="T105">
+        <v>-104.04216666666666</v>
+      </c>
+      <c r="U105" t="s">
+        <v>118</v>
+      </c>
+      <c r="V105">
+        <v>91612</v>
+      </c>
+      <c r="W105">
+        <v>27923.34</v>
+      </c>
+      <c r="X105">
+        <v>302</v>
+      </c>
+      <c r="Y105" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z105">
+        <v>12</v>
+      </c>
+      <c r="AA105">
+        <v>3.66</v>
+      </c>
+      <c r="AB105">
+        <v>0.79</v>
+      </c>
+      <c r="AC105">
+        <v>1.75</v>
+      </c>
+      <c r="AD105">
+        <v>90.57</v>
+      </c>
+      <c r="AE105">
+        <v>56.28</v>
+      </c>
+      <c r="AF105" t="s">
+        <v>574</v>
+      </c>
+      <c r="AG105">
+        <v>1.5</v>
+      </c>
+      <c r="AH105">
+        <v>3.31</v>
+      </c>
+      <c r="AI105">
+        <v>3.46</v>
+      </c>
+      <c r="AJ105">
+        <v>7.62</v>
+      </c>
+      <c r="AK105">
+        <v>1.65</v>
+      </c>
+      <c r="AL105">
+        <v>3.64</v>
+      </c>
+      <c r="AM105">
+        <v>7.4</v>
+      </c>
+      <c r="AN105">
+        <v>16.32</v>
+      </c>
+      <c r="AO105">
+        <v>8.12</v>
+      </c>
+      <c r="AP105">
+        <v>17.91</v>
+      </c>
+      <c r="AQ105">
+        <v>5.9</v>
+      </c>
+      <c r="AR105">
+        <v>13.01</v>
+      </c>
+      <c r="AS105">
+        <v>0.79</v>
+      </c>
+      <c r="AT105">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="106" spans="1:46">
+      <c r="A106" t="s">
+        <v>46</v>
+      </c>
+      <c r="B106" t="s">
+        <v>575</v>
+      </c>
+      <c r="C106" t="s">
+        <v>571</v>
+      </c>
+      <c r="D106">
+        <v>99167</v>
+      </c>
+      <c r="E106">
+        <v>30226.1</v>
+      </c>
+      <c r="F106" t="b">
+        <v>1</v>
+      </c>
+      <c r="G106" t="s">
+        <v>576</v>
+      </c>
+      <c r="H106" t="s">
+        <v>577</v>
+      </c>
+      <c r="I106">
+        <v>6929</v>
+      </c>
+      <c r="J106" t="s">
+        <v>263</v>
+      </c>
+      <c r="K106">
+        <v>4617</v>
+      </c>
+      <c r="L106">
+        <v>1407.26</v>
+      </c>
+      <c r="M106">
+        <v>85.13</v>
+      </c>
+      <c r="N106">
+        <v>52.9</v>
+      </c>
+      <c r="O106">
+        <v>39.89648333333333</v>
+      </c>
+      <c r="P106">
+        <v>-103.11896666666668</v>
+      </c>
+      <c r="Q106">
+        <v>5211</v>
+      </c>
+      <c r="R106">
+        <v>1588.31</v>
+      </c>
+      <c r="S106">
+        <v>39.608</v>
+      </c>
+      <c r="T106">
+        <v>-104.04216666666666</v>
+      </c>
+      <c r="U106" t="s">
+        <v>156</v>
+      </c>
+      <c r="V106">
+        <v>99059</v>
+      </c>
+      <c r="W106">
+        <v>30193.18</v>
+      </c>
+      <c r="X106">
+        <v>353</v>
+      </c>
+      <c r="Y106" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z106">
+        <v>12</v>
+      </c>
+      <c r="AA106">
+        <v>3.66</v>
+      </c>
+      <c r="AB106">
+        <v>0.77</v>
+      </c>
+      <c r="AC106">
+        <v>1.7</v>
+      </c>
+      <c r="AD106">
+        <v>85.13</v>
+      </c>
+      <c r="AE106">
+        <v>52.9</v>
+      </c>
+      <c r="AF106" t="s">
+        <v>578</v>
+      </c>
+      <c r="AG106">
+        <v>3</v>
+      </c>
+      <c r="AH106">
+        <v>6.61</v>
+      </c>
+      <c r="AI106">
+        <v>7.02</v>
+      </c>
+      <c r="AJ106">
+        <v>15.47</v>
+      </c>
+      <c r="AK106">
+        <v>2.08</v>
+      </c>
+      <c r="AL106">
+        <v>4.58</v>
+      </c>
+      <c r="AM106">
+        <v>12.86</v>
+      </c>
+      <c r="AN106">
+        <v>28.36</v>
+      </c>
+      <c r="AO106">
+        <v>12.44</v>
+      </c>
+      <c r="AP106">
+        <v>27.42</v>
+      </c>
+      <c r="AQ106">
+        <v>9.87</v>
+      </c>
+      <c r="AR106">
+        <v>21.75</v>
+      </c>
+      <c r="AS106">
+        <v>0.77</v>
+      </c>
+      <c r="AT106">
+        <v>1.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/www/flightdata/xlsx/flights_metadata.xlsx
+++ b/www/flightdata/xlsx/flights_metadata.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="991" uniqueCount="579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="588">
   <si>
     <t>balloonsize</t>
   </si>
@@ -1751,6 +1751,33 @@
   </si>
   <si>
     <t>[{"altitude_ft":12263.0,"altitude_m":3737.76,"transition":"low_to_high"},{"altitude_ft":64144.0,"altitude_m":19551.09,"transition":"high_to_low"}]</t>
+  </si>
+  <si>
+    <t>2026-04-19</t>
+  </si>
+  <si>
+    <t>EOSS-396</t>
+  </si>
+  <si>
+    <t>359</t>
+  </si>
+  <si>
+    <t>[{"altitude_ft":37233.0,"altitude_m":11348.62,"transition":"high_to_low"}]</t>
+  </si>
+  <si>
+    <t>["AE0SS-1","K0SCC-13","AE0SS-3"]</t>
+  </si>
+  <si>
+    <t>EOSS-397</t>
+  </si>
+  <si>
+    <t>2hrs 19mins 30secs</t>
+  </si>
+  <si>
+    <t>396</t>
+  </si>
+  <si>
+    <t>[{"altitude_ft":36584.0,"altitude_m":11150.8,"transition":"high_to_low"}]</t>
   </si>
 </sst>
 </file>
@@ -2082,7 +2109,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AT106"/>
+  <dimension ref="A1:AT108"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:46">
@@ -16925,6 +16952,286 @@
         <v>1.7</v>
       </c>
     </row>
+    <row r="107" spans="1:46">
+      <c r="A107" t="s">
+        <v>46</v>
+      </c>
+      <c r="B107" t="s">
+        <v>552</v>
+      </c>
+      <c r="C107" t="s">
+        <v>579</v>
+      </c>
+      <c r="D107">
+        <v>84042</v>
+      </c>
+      <c r="E107">
+        <v>25616</v>
+      </c>
+      <c r="F107" t="b">
+        <v>1</v>
+      </c>
+      <c r="G107" t="s">
+        <v>580</v>
+      </c>
+      <c r="H107" t="s">
+        <v>568</v>
+      </c>
+      <c r="I107">
+        <v>7230</v>
+      </c>
+      <c r="J107" t="s">
+        <v>581</v>
+      </c>
+      <c r="K107">
+        <v>4468</v>
+      </c>
+      <c r="L107">
+        <v>1361.85</v>
+      </c>
+      <c r="M107">
+        <v>140.9</v>
+      </c>
+      <c r="N107">
+        <v>87.55</v>
+      </c>
+      <c r="O107">
+        <v>39.20616666666667</v>
+      </c>
+      <c r="P107">
+        <v>-102.48566666666666</v>
+      </c>
+      <c r="Q107">
+        <v>5214</v>
+      </c>
+      <c r="R107">
+        <v>1589.23</v>
+      </c>
+      <c r="S107">
+        <v>39.608</v>
+      </c>
+      <c r="T107">
+        <v>-104.04216666666666</v>
+      </c>
+      <c r="U107" t="s">
+        <v>156</v>
+      </c>
+      <c r="V107">
+        <v>83849</v>
+      </c>
+      <c r="W107">
+        <v>25557.18</v>
+      </c>
+      <c r="X107">
+        <v>251</v>
+      </c>
+      <c r="Y107" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z107">
+        <v>12</v>
+      </c>
+      <c r="AA107">
+        <v>3.66</v>
+      </c>
+      <c r="AB107">
+        <v>0.77</v>
+      </c>
+      <c r="AC107">
+        <v>1.7</v>
+      </c>
+      <c r="AD107">
+        <v>140.9</v>
+      </c>
+      <c r="AE107">
+        <v>87.55</v>
+      </c>
+      <c r="AF107" t="s">
+        <v>582</v>
+      </c>
+      <c r="AG107">
+        <v>3</v>
+      </c>
+      <c r="AH107">
+        <v>6.61</v>
+      </c>
+      <c r="AI107">
+        <v>4.75</v>
+      </c>
+      <c r="AJ107">
+        <v>10.48</v>
+      </c>
+      <c r="AK107">
+        <v>1.53</v>
+      </c>
+      <c r="AL107">
+        <v>3.38</v>
+      </c>
+      <c r="AM107">
+        <v>10.06</v>
+      </c>
+      <c r="AN107">
+        <v>22.17</v>
+      </c>
+      <c r="AO107">
+        <v>9.07</v>
+      </c>
+      <c r="AP107">
+        <v>19.99</v>
+      </c>
+      <c r="AQ107">
+        <v>7.06</v>
+      </c>
+      <c r="AR107">
+        <v>15.56</v>
+      </c>
+      <c r="AS107">
+        <v>0.77</v>
+      </c>
+      <c r="AT107">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="108" spans="1:46">
+      <c r="A108" t="s">
+        <v>46</v>
+      </c>
+      <c r="B108" t="s">
+        <v>583</v>
+      </c>
+      <c r="C108" t="s">
+        <v>579</v>
+      </c>
+      <c r="D108">
+        <v>96668</v>
+      </c>
+      <c r="E108">
+        <v>29464.41</v>
+      </c>
+      <c r="F108" t="b">
+        <v>1</v>
+      </c>
+      <c r="G108" t="s">
+        <v>584</v>
+      </c>
+      <c r="H108" t="s">
+        <v>585</v>
+      </c>
+      <c r="I108">
+        <v>8370</v>
+      </c>
+      <c r="J108" t="s">
+        <v>586</v>
+      </c>
+      <c r="K108">
+        <v>5253</v>
+      </c>
+      <c r="L108">
+        <v>1601.11</v>
+      </c>
+      <c r="M108">
+        <v>166.37</v>
+      </c>
+      <c r="N108">
+        <v>103.38</v>
+      </c>
+      <c r="O108">
+        <v>39.13243333333334</v>
+      </c>
+      <c r="P108">
+        <v>-102.20588333333332</v>
+      </c>
+      <c r="Q108">
+        <v>5224</v>
+      </c>
+      <c r="R108">
+        <v>1592.28</v>
+      </c>
+      <c r="S108">
+        <v>39.6082</v>
+      </c>
+      <c r="T108">
+        <v>-104.0423</v>
+      </c>
+      <c r="U108" t="s">
+        <v>156</v>
+      </c>
+      <c r="V108">
+        <v>96417</v>
+      </c>
+      <c r="W108">
+        <v>29387.9</v>
+      </c>
+      <c r="X108">
+        <v>800</v>
+      </c>
+      <c r="Y108" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z108">
+        <v>12</v>
+      </c>
+      <c r="AA108">
+        <v>3.66</v>
+      </c>
+      <c r="AB108">
+        <v>0.82</v>
+      </c>
+      <c r="AC108">
+        <v>1.81</v>
+      </c>
+      <c r="AD108">
+        <v>166.37</v>
+      </c>
+      <c r="AE108">
+        <v>103.38</v>
+      </c>
+      <c r="AF108" t="s">
+        <v>587</v>
+      </c>
+      <c r="AG108">
+        <v>3</v>
+      </c>
+      <c r="AH108">
+        <v>6.61</v>
+      </c>
+      <c r="AI108">
+        <v>5.06</v>
+      </c>
+      <c r="AJ108">
+        <v>11.15</v>
+      </c>
+      <c r="AK108">
+        <v>2.2</v>
+      </c>
+      <c r="AL108">
+        <v>4.84</v>
+      </c>
+      <c r="AM108">
+        <v>11.07</v>
+      </c>
+      <c r="AN108">
+        <v>24.41</v>
+      </c>
+      <c r="AO108">
+        <v>10.29</v>
+      </c>
+      <c r="AP108">
+        <v>22.68</v>
+      </c>
+      <c r="AQ108">
+        <v>8.07</v>
+      </c>
+      <c r="AR108">
+        <v>17.8</v>
+      </c>
+      <c r="AS108">
+        <v>0.82</v>
+      </c>
+      <c r="AT108">
+        <v>1.81</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/www/flightdata/xlsx/flights_metadata.xlsx
+++ b/www/flightdata/xlsx/flights_metadata.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="602">
   <si>
     <t>balloonsize</t>
   </si>
@@ -1778,6 +1778,48 @@
   </si>
   <si>
     <t>[{"altitude_ft":36584.0,"altitude_m":11150.8,"transition":"high_to_low"}]</t>
+  </si>
+  <si>
+    <t>["KC0D-2","K0SCC-13"]</t>
+  </si>
+  <si>
+    <t>2026-05-02</t>
+  </si>
+  <si>
+    <t>EOSS-398</t>
+  </si>
+  <si>
+    <t>1hrs 48mins 30secs</t>
+  </si>
+  <si>
+    <t>293</t>
+  </si>
+  <si>
+    <t>[{"altitude_ft":52824.0,"altitude_m":16100.76,"transition":"high_to_low"}]</t>
+  </si>
+  <si>
+    <t>["KC0D-3","AE0SS-3"]</t>
+  </si>
+  <si>
+    <t>EOSS-399</t>
+  </si>
+  <si>
+    <t>[{"altitude_ft":46553.0,"altitude_m":14189.35,"transition":"high_to_low"}]</t>
+  </si>
+  <si>
+    <t>["KC0D-14","AE0SS-4","K0SCC-14"]</t>
+  </si>
+  <si>
+    <t>EOSS-400</t>
+  </si>
+  <si>
+    <t>2hrs 13mins 0secs</t>
+  </si>
+  <si>
+    <t>316</t>
+  </si>
+  <si>
+    <t>[{"altitude_ft":41058.0,"altitude_m":12514.48,"transition":"high_to_low"}]</t>
   </si>
 </sst>
 </file>
@@ -2109,7 +2151,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AT108"/>
+  <dimension ref="A1:AT111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:46">
@@ -17232,6 +17274,426 @@
         <v>1.81</v>
       </c>
     </row>
+    <row r="109" spans="1:46">
+      <c r="A109" t="s">
+        <v>62</v>
+      </c>
+      <c r="B109" t="s">
+        <v>588</v>
+      </c>
+      <c r="C109" t="s">
+        <v>589</v>
+      </c>
+      <c r="D109">
+        <v>89253</v>
+      </c>
+      <c r="E109">
+        <v>27204.31</v>
+      </c>
+      <c r="F109" t="b">
+        <v>1</v>
+      </c>
+      <c r="G109" t="s">
+        <v>590</v>
+      </c>
+      <c r="H109" t="s">
+        <v>591</v>
+      </c>
+      <c r="I109">
+        <v>6510</v>
+      </c>
+      <c r="J109" t="s">
+        <v>592</v>
+      </c>
+      <c r="K109">
+        <v>7525</v>
+      </c>
+      <c r="L109">
+        <v>2293.62</v>
+      </c>
+      <c r="M109">
+        <v>54.17</v>
+      </c>
+      <c r="N109">
+        <v>33.66</v>
+      </c>
+      <c r="O109">
+        <v>39.27166666666667</v>
+      </c>
+      <c r="P109">
+        <v>-103.58533333333334</v>
+      </c>
+      <c r="Q109">
+        <v>5222</v>
+      </c>
+      <c r="R109">
+        <v>1591.67</v>
+      </c>
+      <c r="S109">
+        <v>39.608</v>
+      </c>
+      <c r="T109">
+        <v>-104.04216666666666</v>
+      </c>
+      <c r="U109" t="s">
+        <v>118</v>
+      </c>
+      <c r="V109">
+        <v>89063</v>
+      </c>
+      <c r="W109">
+        <v>27146.4</v>
+      </c>
+      <c r="X109">
+        <v>417</v>
+      </c>
+      <c r="Y109" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z109">
+        <v>12</v>
+      </c>
+      <c r="AA109">
+        <v>3.66</v>
+      </c>
+      <c r="AB109">
+        <v>0.77</v>
+      </c>
+      <c r="AC109">
+        <v>1.7</v>
+      </c>
+      <c r="AD109">
+        <v>54.17</v>
+      </c>
+      <c r="AE109">
+        <v>33.66</v>
+      </c>
+      <c r="AF109" t="s">
+        <v>593</v>
+      </c>
+      <c r="AG109">
+        <v>1.5</v>
+      </c>
+      <c r="AH109">
+        <v>3.31</v>
+      </c>
+      <c r="AI109">
+        <v>3.7</v>
+      </c>
+      <c r="AJ109">
+        <v>8.16</v>
+      </c>
+      <c r="AK109">
+        <v>1.61</v>
+      </c>
+      <c r="AL109">
+        <v>3.54</v>
+      </c>
+      <c r="AM109">
+        <v>7.57</v>
+      </c>
+      <c r="AN109">
+        <v>16.7</v>
+      </c>
+      <c r="AO109">
+        <v>8.35</v>
+      </c>
+      <c r="AP109">
+        <v>18.4</v>
+      </c>
+      <c r="AQ109">
+        <v>6.07</v>
+      </c>
+      <c r="AR109">
+        <v>13.39</v>
+      </c>
+      <c r="AS109">
+        <v>0.77</v>
+      </c>
+      <c r="AT109">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="110" spans="1:46">
+      <c r="A110" t="s">
+        <v>62</v>
+      </c>
+      <c r="B110" t="s">
+        <v>594</v>
+      </c>
+      <c r="C110" t="s">
+        <v>589</v>
+      </c>
+      <c r="D110">
+        <v>87335</v>
+      </c>
+      <c r="E110">
+        <v>26619.71</v>
+      </c>
+      <c r="F110" t="b">
+        <v>1</v>
+      </c>
+      <c r="G110" t="s">
+        <v>595</v>
+      </c>
+      <c r="H110" t="s">
+        <v>286</v>
+      </c>
+      <c r="I110">
+        <v>6390</v>
+      </c>
+      <c r="J110" t="s">
+        <v>258</v>
+      </c>
+      <c r="K110">
+        <v>8061</v>
+      </c>
+      <c r="L110">
+        <v>2456.99</v>
+      </c>
+      <c r="M110">
+        <v>54.36</v>
+      </c>
+      <c r="N110">
+        <v>33.78</v>
+      </c>
+      <c r="O110">
+        <v>39.261833333333335</v>
+      </c>
+      <c r="P110">
+        <v>-103.5945</v>
+      </c>
+      <c r="Q110">
+        <v>5202</v>
+      </c>
+      <c r="R110">
+        <v>1585.57</v>
+      </c>
+      <c r="S110">
+        <v>39.608</v>
+      </c>
+      <c r="T110">
+        <v>-104.04216666666666</v>
+      </c>
+      <c r="U110" t="s">
+        <v>118</v>
+      </c>
+      <c r="V110">
+        <v>87123</v>
+      </c>
+      <c r="W110">
+        <v>26555.09</v>
+      </c>
+      <c r="X110">
+        <v>409</v>
+      </c>
+      <c r="Y110" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z110">
+        <v>12</v>
+      </c>
+      <c r="AA110">
+        <v>3.66</v>
+      </c>
+      <c r="AB110">
+        <v>0.82</v>
+      </c>
+      <c r="AC110">
+        <v>1.81</v>
+      </c>
+      <c r="AD110">
+        <v>54.36</v>
+      </c>
+      <c r="AE110">
+        <v>33.78</v>
+      </c>
+      <c r="AF110" t="s">
+        <v>596</v>
+      </c>
+      <c r="AG110">
+        <v>1.5</v>
+      </c>
+      <c r="AH110">
+        <v>3.31</v>
+      </c>
+      <c r="AI110">
+        <v>3.6</v>
+      </c>
+      <c r="AJ110">
+        <v>7.94</v>
+      </c>
+      <c r="AK110">
+        <v>1.77</v>
+      </c>
+      <c r="AL110">
+        <v>3.9</v>
+      </c>
+      <c r="AM110">
+        <v>7.69</v>
+      </c>
+      <c r="AN110">
+        <v>16.95</v>
+      </c>
+      <c r="AO110">
+        <v>8.5</v>
+      </c>
+      <c r="AP110">
+        <v>18.73</v>
+      </c>
+      <c r="AQ110">
+        <v>6.19</v>
+      </c>
+      <c r="AR110">
+        <v>13.65</v>
+      </c>
+      <c r="AS110">
+        <v>0.82</v>
+      </c>
+      <c r="AT110">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="111" spans="1:46">
+      <c r="A111" t="s">
+        <v>46</v>
+      </c>
+      <c r="B111" t="s">
+        <v>597</v>
+      </c>
+      <c r="C111" t="s">
+        <v>589</v>
+      </c>
+      <c r="D111">
+        <v>107271</v>
+      </c>
+      <c r="E111">
+        <v>32696.2</v>
+      </c>
+      <c r="F111" t="b">
+        <v>1</v>
+      </c>
+      <c r="G111" t="s">
+        <v>598</v>
+      </c>
+      <c r="H111" t="s">
+        <v>599</v>
+      </c>
+      <c r="I111">
+        <v>7980</v>
+      </c>
+      <c r="J111" t="s">
+        <v>600</v>
+      </c>
+      <c r="K111">
+        <v>9380</v>
+      </c>
+      <c r="L111">
+        <v>2859.02</v>
+      </c>
+      <c r="M111">
+        <v>65.13</v>
+      </c>
+      <c r="N111">
+        <v>40.47</v>
+      </c>
+      <c r="O111">
+        <v>39.30533333333333</v>
+      </c>
+      <c r="P111">
+        <v>-103.392</v>
+      </c>
+      <c r="Q111">
+        <v>5206</v>
+      </c>
+      <c r="R111">
+        <v>1586.79</v>
+      </c>
+      <c r="S111">
+        <v>39.608</v>
+      </c>
+      <c r="T111">
+        <v>-104.04216666666666</v>
+      </c>
+      <c r="U111" t="s">
+        <v>156</v>
+      </c>
+      <c r="V111">
+        <v>107044</v>
+      </c>
+      <c r="W111">
+        <v>32627.01</v>
+      </c>
+      <c r="X111">
+        <v>705</v>
+      </c>
+      <c r="Y111" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z111">
+        <v>12</v>
+      </c>
+      <c r="AA111">
+        <v>3.66</v>
+      </c>
+      <c r="AB111">
+        <v>0.77</v>
+      </c>
+      <c r="AC111">
+        <v>1.7</v>
+      </c>
+      <c r="AD111">
+        <v>65.13</v>
+      </c>
+      <c r="AE111">
+        <v>40.47</v>
+      </c>
+      <c r="AF111" t="s">
+        <v>601</v>
+      </c>
+      <c r="AG111">
+        <v>3</v>
+      </c>
+      <c r="AH111">
+        <v>6.61</v>
+      </c>
+      <c r="AI111">
+        <v>3</v>
+      </c>
+      <c r="AJ111">
+        <v>6.61</v>
+      </c>
+      <c r="AK111">
+        <v>2.08</v>
+      </c>
+      <c r="AL111">
+        <v>4.59</v>
+      </c>
+      <c r="AM111">
+        <v>8.85</v>
+      </c>
+      <c r="AN111">
+        <v>19.51</v>
+      </c>
+      <c r="AO111">
+        <v>7.62</v>
+      </c>
+      <c r="AP111">
+        <v>16.8</v>
+      </c>
+      <c r="AQ111">
+        <v>5.85</v>
+      </c>
+      <c r="AR111">
+        <v>12.9</v>
+      </c>
+      <c r="AS111">
+        <v>0.77</v>
+      </c>
+      <c r="AT111">
+        <v>1.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/www/flightdata/xlsx/flights_metadata.xlsx
+++ b/www/flightdata/xlsx/flights_metadata.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="610">
   <si>
     <t>balloonsize</t>
   </si>
@@ -1820,6 +1820,30 @@
   </si>
   <si>
     <t>[{"altitude_ft":41058.0,"altitude_m":12514.48,"transition":"high_to_low"}]</t>
+  </si>
+  <si>
+    <t>2026-05-09</t>
+  </si>
+  <si>
+    <t>EOSS-401</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>[{"altitude_ft":41732.0,"altitude_m":12719.91,"transition":"high_to_low"}]</t>
+  </si>
+  <si>
+    <t>EOSS-402</t>
+  </si>
+  <si>
+    <t>2hrs 0mins 0secs</t>
+  </si>
+  <si>
+    <t>319</t>
+  </si>
+  <si>
+    <t>[{"altitude_ft":40554.0,"altitude_m":12360.86,"transition":"high_to_low"}]</t>
   </si>
 </sst>
 </file>
@@ -2151,7 +2175,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AT111"/>
+  <dimension ref="A1:AT113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:46">
@@ -17694,6 +17718,286 @@
         <v>1.7</v>
       </c>
     </row>
+    <row r="112" spans="1:46">
+      <c r="A112" t="s">
+        <v>46</v>
+      </c>
+      <c r="B112" t="s">
+        <v>588</v>
+      </c>
+      <c r="C112" t="s">
+        <v>602</v>
+      </c>
+      <c r="D112">
+        <v>75129</v>
+      </c>
+      <c r="E112">
+        <v>22899.32</v>
+      </c>
+      <c r="F112" t="b">
+        <v>1</v>
+      </c>
+      <c r="G112" t="s">
+        <v>603</v>
+      </c>
+      <c r="H112" t="s">
+        <v>443</v>
+      </c>
+      <c r="I112">
+        <v>6900</v>
+      </c>
+      <c r="J112" t="s">
+        <v>604</v>
+      </c>
+      <c r="K112">
+        <v>4692</v>
+      </c>
+      <c r="L112">
+        <v>1430.12</v>
+      </c>
+      <c r="M112">
+        <v>97.61</v>
+      </c>
+      <c r="N112">
+        <v>60.65</v>
+      </c>
+      <c r="O112">
+        <v>39.30148333333333</v>
+      </c>
+      <c r="P112">
+        <v>-102.97625</v>
+      </c>
+      <c r="Q112">
+        <v>5214</v>
+      </c>
+      <c r="R112">
+        <v>1589.23</v>
+      </c>
+      <c r="S112">
+        <v>39.608183333333336</v>
+      </c>
+      <c r="T112">
+        <v>-104.04228333333332</v>
+      </c>
+      <c r="U112" t="s">
+        <v>156</v>
+      </c>
+      <c r="V112">
+        <v>75055</v>
+      </c>
+      <c r="W112">
+        <v>22876.76</v>
+      </c>
+      <c r="X112">
+        <v>447</v>
+      </c>
+      <c r="Y112" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z112">
+        <v>12</v>
+      </c>
+      <c r="AA112">
+        <v>3.66</v>
+      </c>
+      <c r="AB112">
+        <v>0.77</v>
+      </c>
+      <c r="AC112">
+        <v>1.7</v>
+      </c>
+      <c r="AD112">
+        <v>97.61</v>
+      </c>
+      <c r="AE112">
+        <v>60.65</v>
+      </c>
+      <c r="AF112" t="s">
+        <v>605</v>
+      </c>
+      <c r="AG112">
+        <v>3</v>
+      </c>
+      <c r="AH112">
+        <v>6.61</v>
+      </c>
+      <c r="AI112">
+        <v>3.32</v>
+      </c>
+      <c r="AJ112">
+        <v>7.31</v>
+      </c>
+      <c r="AK112">
+        <v>1.89</v>
+      </c>
+      <c r="AL112">
+        <v>4.16</v>
+      </c>
+      <c r="AM112">
+        <v>8.98</v>
+      </c>
+      <c r="AN112">
+        <v>19.79</v>
+      </c>
+      <c r="AO112">
+        <v>7.77</v>
+      </c>
+      <c r="AP112">
+        <v>17.13</v>
+      </c>
+      <c r="AQ112">
+        <v>5.97</v>
+      </c>
+      <c r="AR112">
+        <v>13.17</v>
+      </c>
+      <c r="AS112">
+        <v>0.77</v>
+      </c>
+      <c r="AT112">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="113" spans="1:46">
+      <c r="A113" t="s">
+        <v>46</v>
+      </c>
+      <c r="B113" t="s">
+        <v>594</v>
+      </c>
+      <c r="C113" t="s">
+        <v>602</v>
+      </c>
+      <c r="D113">
+        <v>72643</v>
+      </c>
+      <c r="E113">
+        <v>22141.59</v>
+      </c>
+      <c r="F113" t="b">
+        <v>1</v>
+      </c>
+      <c r="G113" t="s">
+        <v>606</v>
+      </c>
+      <c r="H113" t="s">
+        <v>607</v>
+      </c>
+      <c r="I113">
+        <v>7200</v>
+      </c>
+      <c r="J113" t="s">
+        <v>608</v>
+      </c>
+      <c r="K113">
+        <v>4824</v>
+      </c>
+      <c r="L113">
+        <v>1470.36</v>
+      </c>
+      <c r="M113">
+        <v>104.12</v>
+      </c>
+      <c r="N113">
+        <v>64.7</v>
+      </c>
+      <c r="O113">
+        <v>39.2435</v>
+      </c>
+      <c r="P113">
+        <v>-102.92466666666668</v>
+      </c>
+      <c r="Q113">
+        <v>5216</v>
+      </c>
+      <c r="R113">
+        <v>1589.84</v>
+      </c>
+      <c r="S113">
+        <v>39.608</v>
+      </c>
+      <c r="T113">
+        <v>-104.04216666666666</v>
+      </c>
+      <c r="U113" t="s">
+        <v>156</v>
+      </c>
+      <c r="V113">
+        <v>72570</v>
+      </c>
+      <c r="W113">
+        <v>22119.34</v>
+      </c>
+      <c r="X113">
+        <v>445</v>
+      </c>
+      <c r="Y113" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z113">
+        <v>12</v>
+      </c>
+      <c r="AA113">
+        <v>3.66</v>
+      </c>
+      <c r="AB113">
+        <v>0.77</v>
+      </c>
+      <c r="AC113">
+        <v>1.7</v>
+      </c>
+      <c r="AD113">
+        <v>104.12</v>
+      </c>
+      <c r="AE113">
+        <v>64.7</v>
+      </c>
+      <c r="AF113" t="s">
+        <v>609</v>
+      </c>
+      <c r="AG113">
+        <v>3</v>
+      </c>
+      <c r="AH113">
+        <v>6.61</v>
+      </c>
+      <c r="AI113">
+        <v>3.45</v>
+      </c>
+      <c r="AJ113">
+        <v>7.61</v>
+      </c>
+      <c r="AK113">
+        <v>1.7</v>
+      </c>
+      <c r="AL113">
+        <v>3.74</v>
+      </c>
+      <c r="AM113">
+        <v>8.92</v>
+      </c>
+      <c r="AN113">
+        <v>19.66</v>
+      </c>
+      <c r="AO113">
+        <v>7.7</v>
+      </c>
+      <c r="AP113">
+        <v>16.97</v>
+      </c>
+      <c r="AQ113">
+        <v>5.91</v>
+      </c>
+      <c r="AR113">
+        <v>13.04</v>
+      </c>
+      <c r="AS113">
+        <v>0.77</v>
+      </c>
+      <c r="AT113">
+        <v>1.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/www/flightdata/xlsx/flights_metadata.xlsx
+++ b/www/flightdata/xlsx/flights_metadata.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1063" uniqueCount="615">
   <si>
     <t>balloonsize</t>
   </si>
@@ -1844,6 +1844,21 @@
   </si>
   <si>
     <t>[{"altitude_ft":40554.0,"altitude_m":12360.86,"transition":"high_to_low"}]</t>
+  </si>
+  <si>
+    <t>2026-06-20</t>
+  </si>
+  <si>
+    <t>EOSS-403</t>
+  </si>
+  <si>
+    <t>2hrs 33mins 0secs</t>
+  </si>
+  <si>
+    <t>159</t>
+  </si>
+  <si>
+    <t>[{"altitude_ft":43043.0,"altitude_m":13119.51,"transition":"high_to_low"},{"altitude_ft":70973.0,"altitude_m":21632.57,"transition":"low_to_high"}]</t>
   </si>
 </sst>
 </file>
@@ -2175,7 +2190,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AT113"/>
+  <dimension ref="A1:AT114"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:46">
@@ -17998,6 +18013,146 @@
         <v>1.7</v>
       </c>
     </row>
+    <row r="114" spans="1:46">
+      <c r="A114" t="s">
+        <v>62</v>
+      </c>
+      <c r="B114" t="s">
+        <v>588</v>
+      </c>
+      <c r="C114" t="s">
+        <v>610</v>
+      </c>
+      <c r="D114">
+        <v>0</v>
+      </c>
+      <c r="E114">
+        <v>0</v>
+      </c>
+      <c r="F114" t="b">
+        <v>0</v>
+      </c>
+      <c r="G114" t="s">
+        <v>611</v>
+      </c>
+      <c r="H114" t="s">
+        <v>612</v>
+      </c>
+      <c r="I114">
+        <v>9180</v>
+      </c>
+      <c r="J114" t="s">
+        <v>613</v>
+      </c>
+      <c r="K114">
+        <v>732</v>
+      </c>
+      <c r="L114">
+        <v>223.11</v>
+      </c>
+      <c r="M114">
+        <v>138.73</v>
+      </c>
+      <c r="N114">
+        <v>86.2</v>
+      </c>
+      <c r="O114">
+        <v>40.74828333333333</v>
+      </c>
+      <c r="P114">
+        <v>-91.4728</v>
+      </c>
+      <c r="Q114">
+        <v>863</v>
+      </c>
+      <c r="R114">
+        <v>263.04</v>
+      </c>
+      <c r="S114">
+        <v>41.39435</v>
+      </c>
+      <c r="T114">
+        <v>-92.88985</v>
+      </c>
+      <c r="U114" t="s">
+        <v>118</v>
+      </c>
+      <c r="V114">
+        <v>100442</v>
+      </c>
+      <c r="W114">
+        <v>30614.72</v>
+      </c>
+      <c r="X114">
+        <v>275</v>
+      </c>
+      <c r="Y114" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z114">
+        <v>10</v>
+      </c>
+      <c r="AA114">
+        <v>3.05</v>
+      </c>
+      <c r="AB114">
+        <v>0.66</v>
+      </c>
+      <c r="AC114">
+        <v>1.46</v>
+      </c>
+      <c r="AD114">
+        <v>138.73</v>
+      </c>
+      <c r="AE114">
+        <v>86.2</v>
+      </c>
+      <c r="AF114" t="s">
+        <v>614</v>
+      </c>
+      <c r="AG114">
+        <v>1.5</v>
+      </c>
+      <c r="AH114">
+        <v>3.31</v>
+      </c>
+      <c r="AI114">
+        <v>0.35</v>
+      </c>
+      <c r="AJ114">
+        <v>0.77</v>
+      </c>
+      <c r="AK114">
+        <v>1.61</v>
+      </c>
+      <c r="AL114">
+        <v>3.54</v>
+      </c>
+      <c r="AM114">
+        <v>4.12</v>
+      </c>
+      <c r="AN114">
+        <v>9.08</v>
+      </c>
+      <c r="AO114">
+        <v>3.85</v>
+      </c>
+      <c r="AP114">
+        <v>8.49</v>
+      </c>
+      <c r="AQ114">
+        <v>2.62</v>
+      </c>
+      <c r="AR114">
+        <v>5.77</v>
+      </c>
+      <c r="AS114">
+        <v>0.66</v>
+      </c>
+      <c r="AT114">
+        <v>1.46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/www/flightdata/xlsx/flights_metadata.xlsx
+++ b/www/flightdata/xlsx/flights_metadata.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1063" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1072" uniqueCount="621">
   <si>
     <t>balloonsize</t>
   </si>
@@ -1859,6 +1859,24 @@
   </si>
   <si>
     <t>[{"altitude_ft":43043.0,"altitude_m":13119.51,"transition":"high_to_low"},{"altitude_ft":70973.0,"altitude_m":21632.57,"transition":"low_to_high"}]</t>
+  </si>
+  <si>
+    <t>["KC0D-2","N0JPS","AE0SS-2","K0SCC-13"]</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>EOSS-404</t>
+  </si>
+  <si>
+    <t>1hrs 17mins 30secs</t>
+  </si>
+  <si>
+    <t>472</t>
+  </si>
+  <si>
+    <t>[{"altitude_ft":56609.0,"altitude_m":17254.42,"transition":"high_to_low"}]</t>
   </si>
 </sst>
 </file>
@@ -2190,7 +2208,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AT114"/>
+  <dimension ref="A1:AT115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:46">
@@ -18153,6 +18171,146 @@
         <v>1.46</v>
       </c>
     </row>
+    <row r="115" spans="1:46">
+      <c r="A115" t="s">
+        <v>46</v>
+      </c>
+      <c r="B115" t="s">
+        <v>615</v>
+      </c>
+      <c r="C115" t="s">
+        <v>616</v>
+      </c>
+      <c r="D115">
+        <v>67585</v>
+      </c>
+      <c r="E115">
+        <v>20599.91</v>
+      </c>
+      <c r="F115" t="b">
+        <v>1</v>
+      </c>
+      <c r="G115" t="s">
+        <v>617</v>
+      </c>
+      <c r="H115" t="s">
+        <v>618</v>
+      </c>
+      <c r="I115">
+        <v>4650</v>
+      </c>
+      <c r="J115" t="s">
+        <v>619</v>
+      </c>
+      <c r="K115">
+        <v>6001</v>
+      </c>
+      <c r="L115">
+        <v>1829.1</v>
+      </c>
+      <c r="M115">
+        <v>17.61</v>
+      </c>
+      <c r="N115">
+        <v>10.94</v>
+      </c>
+      <c r="O115">
+        <v>39.18613333333333</v>
+      </c>
+      <c r="P115">
+        <v>-103.32883333333334</v>
+      </c>
+      <c r="Q115">
+        <v>5606</v>
+      </c>
+      <c r="R115">
+        <v>1708.71</v>
+      </c>
+      <c r="S115">
+        <v>39.278166666666664</v>
+      </c>
+      <c r="T115">
+        <v>-103.49533333333332</v>
+      </c>
+      <c r="U115" t="s">
+        <v>156</v>
+      </c>
+      <c r="V115">
+        <v>67568</v>
+      </c>
+      <c r="W115">
+        <v>20594.73</v>
+      </c>
+      <c r="X115">
+        <v>406</v>
+      </c>
+      <c r="Y115" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z115">
+        <v>12</v>
+      </c>
+      <c r="AA115">
+        <v>3.66</v>
+      </c>
+      <c r="AB115">
+        <v>0.77</v>
+      </c>
+      <c r="AC115">
+        <v>1.7</v>
+      </c>
+      <c r="AD115">
+        <v>17.61</v>
+      </c>
+      <c r="AE115">
+        <v>10.94</v>
+      </c>
+      <c r="AF115" t="s">
+        <v>620</v>
+      </c>
+      <c r="AG115">
+        <v>3</v>
+      </c>
+      <c r="AH115">
+        <v>6.61</v>
+      </c>
+      <c r="AI115">
+        <v>6.86</v>
+      </c>
+      <c r="AJ115">
+        <v>15.12</v>
+      </c>
+      <c r="AK115">
+        <v>2.58</v>
+      </c>
+      <c r="AL115">
+        <v>5.68</v>
+      </c>
+      <c r="AM115">
+        <v>13.2</v>
+      </c>
+      <c r="AN115">
+        <v>29.11</v>
+      </c>
+      <c r="AO115">
+        <v>12.85</v>
+      </c>
+      <c r="AP115">
+        <v>28.32</v>
+      </c>
+      <c r="AQ115">
+        <v>10.21</v>
+      </c>
+      <c r="AR115">
+        <v>22.5</v>
+      </c>
+      <c r="AS115">
+        <v>0.77</v>
+      </c>
+      <c r="AT115">
+        <v>1.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/www/flightdata/xlsx/flights_metadata.xlsx
+++ b/www/flightdata/xlsx/flights_metadata.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1072" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1081" uniqueCount="625">
   <si>
     <t>balloonsize</t>
   </si>
@@ -1877,6 +1877,18 @@
   </si>
   <si>
     <t>[{"altitude_ft":56609.0,"altitude_m":17254.42,"transition":"high_to_low"}]</t>
+  </si>
+  <si>
+    <t>2026-08-22</t>
+  </si>
+  <si>
+    <t>EOSS-405</t>
+  </si>
+  <si>
+    <t>342</t>
+  </si>
+  <si>
+    <t>[{"altitude_ft":10113.0,"altitude_m":3082.44,"transition":"low_to_high"},{"altitude_ft":61473.0,"altitude_m":18736.97,"transition":"high_to_low"}]</t>
   </si>
 </sst>
 </file>
@@ -2208,7 +2220,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AT115"/>
+  <dimension ref="A1:AT116"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:46">
@@ -18311,6 +18323,146 @@
         <v>1.7</v>
       </c>
     </row>
+    <row r="116" spans="1:46">
+      <c r="A116" t="s">
+        <v>46</v>
+      </c>
+      <c r="B116" t="s">
+        <v>588</v>
+      </c>
+      <c r="C116" t="s">
+        <v>621</v>
+      </c>
+      <c r="D116">
+        <v>107526</v>
+      </c>
+      <c r="E116">
+        <v>32773.92</v>
+      </c>
+      <c r="F116" t="b">
+        <v>1</v>
+      </c>
+      <c r="G116" t="s">
+        <v>622</v>
+      </c>
+      <c r="H116" t="s">
+        <v>272</v>
+      </c>
+      <c r="I116">
+        <v>7470</v>
+      </c>
+      <c r="J116" t="s">
+        <v>623</v>
+      </c>
+      <c r="K116">
+        <v>5467</v>
+      </c>
+      <c r="L116">
+        <v>1666.34</v>
+      </c>
+      <c r="M116">
+        <v>27.02</v>
+      </c>
+      <c r="N116">
+        <v>16.79</v>
+      </c>
+      <c r="O116">
+        <v>38.993833333333335</v>
+      </c>
+      <c r="P116">
+        <v>-103.72301666666668</v>
+      </c>
+      <c r="Q116">
+        <v>5408</v>
+      </c>
+      <c r="R116">
+        <v>1648.36</v>
+      </c>
+      <c r="S116">
+        <v>39.23613333333333</v>
+      </c>
+      <c r="T116">
+        <v>-103.69696666666668</v>
+      </c>
+      <c r="U116" t="s">
+        <v>156</v>
+      </c>
+      <c r="V116">
+        <v>106755</v>
+      </c>
+      <c r="W116">
+        <v>32538.92</v>
+      </c>
+      <c r="X116">
+        <v>425</v>
+      </c>
+      <c r="Y116" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z116">
+        <v>12</v>
+      </c>
+      <c r="AA116">
+        <v>3.66</v>
+      </c>
+      <c r="AB116">
+        <v>0.77</v>
+      </c>
+      <c r="AC116">
+        <v>1.7</v>
+      </c>
+      <c r="AD116">
+        <v>27.02</v>
+      </c>
+      <c r="AE116">
+        <v>16.79</v>
+      </c>
+      <c r="AF116" t="s">
+        <v>624</v>
+      </c>
+      <c r="AG116">
+        <v>3</v>
+      </c>
+      <c r="AH116">
+        <v>6.61</v>
+      </c>
+      <c r="AI116">
+        <v>3.72</v>
+      </c>
+      <c r="AJ116">
+        <v>8.21</v>
+      </c>
+      <c r="AK116">
+        <v>2.08</v>
+      </c>
+      <c r="AL116">
+        <v>4.58</v>
+      </c>
+      <c r="AM116">
+        <v>9.57</v>
+      </c>
+      <c r="AN116">
+        <v>21.1</v>
+      </c>
+      <c r="AO116">
+        <v>8.48</v>
+      </c>
+      <c r="AP116">
+        <v>18.7</v>
+      </c>
+      <c r="AQ116">
+        <v>6.57</v>
+      </c>
+      <c r="AR116">
+        <v>14.48</v>
+      </c>
+      <c r="AS116">
+        <v>0.77</v>
+      </c>
+      <c r="AT116">
+        <v>1.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
